--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128102520</v>
+        <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>92639</v>
+        <v>98468</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gáddoajvve, Gáddoajvve, Lu lm</t>
+          <t>Norr om Gáddoajvve, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>690800</v>
+        <v>691382</v>
       </c>
       <c r="R2" t="n">
-        <v>7400819</v>
+        <v>7401218</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-08-31</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +779,4923 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128102520</v>
+      </c>
+      <c r="B3" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Gáddoajvve, Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>690800</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7400819</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128146055</v>
+      </c>
+      <c r="B4" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>690845</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7400680</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128146070</v>
+      </c>
+      <c r="B5" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>690846</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7400687</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:35</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128146075</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78435</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>691077</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7400880</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128146048</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91635</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>71</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>690845</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7400687</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128144823</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>691519</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7400859</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128146061</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91368</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>691859</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7400943</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128146062</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91611</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>65</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>691117</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7400871</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128146056</v>
+      </c>
+      <c r="B11" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>690781</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7400555</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128144819</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>691675</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7401012</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:47</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128146067</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>691067</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7400865</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128144824</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80036</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>691607</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7400989</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128144820</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>691749</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7400999</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128146053</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92670</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>691789</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7400698</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128146069</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>691003</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7400833</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128146046</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90385</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>690842</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7400691</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128144834</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79108</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>864</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>691842</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7400786</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>128146045</v>
+      </c>
+      <c r="B20" t="n">
+        <v>90385</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>691632</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7400779</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>128146063</v>
+      </c>
+      <c r="B21" t="n">
+        <v>91611</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>65</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>690806</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7400768</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>128146066</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>691535</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7400857</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:45</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>128146071</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>690800</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7400737</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>128144825</v>
+      </c>
+      <c r="B24" t="n">
+        <v>80036</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>691427</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7401053</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>16:26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>128146073</v>
+      </c>
+      <c r="B25" t="n">
+        <v>78007</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>691079</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7400877</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>128144829</v>
+      </c>
+      <c r="B26" t="n">
+        <v>78787</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>691811</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7400740</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>128144835</v>
+      </c>
+      <c r="B27" t="n">
+        <v>91511</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>1503</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Gräddporing</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sidera lenis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>691707</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7400750</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>128146074</v>
+      </c>
+      <c r="B28" t="n">
+        <v>92634</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>690796</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7400787</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>128146064</v>
+      </c>
+      <c r="B29" t="n">
+        <v>78696</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>353</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>691003</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7400833</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>128146068</v>
+      </c>
+      <c r="B30" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>691003</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7400832</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>128144837</v>
+      </c>
+      <c r="B31" t="n">
+        <v>92640</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>691657</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7400758</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>128146042</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>691337</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7400753</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128144840</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78435</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>691520</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7400858</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:39</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128144818</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91525</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>1588</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Violmussling</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>691744</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7401003</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128144822</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79647</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>691662</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7400760</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128146047</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91635</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>71</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Urskogsporing</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Neoantrodia infirma</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Renvall &amp; Niemelä) Audet</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>691536</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7400854</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:44</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>128144836</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91611</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>65</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Fläckporing</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Anthoporia albobrunnea</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>691520</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7400888</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>128144839</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78435</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>691806</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7400707</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>17:14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>128146044</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79618</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>691077</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7400881</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>128146057</v>
+      </c>
+      <c r="B40" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>690810</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7400772</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>128146065</v>
+      </c>
+      <c r="B41" t="n">
+        <v>78696</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>353</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>690853</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7400680</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>128144826</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5493</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>691845</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7400932</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>128146043</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79618</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>691657</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7400717</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>128144828</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78788</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>691820</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7400729</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>17:17</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>128144833</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>691471</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7401138</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128144830</v>
+      </c>
+      <c r="B46" t="n">
+        <v>98468</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>691395</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7401068</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128144827</v>
+      </c>
+      <c r="B47" t="n">
+        <v>78788</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>691749</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7400999</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128144838</v>
+      </c>
+      <c r="B48" t="n">
+        <v>78435</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Norr om Gáddoajvve, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>691841</v>
+      </c>
+      <c r="R48" t="n">
+        <v>7400785</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B5" t="n">
-        <v>92640</v>
+        <v>78435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R5" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B6" t="n">
-        <v>78435</v>
+        <v>92640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R6" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B7" t="n">
-        <v>91635</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R7" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>91635</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R8" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128146056</v>
+        <v>128144819</v>
       </c>
       <c r="B11" t="n">
-        <v>92632</v>
+        <v>79647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690781</v>
+        <v>691675</v>
       </c>
       <c r="R11" t="n">
-        <v>7400555</v>
+        <v>7401012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128144819</v>
+        <v>128146056</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>92632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691675</v>
+        <v>690781</v>
       </c>
       <c r="R12" t="n">
-        <v>7401012</v>
+        <v>7400555</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146067</v>
+        <v>128144820</v>
       </c>
       <c r="B13" t="n">
-        <v>92640</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691067</v>
+        <v>691749</v>
       </c>
       <c r="R13" t="n">
-        <v>7400865</v>
+        <v>7400999</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144820</v>
+        <v>128146067</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>92640</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691749</v>
+        <v>691067</v>
       </c>
       <c r="R15" t="n">
-        <v>7400999</v>
+        <v>7400865</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146069</v>
+        <v>128144834</v>
       </c>
       <c r="B17" t="n">
-        <v>92640</v>
+        <v>79108</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691003</v>
+        <v>691842</v>
       </c>
       <c r="R17" t="n">
-        <v>7400833</v>
+        <v>7400786</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146046</v>
+        <v>128146069</v>
       </c>
       <c r="B18" t="n">
-        <v>90385</v>
+        <v>92640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>690842</v>
+        <v>691003</v>
       </c>
       <c r="R18" t="n">
-        <v>7400691</v>
+        <v>7400833</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128144834</v>
+        <v>128146046</v>
       </c>
       <c r="B19" t="n">
-        <v>79108</v>
+        <v>90385</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691842</v>
+        <v>690842</v>
       </c>
       <c r="R19" t="n">
-        <v>7400786</v>
+        <v>7400691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128146066</v>
+        <v>128144825</v>
       </c>
       <c r="B22" t="n">
-        <v>92640</v>
+        <v>80036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691535</v>
+        <v>691427</v>
       </c>
       <c r="R22" t="n">
-        <v>7400857</v>
+        <v>7401053</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,32 +2912,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128146071</v>
+        <v>128144829</v>
       </c>
       <c r="B23" t="n">
-        <v>92640</v>
+        <v>78787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690800</v>
+        <v>691811</v>
       </c>
       <c r="R23" t="n">
-        <v>7400737</v>
+        <v>7400740</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144825</v>
+        <v>128146073</v>
       </c>
       <c r="B24" t="n">
-        <v>80036</v>
+        <v>78007</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6456</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691427</v>
+        <v>691079</v>
       </c>
       <c r="R24" t="n">
-        <v>7401053</v>
+        <v>7400877</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146073</v>
+        <v>128146066</v>
       </c>
       <c r="B25" t="n">
-        <v>78007</v>
+        <v>92640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691079</v>
+        <v>691535</v>
       </c>
       <c r="R25" t="n">
-        <v>7400877</v>
+        <v>7400857</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128144829</v>
+        <v>128146071</v>
       </c>
       <c r="B26" t="n">
-        <v>78787</v>
+        <v>92640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691811</v>
+        <v>690800</v>
       </c>
       <c r="R26" t="n">
-        <v>7400740</v>
+        <v>7400737</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3554,32 +3554,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128146064</v>
+        <v>128146068</v>
       </c>
       <c r="B29" t="n">
-        <v>78696</v>
+        <v>92640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>691003</v>
       </c>
       <c r="R29" t="n">
-        <v>7400833</v>
+        <v>7400832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,7 +3661,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146068</v>
+        <v>128144837</v>
       </c>
       <c r="B30" t="n">
         <v>92640</v>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691003</v>
+        <v>691657</v>
       </c>
       <c r="R30" t="n">
-        <v>7400832</v>
+        <v>7400758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128144837</v>
+        <v>128146064</v>
       </c>
       <c r="B31" t="n">
-        <v>92640</v>
+        <v>78696</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691657</v>
+        <v>691003</v>
       </c>
       <c r="R31" t="n">
-        <v>7400758</v>
+        <v>7400833</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146047</v>
+        <v>128144839</v>
       </c>
       <c r="B36" t="n">
-        <v>91635</v>
+        <v>78435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691536</v>
+        <v>691806</v>
       </c>
       <c r="R36" t="n">
-        <v>7400854</v>
+        <v>7400707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144836</v>
+        <v>128146047</v>
       </c>
       <c r="B37" t="n">
-        <v>91611</v>
+        <v>91635</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691520</v>
+        <v>691536</v>
       </c>
       <c r="R37" t="n">
-        <v>7400888</v>
+        <v>7400854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144839</v>
+        <v>128144836</v>
       </c>
       <c r="B38" t="n">
-        <v>78435</v>
+        <v>91611</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691806</v>
+        <v>691520</v>
       </c>
       <c r="R38" t="n">
-        <v>7400707</v>
+        <v>7400888</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146065</v>
+        <v>128144826</v>
       </c>
       <c r="B41" t="n">
-        <v>78696</v>
+        <v>5493</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690853</v>
+        <v>691845</v>
       </c>
       <c r="R41" t="n">
-        <v>7400680</v>
+        <v>7400932</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128144826</v>
+        <v>128146065</v>
       </c>
       <c r="B42" t="n">
-        <v>5493</v>
+        <v>78696</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691845</v>
+        <v>690853</v>
       </c>
       <c r="R42" t="n">
-        <v>7400932</v>
+        <v>7400680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5485,10 +5485,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128144827</v>
+        <v>128144838</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>78435</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,21 +5496,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691749</v>
+        <v>691841</v>
       </c>
       <c r="R47" t="n">
-        <v>7400999</v>
+        <v>7400785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128144838</v>
+        <v>128144827</v>
       </c>
       <c r="B48" t="n">
-        <v>78435</v>
+        <v>78788</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691841</v>
+        <v>691749</v>
       </c>
       <c r="R48" t="n">
-        <v>7400785</v>
+        <v>7400999</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128102520</v>
       </c>
       <c r="B3" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128146055</v>
       </c>
       <c r="B4" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128146070</v>
       </c>
       <c r="B6" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>91636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R7" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B8" t="n">
-        <v>91635</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R8" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,7 +1417,7 @@
         <v>128146061</v>
       </c>
       <c r="B9" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128146062</v>
       </c>
       <c r="B10" t="n">
-        <v>91611</v>
+        <v>91612</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128144819</v>
+        <v>128146056</v>
       </c>
       <c r="B11" t="n">
-        <v>79647</v>
+        <v>92633</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691675</v>
+        <v>690781</v>
       </c>
       <c r="R11" t="n">
-        <v>7401012</v>
+        <v>7400555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128146056</v>
+        <v>128144819</v>
       </c>
       <c r="B12" t="n">
-        <v>92632</v>
+        <v>79647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690781</v>
+        <v>691675</v>
       </c>
       <c r="R12" t="n">
-        <v>7400555</v>
+        <v>7401012</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128144820</v>
+        <v>128146053</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>92671</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691749</v>
+        <v>691789</v>
       </c>
       <c r="R13" t="n">
-        <v>7400999</v>
+        <v>7400698</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128144824</v>
+        <v>128144820</v>
       </c>
       <c r="B14" t="n">
-        <v>80036</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691607</v>
+        <v>691749</v>
       </c>
       <c r="R14" t="n">
-        <v>7400989</v>
+        <v>7400999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128146067</v>
+        <v>128144824</v>
       </c>
       <c r="B15" t="n">
-        <v>92640</v>
+        <v>80036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691067</v>
+        <v>691607</v>
       </c>
       <c r="R15" t="n">
-        <v>7400865</v>
+        <v>7400989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,32 +2163,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128146053</v>
+        <v>128146067</v>
       </c>
       <c r="B16" t="n">
-        <v>92670</v>
+        <v>92641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691789</v>
+        <v>691067</v>
       </c>
       <c r="R16" t="n">
-        <v>7400698</v>
+        <v>7400865</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146069</v>
+        <v>128146063</v>
       </c>
       <c r="B18" t="n">
-        <v>92640</v>
+        <v>91612</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691003</v>
+        <v>690806</v>
       </c>
       <c r="R18" t="n">
-        <v>7400833</v>
+        <v>7400768</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,32 +2484,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128146046</v>
+        <v>128146069</v>
       </c>
       <c r="B19" t="n">
-        <v>90385</v>
+        <v>92641</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>690842</v>
+        <v>691003</v>
       </c>
       <c r="R19" t="n">
-        <v>7400691</v>
+        <v>7400833</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128146045</v>
+        <v>128146046</v>
       </c>
       <c r="B20" t="n">
-        <v>90385</v>
+        <v>90386</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691632</v>
+        <v>690842</v>
       </c>
       <c r="R20" t="n">
-        <v>7400779</v>
+        <v>7400691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128146063</v>
+        <v>128146045</v>
       </c>
       <c r="B21" t="n">
-        <v>91611</v>
+        <v>90386</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690806</v>
+        <v>691632</v>
       </c>
       <c r="R21" t="n">
-        <v>7400768</v>
+        <v>7400779</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3129,7 +3129,7 @@
         <v>128146066</v>
       </c>
       <c r="B25" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
         <v>128146071</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,7 +3343,7 @@
         <v>128144835</v>
       </c>
       <c r="B27" t="n">
-        <v>91511</v>
+        <v>91512</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128146074</v>
       </c>
       <c r="B28" t="n">
-        <v>92634</v>
+        <v>92635</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,32 +3554,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128146068</v>
+        <v>128146042</v>
       </c>
       <c r="B29" t="n">
-        <v>92640</v>
+        <v>79647</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691003</v>
+        <v>691337</v>
       </c>
       <c r="R29" t="n">
-        <v>7400832</v>
+        <v>7400753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128144837</v>
+        <v>128146068</v>
       </c>
       <c r="B30" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691657</v>
+        <v>691003</v>
       </c>
       <c r="R30" t="n">
-        <v>7400758</v>
+        <v>7400832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128146064</v>
+        <v>128144837</v>
       </c>
       <c r="B31" t="n">
-        <v>78696</v>
+        <v>92641</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691003</v>
+        <v>691657</v>
       </c>
       <c r="R31" t="n">
-        <v>7400833</v>
+        <v>7400758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128146042</v>
+        <v>128146064</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>78696</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691337</v>
+        <v>691003</v>
       </c>
       <c r="R32" t="n">
-        <v>7400753</v>
+        <v>7400833</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4092,7 +4092,7 @@
         <v>128144818</v>
       </c>
       <c r="B34" t="n">
-        <v>91525</v>
+        <v>91526</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128144822</v>
+        <v>128146044</v>
       </c>
       <c r="B35" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691662</v>
+        <v>691077</v>
       </c>
       <c r="R35" t="n">
-        <v>7400760</v>
+        <v>7400881</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144839</v>
+        <v>128144822</v>
       </c>
       <c r="B36" t="n">
-        <v>78435</v>
+        <v>79647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691806</v>
+        <v>691662</v>
       </c>
       <c r="R36" t="n">
-        <v>7400707</v>
+        <v>7400760</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128146047</v>
+        <v>128144839</v>
       </c>
       <c r="B37" t="n">
-        <v>91635</v>
+        <v>78435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>71</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691536</v>
+        <v>691806</v>
       </c>
       <c r="R37" t="n">
-        <v>7400854</v>
+        <v>7400707</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144836</v>
+        <v>128146047</v>
       </c>
       <c r="B38" t="n">
-        <v>91611</v>
+        <v>91636</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691520</v>
+        <v>691536</v>
       </c>
       <c r="R38" t="n">
-        <v>7400888</v>
+        <v>7400854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,32 +4624,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146044</v>
+        <v>128144836</v>
       </c>
       <c r="B39" t="n">
-        <v>79618</v>
+        <v>91612</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691077</v>
+        <v>691520</v>
       </c>
       <c r="R39" t="n">
-        <v>7400881</v>
+        <v>7400888</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4734,7 +4734,7 @@
         <v>128146057</v>
       </c>
       <c r="B40" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128144826</v>
+        <v>128146065</v>
       </c>
       <c r="B41" t="n">
-        <v>5493</v>
+        <v>78696</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691845</v>
+        <v>690853</v>
       </c>
       <c r="R41" t="n">
-        <v>7400932</v>
+        <v>7400680</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146065</v>
+        <v>128144826</v>
       </c>
       <c r="B42" t="n">
-        <v>78696</v>
+        <v>5493</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690853</v>
+        <v>691845</v>
       </c>
       <c r="R42" t="n">
-        <v>7400680</v>
+        <v>7400932</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144828</v>
+        <v>128144833</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>98469</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691820</v>
+        <v>691471</v>
       </c>
       <c r="R44" t="n">
-        <v>7400729</v>
+        <v>7401138</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,10 +5266,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128144833</v>
+        <v>128144830</v>
       </c>
       <c r="B45" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691471</v>
+        <v>691395</v>
       </c>
       <c r="R45" t="n">
-        <v>7401138</v>
+        <v>7401068</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5346,7 +5346,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5373,32 +5378,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144830</v>
+        <v>128144828</v>
       </c>
       <c r="B46" t="n">
-        <v>98468</v>
+        <v>78788</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5408,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691395</v>
+        <v>691820</v>
       </c>
       <c r="R46" t="n">
-        <v>7401068</v>
+        <v>7400729</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,7 +5448,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5453,12 +5458,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128102520</v>
       </c>
       <c r="B3" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128146055</v>
       </c>
       <c r="B4" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128146070</v>
       </c>
       <c r="B6" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128146048</v>
       </c>
       <c r="B7" t="n">
-        <v>91636</v>
+        <v>91637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>128146061</v>
       </c>
       <c r="B9" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128146062</v>
       </c>
       <c r="B10" t="n">
-        <v>91612</v>
+        <v>91613</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128146056</v>
+        <v>128144819</v>
       </c>
       <c r="B11" t="n">
-        <v>92633</v>
+        <v>79647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690781</v>
+        <v>691675</v>
       </c>
       <c r="R11" t="n">
-        <v>7400555</v>
+        <v>7401012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128144819</v>
+        <v>128146056</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>92634</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691675</v>
+        <v>690781</v>
       </c>
       <c r="R12" t="n">
-        <v>7401012</v>
+        <v>7400555</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146053</v>
+        <v>128146067</v>
       </c>
       <c r="B13" t="n">
-        <v>92671</v>
+        <v>92642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691789</v>
+        <v>691067</v>
       </c>
       <c r="R13" t="n">
-        <v>7400698</v>
+        <v>7400865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,32 +2163,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128146067</v>
+        <v>128146053</v>
       </c>
       <c r="B16" t="n">
-        <v>92641</v>
+        <v>92672</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691067</v>
+        <v>691789</v>
       </c>
       <c r="R16" t="n">
-        <v>7400865</v>
+        <v>7400698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128144834</v>
+        <v>128146063</v>
       </c>
       <c r="B17" t="n">
-        <v>79108</v>
+        <v>91613</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>65</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691842</v>
+        <v>690806</v>
       </c>
       <c r="R17" t="n">
-        <v>7400786</v>
+        <v>7400768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146063</v>
+        <v>128144834</v>
       </c>
       <c r="B18" t="n">
-        <v>91612</v>
+        <v>79108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>690806</v>
+        <v>691842</v>
       </c>
       <c r="R18" t="n">
-        <v>7400768</v>
+        <v>7400786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,7 +2487,7 @@
         <v>128146069</v>
       </c>
       <c r="B19" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>128146046</v>
       </c>
       <c r="B20" t="n">
-        <v>90386</v>
+        <v>90387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>128146045</v>
       </c>
       <c r="B21" t="n">
-        <v>90386</v>
+        <v>90387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144825</v>
+        <v>128146066</v>
       </c>
       <c r="B22" t="n">
-        <v>80036</v>
+        <v>92642</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2816,21 +2816,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691427</v>
+        <v>691535</v>
       </c>
       <c r="R22" t="n">
-        <v>7401053</v>
+        <v>7400857</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,32 +2912,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128144829</v>
+        <v>128146071</v>
       </c>
       <c r="B23" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691811</v>
+        <v>690800</v>
       </c>
       <c r="R23" t="n">
-        <v>7400740</v>
+        <v>7400737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128146073</v>
+        <v>128144835</v>
       </c>
       <c r="B24" t="n">
-        <v>78007</v>
+        <v>91513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691079</v>
+        <v>691707</v>
       </c>
       <c r="R24" t="n">
-        <v>7400877</v>
+        <v>7400750</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146066</v>
+        <v>128144825</v>
       </c>
       <c r="B25" t="n">
-        <v>92641</v>
+        <v>80036</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3137,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691535</v>
+        <v>691427</v>
       </c>
       <c r="R25" t="n">
-        <v>7400857</v>
+        <v>7401053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146071</v>
+        <v>128144829</v>
       </c>
       <c r="B26" t="n">
-        <v>92641</v>
+        <v>78787</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>690800</v>
+        <v>691811</v>
       </c>
       <c r="R26" t="n">
-        <v>7400737</v>
+        <v>7400740</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128144835</v>
+        <v>128146073</v>
       </c>
       <c r="B27" t="n">
-        <v>91512</v>
+        <v>78007</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691707</v>
+        <v>691079</v>
       </c>
       <c r="R27" t="n">
-        <v>7400750</v>
+        <v>7400877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,7 +3450,7 @@
         <v>128146074</v>
       </c>
       <c r="B28" t="n">
-        <v>92635</v>
+        <v>92636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128146042</v>
+        <v>128146064</v>
       </c>
       <c r="B29" t="n">
-        <v>79647</v>
+        <v>78696</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691337</v>
+        <v>691003</v>
       </c>
       <c r="R29" t="n">
-        <v>7400753</v>
+        <v>7400833</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3664,7 +3664,7 @@
         <v>128146068</v>
       </c>
       <c r="B30" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128144837</v>
+        <v>128146042</v>
       </c>
       <c r="B31" t="n">
-        <v>92641</v>
+        <v>79647</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691657</v>
+        <v>691337</v>
       </c>
       <c r="R31" t="n">
-        <v>7400758</v>
+        <v>7400753</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,32 +3875,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128146064</v>
+        <v>128144837</v>
       </c>
       <c r="B32" t="n">
-        <v>78696</v>
+        <v>92642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691003</v>
+        <v>691657</v>
       </c>
       <c r="R32" t="n">
-        <v>7400833</v>
+        <v>7400758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4092,7 +4092,7 @@
         <v>128144818</v>
       </c>
       <c r="B34" t="n">
-        <v>91526</v>
+        <v>91527</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144822</v>
+        <v>128146047</v>
       </c>
       <c r="B36" t="n">
-        <v>79647</v>
+        <v>91637</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691662</v>
+        <v>691536</v>
       </c>
       <c r="R36" t="n">
-        <v>7400760</v>
+        <v>7400854</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144839</v>
+        <v>128144836</v>
       </c>
       <c r="B37" t="n">
-        <v>78435</v>
+        <v>91613</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691806</v>
+        <v>691520</v>
       </c>
       <c r="R37" t="n">
-        <v>7400707</v>
+        <v>7400888</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128146047</v>
+        <v>128144822</v>
       </c>
       <c r="B38" t="n">
-        <v>91636</v>
+        <v>79647</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691536</v>
+        <v>691662</v>
       </c>
       <c r="R38" t="n">
-        <v>7400854</v>
+        <v>7400760</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,32 +4624,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128144836</v>
+        <v>128144839</v>
       </c>
       <c r="B39" t="n">
-        <v>91612</v>
+        <v>78435</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691520</v>
+        <v>691806</v>
       </c>
       <c r="R39" t="n">
-        <v>7400888</v>
+        <v>7400707</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4734,7 +4734,7 @@
         <v>128146057</v>
       </c>
       <c r="B40" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146065</v>
+        <v>128144826</v>
       </c>
       <c r="B41" t="n">
-        <v>78696</v>
+        <v>5493</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690853</v>
+        <v>691845</v>
       </c>
       <c r="R41" t="n">
-        <v>7400680</v>
+        <v>7400932</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128144826</v>
+        <v>128146043</v>
       </c>
       <c r="B42" t="n">
-        <v>5493</v>
+        <v>79618</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691845</v>
+        <v>691657</v>
       </c>
       <c r="R42" t="n">
-        <v>7400932</v>
+        <v>7400717</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5052,10 +5052,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128146043</v>
+        <v>128146065</v>
       </c>
       <c r="B43" t="n">
-        <v>79618</v>
+        <v>78696</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5063,21 +5063,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691657</v>
+        <v>690853</v>
       </c>
       <c r="R43" t="n">
-        <v>7400717</v>
+        <v>7400680</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5162,7 +5162,7 @@
         <v>128144833</v>
       </c>
       <c r="B44" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>128144830</v>
       </c>
       <c r="B45" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B5" t="n">
-        <v>78435</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R5" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>78435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R6" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146067</v>
+        <v>128146053</v>
       </c>
       <c r="B13" t="n">
-        <v>92642</v>
+        <v>92672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691067</v>
+        <v>691789</v>
       </c>
       <c r="R13" t="n">
-        <v>7400865</v>
+        <v>7400698</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2163,32 +2163,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128146053</v>
+        <v>128146067</v>
       </c>
       <c r="B16" t="n">
-        <v>92672</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691789</v>
+        <v>691067</v>
       </c>
       <c r="R16" t="n">
-        <v>7400698</v>
+        <v>7400865</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146063</v>
+        <v>128146045</v>
       </c>
       <c r="B17" t="n">
-        <v>91613</v>
+        <v>90387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>690806</v>
+        <v>691632</v>
       </c>
       <c r="R17" t="n">
-        <v>7400768</v>
+        <v>7400779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128144834</v>
+        <v>128146069</v>
       </c>
       <c r="B18" t="n">
-        <v>79108</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691842</v>
+        <v>691003</v>
       </c>
       <c r="R18" t="n">
-        <v>7400786</v>
+        <v>7400833</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,32 +2484,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128146069</v>
+        <v>128146063</v>
       </c>
       <c r="B19" t="n">
-        <v>92642</v>
+        <v>91613</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691003</v>
+        <v>690806</v>
       </c>
       <c r="R19" t="n">
-        <v>7400833</v>
+        <v>7400768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128146046</v>
+        <v>128144834</v>
       </c>
       <c r="B20" t="n">
-        <v>90387</v>
+        <v>79108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690842</v>
+        <v>691842</v>
       </c>
       <c r="R20" t="n">
-        <v>7400691</v>
+        <v>7400786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,7 +2698,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128146045</v>
+        <v>128146046</v>
       </c>
       <c r="B21" t="n">
         <v>90387</v>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691632</v>
+        <v>690842</v>
       </c>
       <c r="R21" t="n">
-        <v>7400779</v>
+        <v>7400691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128146066</v>
+        <v>128144835</v>
       </c>
       <c r="B22" t="n">
-        <v>92642</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691535</v>
+        <v>691707</v>
       </c>
       <c r="R22" t="n">
-        <v>7400857</v>
+        <v>7400750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128146071</v>
+        <v>128144825</v>
       </c>
       <c r="B23" t="n">
-        <v>92642</v>
+        <v>80036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690800</v>
+        <v>691427</v>
       </c>
       <c r="R23" t="n">
-        <v>7400737</v>
+        <v>7401053</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144835</v>
+        <v>128144829</v>
       </c>
       <c r="B24" t="n">
-        <v>91513</v>
+        <v>78787</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691707</v>
+        <v>691811</v>
       </c>
       <c r="R24" t="n">
-        <v>7400750</v>
+        <v>7400740</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128144825</v>
+        <v>128146073</v>
       </c>
       <c r="B25" t="n">
-        <v>80036</v>
+        <v>78007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691427</v>
+        <v>691079</v>
       </c>
       <c r="R25" t="n">
-        <v>7401053</v>
+        <v>7400877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128144829</v>
+        <v>128146066</v>
       </c>
       <c r="B26" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691811</v>
+        <v>691535</v>
       </c>
       <c r="R26" t="n">
-        <v>7400740</v>
+        <v>7400857</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146073</v>
+        <v>128146071</v>
       </c>
       <c r="B27" t="n">
-        <v>78007</v>
+        <v>92642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691079</v>
+        <v>690800</v>
       </c>
       <c r="R27" t="n">
-        <v>7400877</v>
+        <v>7400737</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128146042</v>
+        <v>128144837</v>
       </c>
       <c r="B31" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691337</v>
+        <v>691657</v>
       </c>
       <c r="R31" t="n">
-        <v>7400753</v>
+        <v>7400758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,32 +3875,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128144837</v>
+        <v>128146042</v>
       </c>
       <c r="B32" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691657</v>
+        <v>691337</v>
       </c>
       <c r="R32" t="n">
-        <v>7400758</v>
+        <v>7400753</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146044</v>
+        <v>128144822</v>
       </c>
       <c r="B35" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691077</v>
+        <v>691662</v>
       </c>
       <c r="R35" t="n">
-        <v>7400881</v>
+        <v>7400760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146047</v>
+        <v>128144839</v>
       </c>
       <c r="B36" t="n">
-        <v>91637</v>
+        <v>78435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691536</v>
+        <v>691806</v>
       </c>
       <c r="R36" t="n">
-        <v>7400854</v>
+        <v>7400707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144822</v>
+        <v>128146047</v>
       </c>
       <c r="B38" t="n">
-        <v>79647</v>
+        <v>91637</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691662</v>
+        <v>691536</v>
       </c>
       <c r="R38" t="n">
-        <v>7400760</v>
+        <v>7400854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128144839</v>
+        <v>128146044</v>
       </c>
       <c r="B39" t="n">
-        <v>78435</v>
+        <v>79618</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691806</v>
+        <v>691077</v>
       </c>
       <c r="R39" t="n">
-        <v>7400707</v>
+        <v>7400881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128144826</v>
+        <v>128146043</v>
       </c>
       <c r="B41" t="n">
-        <v>5493</v>
+        <v>79618</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101410</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691845</v>
+        <v>691657</v>
       </c>
       <c r="R41" t="n">
-        <v>7400932</v>
+        <v>7400717</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146043</v>
+        <v>128146065</v>
       </c>
       <c r="B42" t="n">
-        <v>79618</v>
+        <v>78696</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691657</v>
+        <v>690853</v>
       </c>
       <c r="R42" t="n">
-        <v>7400717</v>
+        <v>7400680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5052,10 +5052,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128146065</v>
+        <v>128144826</v>
       </c>
       <c r="B43" t="n">
-        <v>78696</v>
+        <v>5493</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5063,21 +5063,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>690853</v>
+        <v>691845</v>
       </c>
       <c r="R43" t="n">
-        <v>7400680</v>
+        <v>7400932</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144833</v>
+        <v>128144828</v>
       </c>
       <c r="B44" t="n">
-        <v>98470</v>
+        <v>78788</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691471</v>
+        <v>691820</v>
       </c>
       <c r="R44" t="n">
-        <v>7401138</v>
+        <v>7400729</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,7 +5266,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128144830</v>
+        <v>128144833</v>
       </c>
       <c r="B45" t="n">
         <v>98470</v>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691395</v>
+        <v>691471</v>
       </c>
       <c r="R45" t="n">
-        <v>7401068</v>
+        <v>7401138</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5346,12 +5346,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5378,32 +5373,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144828</v>
+        <v>128144830</v>
       </c>
       <c r="B46" t="n">
-        <v>78788</v>
+        <v>98470</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5413,10 +5408,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691820</v>
+        <v>691395</v>
       </c>
       <c r="R46" t="n">
-        <v>7400729</v>
+        <v>7401068</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5443,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5458,7 +5453,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5485,10 +5485,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128144838</v>
+        <v>128144827</v>
       </c>
       <c r="B47" t="n">
-        <v>78435</v>
+        <v>78788</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,21 +5496,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691841</v>
+        <v>691749</v>
       </c>
       <c r="R47" t="n">
-        <v>7400785</v>
+        <v>7400999</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128144827</v>
+        <v>128144838</v>
       </c>
       <c r="B48" t="n">
-        <v>78788</v>
+        <v>78435</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691749</v>
+        <v>691841</v>
       </c>
       <c r="R48" t="n">
-        <v>7400999</v>
+        <v>7400785</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>78435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R5" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B6" t="n">
-        <v>78435</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R6" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B7" t="n">
-        <v>91637</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R7" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>91637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R8" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144835</v>
+        <v>128144825</v>
       </c>
       <c r="B22" t="n">
-        <v>91513</v>
+        <v>80036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691707</v>
+        <v>691427</v>
       </c>
       <c r="R22" t="n">
-        <v>7400750</v>
+        <v>7401053</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,32 +2912,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128144825</v>
+        <v>128144829</v>
       </c>
       <c r="B23" t="n">
-        <v>80036</v>
+        <v>78787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691427</v>
+        <v>691811</v>
       </c>
       <c r="R23" t="n">
-        <v>7401053</v>
+        <v>7400740</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144829</v>
+        <v>128146066</v>
       </c>
       <c r="B24" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691811</v>
+        <v>691535</v>
       </c>
       <c r="R24" t="n">
-        <v>7400740</v>
+        <v>7400857</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146073</v>
+        <v>128146071</v>
       </c>
       <c r="B25" t="n">
-        <v>78007</v>
+        <v>92642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691079</v>
+        <v>690800</v>
       </c>
       <c r="R25" t="n">
-        <v>7400877</v>
+        <v>7400737</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146066</v>
+        <v>128146073</v>
       </c>
       <c r="B26" t="n">
-        <v>92642</v>
+        <v>78007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691535</v>
+        <v>691079</v>
       </c>
       <c r="R26" t="n">
-        <v>7400857</v>
+        <v>7400877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146071</v>
+        <v>128144835</v>
       </c>
       <c r="B27" t="n">
-        <v>92642</v>
+        <v>91513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690800</v>
+        <v>691707</v>
       </c>
       <c r="R27" t="n">
-        <v>7400737</v>
+        <v>7400750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,32 +3661,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146068</v>
+        <v>128146042</v>
       </c>
       <c r="B30" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691003</v>
+        <v>691337</v>
       </c>
       <c r="R30" t="n">
-        <v>7400832</v>
+        <v>7400753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128144837</v>
+        <v>128146068</v>
       </c>
       <c r="B31" t="n">
         <v>92642</v>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691657</v>
+        <v>691003</v>
       </c>
       <c r="R31" t="n">
-        <v>7400758</v>
+        <v>7400832</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,32 +3875,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128146042</v>
+        <v>128144837</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691337</v>
+        <v>691657</v>
       </c>
       <c r="R32" t="n">
-        <v>7400753</v>
+        <v>7400758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128144822</v>
+        <v>128146044</v>
       </c>
       <c r="B35" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691662</v>
+        <v>691077</v>
       </c>
       <c r="R35" t="n">
-        <v>7400760</v>
+        <v>7400881</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144839</v>
+        <v>128144836</v>
       </c>
       <c r="B36" t="n">
-        <v>78435</v>
+        <v>91613</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691806</v>
+        <v>691520</v>
       </c>
       <c r="R36" t="n">
-        <v>7400707</v>
+        <v>7400888</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144836</v>
+        <v>128146047</v>
       </c>
       <c r="B37" t="n">
-        <v>91613</v>
+        <v>91637</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691520</v>
+        <v>691536</v>
       </c>
       <c r="R37" t="n">
-        <v>7400888</v>
+        <v>7400854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128146047</v>
+        <v>128144839</v>
       </c>
       <c r="B38" t="n">
-        <v>91637</v>
+        <v>78435</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691536</v>
+        <v>691806</v>
       </c>
       <c r="R38" t="n">
-        <v>7400854</v>
+        <v>7400707</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146044</v>
+        <v>128144822</v>
       </c>
       <c r="B39" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691077</v>
+        <v>691662</v>
       </c>
       <c r="R39" t="n">
-        <v>7400881</v>
+        <v>7400760</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>91637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R7" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B8" t="n">
-        <v>91637</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R8" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146053</v>
+        <v>128146067</v>
       </c>
       <c r="B13" t="n">
-        <v>92672</v>
+        <v>92642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691789</v>
+        <v>691067</v>
       </c>
       <c r="R13" t="n">
-        <v>7400698</v>
+        <v>7400865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128144820</v>
+        <v>128146053</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>92672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>232140</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691749</v>
+        <v>691789</v>
       </c>
       <c r="R14" t="n">
-        <v>7400999</v>
+        <v>7400698</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144824</v>
+        <v>128144820</v>
       </c>
       <c r="B15" t="n">
-        <v>80036</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691607</v>
+        <v>691749</v>
       </c>
       <c r="R15" t="n">
-        <v>7400989</v>
+        <v>7400999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128146067</v>
+        <v>128144824</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>80036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691067</v>
+        <v>691607</v>
       </c>
       <c r="R16" t="n">
-        <v>7400865</v>
+        <v>7400989</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144825</v>
+        <v>128144835</v>
       </c>
       <c r="B22" t="n">
-        <v>80036</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691427</v>
+        <v>691707</v>
       </c>
       <c r="R22" t="n">
-        <v>7401053</v>
+        <v>7400750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,32 +2912,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128144829</v>
+        <v>128144825</v>
       </c>
       <c r="B23" t="n">
-        <v>78787</v>
+        <v>80036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691811</v>
+        <v>691427</v>
       </c>
       <c r="R23" t="n">
-        <v>7400740</v>
+        <v>7401053</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128146066</v>
+        <v>128144829</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691535</v>
+        <v>691811</v>
       </c>
       <c r="R24" t="n">
-        <v>7400857</v>
+        <v>7400740</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146071</v>
+        <v>128146073</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>78007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690800</v>
+        <v>691079</v>
       </c>
       <c r="R25" t="n">
-        <v>7400737</v>
+        <v>7400877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146073</v>
+        <v>128146066</v>
       </c>
       <c r="B26" t="n">
-        <v>78007</v>
+        <v>92642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691079</v>
+        <v>691535</v>
       </c>
       <c r="R26" t="n">
-        <v>7400877</v>
+        <v>7400857</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128144835</v>
+        <v>128146071</v>
       </c>
       <c r="B27" t="n">
-        <v>91513</v>
+        <v>92642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691707</v>
+        <v>690800</v>
       </c>
       <c r="R27" t="n">
-        <v>7400750</v>
+        <v>7400737</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,32 +3661,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146042</v>
+        <v>128146068</v>
       </c>
       <c r="B30" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691337</v>
+        <v>691003</v>
       </c>
       <c r="R30" t="n">
-        <v>7400753</v>
+        <v>7400832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128146068</v>
+        <v>128144837</v>
       </c>
       <c r="B31" t="n">
         <v>92642</v>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691003</v>
+        <v>691657</v>
       </c>
       <c r="R31" t="n">
-        <v>7400832</v>
+        <v>7400758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,32 +3875,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128144837</v>
+        <v>128146042</v>
       </c>
       <c r="B32" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691657</v>
+        <v>691337</v>
       </c>
       <c r="R32" t="n">
-        <v>7400758</v>
+        <v>7400753</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146044</v>
+        <v>128144822</v>
       </c>
       <c r="B35" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691077</v>
+        <v>691662</v>
       </c>
       <c r="R35" t="n">
-        <v>7400881</v>
+        <v>7400760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144836</v>
+        <v>128144839</v>
       </c>
       <c r="B36" t="n">
-        <v>91613</v>
+        <v>78435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691520</v>
+        <v>691806</v>
       </c>
       <c r="R36" t="n">
-        <v>7400888</v>
+        <v>7400707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128146047</v>
+        <v>128144836</v>
       </c>
       <c r="B37" t="n">
-        <v>91637</v>
+        <v>91613</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691536</v>
+        <v>691520</v>
       </c>
       <c r="R37" t="n">
-        <v>7400854</v>
+        <v>7400888</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144839</v>
+        <v>128146047</v>
       </c>
       <c r="B38" t="n">
-        <v>78435</v>
+        <v>91637</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691806</v>
+        <v>691536</v>
       </c>
       <c r="R38" t="n">
-        <v>7400707</v>
+        <v>7400854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128144822</v>
+        <v>128146044</v>
       </c>
       <c r="B39" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691662</v>
+        <v>691077</v>
       </c>
       <c r="R39" t="n">
-        <v>7400760</v>
+        <v>7400881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146043</v>
+        <v>128146065</v>
       </c>
       <c r="B41" t="n">
-        <v>79618</v>
+        <v>78696</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691657</v>
+        <v>690853</v>
       </c>
       <c r="R41" t="n">
-        <v>7400717</v>
+        <v>7400680</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146065</v>
+        <v>128146043</v>
       </c>
       <c r="B42" t="n">
-        <v>78696</v>
+        <v>79618</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690853</v>
+        <v>691657</v>
       </c>
       <c r="R42" t="n">
-        <v>7400680</v>
+        <v>7400717</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B7" t="n">
-        <v>91637</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R7" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>91637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R8" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146067</v>
+        <v>128146053</v>
       </c>
       <c r="B13" t="n">
-        <v>92642</v>
+        <v>92672</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691067</v>
+        <v>691789</v>
       </c>
       <c r="R13" t="n">
-        <v>7400865</v>
+        <v>7400698</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128146053</v>
+        <v>128144820</v>
       </c>
       <c r="B14" t="n">
-        <v>92672</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>232140</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691789</v>
+        <v>691749</v>
       </c>
       <c r="R14" t="n">
-        <v>7400698</v>
+        <v>7400999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144820</v>
+        <v>128144824</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>80036</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691749</v>
+        <v>691607</v>
       </c>
       <c r="R15" t="n">
-        <v>7400999</v>
+        <v>7400989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128144824</v>
+        <v>128146067</v>
       </c>
       <c r="B16" t="n">
-        <v>80036</v>
+        <v>92642</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691607</v>
+        <v>691067</v>
       </c>
       <c r="R16" t="n">
-        <v>7400989</v>
+        <v>7400865</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -3661,32 +3661,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146068</v>
+        <v>128146042</v>
       </c>
       <c r="B30" t="n">
-        <v>92642</v>
+        <v>79647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691003</v>
+        <v>691337</v>
       </c>
       <c r="R30" t="n">
-        <v>7400832</v>
+        <v>7400753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128144837</v>
+        <v>128146068</v>
       </c>
       <c r="B31" t="n">
         <v>92642</v>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691657</v>
+        <v>691003</v>
       </c>
       <c r="R31" t="n">
-        <v>7400758</v>
+        <v>7400832</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,32 +3875,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128146042</v>
+        <v>128144837</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691337</v>
+        <v>691657</v>
       </c>
       <c r="R32" t="n">
-        <v>7400753</v>
+        <v>7400758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B5" t="n">
-        <v>78435</v>
+        <v>92642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R5" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>78435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R6" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146045</v>
+        <v>128146063</v>
       </c>
       <c r="B17" t="n">
-        <v>90387</v>
+        <v>91613</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691632</v>
+        <v>690806</v>
       </c>
       <c r="R17" t="n">
-        <v>7400779</v>
+        <v>7400768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146069</v>
+        <v>128146046</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>90387</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691003</v>
+        <v>690842</v>
       </c>
       <c r="R18" t="n">
-        <v>7400833</v>
+        <v>7400691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,32 +2484,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128146063</v>
+        <v>128144834</v>
       </c>
       <c r="B19" t="n">
-        <v>91613</v>
+        <v>79108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>690806</v>
+        <v>691842</v>
       </c>
       <c r="R19" t="n">
-        <v>7400768</v>
+        <v>7400786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128144834</v>
+        <v>128146045</v>
       </c>
       <c r="B20" t="n">
-        <v>79108</v>
+        <v>90387</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691842</v>
+        <v>691632</v>
       </c>
       <c r="R20" t="n">
-        <v>7400786</v>
+        <v>7400779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128146046</v>
+        <v>128146069</v>
       </c>
       <c r="B21" t="n">
-        <v>90387</v>
+        <v>92642</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690842</v>
+        <v>691003</v>
       </c>
       <c r="R21" t="n">
-        <v>7400691</v>
+        <v>7400833</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146065</v>
+        <v>128146043</v>
       </c>
       <c r="B41" t="n">
-        <v>78696</v>
+        <v>79618</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690853</v>
+        <v>691657</v>
       </c>
       <c r="R41" t="n">
-        <v>7400680</v>
+        <v>7400717</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146043</v>
+        <v>128146065</v>
       </c>
       <c r="B42" t="n">
-        <v>79618</v>
+        <v>78696</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691657</v>
+        <v>690853</v>
       </c>
       <c r="R42" t="n">
-        <v>7400717</v>
+        <v>7400680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B5" t="n">
-        <v>92642</v>
+        <v>78435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R5" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B6" t="n">
-        <v>78435</v>
+        <v>92642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R6" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>91637</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R7" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B8" t="n">
-        <v>91637</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R8" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146053</v>
+        <v>128146067</v>
       </c>
       <c r="B13" t="n">
-        <v>92672</v>
+        <v>92642</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691789</v>
+        <v>691067</v>
       </c>
       <c r="R13" t="n">
-        <v>7400698</v>
+        <v>7400865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128144820</v>
+        <v>128146053</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>92672</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>232140</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691749</v>
+        <v>691789</v>
       </c>
       <c r="R14" t="n">
-        <v>7400999</v>
+        <v>7400698</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144824</v>
+        <v>128144820</v>
       </c>
       <c r="B15" t="n">
-        <v>80036</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691607</v>
+        <v>691749</v>
       </c>
       <c r="R15" t="n">
-        <v>7400989</v>
+        <v>7400999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,10 +2163,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128146067</v>
+        <v>128144824</v>
       </c>
       <c r="B16" t="n">
-        <v>92642</v>
+        <v>80036</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691067</v>
+        <v>691607</v>
       </c>
       <c r="R16" t="n">
-        <v>7400865</v>
+        <v>7400989</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144835</v>
+        <v>128144825</v>
       </c>
       <c r="B22" t="n">
-        <v>91513</v>
+        <v>80036</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>6456</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691707</v>
+        <v>691427</v>
       </c>
       <c r="R22" t="n">
-        <v>7400750</v>
+        <v>7401053</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,32 +2912,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128144825</v>
+        <v>128144829</v>
       </c>
       <c r="B23" t="n">
-        <v>80036</v>
+        <v>78787</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691427</v>
+        <v>691811</v>
       </c>
       <c r="R23" t="n">
-        <v>7401053</v>
+        <v>7400740</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144829</v>
+        <v>128146066</v>
       </c>
       <c r="B24" t="n">
-        <v>78787</v>
+        <v>92642</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691811</v>
+        <v>691535</v>
       </c>
       <c r="R24" t="n">
-        <v>7400740</v>
+        <v>7400857</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146073</v>
+        <v>128146071</v>
       </c>
       <c r="B25" t="n">
-        <v>78007</v>
+        <v>92642</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691079</v>
+        <v>690800</v>
       </c>
       <c r="R25" t="n">
-        <v>7400877</v>
+        <v>7400737</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146066</v>
+        <v>128146073</v>
       </c>
       <c r="B26" t="n">
-        <v>92642</v>
+        <v>78007</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691535</v>
+        <v>691079</v>
       </c>
       <c r="R26" t="n">
-        <v>7400857</v>
+        <v>7400877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146071</v>
+        <v>128144835</v>
       </c>
       <c r="B27" t="n">
-        <v>92642</v>
+        <v>91513</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690800</v>
+        <v>691707</v>
       </c>
       <c r="R27" t="n">
-        <v>7400737</v>
+        <v>7400750</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146043</v>
+        <v>128146065</v>
       </c>
       <c r="B41" t="n">
-        <v>79618</v>
+        <v>78696</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691657</v>
+        <v>690853</v>
       </c>
       <c r="R41" t="n">
-        <v>7400717</v>
+        <v>7400680</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146065</v>
+        <v>128146043</v>
       </c>
       <c r="B42" t="n">
-        <v>78696</v>
+        <v>79618</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690853</v>
+        <v>691657</v>
       </c>
       <c r="R42" t="n">
-        <v>7400680</v>
+        <v>7400717</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B7" t="n">
-        <v>91637</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R7" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>91637</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R8" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146063</v>
+        <v>128146045</v>
       </c>
       <c r="B17" t="n">
-        <v>91613</v>
+        <v>90387</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>690806</v>
+        <v>691632</v>
       </c>
       <c r="R17" t="n">
-        <v>7400768</v>
+        <v>7400779</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146046</v>
+        <v>128146069</v>
       </c>
       <c r="B18" t="n">
-        <v>90387</v>
+        <v>92642</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>690842</v>
+        <v>691003</v>
       </c>
       <c r="R18" t="n">
-        <v>7400691</v>
+        <v>7400833</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,32 +2484,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128144834</v>
+        <v>128146063</v>
       </c>
       <c r="B19" t="n">
-        <v>79108</v>
+        <v>91613</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>65</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691842</v>
+        <v>690806</v>
       </c>
       <c r="R19" t="n">
-        <v>7400786</v>
+        <v>7400768</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128146045</v>
+        <v>128144834</v>
       </c>
       <c r="B20" t="n">
-        <v>90387</v>
+        <v>79108</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691632</v>
+        <v>691842</v>
       </c>
       <c r="R20" t="n">
-        <v>7400779</v>
+        <v>7400786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128146069</v>
+        <v>128146046</v>
       </c>
       <c r="B21" t="n">
-        <v>92642</v>
+        <v>90387</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691003</v>
+        <v>690842</v>
       </c>
       <c r="R21" t="n">
-        <v>7400833</v>
+        <v>7400691</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144825</v>
+        <v>128144835</v>
       </c>
       <c r="B22" t="n">
-        <v>80036</v>
+        <v>91513</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691427</v>
+        <v>691707</v>
       </c>
       <c r="R22" t="n">
-        <v>7401053</v>
+        <v>7400750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,32 +2912,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128144829</v>
+        <v>128144825</v>
       </c>
       <c r="B23" t="n">
-        <v>78787</v>
+        <v>80036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691811</v>
+        <v>691427</v>
       </c>
       <c r="R23" t="n">
-        <v>7400740</v>
+        <v>7401053</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128146066</v>
+        <v>128144829</v>
       </c>
       <c r="B24" t="n">
-        <v>92642</v>
+        <v>78787</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691535</v>
+        <v>691811</v>
       </c>
       <c r="R24" t="n">
-        <v>7400857</v>
+        <v>7400740</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146071</v>
+        <v>128146073</v>
       </c>
       <c r="B25" t="n">
-        <v>92642</v>
+        <v>78007</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>690800</v>
+        <v>691079</v>
       </c>
       <c r="R25" t="n">
-        <v>7400737</v>
+        <v>7400877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146073</v>
+        <v>128146066</v>
       </c>
       <c r="B26" t="n">
-        <v>78007</v>
+        <v>92642</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691079</v>
+        <v>691535</v>
       </c>
       <c r="R26" t="n">
-        <v>7400877</v>
+        <v>7400857</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128144835</v>
+        <v>128146071</v>
       </c>
       <c r="B27" t="n">
-        <v>91513</v>
+        <v>92642</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691707</v>
+        <v>690800</v>
       </c>
       <c r="R27" t="n">
-        <v>7400750</v>
+        <v>7400737</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128144822</v>
+        <v>128146044</v>
       </c>
       <c r="B35" t="n">
-        <v>79647</v>
+        <v>79618</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691662</v>
+        <v>691077</v>
       </c>
       <c r="R35" t="n">
-        <v>7400760</v>
+        <v>7400881</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144839</v>
+        <v>128144836</v>
       </c>
       <c r="B36" t="n">
-        <v>78435</v>
+        <v>91613</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691806</v>
+        <v>691520</v>
       </c>
       <c r="R36" t="n">
-        <v>7400707</v>
+        <v>7400888</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144836</v>
+        <v>128146047</v>
       </c>
       <c r="B37" t="n">
-        <v>91613</v>
+        <v>91637</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691520</v>
+        <v>691536</v>
       </c>
       <c r="R37" t="n">
-        <v>7400888</v>
+        <v>7400854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128146047</v>
+        <v>128144839</v>
       </c>
       <c r="B38" t="n">
-        <v>91637</v>
+        <v>78435</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691536</v>
+        <v>691806</v>
       </c>
       <c r="R38" t="n">
-        <v>7400854</v>
+        <v>7400707</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146044</v>
+        <v>128144822</v>
       </c>
       <c r="B39" t="n">
-        <v>79618</v>
+        <v>79647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691077</v>
+        <v>691662</v>
       </c>
       <c r="R39" t="n">
-        <v>7400881</v>
+        <v>7400760</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD39" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128102520</v>
       </c>
       <c r="B3" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128146055</v>
       </c>
       <c r="B4" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B5" t="n">
-        <v>78435</v>
+        <v>92650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R5" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B6" t="n">
-        <v>92642</v>
+        <v>78438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R6" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,7 +1203,7 @@
         <v>128144823</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>79650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128146048</v>
       </c>
       <c r="B8" t="n">
-        <v>91637</v>
+        <v>91645</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>128146061</v>
       </c>
       <c r="B9" t="n">
-        <v>91370</v>
+        <v>91378</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128146062</v>
       </c>
       <c r="B10" t="n">
-        <v>91613</v>
+        <v>91621</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128144819</v>
+        <v>128146056</v>
       </c>
       <c r="B11" t="n">
-        <v>79647</v>
+        <v>92642</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691675</v>
+        <v>690781</v>
       </c>
       <c r="R11" t="n">
-        <v>7401012</v>
+        <v>7400555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128146056</v>
+        <v>128144819</v>
       </c>
       <c r="B12" t="n">
-        <v>92634</v>
+        <v>79650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690781</v>
+        <v>691675</v>
       </c>
       <c r="R12" t="n">
-        <v>7400555</v>
+        <v>7401012</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,7 +1845,7 @@
         <v>128146067</v>
       </c>
       <c r="B13" t="n">
-        <v>92642</v>
+        <v>92650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128146053</v>
+        <v>128144820</v>
       </c>
       <c r="B14" t="n">
-        <v>92672</v>
+        <v>79650</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>232140</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691789</v>
+        <v>691749</v>
       </c>
       <c r="R14" t="n">
-        <v>7400698</v>
+        <v>7400999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144820</v>
+        <v>128144824</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>80039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691749</v>
+        <v>691607</v>
       </c>
       <c r="R15" t="n">
-        <v>7400999</v>
+        <v>7400989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,32 +2163,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128144824</v>
+        <v>128146053</v>
       </c>
       <c r="B16" t="n">
-        <v>80036</v>
+        <v>92680</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691607</v>
+        <v>691789</v>
       </c>
       <c r="R16" t="n">
-        <v>7400989</v>
+        <v>7400698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146045</v>
+        <v>128146069</v>
       </c>
       <c r="B17" t="n">
-        <v>90387</v>
+        <v>92650</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691632</v>
+        <v>691003</v>
       </c>
       <c r="R17" t="n">
-        <v>7400779</v>
+        <v>7400833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146069</v>
+        <v>128144834</v>
       </c>
       <c r="B18" t="n">
-        <v>92642</v>
+        <v>79111</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691003</v>
+        <v>691842</v>
       </c>
       <c r="R18" t="n">
-        <v>7400833</v>
+        <v>7400786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,7 +2487,7 @@
         <v>128146063</v>
       </c>
       <c r="B19" t="n">
-        <v>91613</v>
+        <v>91621</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128144834</v>
+        <v>128146046</v>
       </c>
       <c r="B20" t="n">
-        <v>79108</v>
+        <v>90393</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691842</v>
+        <v>690842</v>
       </c>
       <c r="R20" t="n">
-        <v>7400786</v>
+        <v>7400691</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128146046</v>
+        <v>128146045</v>
       </c>
       <c r="B21" t="n">
-        <v>90387</v>
+        <v>90393</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690842</v>
+        <v>691632</v>
       </c>
       <c r="R21" t="n">
-        <v>7400691</v>
+        <v>7400779</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144835</v>
+        <v>128146066</v>
       </c>
       <c r="B22" t="n">
-        <v>91513</v>
+        <v>92650</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691707</v>
+        <v>691535</v>
       </c>
       <c r="R22" t="n">
-        <v>7400750</v>
+        <v>7400857</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128144825</v>
+        <v>128146071</v>
       </c>
       <c r="B23" t="n">
-        <v>80036</v>
+        <v>92650</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691427</v>
+        <v>690800</v>
       </c>
       <c r="R23" t="n">
-        <v>7401053</v>
+        <v>7400737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144829</v>
+        <v>128144835</v>
       </c>
       <c r="B24" t="n">
-        <v>78787</v>
+        <v>91521</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691811</v>
+        <v>691707</v>
       </c>
       <c r="R24" t="n">
-        <v>7400740</v>
+        <v>7400750</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146073</v>
+        <v>128144825</v>
       </c>
       <c r="B25" t="n">
-        <v>78007</v>
+        <v>80039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691079</v>
+        <v>691427</v>
       </c>
       <c r="R25" t="n">
-        <v>7400877</v>
+        <v>7401053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146066</v>
+        <v>128144829</v>
       </c>
       <c r="B26" t="n">
-        <v>92642</v>
+        <v>78790</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691535</v>
+        <v>691811</v>
       </c>
       <c r="R26" t="n">
-        <v>7400857</v>
+        <v>7400740</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146071</v>
+        <v>128146073</v>
       </c>
       <c r="B27" t="n">
-        <v>92642</v>
+        <v>78010</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690800</v>
+        <v>691079</v>
       </c>
       <c r="R27" t="n">
-        <v>7400737</v>
+        <v>7400877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,7 +3450,7 @@
         <v>128146074</v>
       </c>
       <c r="B28" t="n">
-        <v>92636</v>
+        <v>92644</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,32 +3554,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128146064</v>
+        <v>128146068</v>
       </c>
       <c r="B29" t="n">
-        <v>78696</v>
+        <v>92650</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>691003</v>
       </c>
       <c r="R29" t="n">
-        <v>7400833</v>
+        <v>7400832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,32 +3661,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146042</v>
+        <v>128144837</v>
       </c>
       <c r="B30" t="n">
-        <v>79647</v>
+        <v>92650</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691337</v>
+        <v>691657</v>
       </c>
       <c r="R30" t="n">
-        <v>7400753</v>
+        <v>7400758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128146068</v>
+        <v>128146064</v>
       </c>
       <c r="B31" t="n">
-        <v>92642</v>
+        <v>78699</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3806,7 +3806,7 @@
         <v>691003</v>
       </c>
       <c r="R31" t="n">
-        <v>7400832</v>
+        <v>7400833</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3875,32 +3875,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128144837</v>
+        <v>128146042</v>
       </c>
       <c r="B32" t="n">
-        <v>92642</v>
+        <v>79650</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691657</v>
+        <v>691337</v>
       </c>
       <c r="R32" t="n">
-        <v>7400758</v>
+        <v>7400753</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3985,7 +3985,7 @@
         <v>128144840</v>
       </c>
       <c r="B33" t="n">
-        <v>78435</v>
+        <v>78438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>128144818</v>
       </c>
       <c r="B34" t="n">
-        <v>91527</v>
+        <v>91535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4199,7 +4199,7 @@
         <v>128146044</v>
       </c>
       <c r="B35" t="n">
-        <v>79618</v>
+        <v>79621</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144836</v>
+        <v>128144822</v>
       </c>
       <c r="B36" t="n">
-        <v>91613</v>
+        <v>79650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691520</v>
+        <v>691662</v>
       </c>
       <c r="R36" t="n">
-        <v>7400888</v>
+        <v>7400760</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128146047</v>
+        <v>128144839</v>
       </c>
       <c r="B37" t="n">
-        <v>91637</v>
+        <v>78438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>71</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691536</v>
+        <v>691806</v>
       </c>
       <c r="R37" t="n">
-        <v>7400854</v>
+        <v>7400707</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144839</v>
+        <v>128146047</v>
       </c>
       <c r="B38" t="n">
-        <v>78435</v>
+        <v>91645</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6437</v>
+        <v>71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691806</v>
+        <v>691536</v>
       </c>
       <c r="R38" t="n">
-        <v>7400707</v>
+        <v>7400854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,32 +4624,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128144822</v>
+        <v>128144836</v>
       </c>
       <c r="B39" t="n">
-        <v>79647</v>
+        <v>91621</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691662</v>
+        <v>691520</v>
       </c>
       <c r="R39" t="n">
-        <v>7400760</v>
+        <v>7400888</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4734,7 +4734,7 @@
         <v>128146057</v>
       </c>
       <c r="B40" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146065</v>
+        <v>128146043</v>
       </c>
       <c r="B41" t="n">
-        <v>78696</v>
+        <v>79621</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690853</v>
+        <v>691657</v>
       </c>
       <c r="R41" t="n">
-        <v>7400680</v>
+        <v>7400717</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146043</v>
+        <v>128144826</v>
       </c>
       <c r="B42" t="n">
-        <v>79618</v>
+        <v>5493</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691657</v>
+        <v>691845</v>
       </c>
       <c r="R42" t="n">
-        <v>7400717</v>
+        <v>7400932</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5052,10 +5052,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128144826</v>
+        <v>128146065</v>
       </c>
       <c r="B43" t="n">
-        <v>5493</v>
+        <v>78699</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5063,21 +5063,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691845</v>
+        <v>690853</v>
       </c>
       <c r="R43" t="n">
-        <v>7400932</v>
+        <v>7400680</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144828</v>
+        <v>128144830</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>98478</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691820</v>
+        <v>691395</v>
       </c>
       <c r="R44" t="n">
-        <v>7400729</v>
+        <v>7401068</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,7 +5239,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5269,7 +5274,7 @@
         <v>128144833</v>
       </c>
       <c r="B45" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5373,32 +5378,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144830</v>
+        <v>128144828</v>
       </c>
       <c r="B46" t="n">
-        <v>98470</v>
+        <v>78791</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5408,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691395</v>
+        <v>691820</v>
       </c>
       <c r="R46" t="n">
-        <v>7401068</v>
+        <v>7400729</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,7 +5448,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5453,12 +5458,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5485,10 +5485,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128144827</v>
+        <v>128144838</v>
       </c>
       <c r="B47" t="n">
-        <v>78788</v>
+        <v>78438</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,21 +5496,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691749</v>
+        <v>691841</v>
       </c>
       <c r="R47" t="n">
-        <v>7400999</v>
+        <v>7400785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128144838</v>
+        <v>128144827</v>
       </c>
       <c r="B48" t="n">
-        <v>78435</v>
+        <v>78791</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691841</v>
+        <v>691749</v>
       </c>
       <c r="R48" t="n">
-        <v>7400785</v>
+        <v>7400999</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128146066</v>
+        <v>128144835</v>
       </c>
       <c r="B22" t="n">
-        <v>92650</v>
+        <v>91521</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691535</v>
+        <v>691707</v>
       </c>
       <c r="R22" t="n">
-        <v>7400857</v>
+        <v>7400750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128146071</v>
+        <v>128146066</v>
       </c>
       <c r="B23" t="n">
         <v>92650</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690800</v>
+        <v>691535</v>
       </c>
       <c r="R23" t="n">
-        <v>7400737</v>
+        <v>7400857</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144835</v>
+        <v>128146071</v>
       </c>
       <c r="B24" t="n">
-        <v>91521</v>
+        <v>92650</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691707</v>
+        <v>690800</v>
       </c>
       <c r="R24" t="n">
-        <v>7400750</v>
+        <v>7400737</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128144825</v>
+        <v>128146073</v>
       </c>
       <c r="B25" t="n">
-        <v>80039</v>
+        <v>78010</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691427</v>
+        <v>691079</v>
       </c>
       <c r="R25" t="n">
-        <v>7401053</v>
+        <v>7400877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128144829</v>
+        <v>128144825</v>
       </c>
       <c r="B26" t="n">
-        <v>78790</v>
+        <v>80039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691811</v>
+        <v>691427</v>
       </c>
       <c r="R26" t="n">
-        <v>7400740</v>
+        <v>7401053</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146073</v>
+        <v>128144829</v>
       </c>
       <c r="B27" t="n">
-        <v>78010</v>
+        <v>78790</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3351,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691079</v>
+        <v>691811</v>
       </c>
       <c r="R27" t="n">
-        <v>7400877</v>
+        <v>7400740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128146064</v>
+        <v>128146042</v>
       </c>
       <c r="B31" t="n">
-        <v>78699</v>
+        <v>79650</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3779,21 +3779,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691003</v>
+        <v>691337</v>
       </c>
       <c r="R31" t="n">
-        <v>7400833</v>
+        <v>7400753</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128146042</v>
+        <v>128146064</v>
       </c>
       <c r="B32" t="n">
-        <v>79650</v>
+        <v>78699</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691337</v>
+        <v>691003</v>
       </c>
       <c r="R32" t="n">
-        <v>7400753</v>
+        <v>7400833</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5485,10 +5485,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128144838</v>
+        <v>128144827</v>
       </c>
       <c r="B47" t="n">
-        <v>78438</v>
+        <v>78791</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,21 +5496,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691841</v>
+        <v>691749</v>
       </c>
       <c r="R47" t="n">
-        <v>7400785</v>
+        <v>7400999</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128144827</v>
+        <v>128144838</v>
       </c>
       <c r="B48" t="n">
-        <v>78791</v>
+        <v>78438</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691749</v>
+        <v>691841</v>
       </c>
       <c r="R48" t="n">
-        <v>7400999</v>
+        <v>7400785</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128102520</v>
       </c>
       <c r="B3" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128146055</v>
       </c>
       <c r="B4" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128146070</v>
       </c>
       <c r="B5" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128146075</v>
       </c>
       <c r="B6" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>128144823</v>
       </c>
       <c r="B7" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
         <v>128146048</v>
       </c>
       <c r="B8" t="n">
-        <v>91645</v>
+        <v>91737</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>128146061</v>
       </c>
       <c r="B9" t="n">
-        <v>91378</v>
+        <v>91470</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128146062</v>
       </c>
       <c r="B10" t="n">
-        <v>91621</v>
+        <v>91713</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128146056</v>
       </c>
       <c r="B11" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128144819</v>
       </c>
       <c r="B12" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146067</v>
+        <v>128144824</v>
       </c>
       <c r="B13" t="n">
-        <v>92650</v>
+        <v>80092</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691067</v>
+        <v>691607</v>
       </c>
       <c r="R13" t="n">
-        <v>7400865</v>
+        <v>7400989</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1952,7 +1952,7 @@
         <v>128144820</v>
       </c>
       <c r="B14" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2056,10 +2056,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144824</v>
+        <v>128146067</v>
       </c>
       <c r="B15" t="n">
-        <v>80039</v>
+        <v>92742</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2067,21 +2067,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691607</v>
+        <v>691067</v>
       </c>
       <c r="R15" t="n">
-        <v>7400989</v>
+        <v>7400865</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,7 +2166,7 @@
         <v>128146053</v>
       </c>
       <c r="B16" t="n">
-        <v>92680</v>
+        <v>92772</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146069</v>
+        <v>128146063</v>
       </c>
       <c r="B17" t="n">
-        <v>92650</v>
+        <v>91713</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691003</v>
+        <v>690806</v>
       </c>
       <c r="R17" t="n">
-        <v>7400833</v>
+        <v>7400768</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128144834</v>
+        <v>128146069</v>
       </c>
       <c r="B18" t="n">
-        <v>79111</v>
+        <v>92742</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691842</v>
+        <v>691003</v>
       </c>
       <c r="R18" t="n">
-        <v>7400786</v>
+        <v>7400833</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,32 +2484,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128146063</v>
+        <v>128146046</v>
       </c>
       <c r="B19" t="n">
-        <v>91621</v>
+        <v>90485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>65</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>690806</v>
+        <v>690842</v>
       </c>
       <c r="R19" t="n">
-        <v>7400768</v>
+        <v>7400691</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128146046</v>
+        <v>128144834</v>
       </c>
       <c r="B20" t="n">
-        <v>90393</v>
+        <v>79162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690842</v>
+        <v>691842</v>
       </c>
       <c r="R20" t="n">
-        <v>7400691</v>
+        <v>7400786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,7 +2701,7 @@
         <v>128146045</v>
       </c>
       <c r="B21" t="n">
-        <v>90393</v>
+        <v>90485</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144835</v>
+        <v>128146066</v>
       </c>
       <c r="B22" t="n">
-        <v>91521</v>
+        <v>92742</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691707</v>
+        <v>691535</v>
       </c>
       <c r="R22" t="n">
-        <v>7400750</v>
+        <v>7400857</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128146066</v>
+        <v>128146071</v>
       </c>
       <c r="B23" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691535</v>
+        <v>690800</v>
       </c>
       <c r="R23" t="n">
-        <v>7400857</v>
+        <v>7400737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128146071</v>
+        <v>128144835</v>
       </c>
       <c r="B24" t="n">
-        <v>92650</v>
+        <v>91613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690800</v>
+        <v>691707</v>
       </c>
       <c r="R24" t="n">
-        <v>7400737</v>
+        <v>7400750</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146073</v>
+        <v>128144825</v>
       </c>
       <c r="B25" t="n">
-        <v>78010</v>
+        <v>80092</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691079</v>
+        <v>691427</v>
       </c>
       <c r="R25" t="n">
-        <v>7400877</v>
+        <v>7401053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128144825</v>
+        <v>128146073</v>
       </c>
       <c r="B26" t="n">
-        <v>80039</v>
+        <v>78055</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691427</v>
+        <v>691079</v>
       </c>
       <c r="R26" t="n">
-        <v>7401053</v>
+        <v>7400877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3343,7 +3343,7 @@
         <v>128144829</v>
       </c>
       <c r="B27" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>128146074</v>
       </c>
       <c r="B28" t="n">
-        <v>92644</v>
+        <v>92736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,32 +3554,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128146068</v>
+        <v>128146064</v>
       </c>
       <c r="B29" t="n">
-        <v>92650</v>
+        <v>78749</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>691003</v>
       </c>
       <c r="R29" t="n">
-        <v>7400832</v>
+        <v>7400833</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128144837</v>
+        <v>128146068</v>
       </c>
       <c r="B30" t="n">
-        <v>92650</v>
+        <v>92742</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691657</v>
+        <v>691003</v>
       </c>
       <c r="R30" t="n">
-        <v>7400758</v>
+        <v>7400832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128146042</v>
+        <v>128144837</v>
       </c>
       <c r="B31" t="n">
-        <v>79650</v>
+        <v>92742</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691337</v>
+        <v>691657</v>
       </c>
       <c r="R31" t="n">
-        <v>7400753</v>
+        <v>7400758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128146064</v>
+        <v>128146042</v>
       </c>
       <c r="B32" t="n">
-        <v>78699</v>
+        <v>79702</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691003</v>
+        <v>691337</v>
       </c>
       <c r="R32" t="n">
-        <v>7400833</v>
+        <v>7400753</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3985,7 +3985,7 @@
         <v>128144840</v>
       </c>
       <c r="B33" t="n">
-        <v>78438</v>
+        <v>78486</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>128144818</v>
       </c>
       <c r="B34" t="n">
-        <v>91535</v>
+        <v>91627</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146044</v>
+        <v>128144822</v>
       </c>
       <c r="B35" t="n">
-        <v>79621</v>
+        <v>79702</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691077</v>
+        <v>691662</v>
       </c>
       <c r="R35" t="n">
-        <v>7400881</v>
+        <v>7400760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,10 +4303,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144822</v>
+        <v>128144839</v>
       </c>
       <c r="B36" t="n">
-        <v>79650</v>
+        <v>78486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4314,21 +4314,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691662</v>
+        <v>691806</v>
       </c>
       <c r="R36" t="n">
-        <v>7400760</v>
+        <v>7400707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144839</v>
+        <v>128146047</v>
       </c>
       <c r="B37" t="n">
-        <v>78438</v>
+        <v>91737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>71</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691806</v>
+        <v>691536</v>
       </c>
       <c r="R37" t="n">
-        <v>7400707</v>
+        <v>7400854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128146047</v>
+        <v>128144836</v>
       </c>
       <c r="B38" t="n">
-        <v>91645</v>
+        <v>91713</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691536</v>
+        <v>691520</v>
       </c>
       <c r="R38" t="n">
-        <v>7400854</v>
+        <v>7400888</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,32 +4624,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128144836</v>
+        <v>128146044</v>
       </c>
       <c r="B39" t="n">
-        <v>91621</v>
+        <v>79673</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691520</v>
+        <v>691077</v>
       </c>
       <c r="R39" t="n">
-        <v>7400888</v>
+        <v>7400881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4734,7 +4734,7 @@
         <v>128146057</v>
       </c>
       <c r="B40" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146043</v>
+        <v>128146065</v>
       </c>
       <c r="B41" t="n">
-        <v>79621</v>
+        <v>78749</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691657</v>
+        <v>690853</v>
       </c>
       <c r="R41" t="n">
-        <v>7400717</v>
+        <v>7400680</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5052,10 +5052,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128146065</v>
+        <v>128146043</v>
       </c>
       <c r="B43" t="n">
-        <v>78699</v>
+        <v>79673</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5063,21 +5063,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5087,10 +5087,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>690853</v>
+        <v>691657</v>
       </c>
       <c r="R43" t="n">
-        <v>7400680</v>
+        <v>7400717</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144830</v>
+        <v>128144828</v>
       </c>
       <c r="B44" t="n">
-        <v>98478</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691395</v>
+        <v>691820</v>
       </c>
       <c r="R44" t="n">
-        <v>7401068</v>
+        <v>7400729</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,12 +5239,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5274,7 +5269,7 @@
         <v>128144833</v>
       </c>
       <c r="B45" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5378,32 +5373,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144828</v>
+        <v>128144830</v>
       </c>
       <c r="B46" t="n">
-        <v>78791</v>
+        <v>98571</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5413,10 +5408,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691820</v>
+        <v>691395</v>
       </c>
       <c r="R46" t="n">
-        <v>7400729</v>
+        <v>7401068</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5443,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5458,7 +5453,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5485,10 +5485,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128144827</v>
+        <v>128144838</v>
       </c>
       <c r="B47" t="n">
-        <v>78791</v>
+        <v>78486</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,21 +5496,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691749</v>
+        <v>691841</v>
       </c>
       <c r="R47" t="n">
-        <v>7400999</v>
+        <v>7400785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128144838</v>
+        <v>128144827</v>
       </c>
       <c r="B48" t="n">
-        <v>78438</v>
+        <v>78841</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691841</v>
+        <v>691749</v>
       </c>
       <c r="R48" t="n">
-        <v>7400785</v>
+        <v>7400999</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128146056</v>
+        <v>128144819</v>
       </c>
       <c r="B11" t="n">
-        <v>92734</v>
+        <v>79702</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690781</v>
+        <v>691675</v>
       </c>
       <c r="R11" t="n">
-        <v>7400555</v>
+        <v>7401012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128144819</v>
+        <v>128146056</v>
       </c>
       <c r="B12" t="n">
-        <v>79702</v>
+        <v>92734</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691675</v>
+        <v>690781</v>
       </c>
       <c r="R12" t="n">
-        <v>7401012</v>
+        <v>7400555</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128144824</v>
+        <v>128146067</v>
       </c>
       <c r="B13" t="n">
-        <v>80092</v>
+        <v>92742</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1853,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691607</v>
+        <v>691067</v>
       </c>
       <c r="R13" t="n">
-        <v>7400989</v>
+        <v>7400865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128144820</v>
+        <v>128144824</v>
       </c>
       <c r="B14" t="n">
-        <v>79702</v>
+        <v>80092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691749</v>
+        <v>691607</v>
       </c>
       <c r="R14" t="n">
-        <v>7400999</v>
+        <v>7400989</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128146067</v>
+        <v>128144820</v>
       </c>
       <c r="B15" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691067</v>
+        <v>691749</v>
       </c>
       <c r="R15" t="n">
-        <v>7400865</v>
+        <v>7400999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128146066</v>
+        <v>128144835</v>
       </c>
       <c r="B22" t="n">
-        <v>92742</v>
+        <v>91613</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691535</v>
+        <v>691707</v>
       </c>
       <c r="R22" t="n">
-        <v>7400857</v>
+        <v>7400750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,7 +2912,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128146071</v>
+        <v>128146066</v>
       </c>
       <c r="B23" t="n">
         <v>92742</v>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690800</v>
+        <v>691535</v>
       </c>
       <c r="R23" t="n">
-        <v>7400737</v>
+        <v>7400857</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144835</v>
+        <v>128146071</v>
       </c>
       <c r="B24" t="n">
-        <v>91613</v>
+        <v>92742</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691707</v>
+        <v>690800</v>
       </c>
       <c r="R24" t="n">
-        <v>7400750</v>
+        <v>7400737</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128144825</v>
+        <v>128146073</v>
       </c>
       <c r="B25" t="n">
-        <v>80092</v>
+        <v>78055</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691427</v>
+        <v>691079</v>
       </c>
       <c r="R25" t="n">
-        <v>7401053</v>
+        <v>7400877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146073</v>
+        <v>128144829</v>
       </c>
       <c r="B26" t="n">
-        <v>78055</v>
+        <v>78840</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691079</v>
+        <v>691811</v>
       </c>
       <c r="R26" t="n">
-        <v>7400877</v>
+        <v>7400740</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128144829</v>
+        <v>128144825</v>
       </c>
       <c r="B27" t="n">
-        <v>78840</v>
+        <v>80092</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691811</v>
+        <v>691427</v>
       </c>
       <c r="R27" t="n">
-        <v>7400740</v>
+        <v>7401053</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,7 +3661,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146068</v>
+        <v>128144837</v>
       </c>
       <c r="B30" t="n">
         <v>92742</v>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691003</v>
+        <v>691657</v>
       </c>
       <c r="R30" t="n">
-        <v>7400832</v>
+        <v>7400758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,7 +3768,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128144837</v>
+        <v>128146068</v>
       </c>
       <c r="B31" t="n">
         <v>92742</v>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691657</v>
+        <v>691003</v>
       </c>
       <c r="R31" t="n">
-        <v>7400758</v>
+        <v>7400832</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4196,32 +4196,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128144822</v>
+        <v>128146047</v>
       </c>
       <c r="B35" t="n">
-        <v>79702</v>
+        <v>91737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691662</v>
+        <v>691536</v>
       </c>
       <c r="R35" t="n">
-        <v>7400760</v>
+        <v>7400854</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144839</v>
+        <v>128144836</v>
       </c>
       <c r="B36" t="n">
-        <v>78486</v>
+        <v>91713</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691806</v>
+        <v>691520</v>
       </c>
       <c r="R36" t="n">
-        <v>7400707</v>
+        <v>7400888</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128146047</v>
+        <v>128144839</v>
       </c>
       <c r="B37" t="n">
-        <v>91737</v>
+        <v>78486</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>71</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691536</v>
+        <v>691806</v>
       </c>
       <c r="R37" t="n">
-        <v>7400854</v>
+        <v>7400707</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144836</v>
+        <v>128144822</v>
       </c>
       <c r="B38" t="n">
-        <v>91713</v>
+        <v>79702</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691520</v>
+        <v>691662</v>
       </c>
       <c r="R38" t="n">
-        <v>7400888</v>
+        <v>7400760</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146065</v>
+        <v>128144826</v>
       </c>
       <c r="B41" t="n">
-        <v>78749</v>
+        <v>5493</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690853</v>
+        <v>691845</v>
       </c>
       <c r="R41" t="n">
-        <v>7400680</v>
+        <v>7400932</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128144826</v>
+        <v>128146065</v>
       </c>
       <c r="B42" t="n">
-        <v>5493</v>
+        <v>78749</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691845</v>
+        <v>690853</v>
       </c>
       <c r="R42" t="n">
-        <v>7400932</v>
+        <v>7400680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144828</v>
+        <v>128144830</v>
       </c>
       <c r="B44" t="n">
-        <v>78841</v>
+        <v>98571</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691820</v>
+        <v>691395</v>
       </c>
       <c r="R44" t="n">
-        <v>7400729</v>
+        <v>7401068</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,7 +5239,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,32 +5271,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128144833</v>
+        <v>128144828</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>78841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5301,10 +5306,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691471</v>
+        <v>691820</v>
       </c>
       <c r="R45" t="n">
-        <v>7401138</v>
+        <v>7400729</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5341,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5346,7 +5351,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5373,7 +5378,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144830</v>
+        <v>128144833</v>
       </c>
       <c r="B46" t="n">
         <v>98571</v>
@@ -5408,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691395</v>
+        <v>691471</v>
       </c>
       <c r="R46" t="n">
-        <v>7401068</v>
+        <v>7401138</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,7 +5448,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5453,12 +5458,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B5" t="n">
-        <v>92742</v>
+        <v>78486</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R5" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B6" t="n">
-        <v>78486</v>
+        <v>92742</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R6" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128144824</v>
+        <v>128146053</v>
       </c>
       <c r="B14" t="n">
-        <v>80092</v>
+        <v>92772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6456</v>
+        <v>232140</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691607</v>
+        <v>691789</v>
       </c>
       <c r="R14" t="n">
-        <v>7400989</v>
+        <v>7400698</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2163,32 +2163,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128146053</v>
+        <v>128144824</v>
       </c>
       <c r="B16" t="n">
-        <v>92772</v>
+        <v>80092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691789</v>
+        <v>691607</v>
       </c>
       <c r="R16" t="n">
-        <v>7400698</v>
+        <v>7400989</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146063</v>
+        <v>128146069</v>
       </c>
       <c r="B17" t="n">
-        <v>91713</v>
+        <v>92742</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>690806</v>
+        <v>691003</v>
       </c>
       <c r="R17" t="n">
-        <v>7400768</v>
+        <v>7400833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146069</v>
+        <v>128146046</v>
       </c>
       <c r="B18" t="n">
-        <v>92742</v>
+        <v>90485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691003</v>
+        <v>690842</v>
       </c>
       <c r="R18" t="n">
-        <v>7400833</v>
+        <v>7400691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,7 +2484,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128146046</v>
+        <v>128146045</v>
       </c>
       <c r="B19" t="n">
         <v>90485</v>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>690842</v>
+        <v>691632</v>
       </c>
       <c r="R19" t="n">
-        <v>7400691</v>
+        <v>7400779</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,32 +2591,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128144834</v>
+        <v>128146063</v>
       </c>
       <c r="B20" t="n">
-        <v>79162</v>
+        <v>91713</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691842</v>
+        <v>690806</v>
       </c>
       <c r="R20" t="n">
-        <v>7400786</v>
+        <v>7400768</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,10 +2698,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128146045</v>
+        <v>128144834</v>
       </c>
       <c r="B21" t="n">
-        <v>90485</v>
+        <v>79162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2709,21 +2709,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691632</v>
+        <v>691842</v>
       </c>
       <c r="R21" t="n">
-        <v>7400779</v>
+        <v>7400786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128146066</v>
+        <v>128144825</v>
       </c>
       <c r="B23" t="n">
-        <v>92742</v>
+        <v>80092</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691535</v>
+        <v>691427</v>
       </c>
       <c r="R23" t="n">
-        <v>7400857</v>
+        <v>7401053</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128146071</v>
+        <v>128144829</v>
       </c>
       <c r="B24" t="n">
-        <v>92742</v>
+        <v>78840</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690800</v>
+        <v>691811</v>
       </c>
       <c r="R24" t="n">
-        <v>7400737</v>
+        <v>7400740</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128144829</v>
+        <v>128146066</v>
       </c>
       <c r="B26" t="n">
-        <v>78840</v>
+        <v>92742</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691811</v>
+        <v>691535</v>
       </c>
       <c r="R26" t="n">
-        <v>7400740</v>
+        <v>7400857</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128144825</v>
+        <v>128146071</v>
       </c>
       <c r="B27" t="n">
-        <v>80092</v>
+        <v>92742</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3351,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691427</v>
+        <v>690800</v>
       </c>
       <c r="R27" t="n">
-        <v>7401053</v>
+        <v>7400737</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3661,32 +3661,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128144837</v>
+        <v>128146042</v>
       </c>
       <c r="B30" t="n">
-        <v>92742</v>
+        <v>79702</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691657</v>
+        <v>691337</v>
       </c>
       <c r="R30" t="n">
-        <v>7400758</v>
+        <v>7400753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3875,32 +3875,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128146042</v>
+        <v>128144837</v>
       </c>
       <c r="B32" t="n">
-        <v>79702</v>
+        <v>92742</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691337</v>
+        <v>691657</v>
       </c>
       <c r="R32" t="n">
-        <v>7400753</v>
+        <v>7400758</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,32 +4196,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146047</v>
+        <v>128144822</v>
       </c>
       <c r="B35" t="n">
-        <v>91737</v>
+        <v>79702</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691536</v>
+        <v>691662</v>
       </c>
       <c r="R35" t="n">
-        <v>7400854</v>
+        <v>7400760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144836</v>
+        <v>128144839</v>
       </c>
       <c r="B36" t="n">
-        <v>91713</v>
+        <v>78486</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691520</v>
+        <v>691806</v>
       </c>
       <c r="R36" t="n">
-        <v>7400888</v>
+        <v>7400707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144839</v>
+        <v>128144836</v>
       </c>
       <c r="B37" t="n">
-        <v>78486</v>
+        <v>91713</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691806</v>
+        <v>691520</v>
       </c>
       <c r="R37" t="n">
-        <v>7400707</v>
+        <v>7400888</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144822</v>
+        <v>128146047</v>
       </c>
       <c r="B38" t="n">
-        <v>79702</v>
+        <v>91737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691662</v>
+        <v>691536</v>
       </c>
       <c r="R38" t="n">
-        <v>7400760</v>
+        <v>7400854</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128144826</v>
+        <v>128146065</v>
       </c>
       <c r="B41" t="n">
-        <v>5493</v>
+        <v>78749</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691845</v>
+        <v>690853</v>
       </c>
       <c r="R41" t="n">
-        <v>7400932</v>
+        <v>7400680</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146065</v>
+        <v>128144826</v>
       </c>
       <c r="B42" t="n">
-        <v>78749</v>
+        <v>5493</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690853</v>
+        <v>691845</v>
       </c>
       <c r="R42" t="n">
-        <v>7400680</v>
+        <v>7400932</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144830</v>
+        <v>128144828</v>
       </c>
       <c r="B44" t="n">
-        <v>98571</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691395</v>
+        <v>691820</v>
       </c>
       <c r="R44" t="n">
-        <v>7401068</v>
+        <v>7400729</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,12 +5239,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5271,32 +5266,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128144828</v>
+        <v>128144833</v>
       </c>
       <c r="B45" t="n">
-        <v>78841</v>
+        <v>98571</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5306,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691820</v>
+        <v>691471</v>
       </c>
       <c r="R45" t="n">
-        <v>7400729</v>
+        <v>7401138</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5336,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5351,7 +5346,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5378,7 +5373,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144833</v>
+        <v>128144830</v>
       </c>
       <c r="B46" t="n">
         <v>98571</v>
@@ -5413,10 +5408,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691471</v>
+        <v>691395</v>
       </c>
       <c r="R46" t="n">
-        <v>7401138</v>
+        <v>7401068</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5443,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5458,7 +5453,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5485,10 +5485,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128144838</v>
+        <v>128144827</v>
       </c>
       <c r="B47" t="n">
-        <v>78486</v>
+        <v>78841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,21 +5496,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691841</v>
+        <v>691749</v>
       </c>
       <c r="R47" t="n">
-        <v>7400785</v>
+        <v>7400999</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128144827</v>
+        <v>128144838</v>
       </c>
       <c r="B48" t="n">
-        <v>78841</v>
+        <v>78486</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691749</v>
+        <v>691841</v>
       </c>
       <c r="R48" t="n">
-        <v>7400999</v>
+        <v>7400785</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128102520</v>
       </c>
       <c r="B3" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128146055</v>
       </c>
       <c r="B4" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B5" t="n">
-        <v>78486</v>
+        <v>92754</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R5" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B6" t="n">
-        <v>92742</v>
+        <v>78490</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R6" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B7" t="n">
-        <v>79702</v>
+        <v>91749</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R7" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B8" t="n">
-        <v>91737</v>
+        <v>79706</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R8" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,7 +1417,7 @@
         <v>128146061</v>
       </c>
       <c r="B9" t="n">
-        <v>91470</v>
+        <v>91482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128146062</v>
       </c>
       <c r="B10" t="n">
-        <v>91713</v>
+        <v>91725</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>128144819</v>
       </c>
       <c r="B11" t="n">
-        <v>79702</v>
+        <v>79706</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>128146056</v>
       </c>
       <c r="B12" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>128146067</v>
       </c>
       <c r="B13" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128146053</v>
+        <v>128144820</v>
       </c>
       <c r="B14" t="n">
-        <v>92772</v>
+        <v>79706</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>232140</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691789</v>
+        <v>691749</v>
       </c>
       <c r="R14" t="n">
-        <v>7400698</v>
+        <v>7400999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144820</v>
+        <v>128144824</v>
       </c>
       <c r="B15" t="n">
-        <v>79702</v>
+        <v>80096</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691749</v>
+        <v>691607</v>
       </c>
       <c r="R15" t="n">
-        <v>7400999</v>
+        <v>7400989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,32 +2163,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128144824</v>
+        <v>128146053</v>
       </c>
       <c r="B16" t="n">
-        <v>80092</v>
+        <v>92784</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691607</v>
+        <v>691789</v>
       </c>
       <c r="R16" t="n">
-        <v>7400989</v>
+        <v>7400698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146069</v>
+        <v>128146046</v>
       </c>
       <c r="B17" t="n">
-        <v>92742</v>
+        <v>90497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691003</v>
+        <v>690842</v>
       </c>
       <c r="R17" t="n">
-        <v>7400833</v>
+        <v>7400691</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,10 +2377,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146046</v>
+        <v>128144834</v>
       </c>
       <c r="B18" t="n">
-        <v>90485</v>
+        <v>79166</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2388,21 +2388,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>690842</v>
+        <v>691842</v>
       </c>
       <c r="R18" t="n">
-        <v>7400691</v>
+        <v>7400786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,7 +2487,7 @@
         <v>128146045</v>
       </c>
       <c r="B19" t="n">
-        <v>90485</v>
+        <v>90497</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2591,32 +2591,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128146063</v>
+        <v>128146069</v>
       </c>
       <c r="B20" t="n">
-        <v>91713</v>
+        <v>92754</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690806</v>
+        <v>691003</v>
       </c>
       <c r="R20" t="n">
-        <v>7400768</v>
+        <v>7400833</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128144834</v>
+        <v>128146063</v>
       </c>
       <c r="B21" t="n">
-        <v>79162</v>
+        <v>91725</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>864</v>
+        <v>65</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691842</v>
+        <v>690806</v>
       </c>
       <c r="R21" t="n">
-        <v>7400786</v>
+        <v>7400768</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144835</v>
+        <v>128146066</v>
       </c>
       <c r="B22" t="n">
-        <v>91613</v>
+        <v>92754</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691707</v>
+        <v>691535</v>
       </c>
       <c r="R22" t="n">
-        <v>7400750</v>
+        <v>7400857</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128144825</v>
+        <v>128146071</v>
       </c>
       <c r="B23" t="n">
-        <v>80092</v>
+        <v>92754</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691427</v>
+        <v>690800</v>
       </c>
       <c r="R23" t="n">
-        <v>7401053</v>
+        <v>7400737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144829</v>
+        <v>128144835</v>
       </c>
       <c r="B24" t="n">
-        <v>78840</v>
+        <v>91625</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691811</v>
+        <v>691707</v>
       </c>
       <c r="R24" t="n">
-        <v>7400740</v>
+        <v>7400750</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146073</v>
+        <v>128144829</v>
       </c>
       <c r="B25" t="n">
-        <v>78055</v>
+        <v>78844</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3137,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691079</v>
+        <v>691811</v>
       </c>
       <c r="R25" t="n">
-        <v>7400877</v>
+        <v>7400740</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146066</v>
+        <v>128144825</v>
       </c>
       <c r="B26" t="n">
-        <v>92742</v>
+        <v>80096</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691535</v>
+        <v>691427</v>
       </c>
       <c r="R26" t="n">
-        <v>7400857</v>
+        <v>7401053</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146071</v>
+        <v>128146073</v>
       </c>
       <c r="B27" t="n">
-        <v>92742</v>
+        <v>78059</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690800</v>
+        <v>691079</v>
       </c>
       <c r="R27" t="n">
-        <v>7400737</v>
+        <v>7400877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,7 +3450,7 @@
         <v>128146074</v>
       </c>
       <c r="B28" t="n">
-        <v>92736</v>
+        <v>92748</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128146064</v>
+        <v>128146042</v>
       </c>
       <c r="B29" t="n">
-        <v>78749</v>
+        <v>79706</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691003</v>
+        <v>691337</v>
       </c>
       <c r="R29" t="n">
-        <v>7400833</v>
+        <v>7400753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146042</v>
+        <v>128146064</v>
       </c>
       <c r="B30" t="n">
-        <v>79702</v>
+        <v>78753</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3672,21 +3672,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691337</v>
+        <v>691003</v>
       </c>
       <c r="R30" t="n">
-        <v>7400753</v>
+        <v>7400833</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3771,7 +3771,7 @@
         <v>128146068</v>
       </c>
       <c r="B31" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>128144837</v>
       </c>
       <c r="B32" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>128144840</v>
       </c>
       <c r="B33" t="n">
-        <v>78486</v>
+        <v>78490</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>128144818</v>
       </c>
       <c r="B34" t="n">
-        <v>91627</v>
+        <v>91639</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,32 +4196,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128144822</v>
+        <v>128146047</v>
       </c>
       <c r="B35" t="n">
-        <v>79702</v>
+        <v>91749</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691662</v>
+        <v>691536</v>
       </c>
       <c r="R35" t="n">
-        <v>7400760</v>
+        <v>7400854</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144839</v>
+        <v>128144836</v>
       </c>
       <c r="B36" t="n">
-        <v>78486</v>
+        <v>91725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>65</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691806</v>
+        <v>691520</v>
       </c>
       <c r="R36" t="n">
-        <v>7400707</v>
+        <v>7400888</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144836</v>
+        <v>128144839</v>
       </c>
       <c r="B37" t="n">
-        <v>91713</v>
+        <v>78490</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691520</v>
+        <v>691806</v>
       </c>
       <c r="R37" t="n">
-        <v>7400888</v>
+        <v>7400707</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128146047</v>
+        <v>128144822</v>
       </c>
       <c r="B38" t="n">
-        <v>91737</v>
+        <v>79706</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691536</v>
+        <v>691662</v>
       </c>
       <c r="R38" t="n">
-        <v>7400854</v>
+        <v>7400760</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4627,7 +4627,7 @@
         <v>128146044</v>
       </c>
       <c r="B39" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>128146057</v>
       </c>
       <c r="B40" t="n">
-        <v>92734</v>
+        <v>92746</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4841,7 +4841,7 @@
         <v>128146065</v>
       </c>
       <c r="B41" t="n">
-        <v>78749</v>
+        <v>78753</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>128146043</v>
       </c>
       <c r="B43" t="n">
-        <v>79673</v>
+        <v>79677</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144828</v>
+        <v>128144830</v>
       </c>
       <c r="B44" t="n">
-        <v>78841</v>
+        <v>98585</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691820</v>
+        <v>691395</v>
       </c>
       <c r="R44" t="n">
-        <v>7400729</v>
+        <v>7401068</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,7 +5239,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5269,7 +5274,7 @@
         <v>128144833</v>
       </c>
       <c r="B45" t="n">
-        <v>98571</v>
+        <v>98585</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5373,32 +5378,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144830</v>
+        <v>128144828</v>
       </c>
       <c r="B46" t="n">
-        <v>98571</v>
+        <v>78845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5408,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691395</v>
+        <v>691820</v>
       </c>
       <c r="R46" t="n">
-        <v>7401068</v>
+        <v>7400729</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,7 +5448,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5453,12 +5458,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5485,10 +5485,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128144827</v>
+        <v>128144838</v>
       </c>
       <c r="B47" t="n">
-        <v>78841</v>
+        <v>78490</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5496,21 +5496,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6437</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5520,10 +5520,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691749</v>
+        <v>691841</v>
       </c>
       <c r="R47" t="n">
-        <v>7400999</v>
+        <v>7400785</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5555,7 +5555,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5592,10 +5592,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128144838</v>
+        <v>128144827</v>
       </c>
       <c r="B48" t="n">
-        <v>78486</v>
+        <v>78845</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5603,21 +5603,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6437</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691841</v>
+        <v>691749</v>
       </c>
       <c r="R48" t="n">
-        <v>7400785</v>
+        <v>7400999</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5662,7 +5662,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5672,7 +5672,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128144819</v>
+        <v>128146056</v>
       </c>
       <c r="B11" t="n">
-        <v>79706</v>
+        <v>92746</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691675</v>
+        <v>690781</v>
       </c>
       <c r="R11" t="n">
-        <v>7401012</v>
+        <v>7400555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128146056</v>
+        <v>128144819</v>
       </c>
       <c r="B12" t="n">
-        <v>92746</v>
+        <v>79706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690781</v>
+        <v>691675</v>
       </c>
       <c r="R12" t="n">
-        <v>7400555</v>
+        <v>7401012</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -5159,7 +5159,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144830</v>
+        <v>128144833</v>
       </c>
       <c r="B44" t="n">
         <v>98585</v>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691395</v>
+        <v>691471</v>
       </c>
       <c r="R44" t="n">
-        <v>7401068</v>
+        <v>7401138</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,12 +5239,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5271,32 +5266,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128144833</v>
+        <v>128144828</v>
       </c>
       <c r="B45" t="n">
-        <v>98585</v>
+        <v>78845</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5306,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691471</v>
+        <v>691820</v>
       </c>
       <c r="R45" t="n">
-        <v>7401138</v>
+        <v>7400729</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5341,7 +5336,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5351,7 +5346,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5378,32 +5373,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144828</v>
+        <v>128144830</v>
       </c>
       <c r="B46" t="n">
-        <v>78845</v>
+        <v>98585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5413,10 +5408,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691820</v>
+        <v>691395</v>
       </c>
       <c r="R46" t="n">
-        <v>7400729</v>
+        <v>7401068</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5443,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5458,7 +5453,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128146055</v>
       </c>
       <c r="B4" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>128146070</v>
       </c>
       <c r="B5" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128146075</v>
       </c>
       <c r="B6" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B7" t="n">
-        <v>91749</v>
+        <v>79708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R7" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B8" t="n">
-        <v>79706</v>
+        <v>91751</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R8" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,7 +1417,7 @@
         <v>128146061</v>
       </c>
       <c r="B9" t="n">
-        <v>91482</v>
+        <v>91484</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128146062</v>
       </c>
       <c r="B10" t="n">
-        <v>91725</v>
+        <v>91727</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128146056</v>
+        <v>128144819</v>
       </c>
       <c r="B11" t="n">
-        <v>92746</v>
+        <v>79708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>690781</v>
+        <v>691675</v>
       </c>
       <c r="R11" t="n">
-        <v>7400555</v>
+        <v>7401012</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128144819</v>
+        <v>128146056</v>
       </c>
       <c r="B12" t="n">
-        <v>79706</v>
+        <v>92748</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691675</v>
+        <v>690781</v>
       </c>
       <c r="R12" t="n">
-        <v>7401012</v>
+        <v>7400555</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1845,7 +1845,7 @@
         <v>128146067</v>
       </c>
       <c r="B13" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>128144820</v>
       </c>
       <c r="B14" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
         <v>128144824</v>
       </c>
       <c r="B15" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>128146053</v>
       </c>
       <c r="B16" t="n">
-        <v>92784</v>
+        <v>92786</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         <v>128146046</v>
       </c>
       <c r="B17" t="n">
-        <v>90497</v>
+        <v>90499</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128144834</v>
+        <v>128146069</v>
       </c>
       <c r="B18" t="n">
-        <v>79166</v>
+        <v>92756</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691842</v>
+        <v>691003</v>
       </c>
       <c r="R18" t="n">
-        <v>7400786</v>
+        <v>7400833</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128146045</v>
+        <v>128144834</v>
       </c>
       <c r="B19" t="n">
-        <v>90497</v>
+        <v>79168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691632</v>
+        <v>691842</v>
       </c>
       <c r="R19" t="n">
-        <v>7400779</v>
+        <v>7400786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,32 +2591,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128146069</v>
+        <v>128146045</v>
       </c>
       <c r="B20" t="n">
-        <v>92754</v>
+        <v>90499</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691003</v>
+        <v>691632</v>
       </c>
       <c r="R20" t="n">
-        <v>7400833</v>
+        <v>7400779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,7 +2701,7 @@
         <v>128146063</v>
       </c>
       <c r="B21" t="n">
-        <v>91725</v>
+        <v>91727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128146066</v>
+        <v>128144835</v>
       </c>
       <c r="B22" t="n">
-        <v>92754</v>
+        <v>91627</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691535</v>
+        <v>691707</v>
       </c>
       <c r="R22" t="n">
-        <v>7400857</v>
+        <v>7400750</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128146071</v>
+        <v>128146066</v>
       </c>
       <c r="B23" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>690800</v>
+        <v>691535</v>
       </c>
       <c r="R23" t="n">
-        <v>7400737</v>
+        <v>7400857</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144835</v>
+        <v>128146071</v>
       </c>
       <c r="B24" t="n">
-        <v>91625</v>
+        <v>92756</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691707</v>
+        <v>690800</v>
       </c>
       <c r="R24" t="n">
-        <v>7400750</v>
+        <v>7400737</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,10 +3126,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128144829</v>
+        <v>128146073</v>
       </c>
       <c r="B25" t="n">
-        <v>78844</v>
+        <v>78061</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3137,21 +3137,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>6487</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691811</v>
+        <v>691079</v>
       </c>
       <c r="R25" t="n">
-        <v>7400740</v>
+        <v>7400877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3236,7 +3236,7 @@
         <v>128144825</v>
       </c>
       <c r="B26" t="n">
-        <v>80096</v>
+        <v>80098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3340,10 +3340,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146073</v>
+        <v>128144829</v>
       </c>
       <c r="B27" t="n">
-        <v>78059</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3351,21 +3351,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691079</v>
+        <v>691811</v>
       </c>
       <c r="R27" t="n">
-        <v>7400877</v>
+        <v>7400740</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3450,7 +3450,7 @@
         <v>128146074</v>
       </c>
       <c r="B28" t="n">
-        <v>92748</v>
+        <v>92750</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3557,7 +3557,7 @@
         <v>128146042</v>
       </c>
       <c r="B29" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3661,32 +3661,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146064</v>
+        <v>128146068</v>
       </c>
       <c r="B30" t="n">
-        <v>78753</v>
+        <v>92756</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3699,7 +3699,7 @@
         <v>691003</v>
       </c>
       <c r="R30" t="n">
-        <v>7400833</v>
+        <v>7400832</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3768,10 +3768,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128146068</v>
+        <v>128144837</v>
       </c>
       <c r="B31" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691003</v>
+        <v>691657</v>
       </c>
       <c r="R31" t="n">
-        <v>7400832</v>
+        <v>7400758</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3875,32 +3875,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128144837</v>
+        <v>128146064</v>
       </c>
       <c r="B32" t="n">
-        <v>92754</v>
+        <v>78755</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691657</v>
+        <v>691003</v>
       </c>
       <c r="R32" t="n">
-        <v>7400758</v>
+        <v>7400833</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3985,7 +3985,7 @@
         <v>128144840</v>
       </c>
       <c r="B33" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>128144818</v>
       </c>
       <c r="B34" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,32 +4196,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146047</v>
+        <v>128144822</v>
       </c>
       <c r="B35" t="n">
-        <v>91749</v>
+        <v>79708</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691536</v>
+        <v>691662</v>
       </c>
       <c r="R35" t="n">
-        <v>7400854</v>
+        <v>7400760</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144836</v>
+        <v>128144839</v>
       </c>
       <c r="B36" t="n">
-        <v>91725</v>
+        <v>78492</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691520</v>
+        <v>691806</v>
       </c>
       <c r="R36" t="n">
-        <v>7400888</v>
+        <v>7400707</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144839</v>
+        <v>128146047</v>
       </c>
       <c r="B37" t="n">
-        <v>78490</v>
+        <v>91751</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6437</v>
+        <v>71</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691806</v>
+        <v>691536</v>
       </c>
       <c r="R37" t="n">
-        <v>7400707</v>
+        <v>7400854</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144822</v>
+        <v>128144836</v>
       </c>
       <c r="B38" t="n">
-        <v>79706</v>
+        <v>91727</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>65</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691662</v>
+        <v>691520</v>
       </c>
       <c r="R38" t="n">
-        <v>7400760</v>
+        <v>7400888</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4627,7 +4627,7 @@
         <v>128146044</v>
       </c>
       <c r="B39" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4734,7 +4734,7 @@
         <v>128146057</v>
       </c>
       <c r="B40" t="n">
-        <v>92746</v>
+        <v>92748</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128146065</v>
+        <v>128144826</v>
       </c>
       <c r="B41" t="n">
-        <v>78753</v>
+        <v>5493</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>690853</v>
+        <v>691845</v>
       </c>
       <c r="R41" t="n">
-        <v>7400680</v>
+        <v>7400932</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128144826</v>
+        <v>128146065</v>
       </c>
       <c r="B42" t="n">
-        <v>5493</v>
+        <v>78755</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691845</v>
+        <v>690853</v>
       </c>
       <c r="R42" t="n">
-        <v>7400932</v>
+        <v>7400680</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5055,7 +5055,7 @@
         <v>128146043</v>
       </c>
       <c r="B43" t="n">
-        <v>79677</v>
+        <v>79679</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144833</v>
+        <v>128144828</v>
       </c>
       <c r="B44" t="n">
-        <v>98585</v>
+        <v>78847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691471</v>
+        <v>691820</v>
       </c>
       <c r="R44" t="n">
-        <v>7401138</v>
+        <v>7400729</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,32 +5266,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128144828</v>
+        <v>128144833</v>
       </c>
       <c r="B45" t="n">
-        <v>78845</v>
+        <v>98588</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691820</v>
+        <v>691471</v>
       </c>
       <c r="R45" t="n">
-        <v>7400729</v>
+        <v>7401138</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5376,7 +5376,7 @@
         <v>128144830</v>
       </c>
       <c r="B46" t="n">
-        <v>98585</v>
+        <v>98588</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>128144838</v>
       </c>
       <c r="B47" t="n">
-        <v>78490</v>
+        <v>78492</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>128144827</v>
       </c>
       <c r="B48" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>128102520</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B5" t="n">
-        <v>92756</v>
+        <v>78492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R5" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B6" t="n">
-        <v>78492</v>
+        <v>92756</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R6" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2377,32 +2377,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146069</v>
+        <v>128146045</v>
       </c>
       <c r="B18" t="n">
-        <v>92756</v>
+        <v>90499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691003</v>
+        <v>691632</v>
       </c>
       <c r="R18" t="n">
-        <v>7400833</v>
+        <v>7400779</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2591,32 +2591,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128146045</v>
+        <v>128146063</v>
       </c>
       <c r="B20" t="n">
-        <v>90499</v>
+        <v>91727</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1962</v>
+        <v>65</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691632</v>
+        <v>690806</v>
       </c>
       <c r="R20" t="n">
-        <v>7400779</v>
+        <v>7400768</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128146063</v>
+        <v>128146069</v>
       </c>
       <c r="B21" t="n">
-        <v>91727</v>
+        <v>92756</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>690806</v>
+        <v>691003</v>
       </c>
       <c r="R21" t="n">
-        <v>7400768</v>
+        <v>7400833</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128146066</v>
+        <v>128144825</v>
       </c>
       <c r="B23" t="n">
-        <v>92756</v>
+        <v>80098</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6456</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691535</v>
+        <v>691427</v>
       </c>
       <c r="R23" t="n">
-        <v>7400857</v>
+        <v>7401053</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128146071</v>
+        <v>128144829</v>
       </c>
       <c r="B24" t="n">
-        <v>92756</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>690800</v>
+        <v>691811</v>
       </c>
       <c r="R24" t="n">
-        <v>7400737</v>
+        <v>7400740</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3233,10 +3233,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128144825</v>
+        <v>128146066</v>
       </c>
       <c r="B26" t="n">
-        <v>80098</v>
+        <v>92756</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3244,21 +3244,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691427</v>
+        <v>691535</v>
       </c>
       <c r="R26" t="n">
-        <v>7401053</v>
+        <v>7400857</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128144829</v>
+        <v>128146071</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>92756</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691811</v>
+        <v>690800</v>
       </c>
       <c r="R27" t="n">
-        <v>7400740</v>
+        <v>7400737</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3554,10 +3554,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128146042</v>
+        <v>128146064</v>
       </c>
       <c r="B29" t="n">
-        <v>79708</v>
+        <v>78755</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3565,21 +3565,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3589,10 +3589,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691337</v>
+        <v>691003</v>
       </c>
       <c r="R29" t="n">
-        <v>7400753</v>
+        <v>7400833</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3875,10 +3875,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128146064</v>
+        <v>128146042</v>
       </c>
       <c r="B32" t="n">
-        <v>78755</v>
+        <v>79708</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3886,21 +3886,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691003</v>
+        <v>691337</v>
       </c>
       <c r="R32" t="n">
-        <v>7400833</v>
+        <v>7400753</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3945,7 +3945,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128144822</v>
+        <v>128146044</v>
       </c>
       <c r="B35" t="n">
-        <v>79708</v>
+        <v>79679</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691662</v>
+        <v>691077</v>
       </c>
       <c r="R35" t="n">
-        <v>7400760</v>
+        <v>7400881</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128144839</v>
+        <v>128146047</v>
       </c>
       <c r="B36" t="n">
-        <v>78492</v>
+        <v>91751</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6437</v>
+        <v>71</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691806</v>
+        <v>691536</v>
       </c>
       <c r="R36" t="n">
-        <v>7400707</v>
+        <v>7400854</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128146047</v>
+        <v>128144836</v>
       </c>
       <c r="B37" t="n">
-        <v>91751</v>
+        <v>91727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691536</v>
+        <v>691520</v>
       </c>
       <c r="R37" t="n">
-        <v>7400854</v>
+        <v>7400888</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,32 +4517,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144836</v>
+        <v>128144822</v>
       </c>
       <c r="B38" t="n">
-        <v>91727</v>
+        <v>79708</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691520</v>
+        <v>691662</v>
       </c>
       <c r="R38" t="n">
-        <v>7400888</v>
+        <v>7400760</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4624,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128146044</v>
+        <v>128144839</v>
       </c>
       <c r="B39" t="n">
-        <v>79679</v>
+        <v>78492</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691077</v>
+        <v>691806</v>
       </c>
       <c r="R39" t="n">
-        <v>7400881</v>
+        <v>7400707</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4838,10 +4838,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128144826</v>
+        <v>128146065</v>
       </c>
       <c r="B41" t="n">
-        <v>5493</v>
+        <v>78755</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>101410</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691845</v>
+        <v>690853</v>
       </c>
       <c r="R41" t="n">
-        <v>7400932</v>
+        <v>7400680</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4945,10 +4945,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128146065</v>
+        <v>128144826</v>
       </c>
       <c r="B42" t="n">
-        <v>78755</v>
+        <v>5493</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4956,21 +4956,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>101410</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4980,10 +4980,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>690853</v>
+        <v>691845</v>
       </c>
       <c r="R42" t="n">
-        <v>7400680</v>
+        <v>7400932</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5015,7 +5015,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5025,7 +5025,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5269,7 +5269,7 @@
         <v>128144833</v>
       </c>
       <c r="B45" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>128144830</v>
       </c>
       <c r="B46" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -2270,32 +2270,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128146046</v>
+        <v>128146069</v>
       </c>
       <c r="B17" t="n">
-        <v>90499</v>
+        <v>92756</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2305,10 +2305,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>690842</v>
+        <v>691003</v>
       </c>
       <c r="R17" t="n">
-        <v>7400691</v>
+        <v>7400833</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2340,7 +2340,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2350,7 +2350,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2377,7 +2377,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128146045</v>
+        <v>128146046</v>
       </c>
       <c r="B18" t="n">
         <v>90499</v>
@@ -2412,10 +2412,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691632</v>
+        <v>690842</v>
       </c>
       <c r="R18" t="n">
-        <v>7400779</v>
+        <v>7400691</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128144834</v>
+        <v>128146045</v>
       </c>
       <c r="B19" t="n">
-        <v>79168</v>
+        <v>90499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>1962</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691842</v>
+        <v>691632</v>
       </c>
       <c r="R19" t="n">
-        <v>7400786</v>
+        <v>7400779</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,32 +2591,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128146063</v>
+        <v>128144834</v>
       </c>
       <c r="B20" t="n">
-        <v>91727</v>
+        <v>79168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65</v>
+        <v>864</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>690806</v>
+        <v>691842</v>
       </c>
       <c r="R20" t="n">
-        <v>7400768</v>
+        <v>7400786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2698,32 +2698,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128146069</v>
+        <v>128146063</v>
       </c>
       <c r="B21" t="n">
-        <v>92756</v>
+        <v>91727</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>65</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2733,10 +2733,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691003</v>
+        <v>690806</v>
       </c>
       <c r="R21" t="n">
-        <v>7400833</v>
+        <v>7400768</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2805,32 +2805,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128144835</v>
+        <v>128146066</v>
       </c>
       <c r="B22" t="n">
-        <v>91627</v>
+        <v>92756</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2840,10 +2840,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691707</v>
+        <v>691535</v>
       </c>
       <c r="R22" t="n">
-        <v>7400750</v>
+        <v>7400857</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2912,10 +2912,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128144825</v>
+        <v>128146071</v>
       </c>
       <c r="B23" t="n">
-        <v>80098</v>
+        <v>92756</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,21 +2923,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6456</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2947,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691427</v>
+        <v>690800</v>
       </c>
       <c r="R23" t="n">
-        <v>7401053</v>
+        <v>7400737</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144829</v>
+        <v>128144835</v>
       </c>
       <c r="B24" t="n">
-        <v>78846</v>
+        <v>91627</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691811</v>
+        <v>691707</v>
       </c>
       <c r="R24" t="n">
-        <v>7400740</v>
+        <v>7400750</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128146073</v>
+        <v>128144825</v>
       </c>
       <c r="B25" t="n">
-        <v>78061</v>
+        <v>80098</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6487</v>
+        <v>6456</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691079</v>
+        <v>691427</v>
       </c>
       <c r="R25" t="n">
-        <v>7400877</v>
+        <v>7401053</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128146066</v>
+        <v>128144829</v>
       </c>
       <c r="B26" t="n">
-        <v>92756</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691535</v>
+        <v>691811</v>
       </c>
       <c r="R26" t="n">
-        <v>7400857</v>
+        <v>7400740</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3340,32 +3340,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128146071</v>
+        <v>128146073</v>
       </c>
       <c r="B27" t="n">
-        <v>92756</v>
+        <v>78061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>690800</v>
+        <v>691079</v>
       </c>
       <c r="R27" t="n">
-        <v>7400737</v>
+        <v>7400877</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4196,10 +4196,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128146044</v>
+        <v>128144839</v>
       </c>
       <c r="B35" t="n">
-        <v>79679</v>
+        <v>78492</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4207,21 +4207,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691077</v>
+        <v>691806</v>
       </c>
       <c r="R35" t="n">
-        <v>7400881</v>
+        <v>7400707</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4624,10 +4624,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128144839</v>
+        <v>128146044</v>
       </c>
       <c r="B39" t="n">
-        <v>78492</v>
+        <v>79679</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4635,21 +4635,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691806</v>
+        <v>691077</v>
       </c>
       <c r="R39" t="n">
-        <v>7400707</v>
+        <v>7400881</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144828</v>
+        <v>128144833</v>
       </c>
       <c r="B44" t="n">
-        <v>78847</v>
+        <v>98591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691820</v>
+        <v>691471</v>
       </c>
       <c r="R44" t="n">
-        <v>7400729</v>
+        <v>7401138</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,7 +5266,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128144833</v>
+        <v>128144830</v>
       </c>
       <c r="B45" t="n">
         <v>98591</v>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691471</v>
+        <v>691395</v>
       </c>
       <c r="R45" t="n">
-        <v>7401138</v>
+        <v>7401068</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5346,7 +5346,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5373,32 +5378,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144830</v>
+        <v>128144828</v>
       </c>
       <c r="B46" t="n">
-        <v>98591</v>
+        <v>78847</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5408,10 +5413,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691395</v>
+        <v>691820</v>
       </c>
       <c r="R46" t="n">
-        <v>7401068</v>
+        <v>7400729</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5443,7 +5448,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5453,12 +5458,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128144832</v>
       </c>
       <c r="B2" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>128146055</v>
       </c>
       <c r="B4" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>128146070</v>
       </c>
       <c r="B6" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B7" t="n">
-        <v>79708</v>
+        <v>91752</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R7" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B8" t="n">
-        <v>91751</v>
+        <v>79708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R8" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1417,7 +1417,7 @@
         <v>128146061</v>
       </c>
       <c r="B9" t="n">
-        <v>91484</v>
+        <v>91485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1524,7 +1524,7 @@
         <v>128146062</v>
       </c>
       <c r="B10" t="n">
-        <v>91727</v>
+        <v>91728</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1628,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128144819</v>
+        <v>128146056</v>
       </c>
       <c r="B11" t="n">
-        <v>79708</v>
+        <v>92749</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691675</v>
+        <v>690781</v>
       </c>
       <c r="R11" t="n">
-        <v>7401012</v>
+        <v>7400555</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1735,10 +1735,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128146056</v>
+        <v>128144819</v>
       </c>
       <c r="B12" t="n">
-        <v>92748</v>
+        <v>79708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4361</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>690781</v>
+        <v>691675</v>
       </c>
       <c r="R12" t="n">
-        <v>7400555</v>
+        <v>7401012</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1805,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146067</v>
+        <v>128146053</v>
       </c>
       <c r="B13" t="n">
-        <v>92756</v>
+        <v>92787</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691067</v>
+        <v>691789</v>
       </c>
       <c r="R13" t="n">
-        <v>7400865</v>
+        <v>7400698</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128144820</v>
+        <v>128146067</v>
       </c>
       <c r="B14" t="n">
-        <v>79708</v>
+        <v>92757</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691749</v>
+        <v>691067</v>
       </c>
       <c r="R14" t="n">
-        <v>7400999</v>
+        <v>7400865</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144824</v>
+        <v>128144820</v>
       </c>
       <c r="B15" t="n">
-        <v>80098</v>
+        <v>79708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691607</v>
+        <v>691749</v>
       </c>
       <c r="R15" t="n">
-        <v>7400989</v>
+        <v>7400999</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,32 +2163,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128146053</v>
+        <v>128144824</v>
       </c>
       <c r="B16" t="n">
-        <v>92786</v>
+        <v>80098</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>232140</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691789</v>
+        <v>691607</v>
       </c>
       <c r="R16" t="n">
-        <v>7400698</v>
+        <v>7400989</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2273,7 +2273,7 @@
         <v>128146069</v>
       </c>
       <c r="B17" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128146045</v>
+        <v>128144834</v>
       </c>
       <c r="B19" t="n">
-        <v>90499</v>
+        <v>79168</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,21 +2495,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1962</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2519,10 +2519,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691632</v>
+        <v>691842</v>
       </c>
       <c r="R19" t="n">
-        <v>7400779</v>
+        <v>7400786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2554,7 +2554,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2591,10 +2591,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128144834</v>
+        <v>128146045</v>
       </c>
       <c r="B20" t="n">
-        <v>79168</v>
+        <v>90499</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2602,21 +2602,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>864</v>
+        <v>1962</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2626,10 +2626,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691842</v>
+        <v>691632</v>
       </c>
       <c r="R20" t="n">
-        <v>7400786</v>
+        <v>7400779</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,7 +2701,7 @@
         <v>128146063</v>
       </c>
       <c r="B21" t="n">
-        <v>91727</v>
+        <v>91728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2808,7 +2808,7 @@
         <v>128146066</v>
       </c>
       <c r="B22" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>128146071</v>
       </c>
       <c r="B23" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3019,32 +3019,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128144835</v>
+        <v>128144829</v>
       </c>
       <c r="B24" t="n">
-        <v>91627</v>
+        <v>78846</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1503</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691707</v>
+        <v>691811</v>
       </c>
       <c r="R24" t="n">
-        <v>7400750</v>
+        <v>7400740</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3089,7 +3089,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3099,7 +3099,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3126,32 +3126,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128144825</v>
+        <v>128144835</v>
       </c>
       <c r="B25" t="n">
-        <v>80098</v>
+        <v>91628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6456</v>
+        <v>1503</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3161,10 +3161,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691427</v>
+        <v>691707</v>
       </c>
       <c r="R25" t="n">
-        <v>7401053</v>
+        <v>7400750</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:26</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,32 +3233,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128144829</v>
+        <v>128144825</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>80098</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6446</v>
+        <v>6456</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3268,10 +3268,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691811</v>
+        <v>691427</v>
       </c>
       <c r="R26" t="n">
-        <v>7400740</v>
+        <v>7401053</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:18</t>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3450,7 +3450,7 @@
         <v>128146074</v>
       </c>
       <c r="B28" t="n">
-        <v>92750</v>
+        <v>92751</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3554,32 +3554,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128146064</v>
+        <v>128146068</v>
       </c>
       <c r="B29" t="n">
-        <v>78755</v>
+        <v>92757</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3592,7 +3592,7 @@
         <v>691003</v>
       </c>
       <c r="R29" t="n">
-        <v>7400833</v>
+        <v>7400832</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3661,10 +3661,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128146068</v>
+        <v>128144837</v>
       </c>
       <c r="B30" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691003</v>
+        <v>691657</v>
       </c>
       <c r="R30" t="n">
-        <v>7400832</v>
+        <v>7400758</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3768,32 +3768,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128144837</v>
+        <v>128146064</v>
       </c>
       <c r="B31" t="n">
-        <v>92756</v>
+        <v>78755</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3803,10 +3803,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691657</v>
+        <v>691003</v>
       </c>
       <c r="R31" t="n">
-        <v>7400758</v>
+        <v>7400833</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4092,7 +4092,7 @@
         <v>128144818</v>
       </c>
       <c r="B34" t="n">
-        <v>91641</v>
+        <v>91642</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4196,32 +4196,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128144839</v>
+        <v>128146047</v>
       </c>
       <c r="B35" t="n">
-        <v>78492</v>
+        <v>91752</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6437</v>
+        <v>71</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4231,10 +4231,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691806</v>
+        <v>691536</v>
       </c>
       <c r="R35" t="n">
-        <v>7400707</v>
+        <v>7400854</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4303,32 +4303,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128146047</v>
+        <v>128144836</v>
       </c>
       <c r="B36" t="n">
-        <v>91751</v>
+        <v>91728</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4338,10 +4338,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691536</v>
+        <v>691520</v>
       </c>
       <c r="R36" t="n">
-        <v>7400854</v>
+        <v>7400888</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4410,32 +4410,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128144836</v>
+        <v>128144822</v>
       </c>
       <c r="B37" t="n">
-        <v>91727</v>
+        <v>79708</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>65</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4445,10 +4445,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691520</v>
+        <v>691662</v>
       </c>
       <c r="R37" t="n">
-        <v>7400888</v>
+        <v>7400760</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4490,7 +4490,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4517,10 +4517,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128144822</v>
+        <v>128144839</v>
       </c>
       <c r="B38" t="n">
-        <v>79708</v>
+        <v>78492</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4528,21 +4528,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4552,10 +4552,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691662</v>
+        <v>691806</v>
       </c>
       <c r="R38" t="n">
-        <v>7400760</v>
+        <v>7400707</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4587,7 +4587,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:02</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4734,7 +4734,7 @@
         <v>128146057</v>
       </c>
       <c r="B40" t="n">
-        <v>92748</v>
+        <v>92749</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>128144833</v>
       </c>
       <c r="B44" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5269,7 +5269,7 @@
         <v>128144830</v>
       </c>
       <c r="B45" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -986,32 +986,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128146075</v>
+        <v>128146070</v>
       </c>
       <c r="B5" t="n">
-        <v>78492</v>
+        <v>92757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691077</v>
+        <v>690846</v>
       </c>
       <c r="R5" t="n">
-        <v>7400880</v>
+        <v>7400687</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1066,7 +1066,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,32 +1093,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128146070</v>
+        <v>128146075</v>
       </c>
       <c r="B6" t="n">
-        <v>92757</v>
+        <v>78492</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>690846</v>
+        <v>691077</v>
       </c>
       <c r="R6" t="n">
-        <v>7400687</v>
+        <v>7400880</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,32 +1200,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128146048</v>
+        <v>128144823</v>
       </c>
       <c r="B7" t="n">
-        <v>91752</v>
+        <v>79708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>71</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neoantrodia infirma</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Audet</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>690845</v>
+        <v>691519</v>
       </c>
       <c r="R7" t="n">
-        <v>7400687</v>
+        <v>7400859</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,32 +1307,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128144823</v>
+        <v>128146048</v>
       </c>
       <c r="B8" t="n">
-        <v>79708</v>
+        <v>91752</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>71</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neoantrodia infirma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Renvall &amp; Niemelä) Audet</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691519</v>
+        <v>690845</v>
       </c>
       <c r="R8" t="n">
-        <v>7400859</v>
+        <v>7400687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1377,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:39</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1842,32 +1842,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128146053</v>
+        <v>128146067</v>
       </c>
       <c r="B13" t="n">
-        <v>92787</v>
+        <v>92757</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691789</v>
+        <v>691067</v>
       </c>
       <c r="R13" t="n">
-        <v>7400698</v>
+        <v>7400865</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1949,32 +1949,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128146067</v>
+        <v>128144820</v>
       </c>
       <c r="B14" t="n">
-        <v>92757</v>
+        <v>79708</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691067</v>
+        <v>691749</v>
       </c>
       <c r="R14" t="n">
-        <v>7400865</v>
+        <v>7400999</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2019,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2029,7 +2029,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2056,32 +2056,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128144820</v>
+        <v>128144824</v>
       </c>
       <c r="B15" t="n">
-        <v>79708</v>
+        <v>80098</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2091,10 +2091,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691749</v>
+        <v>691607</v>
       </c>
       <c r="R15" t="n">
-        <v>7400999</v>
+        <v>7400989</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,32 +2163,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128144824</v>
+        <v>128146053</v>
       </c>
       <c r="B16" t="n">
-        <v>80098</v>
+        <v>92787</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>232140</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691607</v>
+        <v>691789</v>
       </c>
       <c r="R16" t="n">
-        <v>7400989</v>
+        <v>7400698</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2233,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -5159,32 +5159,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128144833</v>
+        <v>128144828</v>
       </c>
       <c r="B44" t="n">
-        <v>98592</v>
+        <v>78847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5194,10 +5194,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691471</v>
+        <v>691820</v>
       </c>
       <c r="R44" t="n">
-        <v>7401138</v>
+        <v>7400729</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,7 +5266,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128144830</v>
+        <v>128144833</v>
       </c>
       <c r="B45" t="n">
         <v>98592</v>
@@ -5301,10 +5301,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691395</v>
+        <v>691471</v>
       </c>
       <c r="R45" t="n">
-        <v>7401068</v>
+        <v>7401138</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5346,12 +5346,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>30 plantor</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5378,32 +5373,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128144828</v>
+        <v>128144830</v>
       </c>
       <c r="B46" t="n">
-        <v>78847</v>
+        <v>98592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5413,10 +5408,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691820</v>
+        <v>691395</v>
       </c>
       <c r="R46" t="n">
-        <v>7400729</v>
+        <v>7401068</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5448,7 +5443,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5458,7 +5453,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>30 plantor</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -1448,32 +1448,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128960498</v>
+        <v>128960670</v>
       </c>
       <c r="B9" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691438</v>
+        <v>691851</v>
       </c>
       <c r="R9" t="n">
-        <v>7401141</v>
+        <v>7401441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,22 +1513,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,32 +1559,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128960544</v>
+        <v>128960343</v>
       </c>
       <c r="B10" t="n">
-        <v>98651</v>
+        <v>91442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691695</v>
+        <v>691612</v>
       </c>
       <c r="R10" t="n">
-        <v>7401360</v>
+        <v>7401171</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,32 +1670,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128960426</v>
+        <v>128960689</v>
       </c>
       <c r="B11" t="n">
-        <v>98540</v>
+        <v>78437</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>233</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691727</v>
+        <v>691341</v>
       </c>
       <c r="R11" t="n">
-        <v>7401372</v>
+        <v>7401206</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,22 +1735,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,32 +1781,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128960670</v>
+        <v>128960426</v>
       </c>
       <c r="B12" t="n">
-        <v>92811</v>
+        <v>98540</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>233</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691851</v>
+        <v>691727</v>
       </c>
       <c r="R12" t="n">
-        <v>7401441</v>
+        <v>7401372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128960343</v>
+        <v>128960616</v>
       </c>
       <c r="B13" t="n">
-        <v>91442</v>
+        <v>78700</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691612</v>
+        <v>691854</v>
       </c>
       <c r="R13" t="n">
-        <v>7401171</v>
+        <v>7401445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,22 +1957,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128960689</v>
+        <v>128960498</v>
       </c>
       <c r="B14" t="n">
-        <v>78437</v>
+        <v>98651</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691341</v>
+        <v>691438</v>
       </c>
       <c r="R14" t="n">
-        <v>7401206</v>
+        <v>7401141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,32 +2114,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128960616</v>
+        <v>128960544</v>
       </c>
       <c r="B15" t="n">
-        <v>78700</v>
+        <v>98651</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691854</v>
+        <v>691695</v>
       </c>
       <c r="R15" t="n">
-        <v>7401445</v>
+        <v>7401360</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2336,32 +2336,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128960348</v>
+        <v>128960542</v>
       </c>
       <c r="B17" t="n">
-        <v>91442</v>
+        <v>98651</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691730</v>
+        <v>691733</v>
       </c>
       <c r="R17" t="n">
-        <v>7401383</v>
+        <v>7401377</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,32 +2447,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128960618</v>
+        <v>128960519</v>
       </c>
       <c r="B18" t="n">
-        <v>78700</v>
+        <v>98651</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691741</v>
+        <v>691230</v>
       </c>
       <c r="R18" t="n">
-        <v>7401356</v>
+        <v>7401270</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128960542</v>
+        <v>128960348</v>
       </c>
       <c r="B19" t="n">
-        <v>98651</v>
+        <v>91442</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691733</v>
+        <v>691730</v>
       </c>
       <c r="R19" t="n">
-        <v>7401377</v>
+        <v>7401383</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,32 +2669,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128960519</v>
+        <v>128960618</v>
       </c>
       <c r="B20" t="n">
-        <v>98651</v>
+        <v>78700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691230</v>
+        <v>691741</v>
       </c>
       <c r="R20" t="n">
-        <v>7401270</v>
+        <v>7401356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -4556,32 +4556,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128960561</v>
+        <v>128960686</v>
       </c>
       <c r="B37" t="n">
-        <v>91681</v>
+        <v>78042</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691650</v>
+        <v>691639</v>
       </c>
       <c r="R37" t="n">
-        <v>7401329</v>
+        <v>7401330</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,10 +4667,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128960571</v>
+        <v>128960424</v>
       </c>
       <c r="B38" t="n">
-        <v>91681</v>
+        <v>98540</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>233</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691659</v>
+        <v>691756</v>
       </c>
       <c r="R38" t="n">
-        <v>7401322</v>
+        <v>7401403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,32 +4778,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128960686</v>
+        <v>128960561</v>
       </c>
       <c r="B39" t="n">
-        <v>78042</v>
+        <v>91681</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691639</v>
+        <v>691650</v>
       </c>
       <c r="R39" t="n">
-        <v>7401330</v>
+        <v>7401329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,10 +4889,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128960424</v>
+        <v>128960571</v>
       </c>
       <c r="B40" t="n">
-        <v>98540</v>
+        <v>91681</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4900,21 +4900,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>233</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691756</v>
+        <v>691659</v>
       </c>
       <c r="R40" t="n">
-        <v>7401403</v>
+        <v>7401322</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128960434</v>
+        <v>128960622</v>
       </c>
       <c r="B47" t="n">
-        <v>93006</v>
+        <v>78700</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691450</v>
+        <v>691669</v>
       </c>
       <c r="R47" t="n">
-        <v>7401402</v>
+        <v>7401313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5777,32 +5777,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128960622</v>
+        <v>128960586</v>
       </c>
       <c r="B48" t="n">
-        <v>78700</v>
+        <v>91781</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691669</v>
+        <v>691611</v>
       </c>
       <c r="R48" t="n">
-        <v>7401313</v>
+        <v>7401170</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5842,22 +5842,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5888,32 +5888,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128960586</v>
+        <v>128960434</v>
       </c>
       <c r="B49" t="n">
-        <v>91781</v>
+        <v>93006</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691611</v>
+        <v>691450</v>
       </c>
       <c r="R49" t="n">
-        <v>7401170</v>
+        <v>7401402</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5953,22 +5953,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6665,32 +6665,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128960664</v>
+        <v>128960533</v>
       </c>
       <c r="B56" t="n">
-        <v>92811</v>
+        <v>98651</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691754</v>
+        <v>691773</v>
       </c>
       <c r="R56" t="n">
-        <v>7401434</v>
+        <v>7401347</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6776,32 +6776,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128960395</v>
+        <v>128960534</v>
       </c>
       <c r="B57" t="n">
-        <v>92428</v>
+        <v>98651</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691427</v>
+        <v>691770</v>
       </c>
       <c r="R57" t="n">
-        <v>7401226</v>
+        <v>7401379</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6841,22 +6841,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6887,32 +6887,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128960533</v>
+        <v>128960664</v>
       </c>
       <c r="B58" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691773</v>
+        <v>691754</v>
       </c>
       <c r="R58" t="n">
-        <v>7401347</v>
+        <v>7401434</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6998,32 +6998,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128960534</v>
+        <v>128960395</v>
       </c>
       <c r="B59" t="n">
-        <v>98651</v>
+        <v>92428</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691770</v>
+        <v>691427</v>
       </c>
       <c r="R59" t="n">
-        <v>7401379</v>
+        <v>7401226</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7063,22 +7063,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128960624</v>
+        <v>128960536</v>
       </c>
       <c r="B67" t="n">
-        <v>78700</v>
+        <v>98651</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691444</v>
+        <v>691728</v>
       </c>
       <c r="R67" t="n">
-        <v>7401426</v>
+        <v>7401388</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7997,7 +7997,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128960536</v>
+        <v>128960518</v>
       </c>
       <c r="B68" t="n">
         <v>98651</v>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>691728</v>
+        <v>691236</v>
       </c>
       <c r="R68" t="n">
-        <v>7401388</v>
+        <v>7401263</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8108,32 +8108,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128960518</v>
+        <v>128960624</v>
       </c>
       <c r="B69" t="n">
-        <v>98651</v>
+        <v>78700</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>691236</v>
+        <v>691444</v>
       </c>
       <c r="R69" t="n">
-        <v>7401263</v>
+        <v>7401426</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -13913,10 +13913,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128960650</v>
+        <v>128960405</v>
       </c>
       <c r="B123" t="n">
-        <v>92811</v>
+        <v>80168</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13924,21 +13924,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>690728</v>
+        <v>690835</v>
       </c>
       <c r="R123" t="n">
-        <v>7400633</v>
+        <v>7400894</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14024,32 +14024,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128960646</v>
+        <v>128960370</v>
       </c>
       <c r="B124" t="n">
-        <v>92811</v>
+        <v>79624</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>691445</v>
+        <v>691375</v>
       </c>
       <c r="R124" t="n">
-        <v>7400907</v>
+        <v>7400750</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14135,32 +14135,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128960399</v>
+        <v>128960503</v>
       </c>
       <c r="B125" t="n">
-        <v>92428</v>
+        <v>98651</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>690819</v>
+        <v>690957</v>
       </c>
       <c r="R125" t="n">
-        <v>7400882</v>
+        <v>7400856</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14246,32 +14246,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128960405</v>
+        <v>128960476</v>
       </c>
       <c r="B126" t="n">
-        <v>80168</v>
+        <v>98651</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>690835</v>
+        <v>691094</v>
       </c>
       <c r="R126" t="n">
-        <v>7400894</v>
+        <v>7400693</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14311,22 +14311,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14357,32 +14357,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128960370</v>
+        <v>128960650</v>
       </c>
       <c r="B127" t="n">
-        <v>79624</v>
+        <v>92811</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>691375</v>
+        <v>690728</v>
       </c>
       <c r="R127" t="n">
-        <v>7400750</v>
+        <v>7400633</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14422,22 +14422,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14468,32 +14468,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128960503</v>
+        <v>128960646</v>
       </c>
       <c r="B128" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>690957</v>
+        <v>691445</v>
       </c>
       <c r="R128" t="n">
-        <v>7400856</v>
+        <v>7400907</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14533,22 +14533,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14579,32 +14579,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128960476</v>
+        <v>128960399</v>
       </c>
       <c r="B129" t="n">
-        <v>98651</v>
+        <v>92428</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14614,10 +14614,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>691094</v>
+        <v>690819</v>
       </c>
       <c r="R129" t="n">
-        <v>7400693</v>
+        <v>7400882</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14644,22 +14644,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14690,32 +14690,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128960402</v>
+        <v>128960511</v>
       </c>
       <c r="B130" t="n">
-        <v>92837</v>
+        <v>98651</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>690717</v>
+        <v>690875</v>
       </c>
       <c r="R130" t="n">
-        <v>7400812</v>
+        <v>7400942</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14801,32 +14801,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128960369</v>
+        <v>128960488</v>
       </c>
       <c r="B131" t="n">
-        <v>79624</v>
+        <v>98651</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14836,10 +14836,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>691330</v>
+        <v>691464</v>
       </c>
       <c r="R131" t="n">
-        <v>7400743</v>
+        <v>7400741</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14912,7 +14912,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128960511</v>
+        <v>128960464</v>
       </c>
       <c r="B132" t="n">
         <v>98651</v>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>690875</v>
+        <v>691251</v>
       </c>
       <c r="R132" t="n">
-        <v>7400942</v>
+        <v>7400808</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14977,22 +14977,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15023,7 +15023,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128960488</v>
+        <v>128960496</v>
       </c>
       <c r="B133" t="n">
         <v>98651</v>
@@ -15058,10 +15058,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>691464</v>
+        <v>691471</v>
       </c>
       <c r="R133" t="n">
-        <v>7400741</v>
+        <v>7401095</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15134,32 +15134,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128960464</v>
+        <v>128960369</v>
       </c>
       <c r="B134" t="n">
-        <v>98651</v>
+        <v>79624</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>691251</v>
+        <v>691330</v>
       </c>
       <c r="R134" t="n">
-        <v>7400808</v>
+        <v>7400743</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15204,7 +15204,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15245,32 +15245,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128960496</v>
+        <v>128960626</v>
       </c>
       <c r="B135" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>691471</v>
+        <v>691772</v>
       </c>
       <c r="R135" t="n">
-        <v>7401095</v>
+        <v>7400877</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15356,7 +15356,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128960626</v>
+        <v>128960629</v>
       </c>
       <c r="B136" t="n">
         <v>92811</v>
@@ -15391,10 +15391,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>691772</v>
+        <v>691778</v>
       </c>
       <c r="R136" t="n">
-        <v>7400877</v>
+        <v>7401031</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15467,32 +15467,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128960629</v>
+        <v>128960432</v>
       </c>
       <c r="B137" t="n">
-        <v>92811</v>
+        <v>93006</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15502,10 +15502,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>691778</v>
+        <v>690722</v>
       </c>
       <c r="R137" t="n">
-        <v>7401031</v>
+        <v>7400676</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15532,22 +15532,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15578,10 +15578,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128960432</v>
+        <v>128960556</v>
       </c>
       <c r="B138" t="n">
-        <v>93006</v>
+        <v>91534</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15589,21 +15589,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>2079</v>
+        <v>1204</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15613,10 +15613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>690722</v>
+        <v>691520</v>
       </c>
       <c r="R138" t="n">
-        <v>7400676</v>
+        <v>7401010</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15643,22 +15643,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15689,10 +15689,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128960556</v>
+        <v>128960378</v>
       </c>
       <c r="B139" t="n">
-        <v>91534</v>
+        <v>90552</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15700,21 +15700,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15724,10 +15724,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691520</v>
+        <v>690754</v>
       </c>
       <c r="R139" t="n">
-        <v>7401010</v>
+        <v>7400823</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15754,22 +15754,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15800,10 +15800,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128960378</v>
+        <v>128960402</v>
       </c>
       <c r="B140" t="n">
-        <v>90552</v>
+        <v>92837</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15811,21 +15811,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1962</v>
+        <v>5448</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>690754</v>
+        <v>690717</v>
       </c>
       <c r="R140" t="n">
-        <v>7400823</v>
+        <v>7400812</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16799,32 +16799,32 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128960510</v>
+        <v>128960602</v>
       </c>
       <c r="B149" t="n">
-        <v>98651</v>
+        <v>78700</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16834,10 +16834,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>690855</v>
+        <v>691546</v>
       </c>
       <c r="R149" t="n">
-        <v>7400940</v>
+        <v>7400957</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16864,22 +16864,22 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16910,32 +16910,32 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128960602</v>
+        <v>128960510</v>
       </c>
       <c r="B150" t="n">
-        <v>78700</v>
+        <v>98651</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16945,10 +16945,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>691546</v>
+        <v>690855</v>
       </c>
       <c r="R150" t="n">
-        <v>7400957</v>
+        <v>7400940</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16975,22 +16975,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>13:09</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17243,10 +17243,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128960421</v>
+        <v>128960465</v>
       </c>
       <c r="B153" t="n">
-        <v>98540</v>
+        <v>98651</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17254,21 +17254,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>233</v>
+        <v>220787</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>691475</v>
+        <v>691184</v>
       </c>
       <c r="R153" t="n">
-        <v>7401113</v>
+        <v>7400869</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17354,10 +17354,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128960465</v>
+        <v>128960421</v>
       </c>
       <c r="B154" t="n">
-        <v>98651</v>
+        <v>98540</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17365,21 +17365,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>233</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17389,10 +17389,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>691184</v>
+        <v>691475</v>
       </c>
       <c r="R154" t="n">
-        <v>7400869</v>
+        <v>7401113</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17424,7 +17424,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -18686,32 +18686,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128960569</v>
+        <v>128960397</v>
       </c>
       <c r="B166" t="n">
-        <v>91681</v>
+        <v>92428</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1503</v>
+        <v>4745</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18721,10 +18721,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>691471</v>
+        <v>690679</v>
       </c>
       <c r="R166" t="n">
-        <v>7400861</v>
+        <v>7400680</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18751,22 +18751,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18797,32 +18797,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128960397</v>
+        <v>128960569</v>
       </c>
       <c r="B167" t="n">
-        <v>92428</v>
+        <v>91681</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4745</v>
+        <v>1503</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18832,10 +18832,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>690679</v>
+        <v>691471</v>
       </c>
       <c r="R167" t="n">
-        <v>7400680</v>
+        <v>7400861</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18862,22 +18862,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -23570,32 +23570,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128960587</v>
+        <v>128960611</v>
       </c>
       <c r="B210" t="n">
-        <v>91781</v>
+        <v>78700</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23605,10 +23605,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>691522</v>
+        <v>690824</v>
       </c>
       <c r="R210" t="n">
-        <v>7401008</v>
+        <v>7400642</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23635,22 +23635,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23681,32 +23681,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128960371</v>
+        <v>128960587</v>
       </c>
       <c r="B211" t="n">
-        <v>79624</v>
+        <v>91781</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23716,10 +23716,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>691493</v>
+        <v>691522</v>
       </c>
       <c r="R211" t="n">
-        <v>7400837</v>
+        <v>7401008</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23751,7 +23751,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23792,10 +23792,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128960687</v>
+        <v>128960371</v>
       </c>
       <c r="B212" t="n">
-        <v>78042</v>
+        <v>79624</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23803,21 +23803,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23827,10 +23827,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>691772</v>
+        <v>691493</v>
       </c>
       <c r="R212" t="n">
-        <v>7401045</v>
+        <v>7400837</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23862,7 +23862,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -23872,7 +23872,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23903,32 +23903,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128960611</v>
+        <v>128960483</v>
       </c>
       <c r="B213" t="n">
-        <v>78700</v>
+        <v>98651</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23938,10 +23938,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>690824</v>
+        <v>691042</v>
       </c>
       <c r="R213" t="n">
-        <v>7400642</v>
+        <v>7400691</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23968,22 +23968,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24014,10 +24014,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128960690</v>
+        <v>128960687</v>
       </c>
       <c r="B214" t="n">
-        <v>78437</v>
+        <v>78042</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24025,21 +24025,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -24049,10 +24049,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>690817</v>
+        <v>691772</v>
       </c>
       <c r="R214" t="n">
-        <v>7400668</v>
+        <v>7401045</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24079,22 +24079,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24125,32 +24125,32 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128960483</v>
+        <v>128960690</v>
       </c>
       <c r="B215" t="n">
-        <v>98651</v>
+        <v>78437</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24160,10 +24160,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>691042</v>
+        <v>690817</v>
       </c>
       <c r="R215" t="n">
-        <v>7400691</v>
+        <v>7400668</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24190,22 +24190,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24236,32 +24236,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128960489</v>
+        <v>128960655</v>
       </c>
       <c r="B216" t="n">
-        <v>98651</v>
+        <v>92811</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24271,10 +24271,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>691434</v>
+        <v>690734</v>
       </c>
       <c r="R216" t="n">
-        <v>7400760</v>
+        <v>7400797</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24301,22 +24301,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24347,32 +24347,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128960513</v>
+        <v>128960344</v>
       </c>
       <c r="B217" t="n">
-        <v>98651</v>
+        <v>91442</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24382,10 +24382,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>691071</v>
+        <v>691060</v>
       </c>
       <c r="R217" t="n">
-        <v>7401097</v>
+        <v>7400887</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24412,22 +24412,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24458,7 +24458,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128960467</v>
+        <v>128960489</v>
       </c>
       <c r="B218" t="n">
         <v>98651</v>
@@ -24493,10 +24493,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>691182</v>
+        <v>691434</v>
       </c>
       <c r="R218" t="n">
-        <v>7400878</v>
+        <v>7400760</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24538,7 +24538,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24569,32 +24569,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128960655</v>
+        <v>128960513</v>
       </c>
       <c r="B219" t="n">
-        <v>92811</v>
+        <v>98651</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24604,10 +24604,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>690734</v>
+        <v>691071</v>
       </c>
       <c r="R219" t="n">
-        <v>7400797</v>
+        <v>7401097</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24639,7 +24639,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24680,32 +24680,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128960344</v>
+        <v>128960467</v>
       </c>
       <c r="B220" t="n">
-        <v>91442</v>
+        <v>98651</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24715,10 +24715,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>691060</v>
+        <v>691182</v>
       </c>
       <c r="R220" t="n">
-        <v>7400887</v>
+        <v>7400878</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24750,7 +24750,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24760,7 +24760,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -27455,32 +27455,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128960398</v>
+        <v>128960628</v>
       </c>
       <c r="B245" t="n">
-        <v>92428</v>
+        <v>92811</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>690713</v>
+        <v>691884</v>
       </c>
       <c r="R245" t="n">
-        <v>7400706</v>
+        <v>7401043</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27520,22 +27520,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27677,32 +27677,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128960628</v>
+        <v>128960460</v>
       </c>
       <c r="B247" t="n">
-        <v>92811</v>
+        <v>98651</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -27712,10 +27712,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>691884</v>
+        <v>691513</v>
       </c>
       <c r="R247" t="n">
-        <v>7401043</v>
+        <v>7401038</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -27757,7 +27757,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27788,32 +27788,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128960460</v>
+        <v>128960398</v>
       </c>
       <c r="B248" t="n">
-        <v>98651</v>
+        <v>92428</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -27823,10 +27823,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>691513</v>
+        <v>690713</v>
       </c>
       <c r="R248" t="n">
-        <v>7401038</v>
+        <v>7400706</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -27853,22 +27853,22 @@
       </c>
       <c r="Y248" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD248" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -1448,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128960616</v>
+        <v>128960343</v>
       </c>
       <c r="B9" t="n">
-        <v>78701</v>
+        <v>91448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691854</v>
+        <v>691612</v>
       </c>
       <c r="R9" t="n">
-        <v>7401445</v>
+        <v>7401171</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,22 +1513,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,32 +1559,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128960426</v>
+        <v>128960670</v>
       </c>
       <c r="B10" t="n">
-        <v>98548</v>
+        <v>92819</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>233</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691727</v>
+        <v>691851</v>
       </c>
       <c r="R10" t="n">
-        <v>7401372</v>
+        <v>7401441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128960689</v>
+        <v>128960616</v>
       </c>
       <c r="B11" t="n">
-        <v>78438</v>
+        <v>78701</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691341</v>
+        <v>691854</v>
       </c>
       <c r="R11" t="n">
-        <v>7401206</v>
+        <v>7401445</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,22 +1735,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128960498</v>
+        <v>128960426</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>98548</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>233</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691438</v>
+        <v>691727</v>
       </c>
       <c r="R12" t="n">
-        <v>7401141</v>
+        <v>7401372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,22 +1846,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,32 +1892,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128960544</v>
+        <v>128960689</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>78438</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691695</v>
+        <v>691341</v>
       </c>
       <c r="R13" t="n">
-        <v>7401360</v>
+        <v>7401206</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,22 +1957,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,32 +2003,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128960343</v>
+        <v>128960498</v>
       </c>
       <c r="B14" t="n">
-        <v>91448</v>
+        <v>98659</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691612</v>
+        <v>691438</v>
       </c>
       <c r="R14" t="n">
-        <v>7401171</v>
+        <v>7401141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2073,7 +2073,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,32 +2114,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128960670</v>
+        <v>128960544</v>
       </c>
       <c r="B15" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691851</v>
+        <v>691695</v>
       </c>
       <c r="R15" t="n">
-        <v>7401441</v>
+        <v>7401360</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -3113,32 +3113,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128960541</v>
+        <v>128960688</v>
       </c>
       <c r="B24" t="n">
-        <v>98659</v>
+        <v>78043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691727</v>
+        <v>691253</v>
       </c>
       <c r="R24" t="n">
-        <v>7401372</v>
+        <v>7401236</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3224,32 +3224,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128960373</v>
+        <v>128960539</v>
       </c>
       <c r="B25" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691245</v>
+        <v>691733</v>
       </c>
       <c r="R25" t="n">
-        <v>7401304</v>
+        <v>7401349</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,32 +3335,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128960688</v>
+        <v>128960541</v>
       </c>
       <c r="B26" t="n">
-        <v>78043</v>
+        <v>98659</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691253</v>
+        <v>691727</v>
       </c>
       <c r="R26" t="n">
-        <v>7401236</v>
+        <v>7401372</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,32 +3446,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128960539</v>
+        <v>128960373</v>
       </c>
       <c r="B27" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691733</v>
+        <v>691245</v>
       </c>
       <c r="R27" t="n">
-        <v>7401349</v>
+        <v>7401304</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3557,32 +3557,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128960400</v>
+        <v>128960454</v>
       </c>
       <c r="B28" t="n">
-        <v>92436</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691245</v>
+        <v>691681</v>
       </c>
       <c r="R28" t="n">
-        <v>7401292</v>
+        <v>7401433</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128960666</v>
+        <v>128960540</v>
       </c>
       <c r="B29" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691773</v>
+        <v>691741</v>
       </c>
       <c r="R29" t="n">
-        <v>7401444</v>
+        <v>7401356</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3779,32 +3779,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128960573</v>
+        <v>128960400</v>
       </c>
       <c r="B30" t="n">
-        <v>91687</v>
+        <v>92436</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>4745</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691704</v>
+        <v>691245</v>
       </c>
       <c r="R30" t="n">
-        <v>7401335</v>
+        <v>7401292</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3890,32 +3890,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128960454</v>
+        <v>128960666</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691681</v>
+        <v>691773</v>
       </c>
       <c r="R31" t="n">
-        <v>7401433</v>
+        <v>7401444</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,10 +4001,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128960540</v>
+        <v>128960573</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>91687</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,21 +4012,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691741</v>
+        <v>691704</v>
       </c>
       <c r="R32" t="n">
-        <v>7401356</v>
+        <v>7401335</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5000,32 +5000,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128960527</v>
+        <v>128960662</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691373</v>
+        <v>691259</v>
       </c>
       <c r="R41" t="n">
-        <v>7401425</v>
+        <v>7401348</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,32 +5111,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128960662</v>
+        <v>128960695</v>
       </c>
       <c r="B42" t="n">
-        <v>92819</v>
+        <v>78438</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691259</v>
+        <v>691255</v>
       </c>
       <c r="R42" t="n">
-        <v>7401348</v>
+        <v>7401234</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5444,32 +5444,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128960695</v>
+        <v>128960527</v>
       </c>
       <c r="B45" t="n">
-        <v>78438</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691255</v>
+        <v>691373</v>
       </c>
       <c r="R45" t="n">
-        <v>7401234</v>
+        <v>7401425</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5666,10 +5666,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128960434</v>
+        <v>128960622</v>
       </c>
       <c r="B47" t="n">
-        <v>93014</v>
+        <v>78701</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5677,21 +5677,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691450</v>
+        <v>691669</v>
       </c>
       <c r="R47" t="n">
-        <v>7401402</v>
+        <v>7401313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5777,10 +5777,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128960458</v>
+        <v>128960586</v>
       </c>
       <c r="B48" t="n">
-        <v>98659</v>
+        <v>91787</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5788,21 +5788,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691458</v>
+        <v>691611</v>
       </c>
       <c r="R48" t="n">
-        <v>7401226</v>
+        <v>7401170</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5847,7 +5847,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5857,7 +5857,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5888,32 +5888,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128960520</v>
+        <v>128960434</v>
       </c>
       <c r="B49" t="n">
-        <v>98659</v>
+        <v>93014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691345</v>
+        <v>691450</v>
       </c>
       <c r="R49" t="n">
-        <v>7401412</v>
+        <v>7401402</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5999,7 +5999,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128960531</v>
+        <v>128960458</v>
       </c>
       <c r="B50" t="n">
         <v>98659</v>
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691819</v>
+        <v>691458</v>
       </c>
       <c r="R50" t="n">
-        <v>7401453</v>
+        <v>7401226</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6064,22 +6064,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6110,7 +6110,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128960529</v>
+        <v>128960520</v>
       </c>
       <c r="B51" t="n">
         <v>98659</v>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691510</v>
+        <v>691345</v>
       </c>
       <c r="R51" t="n">
-        <v>7401400</v>
+        <v>7401412</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6221,32 +6221,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128960622</v>
+        <v>128960531</v>
       </c>
       <c r="B52" t="n">
-        <v>78701</v>
+        <v>98659</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691669</v>
+        <v>691819</v>
       </c>
       <c r="R52" t="n">
-        <v>7401313</v>
+        <v>7401453</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6291,7 +6291,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128960586</v>
+        <v>128960529</v>
       </c>
       <c r="B53" t="n">
-        <v>91787</v>
+        <v>98659</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6343,21 +6343,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>65</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691611</v>
+        <v>691510</v>
       </c>
       <c r="R53" t="n">
-        <v>7401170</v>
+        <v>7401400</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6397,7 +6397,7 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
@@ -6665,32 +6665,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128960533</v>
+        <v>128960664</v>
       </c>
       <c r="B56" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691773</v>
+        <v>691754</v>
       </c>
       <c r="R56" t="n">
-        <v>7401347</v>
+        <v>7401434</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6745,7 +6745,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6776,32 +6776,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128960534</v>
+        <v>128960395</v>
       </c>
       <c r="B57" t="n">
-        <v>98659</v>
+        <v>92436</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691770</v>
+        <v>691427</v>
       </c>
       <c r="R57" t="n">
-        <v>7401379</v>
+        <v>7401226</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6841,22 +6841,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6887,32 +6887,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128960664</v>
+        <v>128960533</v>
       </c>
       <c r="B58" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691754</v>
+        <v>691773</v>
       </c>
       <c r="R58" t="n">
-        <v>7401434</v>
+        <v>7401347</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6998,32 +6998,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128960395</v>
+        <v>128960534</v>
       </c>
       <c r="B59" t="n">
-        <v>92436</v>
+        <v>98659</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691427</v>
+        <v>691770</v>
       </c>
       <c r="R59" t="n">
-        <v>7401226</v>
+        <v>7401379</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7063,22 +7063,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -14357,32 +14357,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128960476</v>
+        <v>128960370</v>
       </c>
       <c r="B127" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>691094</v>
+        <v>691375</v>
       </c>
       <c r="R127" t="n">
-        <v>7400693</v>
+        <v>7400750</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14579,32 +14579,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128960370</v>
+        <v>128960476</v>
       </c>
       <c r="B129" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14614,10 +14614,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>691375</v>
+        <v>691094</v>
       </c>
       <c r="R129" t="n">
-        <v>7400750</v>
+        <v>7400693</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14690,32 +14690,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128960556</v>
+        <v>128960511</v>
       </c>
       <c r="B130" t="n">
-        <v>91540</v>
+        <v>98659</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1204</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>691520</v>
+        <v>690875</v>
       </c>
       <c r="R130" t="n">
-        <v>7401010</v>
+        <v>7400942</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14755,22 +14755,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14801,32 +14801,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128960402</v>
+        <v>128960488</v>
       </c>
       <c r="B131" t="n">
-        <v>92845</v>
+        <v>98659</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14836,10 +14836,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>690717</v>
+        <v>691464</v>
       </c>
       <c r="R131" t="n">
-        <v>7400812</v>
+        <v>7400741</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14866,22 +14866,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14912,32 +14912,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128960629</v>
+        <v>128960464</v>
       </c>
       <c r="B132" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>691778</v>
+        <v>691251</v>
       </c>
       <c r="R132" t="n">
-        <v>7401031</v>
+        <v>7400808</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14982,7 +14982,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14992,7 +14992,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15023,32 +15023,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128960626</v>
+        <v>128960496</v>
       </c>
       <c r="B133" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15058,10 +15058,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>691772</v>
+        <v>691471</v>
       </c>
       <c r="R133" t="n">
-        <v>7400877</v>
+        <v>7401095</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15134,10 +15134,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128960432</v>
+        <v>128960354</v>
       </c>
       <c r="B134" t="n">
-        <v>93014</v>
+        <v>96905</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15145,21 +15145,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>2079</v>
+        <v>53</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>690722</v>
+        <v>691515</v>
       </c>
       <c r="R134" t="n">
-        <v>7400676</v>
+        <v>7401011</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15199,22 +15199,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15245,10 +15245,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128960378</v>
+        <v>128960432</v>
       </c>
       <c r="B135" t="n">
-        <v>90558</v>
+        <v>93014</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15256,21 +15256,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1962</v>
+        <v>2079</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>690754</v>
+        <v>690722</v>
       </c>
       <c r="R135" t="n">
-        <v>7400823</v>
+        <v>7400676</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15325,7 +15325,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15356,10 +15356,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128960354</v>
+        <v>128960556</v>
       </c>
       <c r="B136" t="n">
-        <v>96905</v>
+        <v>91540</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15367,21 +15367,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>53</v>
+        <v>1204</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15391,10 +15391,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>691515</v>
+        <v>691520</v>
       </c>
       <c r="R136" t="n">
-        <v>7401011</v>
+        <v>7401010</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15467,32 +15467,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128960511</v>
+        <v>128960378</v>
       </c>
       <c r="B137" t="n">
-        <v>98659</v>
+        <v>90558</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15502,10 +15502,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>690875</v>
+        <v>690754</v>
       </c>
       <c r="R137" t="n">
-        <v>7400942</v>
+        <v>7400823</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15578,32 +15578,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128960488</v>
+        <v>128960402</v>
       </c>
       <c r="B138" t="n">
-        <v>98659</v>
+        <v>92845</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15613,10 +15613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>691464</v>
+        <v>690717</v>
       </c>
       <c r="R138" t="n">
-        <v>7400741</v>
+        <v>7400812</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15643,22 +15643,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15689,32 +15689,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128960464</v>
+        <v>128960369</v>
       </c>
       <c r="B139" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15724,10 +15724,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691251</v>
+        <v>691330</v>
       </c>
       <c r="R139" t="n">
-        <v>7400808</v>
+        <v>7400743</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15800,32 +15800,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128960496</v>
+        <v>128960629</v>
       </c>
       <c r="B140" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>691471</v>
+        <v>691778</v>
       </c>
       <c r="R140" t="n">
-        <v>7401095</v>
+        <v>7401031</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15911,32 +15911,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128960369</v>
+        <v>128960626</v>
       </c>
       <c r="B141" t="n">
-        <v>79625</v>
+        <v>92819</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15946,10 +15946,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>691330</v>
+        <v>691772</v>
       </c>
       <c r="R141" t="n">
-        <v>7400743</v>
+        <v>7400877</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15981,7 +15981,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -19796,32 +19796,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128960495</v>
+        <v>128960406</v>
       </c>
       <c r="B176" t="n">
-        <v>98659</v>
+        <v>80169</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19831,10 +19831,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>691488</v>
+        <v>691215</v>
       </c>
       <c r="R176" t="n">
-        <v>7401092</v>
+        <v>7400790</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19907,7 +19907,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128960475</v>
+        <v>128960495</v>
       </c>
       <c r="B177" t="n">
         <v>98659</v>
@@ -19942,10 +19942,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>691050</v>
+        <v>691488</v>
       </c>
       <c r="R177" t="n">
-        <v>7400705</v>
+        <v>7401092</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20018,32 +20018,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128960406</v>
+        <v>128960475</v>
       </c>
       <c r="B178" t="n">
-        <v>80169</v>
+        <v>98659</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20053,10 +20053,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>691215</v>
+        <v>691050</v>
       </c>
       <c r="R178" t="n">
-        <v>7400790</v>
+        <v>7400705</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20351,32 +20351,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128960598</v>
+        <v>128960472</v>
       </c>
       <c r="B181" t="n">
-        <v>78701</v>
+        <v>98659</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20386,10 +20386,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>691672</v>
+        <v>690998</v>
       </c>
       <c r="R181" t="n">
-        <v>7401058</v>
+        <v>7400789</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20462,32 +20462,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128960472</v>
+        <v>128960598</v>
       </c>
       <c r="B182" t="n">
-        <v>98659</v>
+        <v>78701</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20497,10 +20497,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>690998</v>
+        <v>691672</v>
       </c>
       <c r="R182" t="n">
-        <v>7400789</v>
+        <v>7401058</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21683,32 +21683,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128960507</v>
+        <v>128960644</v>
       </c>
       <c r="B193" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21718,10 +21718,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>690928</v>
+        <v>691471</v>
       </c>
       <c r="R193" t="n">
-        <v>7400812</v>
+        <v>7400823</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21748,22 +21748,22 @@
       </c>
       <c r="Y193" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21794,32 +21794,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128960493</v>
+        <v>128960684</v>
       </c>
       <c r="B194" t="n">
-        <v>98659</v>
+        <v>78043</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21829,10 +21829,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>691483</v>
+        <v>691442</v>
       </c>
       <c r="R194" t="n">
-        <v>7401085</v>
+        <v>7400932</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21905,32 +21905,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128960506</v>
+        <v>128960342</v>
       </c>
       <c r="B195" t="n">
-        <v>98659</v>
+        <v>91448</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21940,10 +21940,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>690964</v>
+        <v>691704</v>
       </c>
       <c r="R195" t="n">
-        <v>7400788</v>
+        <v>7401045</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21970,22 +21970,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22016,32 +22016,32 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128960342</v>
+        <v>128960507</v>
       </c>
       <c r="B196" t="n">
-        <v>91448</v>
+        <v>98659</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -22051,10 +22051,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>691704</v>
+        <v>690928</v>
       </c>
       <c r="R196" t="n">
-        <v>7401045</v>
+        <v>7400812</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22081,22 +22081,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22127,32 +22127,32 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128960644</v>
+        <v>128960493</v>
       </c>
       <c r="B197" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -22162,10 +22162,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>691471</v>
+        <v>691483</v>
       </c>
       <c r="R197" t="n">
-        <v>7400823</v>
+        <v>7401085</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22238,32 +22238,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128960684</v>
+        <v>128960506</v>
       </c>
       <c r="B198" t="n">
-        <v>78043</v>
+        <v>98659</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22273,10 +22273,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>691442</v>
+        <v>690964</v>
       </c>
       <c r="R198" t="n">
-        <v>7400932</v>
+        <v>7400788</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22303,22 +22303,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23570,10 +23570,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128960483</v>
+        <v>128960587</v>
       </c>
       <c r="B210" t="n">
-        <v>98659</v>
+        <v>91787</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23581,21 +23581,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23605,10 +23605,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>691042</v>
+        <v>691522</v>
       </c>
       <c r="R210" t="n">
-        <v>7400691</v>
+        <v>7401008</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23681,10 +23681,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128960371</v>
+        <v>128960611</v>
       </c>
       <c r="B211" t="n">
-        <v>79625</v>
+        <v>78701</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23692,21 +23692,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23716,10 +23716,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>691493</v>
+        <v>690824</v>
       </c>
       <c r="R211" t="n">
-        <v>7400837</v>
+        <v>7400642</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23746,22 +23746,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23792,32 +23792,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128960587</v>
+        <v>128960690</v>
       </c>
       <c r="B212" t="n">
-        <v>91787</v>
+        <v>78438</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23827,10 +23827,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>691522</v>
+        <v>690817</v>
       </c>
       <c r="R212" t="n">
-        <v>7401008</v>
+        <v>7400668</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23857,22 +23857,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23903,10 +23903,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128960611</v>
+        <v>128960687</v>
       </c>
       <c r="B213" t="n">
-        <v>78701</v>
+        <v>78043</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23914,21 +23914,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>353</v>
+        <v>6487</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23938,10 +23938,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>690824</v>
+        <v>691772</v>
       </c>
       <c r="R213" t="n">
-        <v>7400642</v>
+        <v>7401045</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23968,22 +23968,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24014,32 +24014,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128960690</v>
+        <v>128960483</v>
       </c>
       <c r="B214" t="n">
-        <v>78438</v>
+        <v>98659</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -24049,10 +24049,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>690817</v>
+        <v>691042</v>
       </c>
       <c r="R214" t="n">
-        <v>7400668</v>
+        <v>7400691</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24079,22 +24079,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24125,10 +24125,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128960687</v>
+        <v>128960371</v>
       </c>
       <c r="B215" t="n">
-        <v>78043</v>
+        <v>79625</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24136,21 +24136,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24160,10 +24160,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>691772</v>
+        <v>691493</v>
       </c>
       <c r="R215" t="n">
-        <v>7401045</v>
+        <v>7400837</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24195,7 +24195,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24791,10 +24791,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128960455</v>
+        <v>128960582</v>
       </c>
       <c r="B221" t="n">
-        <v>98659</v>
+        <v>91787</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24802,21 +24802,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24826,10 +24826,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>691615</v>
+        <v>691723</v>
       </c>
       <c r="R221" t="n">
-        <v>7400959</v>
+        <v>7400616</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24861,7 +24861,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24902,32 +24902,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128960451</v>
+        <v>128960608</v>
       </c>
       <c r="B222" t="n">
-        <v>98659</v>
+        <v>78701</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24937,10 +24937,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>691520</v>
+        <v>691209</v>
       </c>
       <c r="R222" t="n">
-        <v>7401010</v>
+        <v>7400623</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24972,7 +24972,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25013,32 +25013,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128960487</v>
+        <v>128960356</v>
       </c>
       <c r="B223" t="n">
-        <v>98659</v>
+        <v>91491</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25048,10 +25048,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>691504</v>
+        <v>691028</v>
       </c>
       <c r="R223" t="n">
-        <v>7400725</v>
+        <v>7400838</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25124,32 +25124,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128960497</v>
+        <v>128960436</v>
       </c>
       <c r="B224" t="n">
-        <v>98659</v>
+        <v>90152</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>4962</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25159,10 +25159,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>691469</v>
+        <v>691019</v>
       </c>
       <c r="R224" t="n">
-        <v>7401129</v>
+        <v>7400845</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25194,7 +25194,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25235,32 +25235,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128960486</v>
+        <v>128960693</v>
       </c>
       <c r="B225" t="n">
-        <v>98659</v>
+        <v>78438</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25270,10 +25270,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>691497</v>
+        <v>691595</v>
       </c>
       <c r="R225" t="n">
-        <v>7400703</v>
+        <v>7401115</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25346,10 +25346,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128960358</v>
+        <v>128960366</v>
       </c>
       <c r="B226" t="n">
-        <v>79654</v>
+        <v>79625</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25357,21 +25357,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25381,10 +25381,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>691772</v>
+        <v>691628</v>
       </c>
       <c r="R226" t="n">
-        <v>7400877</v>
+        <v>7401071</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25416,7 +25416,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25426,7 +25426,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25457,32 +25457,32 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128960582</v>
+        <v>128960360</v>
       </c>
       <c r="B227" t="n">
-        <v>91787</v>
+        <v>79625</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25492,10 +25492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>691723</v>
+        <v>691748</v>
       </c>
       <c r="R227" t="n">
-        <v>7400616</v>
+        <v>7400820</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25568,10 +25568,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128960608</v>
+        <v>128960358</v>
       </c>
       <c r="B228" t="n">
-        <v>78701</v>
+        <v>79654</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25579,21 +25579,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25603,10 +25603,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>691209</v>
+        <v>691772</v>
       </c>
       <c r="R228" t="n">
-        <v>7400623</v>
+        <v>7400877</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25638,7 +25638,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25648,7 +25648,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25679,32 +25679,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128960356</v>
+        <v>128960455</v>
       </c>
       <c r="B229" t="n">
-        <v>91491</v>
+        <v>98659</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -25714,10 +25714,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>691028</v>
+        <v>691615</v>
       </c>
       <c r="R229" t="n">
-        <v>7400838</v>
+        <v>7400959</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25790,32 +25790,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128960436</v>
+        <v>128960451</v>
       </c>
       <c r="B230" t="n">
-        <v>90152</v>
+        <v>98659</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25825,10 +25825,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691019</v>
+        <v>691520</v>
       </c>
       <c r="R230" t="n">
-        <v>7400845</v>
+        <v>7401010</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25860,7 +25860,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25901,32 +25901,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128960693</v>
+        <v>128960487</v>
       </c>
       <c r="B231" t="n">
-        <v>78438</v>
+        <v>98659</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25936,10 +25936,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>691595</v>
+        <v>691504</v>
       </c>
       <c r="R231" t="n">
-        <v>7401115</v>
+        <v>7400725</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25971,7 +25971,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26012,32 +26012,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128960366</v>
+        <v>128960497</v>
       </c>
       <c r="B232" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26047,10 +26047,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>691628</v>
+        <v>691469</v>
       </c>
       <c r="R232" t="n">
-        <v>7401071</v>
+        <v>7401129</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26123,32 +26123,32 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128960360</v>
+        <v>128960486</v>
       </c>
       <c r="B233" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -26158,10 +26158,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>691748</v>
+        <v>691497</v>
       </c>
       <c r="R233" t="n">
-        <v>7400820</v>
+        <v>7400703</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26193,7 +26193,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26203,7 +26203,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -27122,32 +27122,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128960363</v>
+        <v>128960563</v>
       </c>
       <c r="B242" t="n">
-        <v>79625</v>
+        <v>91687</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27157,10 +27157,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>690997</v>
+        <v>691283</v>
       </c>
       <c r="R242" t="n">
-        <v>7401042</v>
+        <v>7400566</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27187,22 +27187,22 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27233,7 +27233,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128960361</v>
+        <v>128960363</v>
       </c>
       <c r="B243" t="n">
         <v>79625</v>
@@ -27268,10 +27268,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>691629</v>
+        <v>690997</v>
       </c>
       <c r="R243" t="n">
-        <v>7400883</v>
+        <v>7401042</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27298,22 +27298,22 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27344,32 +27344,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128960563</v>
+        <v>128960361</v>
       </c>
       <c r="B244" t="n">
-        <v>91687</v>
+        <v>79625</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27379,10 +27379,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>691283</v>
+        <v>691629</v>
       </c>
       <c r="R244" t="n">
-        <v>7400566</v>
+        <v>7400883</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27414,7 +27414,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27424,7 +27424,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -28343,7 +28343,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128960380</v>
+        <v>128960381</v>
       </c>
       <c r="B253" t="n">
         <v>91801</v>
@@ -28378,10 +28378,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>691721</v>
+        <v>691489</v>
       </c>
       <c r="R253" t="n">
-        <v>7400617</v>
+        <v>7400750</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28413,7 +28413,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28423,7 +28423,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28454,7 +28454,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128960381</v>
+        <v>128960380</v>
       </c>
       <c r="B254" t="n">
         <v>91801</v>
@@ -28489,10 +28489,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>691489</v>
+        <v>691721</v>
       </c>
       <c r="R254" t="n">
-        <v>7400750</v>
+        <v>7400617</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD254" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128960691</v>
+        <v>128960450</v>
       </c>
       <c r="B5" t="n">
-        <v>78438</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691190</v>
+        <v>691723</v>
       </c>
       <c r="R5" t="n">
-        <v>7401223</v>
+        <v>7401427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,22 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128960450</v>
+        <v>128960524</v>
       </c>
       <c r="B6" t="n">
         <v>98659</v>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691723</v>
+        <v>691395</v>
       </c>
       <c r="R6" t="n">
-        <v>7401427</v>
+        <v>7401429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,32 +1226,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128960524</v>
+        <v>128960372</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691395</v>
+        <v>691253</v>
       </c>
       <c r="R7" t="n">
-        <v>7401429</v>
+        <v>7401236</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128960372</v>
+        <v>128960691</v>
       </c>
       <c r="B8" t="n">
-        <v>79625</v>
+        <v>78438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691253</v>
+        <v>691190</v>
       </c>
       <c r="R8" t="n">
-        <v>7401236</v>
+        <v>7401223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,32 +1448,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128960343</v>
+        <v>128960426</v>
       </c>
       <c r="B9" t="n">
-        <v>91448</v>
+        <v>98548</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>233</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691612</v>
+        <v>691727</v>
       </c>
       <c r="R9" t="n">
-        <v>7401171</v>
+        <v>7401372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,22 +1513,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,32 +1559,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128960670</v>
+        <v>128960616</v>
       </c>
       <c r="B10" t="n">
-        <v>92819</v>
+        <v>78701</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691851</v>
+        <v>691854</v>
       </c>
       <c r="R10" t="n">
-        <v>7401441</v>
+        <v>7401445</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,32 +1670,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128960616</v>
+        <v>128960670</v>
       </c>
       <c r="B11" t="n">
-        <v>78701</v>
+        <v>92819</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691854</v>
+        <v>691851</v>
       </c>
       <c r="R11" t="n">
-        <v>7401445</v>
+        <v>7401441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,32 +1781,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128960426</v>
+        <v>128960689</v>
       </c>
       <c r="B12" t="n">
-        <v>98548</v>
+        <v>78438</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>233</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691727</v>
+        <v>691341</v>
       </c>
       <c r="R12" t="n">
-        <v>7401372</v>
+        <v>7401206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,22 +1846,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128960689</v>
+        <v>128960343</v>
       </c>
       <c r="B13" t="n">
-        <v>78438</v>
+        <v>91448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691341</v>
+        <v>691612</v>
       </c>
       <c r="R13" t="n">
-        <v>7401206</v>
+        <v>7401171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,7 +2003,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128960498</v>
+        <v>128960544</v>
       </c>
       <c r="B14" t="n">
         <v>98659</v>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691438</v>
+        <v>691695</v>
       </c>
       <c r="R14" t="n">
-        <v>7401141</v>
+        <v>7401360</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,22 +2068,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,7 +2114,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128960544</v>
+        <v>128960498</v>
       </c>
       <c r="B15" t="n">
         <v>98659</v>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691695</v>
+        <v>691438</v>
       </c>
       <c r="R15" t="n">
-        <v>7401360</v>
+        <v>7401141</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,22 +2179,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,32 +2225,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128960542</v>
+        <v>128960618</v>
       </c>
       <c r="B16" t="n">
-        <v>98659</v>
+        <v>78701</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691733</v>
+        <v>691741</v>
       </c>
       <c r="R16" t="n">
-        <v>7401377</v>
+        <v>7401356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,32 +2336,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128960519</v>
+        <v>128960433</v>
       </c>
       <c r="B17" t="n">
-        <v>98659</v>
+        <v>93014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691230</v>
+        <v>691276</v>
       </c>
       <c r="R17" t="n">
-        <v>7401270</v>
+        <v>7401328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2558,32 +2558,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128960433</v>
+        <v>128960519</v>
       </c>
       <c r="B19" t="n">
-        <v>93014</v>
+        <v>98659</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691276</v>
+        <v>691230</v>
       </c>
       <c r="R19" t="n">
-        <v>7401328</v>
+        <v>7401270</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,32 +2669,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128960618</v>
+        <v>128960542</v>
       </c>
       <c r="B20" t="n">
-        <v>78701</v>
+        <v>98659</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691741</v>
+        <v>691733</v>
       </c>
       <c r="R20" t="n">
-        <v>7401356</v>
+        <v>7401377</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3557,10 +3557,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128960454</v>
+        <v>128960573</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>91687</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3568,21 +3568,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691681</v>
+        <v>691704</v>
       </c>
       <c r="R28" t="n">
-        <v>7401433</v>
+        <v>7401335</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128960540</v>
+        <v>128960666</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691741</v>
+        <v>691773</v>
       </c>
       <c r="R29" t="n">
-        <v>7401356</v>
+        <v>7401444</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3890,32 +3890,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128960666</v>
+        <v>128960454</v>
       </c>
       <c r="B31" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691773</v>
+        <v>691681</v>
       </c>
       <c r="R31" t="n">
-        <v>7401444</v>
+        <v>7401433</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,10 +4001,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128960573</v>
+        <v>128960540</v>
       </c>
       <c r="B32" t="n">
-        <v>91687</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4012,21 +4012,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691704</v>
+        <v>691741</v>
       </c>
       <c r="R32" t="n">
-        <v>7401335</v>
+        <v>7401356</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4112,32 +4112,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128960675</v>
+        <v>128960551</v>
       </c>
       <c r="B33" t="n">
-        <v>92819</v>
+        <v>92150</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5454</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691653</v>
+        <v>691848</v>
       </c>
       <c r="R33" t="n">
-        <v>7401394</v>
+        <v>7401397</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4334,32 +4334,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128960551</v>
+        <v>128960675</v>
       </c>
       <c r="B35" t="n">
-        <v>92150</v>
+        <v>92819</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5454</v>
+        <v>4364</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691848</v>
+        <v>691653</v>
       </c>
       <c r="R35" t="n">
-        <v>7401397</v>
+        <v>7401394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4556,10 +4556,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128960561</v>
+        <v>128960424</v>
       </c>
       <c r="B37" t="n">
-        <v>91687</v>
+        <v>98548</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>233</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691650</v>
+        <v>691756</v>
       </c>
       <c r="R37" t="n">
-        <v>7401329</v>
+        <v>7401403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128960571</v>
+        <v>128960561</v>
       </c>
       <c r="B38" t="n">
         <v>91687</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691659</v>
+        <v>691650</v>
       </c>
       <c r="R38" t="n">
-        <v>7401322</v>
+        <v>7401329</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,10 +4778,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128960424</v>
+        <v>128960571</v>
       </c>
       <c r="B39" t="n">
-        <v>98548</v>
+        <v>91687</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4789,21 +4789,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>233</v>
+        <v>1503</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691756</v>
+        <v>691659</v>
       </c>
       <c r="R39" t="n">
-        <v>7401403</v>
+        <v>7401322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5111,32 +5111,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128960695</v>
+        <v>128960527</v>
       </c>
       <c r="B42" t="n">
-        <v>78438</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691255</v>
+        <v>691373</v>
       </c>
       <c r="R42" t="n">
-        <v>7401234</v>
+        <v>7401425</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5181,7 +5181,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128960422</v>
+        <v>128960377</v>
       </c>
       <c r="B43" t="n">
-        <v>98548</v>
+        <v>79625</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>233</v>
+        <v>229821</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691717</v>
+        <v>691728</v>
       </c>
       <c r="R43" t="n">
-        <v>7401426</v>
+        <v>7401382</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5287,22 +5287,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,7 +5333,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128960431</v>
+        <v>128960422</v>
       </c>
       <c r="B44" t="n">
         <v>98548</v>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691733</v>
+        <v>691717</v>
       </c>
       <c r="R44" t="n">
-        <v>7401377</v>
+        <v>7401426</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5398,22 +5398,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5444,10 +5444,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128960527</v>
+        <v>128960431</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>98548</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>233</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691373</v>
+        <v>691733</v>
       </c>
       <c r="R45" t="n">
-        <v>7401425</v>
+        <v>7401377</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5555,10 +5555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128960377</v>
+        <v>128960695</v>
       </c>
       <c r="B46" t="n">
-        <v>79625</v>
+        <v>78438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691728</v>
+        <v>691255</v>
       </c>
       <c r="R46" t="n">
-        <v>7401382</v>
+        <v>7401234</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5999,7 +5999,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128960458</v>
+        <v>128960531</v>
       </c>
       <c r="B50" t="n">
         <v>98659</v>
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691458</v>
+        <v>691819</v>
       </c>
       <c r="R50" t="n">
-        <v>7401226</v>
+        <v>7401453</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6064,22 +6064,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6110,7 +6110,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128960520</v>
+        <v>128960529</v>
       </c>
       <c r="B51" t="n">
         <v>98659</v>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691345</v>
+        <v>691510</v>
       </c>
       <c r="R51" t="n">
-        <v>7401412</v>
+        <v>7401400</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6221,7 +6221,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128960531</v>
+        <v>128960458</v>
       </c>
       <c r="B52" t="n">
         <v>98659</v>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691819</v>
+        <v>691458</v>
       </c>
       <c r="R52" t="n">
-        <v>7401453</v>
+        <v>7401226</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6286,22 +6286,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6332,7 +6332,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128960529</v>
+        <v>128960520</v>
       </c>
       <c r="B53" t="n">
         <v>98659</v>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691510</v>
+        <v>691345</v>
       </c>
       <c r="R53" t="n">
-        <v>7401400</v>
+        <v>7401412</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6443,32 +6443,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128960457</v>
+        <v>128960617</v>
       </c>
       <c r="B54" t="n">
-        <v>98659</v>
+        <v>78701</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6478,10 +6478,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>691411</v>
+        <v>691849</v>
       </c>
       <c r="R54" t="n">
-        <v>7401213</v>
+        <v>7401401</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6508,22 +6508,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6554,32 +6554,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128960617</v>
+        <v>128960457</v>
       </c>
       <c r="B55" t="n">
-        <v>78701</v>
+        <v>98659</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6589,10 +6589,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>691849</v>
+        <v>691411</v>
       </c>
       <c r="R55" t="n">
-        <v>7401401</v>
+        <v>7401213</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6619,22 +6619,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6887,7 +6887,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128960533</v>
+        <v>128960534</v>
       </c>
       <c r="B58" t="n">
         <v>98659</v>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691773</v>
+        <v>691770</v>
       </c>
       <c r="R58" t="n">
-        <v>7401347</v>
+        <v>7401379</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6998,7 +6998,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128960534</v>
+        <v>128960533</v>
       </c>
       <c r="B59" t="n">
         <v>98659</v>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691770</v>
+        <v>691773</v>
       </c>
       <c r="R59" t="n">
-        <v>7401379</v>
+        <v>7401347</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7220,10 +7220,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128960401</v>
+        <v>128960613</v>
       </c>
       <c r="B61" t="n">
-        <v>92436</v>
+        <v>78701</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7231,21 +7231,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4745</v>
+        <v>353</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7255,10 +7255,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>691473</v>
+        <v>691174</v>
       </c>
       <c r="R61" t="n">
-        <v>7401417</v>
+        <v>7401210</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7290,7 +7290,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>16:08</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7331,10 +7331,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128960613</v>
+        <v>128960401</v>
       </c>
       <c r="B62" t="n">
-        <v>78701</v>
+        <v>92436</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7342,21 +7342,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691174</v>
+        <v>691473</v>
       </c>
       <c r="R62" t="n">
-        <v>7401210</v>
+        <v>7401417</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>16:08</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7664,32 +7664,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128960536</v>
+        <v>128960624</v>
       </c>
       <c r="B65" t="n">
-        <v>98659</v>
+        <v>78701</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>691728</v>
+        <v>691444</v>
       </c>
       <c r="R65" t="n">
-        <v>7401388</v>
+        <v>7401426</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7775,32 +7775,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128960518</v>
+        <v>128960347</v>
       </c>
       <c r="B66" t="n">
-        <v>98659</v>
+        <v>91448</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>691236</v>
+        <v>691668</v>
       </c>
       <c r="R66" t="n">
-        <v>7401263</v>
+        <v>7401306</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,10 +7886,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128960624</v>
+        <v>128960692</v>
       </c>
       <c r="B67" t="n">
-        <v>78701</v>
+        <v>78438</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7897,21 +7897,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691444</v>
+        <v>691580</v>
       </c>
       <c r="R67" t="n">
-        <v>7401426</v>
+        <v>7401425</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7997,32 +7997,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128960692</v>
+        <v>128960518</v>
       </c>
       <c r="B68" t="n">
-        <v>78438</v>
+        <v>98659</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>691580</v>
+        <v>691236</v>
       </c>
       <c r="R68" t="n">
-        <v>7401425</v>
+        <v>7401263</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8108,32 +8108,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128960347</v>
+        <v>128960536</v>
       </c>
       <c r="B69" t="n">
-        <v>91448</v>
+        <v>98659</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>691668</v>
+        <v>691728</v>
       </c>
       <c r="R69" t="n">
-        <v>7401306</v>
+        <v>7401388</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8219,32 +8219,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128960537</v>
+        <v>128960364</v>
       </c>
       <c r="B70" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>691719</v>
+        <v>691580</v>
       </c>
       <c r="R70" t="n">
-        <v>7401396</v>
+        <v>7401428</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8330,7 +8330,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128960452</v>
+        <v>128960537</v>
       </c>
       <c r="B71" t="n">
         <v>98659</v>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>691486</v>
+        <v>691719</v>
       </c>
       <c r="R71" t="n">
-        <v>7401432</v>
+        <v>7401396</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8441,32 +8441,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128960364</v>
+        <v>128960452</v>
       </c>
       <c r="B72" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>691580</v>
+        <v>691486</v>
       </c>
       <c r="R72" t="n">
-        <v>7401428</v>
+        <v>7401432</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -13913,32 +13913,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128960399</v>
+        <v>128960650</v>
       </c>
       <c r="B123" t="n">
-        <v>92436</v>
+        <v>92819</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>690819</v>
+        <v>690728</v>
       </c>
       <c r="R123" t="n">
-        <v>7400882</v>
+        <v>7400633</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14024,7 +14024,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128960650</v>
+        <v>128960646</v>
       </c>
       <c r="B124" t="n">
         <v>92819</v>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>690728</v>
+        <v>691445</v>
       </c>
       <c r="R124" t="n">
-        <v>7400633</v>
+        <v>7400907</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14089,22 +14089,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14135,32 +14135,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128960646</v>
+        <v>128960399</v>
       </c>
       <c r="B125" t="n">
-        <v>92819</v>
+        <v>92436</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>691445</v>
+        <v>690819</v>
       </c>
       <c r="R125" t="n">
-        <v>7400907</v>
+        <v>7400882</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,22 +14200,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14357,32 +14357,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128960370</v>
+        <v>128960476</v>
       </c>
       <c r="B127" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>691375</v>
+        <v>691094</v>
       </c>
       <c r="R127" t="n">
-        <v>7400750</v>
+        <v>7400693</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14579,32 +14579,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128960476</v>
+        <v>128960370</v>
       </c>
       <c r="B129" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14614,10 +14614,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>691094</v>
+        <v>691375</v>
       </c>
       <c r="R129" t="n">
-        <v>7400693</v>
+        <v>7400750</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14690,32 +14690,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128960511</v>
+        <v>128960369</v>
       </c>
       <c r="B130" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>690875</v>
+        <v>691330</v>
       </c>
       <c r="R130" t="n">
-        <v>7400942</v>
+        <v>7400743</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14755,22 +14755,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14801,7 +14801,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128960488</v>
+        <v>128960496</v>
       </c>
       <c r="B131" t="n">
         <v>98659</v>
@@ -14836,10 +14836,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>691464</v>
+        <v>691471</v>
       </c>
       <c r="R131" t="n">
-        <v>7400741</v>
+        <v>7401095</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14912,7 +14912,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128960464</v>
+        <v>128960511</v>
       </c>
       <c r="B132" t="n">
         <v>98659</v>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>691251</v>
+        <v>690875</v>
       </c>
       <c r="R132" t="n">
-        <v>7400808</v>
+        <v>7400942</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14977,22 +14977,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15023,7 +15023,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128960496</v>
+        <v>128960464</v>
       </c>
       <c r="B133" t="n">
         <v>98659</v>
@@ -15058,10 +15058,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>691471</v>
+        <v>691251</v>
       </c>
       <c r="R133" t="n">
-        <v>7401095</v>
+        <v>7400808</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15134,32 +15134,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128960354</v>
+        <v>128960488</v>
       </c>
       <c r="B134" t="n">
-        <v>96905</v>
+        <v>98659</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>691515</v>
+        <v>691464</v>
       </c>
       <c r="R134" t="n">
-        <v>7401011</v>
+        <v>7400741</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15204,7 +15204,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15245,10 +15245,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128960432</v>
+        <v>128960556</v>
       </c>
       <c r="B135" t="n">
-        <v>93014</v>
+        <v>91540</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15256,21 +15256,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2079</v>
+        <v>1204</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>690722</v>
+        <v>691520</v>
       </c>
       <c r="R135" t="n">
-        <v>7400676</v>
+        <v>7401010</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15310,22 +15310,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15356,10 +15356,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128960556</v>
+        <v>128960378</v>
       </c>
       <c r="B136" t="n">
-        <v>91540</v>
+        <v>90558</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15367,21 +15367,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15391,10 +15391,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>691520</v>
+        <v>690754</v>
       </c>
       <c r="R136" t="n">
-        <v>7401010</v>
+        <v>7400823</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15421,22 +15421,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15467,32 +15467,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128960378</v>
+        <v>128960626</v>
       </c>
       <c r="B137" t="n">
-        <v>90558</v>
+        <v>92819</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15502,10 +15502,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>690754</v>
+        <v>691772</v>
       </c>
       <c r="R137" t="n">
-        <v>7400823</v>
+        <v>7400877</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15532,22 +15532,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15578,32 +15578,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128960402</v>
+        <v>128960629</v>
       </c>
       <c r="B138" t="n">
-        <v>92845</v>
+        <v>92819</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15613,10 +15613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>690717</v>
+        <v>691778</v>
       </c>
       <c r="R138" t="n">
-        <v>7400812</v>
+        <v>7401031</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15643,22 +15643,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15689,10 +15689,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128960369</v>
+        <v>128960402</v>
       </c>
       <c r="B139" t="n">
-        <v>79625</v>
+        <v>92845</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15700,21 +15700,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>229821</v>
+        <v>5448</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15724,10 +15724,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691330</v>
+        <v>690717</v>
       </c>
       <c r="R139" t="n">
-        <v>7400743</v>
+        <v>7400812</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15754,22 +15754,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15800,32 +15800,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128960629</v>
+        <v>128960354</v>
       </c>
       <c r="B140" t="n">
-        <v>92819</v>
+        <v>96905</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>4364</v>
+        <v>53</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>691778</v>
+        <v>691515</v>
       </c>
       <c r="R140" t="n">
-        <v>7401031</v>
+        <v>7401011</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15911,32 +15911,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128960626</v>
+        <v>128960432</v>
       </c>
       <c r="B141" t="n">
-        <v>92819</v>
+        <v>93014</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15946,10 +15946,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>691772</v>
+        <v>690722</v>
       </c>
       <c r="R141" t="n">
-        <v>7400877</v>
+        <v>7400676</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15976,22 +15976,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16022,32 +16022,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128960414</v>
+        <v>128960479</v>
       </c>
       <c r="B142" t="n">
-        <v>80141</v>
+        <v>98659</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16057,10 +16057,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>691163</v>
+        <v>691286</v>
       </c>
       <c r="R142" t="n">
-        <v>7400622</v>
+        <v>7400554</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16133,32 +16133,32 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128960636</v>
+        <v>128960504</v>
       </c>
       <c r="B143" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>691313</v>
+        <v>690949</v>
       </c>
       <c r="R143" t="n">
-        <v>7400890</v>
+        <v>7400850</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16198,22 +16198,22 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16244,32 +16244,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128960642</v>
+        <v>128960480</v>
       </c>
       <c r="B144" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16279,10 +16279,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>691479</v>
+        <v>691030</v>
       </c>
       <c r="R144" t="n">
-        <v>7400776</v>
+        <v>7400688</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16314,7 +16314,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16466,32 +16466,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128960479</v>
+        <v>128960414</v>
       </c>
       <c r="B146" t="n">
-        <v>98659</v>
+        <v>80141</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>691286</v>
+        <v>691163</v>
       </c>
       <c r="R146" t="n">
-        <v>7400554</v>
+        <v>7400622</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16577,32 +16577,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128960480</v>
+        <v>128960642</v>
       </c>
       <c r="B147" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16612,10 +16612,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>691030</v>
+        <v>691479</v>
       </c>
       <c r="R147" t="n">
-        <v>7400688</v>
+        <v>7400776</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16647,7 +16647,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16688,32 +16688,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128960504</v>
+        <v>128960636</v>
       </c>
       <c r="B148" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16723,10 +16723,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>690949</v>
+        <v>691313</v>
       </c>
       <c r="R148" t="n">
-        <v>7400850</v>
+        <v>7400890</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16753,22 +16753,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17021,32 +17021,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128960465</v>
+        <v>128960683</v>
       </c>
       <c r="B151" t="n">
-        <v>98659</v>
+        <v>80175</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17056,10 +17056,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>691184</v>
+        <v>690835</v>
       </c>
       <c r="R151" t="n">
-        <v>7400869</v>
+        <v>7400892</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17086,22 +17086,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17132,32 +17132,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128960421</v>
+        <v>128960685</v>
       </c>
       <c r="B152" t="n">
-        <v>98548</v>
+        <v>78043</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>233</v>
+        <v>6487</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17167,10 +17167,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>691475</v>
+        <v>690998</v>
       </c>
       <c r="R152" t="n">
-        <v>7401113</v>
+        <v>7401040</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17197,22 +17197,22 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128960683</v>
+        <v>128960421</v>
       </c>
       <c r="B153" t="n">
-        <v>80175</v>
+        <v>98548</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6463</v>
+        <v>233</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>690835</v>
+        <v>691475</v>
       </c>
       <c r="R153" t="n">
-        <v>7400892</v>
+        <v>7401113</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17308,22 +17308,22 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17354,32 +17354,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128960685</v>
+        <v>128960465</v>
       </c>
       <c r="B154" t="n">
-        <v>78043</v>
+        <v>98659</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17389,10 +17389,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>690998</v>
+        <v>691184</v>
       </c>
       <c r="R154" t="n">
-        <v>7401040</v>
+        <v>7400869</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17419,22 +17419,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17465,7 +17465,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128960634</v>
+        <v>128960639</v>
       </c>
       <c r="B155" t="n">
         <v>92819</v>
@@ -17500,10 +17500,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>691432</v>
+        <v>691173</v>
       </c>
       <c r="R155" t="n">
-        <v>7400884</v>
+        <v>7400751</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17576,7 +17576,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128960633</v>
+        <v>128960634</v>
       </c>
       <c r="B156" t="n">
         <v>92819</v>
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>691476</v>
+        <v>691432</v>
       </c>
       <c r="R156" t="n">
-        <v>7400909</v>
+        <v>7400884</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17687,10 +17687,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128960416</v>
+        <v>128960633</v>
       </c>
       <c r="B157" t="n">
-        <v>92831</v>
+        <v>92819</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17698,21 +17698,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17722,10 +17722,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>690733</v>
+        <v>691476</v>
       </c>
       <c r="R157" t="n">
-        <v>7400794</v>
+        <v>7400909</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17752,22 +17752,22 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17798,32 +17798,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128960639</v>
+        <v>128960394</v>
       </c>
       <c r="B158" t="n">
-        <v>92819</v>
+        <v>92436</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17833,10 +17833,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>691173</v>
+        <v>691657</v>
       </c>
       <c r="R158" t="n">
-        <v>7400751</v>
+        <v>7400847</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17909,32 +17909,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128960394</v>
+        <v>128960416</v>
       </c>
       <c r="B159" t="n">
-        <v>92436</v>
+        <v>92831</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17944,10 +17944,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>691657</v>
+        <v>690733</v>
       </c>
       <c r="R159" t="n">
-        <v>7400847</v>
+        <v>7400794</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17974,22 +17974,22 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18020,10 +18020,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128960606</v>
+        <v>128960357</v>
       </c>
       <c r="B160" t="n">
-        <v>78701</v>
+        <v>79654</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18031,21 +18031,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18055,10 +18055,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691096</v>
+        <v>691748</v>
       </c>
       <c r="R160" t="n">
-        <v>7400927</v>
+        <v>7400820</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18131,10 +18131,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128960357</v>
+        <v>128960365</v>
       </c>
       <c r="B161" t="n">
-        <v>79654</v>
+        <v>79625</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18142,21 +18142,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>691748</v>
+        <v>691772</v>
       </c>
       <c r="R161" t="n">
-        <v>7400820</v>
+        <v>7401045</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18242,32 +18242,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128960365</v>
+        <v>128960469</v>
       </c>
       <c r="B162" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>691772</v>
+        <v>691149</v>
       </c>
       <c r="R162" t="n">
-        <v>7401045</v>
+        <v>7400912</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18312,7 +18312,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18353,7 +18353,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128960469</v>
+        <v>128960477</v>
       </c>
       <c r="B163" t="n">
         <v>98659</v>
@@ -18388,10 +18388,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>691149</v>
+        <v>691104</v>
       </c>
       <c r="R163" t="n">
-        <v>7400912</v>
+        <v>7400683</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18575,32 +18575,32 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128960477</v>
+        <v>128960606</v>
       </c>
       <c r="B165" t="n">
-        <v>98659</v>
+        <v>78701</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18610,10 +18610,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>691104</v>
+        <v>691096</v>
       </c>
       <c r="R165" t="n">
-        <v>7400683</v>
+        <v>7400927</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18686,32 +18686,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128960569</v>
+        <v>128960620</v>
       </c>
       <c r="B166" t="n">
-        <v>91687</v>
+        <v>78701</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18721,10 +18721,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>691471</v>
+        <v>691007</v>
       </c>
       <c r="R166" t="n">
-        <v>7400861</v>
+        <v>7401068</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18751,22 +18751,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18797,10 +18797,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128960485</v>
+        <v>128960569</v>
       </c>
       <c r="B167" t="n">
-        <v>98659</v>
+        <v>91687</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18808,21 +18808,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18832,10 +18832,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691491</v>
+        <v>691471</v>
       </c>
       <c r="R167" t="n">
-        <v>7400689</v>
+        <v>7400861</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18867,7 +18867,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18908,32 +18908,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128960484</v>
+        <v>128960397</v>
       </c>
       <c r="B168" t="n">
-        <v>98659</v>
+        <v>92436</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18943,10 +18943,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691205</v>
+        <v>690679</v>
       </c>
       <c r="R168" t="n">
-        <v>7400756</v>
+        <v>7400680</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18973,22 +18973,22 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19130,7 +19130,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128960456</v>
+        <v>128960485</v>
       </c>
       <c r="B170" t="n">
         <v>98659</v>
@@ -19165,10 +19165,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691641</v>
+        <v>691491</v>
       </c>
       <c r="R170" t="n">
-        <v>7400939</v>
+        <v>7400689</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19200,7 +19200,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19241,7 +19241,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128960515</v>
+        <v>128960508</v>
       </c>
       <c r="B171" t="n">
         <v>98659</v>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>691061</v>
+        <v>690820</v>
       </c>
       <c r="R171" t="n">
-        <v>7401094</v>
+        <v>7400917</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19311,7 +19311,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19352,32 +19352,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128960397</v>
+        <v>128960515</v>
       </c>
       <c r="B172" t="n">
-        <v>92436</v>
+        <v>98659</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19387,10 +19387,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>690679</v>
+        <v>691061</v>
       </c>
       <c r="R172" t="n">
-        <v>7400680</v>
+        <v>7401094</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19463,32 +19463,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128960620</v>
+        <v>128960484</v>
       </c>
       <c r="B173" t="n">
-        <v>78701</v>
+        <v>98659</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691007</v>
+        <v>691205</v>
       </c>
       <c r="R173" t="n">
-        <v>7401068</v>
+        <v>7400756</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19528,22 +19528,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19574,7 +19574,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128960508</v>
+        <v>128960456</v>
       </c>
       <c r="B174" t="n">
         <v>98659</v>
@@ -19609,10 +19609,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>690820</v>
+        <v>691641</v>
       </c>
       <c r="R174" t="n">
-        <v>7400917</v>
+        <v>7400939</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19639,22 +19639,22 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -20351,32 +20351,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128960472</v>
+        <v>128960598</v>
       </c>
       <c r="B181" t="n">
-        <v>98659</v>
+        <v>78701</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20386,10 +20386,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>690998</v>
+        <v>691672</v>
       </c>
       <c r="R181" t="n">
-        <v>7400789</v>
+        <v>7401058</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20462,32 +20462,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128960598</v>
+        <v>128960472</v>
       </c>
       <c r="B182" t="n">
-        <v>78701</v>
+        <v>98659</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20497,10 +20497,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>691672</v>
+        <v>690998</v>
       </c>
       <c r="R182" t="n">
-        <v>7401058</v>
+        <v>7400789</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20532,7 +20532,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20542,7 +20542,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20684,7 +20684,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128960512</v>
+        <v>128960474</v>
       </c>
       <c r="B184" t="n">
         <v>98659</v>
@@ -20719,10 +20719,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>691026</v>
+        <v>691032</v>
       </c>
       <c r="R184" t="n">
-        <v>7401085</v>
+        <v>7400748</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20749,22 +20749,22 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -21128,7 +21128,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128960474</v>
+        <v>128960505</v>
       </c>
       <c r="B188" t="n">
         <v>98659</v>
@@ -21163,10 +21163,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>691032</v>
+        <v>690992</v>
       </c>
       <c r="R188" t="n">
-        <v>7400748</v>
+        <v>7400806</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21193,22 +21193,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21350,7 +21350,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128960505</v>
+        <v>128960512</v>
       </c>
       <c r="B190" t="n">
         <v>98659</v>
@@ -21385,10 +21385,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>690992</v>
+        <v>691026</v>
       </c>
       <c r="R190" t="n">
-        <v>7400806</v>
+        <v>7401085</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21420,7 +21420,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21683,32 +21683,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128960644</v>
+        <v>128960684</v>
       </c>
       <c r="B193" t="n">
-        <v>92819</v>
+        <v>78043</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21718,10 +21718,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>691471</v>
+        <v>691442</v>
       </c>
       <c r="R193" t="n">
-        <v>7400823</v>
+        <v>7400932</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21794,10 +21794,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128960684</v>
+        <v>128960342</v>
       </c>
       <c r="B194" t="n">
-        <v>78043</v>
+        <v>91448</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21805,21 +21805,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6487</v>
+        <v>3242</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21829,10 +21829,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>691442</v>
+        <v>691704</v>
       </c>
       <c r="R194" t="n">
-        <v>7400932</v>
+        <v>7401045</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21905,32 +21905,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128960342</v>
+        <v>128960644</v>
       </c>
       <c r="B195" t="n">
-        <v>91448</v>
+        <v>92819</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21940,10 +21940,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>691704</v>
+        <v>691471</v>
       </c>
       <c r="R195" t="n">
-        <v>7401045</v>
+        <v>7400823</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21975,7 +21975,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22016,7 +22016,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128960507</v>
+        <v>128960493</v>
       </c>
       <c r="B196" t="n">
         <v>98659</v>
@@ -22051,10 +22051,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>690928</v>
+        <v>691483</v>
       </c>
       <c r="R196" t="n">
-        <v>7400812</v>
+        <v>7401085</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22081,22 +22081,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22127,7 +22127,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128960493</v>
+        <v>128960507</v>
       </c>
       <c r="B197" t="n">
         <v>98659</v>
@@ -22162,10 +22162,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>691483</v>
+        <v>690928</v>
       </c>
       <c r="R197" t="n">
-        <v>7401085</v>
+        <v>7400812</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22192,22 +22192,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22682,32 +22682,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128960459</v>
+        <v>128960341</v>
       </c>
       <c r="B202" t="n">
-        <v>98659</v>
+        <v>91448</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22717,10 +22717,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>691498</v>
+        <v>691820</v>
       </c>
       <c r="R202" t="n">
-        <v>7401073</v>
+        <v>7400734</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22793,10 +22793,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128960463</v>
+        <v>128960578</v>
       </c>
       <c r="B203" t="n">
-        <v>98659</v>
+        <v>91787</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22804,21 +22804,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22828,10 +22828,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>691259</v>
+        <v>691498</v>
       </c>
       <c r="R203" t="n">
-        <v>7400802</v>
+        <v>7400703</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22904,10 +22904,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128960341</v>
+        <v>128960605</v>
       </c>
       <c r="B204" t="n">
-        <v>91448</v>
+        <v>78701</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22915,21 +22915,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22939,10 +22939,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>691820</v>
+        <v>691194</v>
       </c>
       <c r="R204" t="n">
-        <v>7400734</v>
+        <v>7400846</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23015,32 +23015,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128960661</v>
+        <v>128960599</v>
       </c>
       <c r="B205" t="n">
-        <v>92819</v>
+        <v>78701</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23050,10 +23050,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>691007</v>
+        <v>691564</v>
       </c>
       <c r="R205" t="n">
-        <v>7401047</v>
+        <v>7401001</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23080,22 +23080,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23126,32 +23126,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128960578</v>
+        <v>128960661</v>
       </c>
       <c r="B206" t="n">
-        <v>91787</v>
+        <v>92819</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23161,10 +23161,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>691498</v>
+        <v>691007</v>
       </c>
       <c r="R206" t="n">
-        <v>7400703</v>
+        <v>7401047</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23191,22 +23191,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23237,10 +23237,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128960599</v>
+        <v>128960437</v>
       </c>
       <c r="B207" t="n">
-        <v>78701</v>
+        <v>90152</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23248,21 +23248,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>353</v>
+        <v>4962</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23272,10 +23272,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>691564</v>
+        <v>691225</v>
       </c>
       <c r="R207" t="n">
-        <v>7401001</v>
+        <v>7400593</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23307,7 +23307,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23348,32 +23348,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128960605</v>
+        <v>128960463</v>
       </c>
       <c r="B208" t="n">
-        <v>78701</v>
+        <v>98659</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23383,10 +23383,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>691194</v>
+        <v>691259</v>
       </c>
       <c r="R208" t="n">
-        <v>7400846</v>
+        <v>7400802</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23459,32 +23459,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128960437</v>
+        <v>128960459</v>
       </c>
       <c r="B209" t="n">
-        <v>90152</v>
+        <v>98659</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23494,10 +23494,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>691225</v>
+        <v>691498</v>
       </c>
       <c r="R209" t="n">
-        <v>7400593</v>
+        <v>7401073</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23570,32 +23570,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128960587</v>
+        <v>128960611</v>
       </c>
       <c r="B210" t="n">
-        <v>91787</v>
+        <v>78701</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23605,10 +23605,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>691522</v>
+        <v>690824</v>
       </c>
       <c r="R210" t="n">
-        <v>7401008</v>
+        <v>7400642</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23635,22 +23635,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23681,32 +23681,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128960611</v>
+        <v>128960587</v>
       </c>
       <c r="B211" t="n">
-        <v>78701</v>
+        <v>91787</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23716,10 +23716,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>690824</v>
+        <v>691522</v>
       </c>
       <c r="R211" t="n">
-        <v>7400642</v>
+        <v>7401008</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23746,22 +23746,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23792,10 +23792,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128960690</v>
+        <v>128960687</v>
       </c>
       <c r="B212" t="n">
-        <v>78438</v>
+        <v>78043</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23803,21 +23803,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6437</v>
+        <v>6487</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23827,10 +23827,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>690817</v>
+        <v>691772</v>
       </c>
       <c r="R212" t="n">
-        <v>7400668</v>
+        <v>7401045</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23857,22 +23857,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23903,10 +23903,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128960687</v>
+        <v>128960690</v>
       </c>
       <c r="B213" t="n">
-        <v>78043</v>
+        <v>78438</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23914,21 +23914,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23938,10 +23938,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>691772</v>
+        <v>690817</v>
       </c>
       <c r="R213" t="n">
-        <v>7401045</v>
+        <v>7400668</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23968,22 +23968,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24236,32 +24236,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128960489</v>
+        <v>128960655</v>
       </c>
       <c r="B216" t="n">
-        <v>98659</v>
+        <v>92819</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24271,10 +24271,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>691434</v>
+        <v>690734</v>
       </c>
       <c r="R216" t="n">
-        <v>7400760</v>
+        <v>7400797</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24301,22 +24301,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24347,32 +24347,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128960467</v>
+        <v>128960344</v>
       </c>
       <c r="B217" t="n">
-        <v>98659</v>
+        <v>91448</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24382,10 +24382,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>691182</v>
+        <v>691060</v>
       </c>
       <c r="R217" t="n">
-        <v>7400878</v>
+        <v>7400887</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24417,7 +24417,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24427,7 +24427,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24458,32 +24458,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>128960344</v>
+        <v>128960489</v>
       </c>
       <c r="B218" t="n">
-        <v>91448</v>
+        <v>98659</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24493,10 +24493,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>691060</v>
+        <v>691434</v>
       </c>
       <c r="R218" t="n">
-        <v>7400887</v>
+        <v>7400760</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24528,7 +24528,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24538,7 +24538,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24569,32 +24569,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>128960655</v>
+        <v>128960513</v>
       </c>
       <c r="B219" t="n">
-        <v>92819</v>
+        <v>98659</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24604,10 +24604,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>690734</v>
+        <v>691071</v>
       </c>
       <c r="R219" t="n">
-        <v>7400797</v>
+        <v>7401097</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24639,7 +24639,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24680,7 +24680,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>128960513</v>
+        <v>128960467</v>
       </c>
       <c r="B220" t="n">
         <v>98659</v>
@@ -24715,10 +24715,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>691071</v>
+        <v>691182</v>
       </c>
       <c r="R220" t="n">
-        <v>7401097</v>
+        <v>7400878</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24745,22 +24745,22 @@
       </c>
       <c r="Y220" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24791,32 +24791,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128960582</v>
+        <v>128960608</v>
       </c>
       <c r="B221" t="n">
-        <v>91787</v>
+        <v>78701</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24826,10 +24826,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>691723</v>
+        <v>691209</v>
       </c>
       <c r="R221" t="n">
-        <v>7400616</v>
+        <v>7400623</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24861,7 +24861,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24902,32 +24902,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128960608</v>
+        <v>128960582</v>
       </c>
       <c r="B222" t="n">
-        <v>78701</v>
+        <v>91787</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24937,10 +24937,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>691209</v>
+        <v>691723</v>
       </c>
       <c r="R222" t="n">
-        <v>7400623</v>
+        <v>7400616</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24972,7 +24972,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25124,10 +25124,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128960436</v>
+        <v>128960693</v>
       </c>
       <c r="B224" t="n">
-        <v>90152</v>
+        <v>78438</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25135,21 +25135,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4962</v>
+        <v>6437</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25159,10 +25159,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>691019</v>
+        <v>691595</v>
       </c>
       <c r="R224" t="n">
-        <v>7400845</v>
+        <v>7401115</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25194,7 +25194,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25235,10 +25235,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128960693</v>
+        <v>128960358</v>
       </c>
       <c r="B225" t="n">
-        <v>78438</v>
+        <v>79654</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25246,21 +25246,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25270,10 +25270,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>691595</v>
+        <v>691772</v>
       </c>
       <c r="R225" t="n">
-        <v>7401115</v>
+        <v>7400877</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25346,10 +25346,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128960366</v>
+        <v>128960436</v>
       </c>
       <c r="B226" t="n">
-        <v>79625</v>
+        <v>90152</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25357,21 +25357,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>229821</v>
+        <v>4962</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25381,10 +25381,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>691628</v>
+        <v>691019</v>
       </c>
       <c r="R226" t="n">
-        <v>7401071</v>
+        <v>7400845</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25416,7 +25416,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25426,7 +25426,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25457,32 +25457,32 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128960360</v>
+        <v>128960486</v>
       </c>
       <c r="B227" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25492,10 +25492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>691748</v>
+        <v>691497</v>
       </c>
       <c r="R227" t="n">
-        <v>7400820</v>
+        <v>7400703</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25568,32 +25568,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128960358</v>
+        <v>128960497</v>
       </c>
       <c r="B228" t="n">
-        <v>79654</v>
+        <v>98659</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25603,10 +25603,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>691772</v>
+        <v>691469</v>
       </c>
       <c r="R228" t="n">
-        <v>7400877</v>
+        <v>7401129</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25638,7 +25638,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25648,7 +25648,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25679,7 +25679,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128960455</v>
+        <v>128960451</v>
       </c>
       <c r="B229" t="n">
         <v>98659</v>
@@ -25714,10 +25714,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>691615</v>
+        <v>691520</v>
       </c>
       <c r="R229" t="n">
-        <v>7400959</v>
+        <v>7401010</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25790,7 +25790,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128960451</v>
+        <v>128960455</v>
       </c>
       <c r="B230" t="n">
         <v>98659</v>
@@ -25825,10 +25825,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691520</v>
+        <v>691615</v>
       </c>
       <c r="R230" t="n">
-        <v>7401010</v>
+        <v>7400959</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25860,7 +25860,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -26012,32 +26012,32 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128960497</v>
+        <v>128960366</v>
       </c>
       <c r="B232" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E232" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26047,10 +26047,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>691469</v>
+        <v>691628</v>
       </c>
       <c r="R232" t="n">
-        <v>7401129</v>
+        <v>7401071</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26123,32 +26123,32 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128960486</v>
+        <v>128960360</v>
       </c>
       <c r="B233" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -26158,10 +26158,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>691497</v>
+        <v>691748</v>
       </c>
       <c r="R233" t="n">
-        <v>7400703</v>
+        <v>7400820</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26193,7 +26193,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26203,7 +26203,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26234,10 +26234,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128960368</v>
+        <v>128960409</v>
       </c>
       <c r="B234" t="n">
-        <v>79625</v>
+        <v>91476</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26245,21 +26245,21 @@
         </is>
       </c>
       <c r="E234" t="n">
-        <v>229821</v>
+        <v>112</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>691561</v>
+        <v>691353</v>
       </c>
       <c r="R234" t="n">
-        <v>7401113</v>
+        <v>7400865</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26304,7 +26304,7 @@
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
@@ -26314,7 +26314,7 @@
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26345,10 +26345,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128960393</v>
+        <v>128960596</v>
       </c>
       <c r="B235" t="n">
-        <v>92844</v>
+        <v>78701</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26356,21 +26356,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26380,10 +26380,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>690878</v>
+        <v>691802</v>
       </c>
       <c r="R235" t="n">
-        <v>7400754</v>
+        <v>7400967</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26410,22 +26410,22 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26456,10 +26456,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128960345</v>
+        <v>128960545</v>
       </c>
       <c r="B236" t="n">
-        <v>91448</v>
+        <v>79114</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26467,21 +26467,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3242</v>
+        <v>864</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -26491,10 +26491,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>691005</v>
+        <v>691266</v>
       </c>
       <c r="R236" t="n">
-        <v>7401070</v>
+        <v>7400806</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26521,22 +26521,22 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26567,32 +26567,32 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128960653</v>
+        <v>128960345</v>
       </c>
       <c r="B237" t="n">
-        <v>92819</v>
+        <v>91448</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -26602,10 +26602,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>690703</v>
+        <v>691005</v>
       </c>
       <c r="R237" t="n">
-        <v>7400802</v>
+        <v>7401070</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -26647,7 +26647,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26678,10 +26678,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128960409</v>
+        <v>128960393</v>
       </c>
       <c r="B238" t="n">
-        <v>91476</v>
+        <v>92844</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26689,21 +26689,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>112</v>
+        <v>3100</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -26713,10 +26713,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>691353</v>
+        <v>690878</v>
       </c>
       <c r="R238" t="n">
-        <v>7400865</v>
+        <v>7400754</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26743,22 +26743,22 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26789,32 +26789,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128960596</v>
+        <v>128960653</v>
       </c>
       <c r="B239" t="n">
-        <v>78701</v>
+        <v>92819</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26824,10 +26824,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>691802</v>
+        <v>690703</v>
       </c>
       <c r="R239" t="n">
-        <v>7400967</v>
+        <v>7400802</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26854,22 +26854,22 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26900,10 +26900,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128960545</v>
+        <v>128960368</v>
       </c>
       <c r="B240" t="n">
-        <v>79114</v>
+        <v>79625</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26911,21 +26911,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>864</v>
+        <v>229821</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26935,10 +26935,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>691266</v>
+        <v>691561</v>
       </c>
       <c r="R240" t="n">
-        <v>7400806</v>
+        <v>7401113</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27677,32 +27677,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128960460</v>
+        <v>128960362</v>
       </c>
       <c r="B247" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -27712,10 +27712,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>691513</v>
+        <v>691425</v>
       </c>
       <c r="R247" t="n">
-        <v>7401038</v>
+        <v>7400943</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -27757,7 +27757,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27788,32 +27788,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128960362</v>
+        <v>128960460</v>
       </c>
       <c r="B248" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -27823,10 +27823,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>691425</v>
+        <v>691513</v>
       </c>
       <c r="R248" t="n">
-        <v>7400943</v>
+        <v>7401038</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -27858,7 +27858,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -27868,7 +27868,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -28010,32 +28010,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128960382</v>
+        <v>128960419</v>
       </c>
       <c r="B250" t="n">
-        <v>91801</v>
+        <v>92151</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>71</v>
+        <v>483</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28045,10 +28045,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>691067</v>
+        <v>690849</v>
       </c>
       <c r="R250" t="n">
-        <v>7401023</v>
+        <v>7400685</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28080,7 +28080,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28090,7 +28090,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28121,32 +28121,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128960419</v>
+        <v>128960382</v>
       </c>
       <c r="B251" t="n">
-        <v>92151</v>
+        <v>91801</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>483</v>
+        <v>71</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28156,10 +28156,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>690849</v>
+        <v>691067</v>
       </c>
       <c r="R251" t="n">
-        <v>7400685</v>
+        <v>7401023</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28191,7 +28191,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28201,7 +28201,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28343,7 +28343,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>128960381</v>
+        <v>128960380</v>
       </c>
       <c r="B253" t="n">
         <v>91801</v>
@@ -28378,10 +28378,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>691489</v>
+        <v>691721</v>
       </c>
       <c r="R253" t="n">
-        <v>7400750</v>
+        <v>7400617</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -28413,7 +28413,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -28423,7 +28423,7 @@
       </c>
       <c r="AB253" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD253" t="b">
@@ -28454,7 +28454,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>128960380</v>
+        <v>128960381</v>
       </c>
       <c r="B254" t="n">
         <v>91801</v>
@@ -28489,10 +28489,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>691721</v>
+        <v>691489</v>
       </c>
       <c r="R254" t="n">
-        <v>7400617</v>
+        <v>7400750</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -28524,7 +28524,7 @@
       </c>
       <c r="Z254" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
@@ -28534,7 +28534,7 @@
       </c>
       <c r="AB254" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD254" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128960549</v>
+        <v>128960696</v>
       </c>
       <c r="B3" t="n">
-        <v>92150</v>
+        <v>78442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5454</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691837</v>
+        <v>691640</v>
       </c>
       <c r="R3" t="n">
-        <v>7401375</v>
+        <v>7401329</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128960696</v>
+        <v>128960549</v>
       </c>
       <c r="B4" t="n">
-        <v>78438</v>
+        <v>92157</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>5454</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691640</v>
+        <v>691837</v>
       </c>
       <c r="R4" t="n">
-        <v>7401329</v>
+        <v>7401375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128960450</v>
+        <v>128960691</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>78442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691723</v>
+        <v>691190</v>
       </c>
       <c r="R5" t="n">
-        <v>7401427</v>
+        <v>7401223</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,22 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,32 +1115,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128960524</v>
+        <v>128960372</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691395</v>
+        <v>691253</v>
       </c>
       <c r="R6" t="n">
-        <v>7401429</v>
+        <v>7401236</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,32 +1226,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128960372</v>
+        <v>128960450</v>
       </c>
       <c r="B7" t="n">
-        <v>79625</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691253</v>
+        <v>691723</v>
       </c>
       <c r="R7" t="n">
-        <v>7401236</v>
+        <v>7401427</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128960691</v>
+        <v>128960524</v>
       </c>
       <c r="B8" t="n">
-        <v>78438</v>
+        <v>98669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691190</v>
+        <v>691395</v>
       </c>
       <c r="R8" t="n">
-        <v>7401223</v>
+        <v>7401429</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,32 +1448,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128960426</v>
+        <v>128960670</v>
       </c>
       <c r="B9" t="n">
-        <v>98548</v>
+        <v>92826</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>233</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691727</v>
+        <v>691851</v>
       </c>
       <c r="R9" t="n">
-        <v>7401372</v>
+        <v>7401441</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128960616</v>
+        <v>128960343</v>
       </c>
       <c r="B10" t="n">
-        <v>78701</v>
+        <v>91454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1570,21 +1570,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691854</v>
+        <v>691612</v>
       </c>
       <c r="R10" t="n">
-        <v>7401445</v>
+        <v>7401171</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,32 +1670,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128960670</v>
+        <v>128960426</v>
       </c>
       <c r="B11" t="n">
-        <v>92819</v>
+        <v>98558</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>233</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691851</v>
+        <v>691727</v>
       </c>
       <c r="R11" t="n">
-        <v>7401441</v>
+        <v>7401372</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128960689</v>
+        <v>128960616</v>
       </c>
       <c r="B12" t="n">
-        <v>78438</v>
+        <v>78705</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691341</v>
+        <v>691854</v>
       </c>
       <c r="R12" t="n">
-        <v>7401206</v>
+        <v>7401445</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,22 +1846,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128960343</v>
+        <v>128960689</v>
       </c>
       <c r="B13" t="n">
-        <v>91448</v>
+        <v>78442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3242</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691612</v>
+        <v>691341</v>
       </c>
       <c r="R13" t="n">
-        <v>7401171</v>
+        <v>7401206</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2003,10 +2003,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128960544</v>
+        <v>128960498</v>
       </c>
       <c r="B14" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691695</v>
+        <v>691438</v>
       </c>
       <c r="R14" t="n">
-        <v>7401360</v>
+        <v>7401141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2068,22 +2068,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>08:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2114,10 +2114,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128960498</v>
+        <v>128960544</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691438</v>
+        <v>691695</v>
       </c>
       <c r="R15" t="n">
-        <v>7401141</v>
+        <v>7401360</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2179,22 +2179,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:28</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2225,10 +2225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128960618</v>
+        <v>128960348</v>
       </c>
       <c r="B16" t="n">
-        <v>78701</v>
+        <v>91454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691741</v>
+        <v>691730</v>
       </c>
       <c r="R16" t="n">
-        <v>7401356</v>
+        <v>7401383</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2339,7 +2339,7 @@
         <v>128960433</v>
       </c>
       <c r="B17" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128960348</v>
+        <v>128960618</v>
       </c>
       <c r="B18" t="n">
-        <v>91448</v>
+        <v>78705</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,21 +2458,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691730</v>
+        <v>691741</v>
       </c>
       <c r="R18" t="n">
-        <v>7401383</v>
+        <v>7401356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128960519</v>
+        <v>128960542</v>
       </c>
       <c r="B19" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691230</v>
+        <v>691733</v>
       </c>
       <c r="R19" t="n">
-        <v>7401270</v>
+        <v>7401377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,10 +2669,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128960542</v>
+        <v>128960519</v>
       </c>
       <c r="B20" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691733</v>
+        <v>691230</v>
       </c>
       <c r="R20" t="n">
-        <v>7401377</v>
+        <v>7401270</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2783,7 +2783,7 @@
         <v>128960673</v>
       </c>
       <c r="B21" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>128960379</v>
       </c>
       <c r="B22" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3002,10 +3002,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128960423</v>
+        <v>128960539</v>
       </c>
       <c r="B23" t="n">
-        <v>98548</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,21 +3013,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>233</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691723</v>
+        <v>691733</v>
       </c>
       <c r="R23" t="n">
-        <v>7401406</v>
+        <v>7401349</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,22 +3067,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,32 +3113,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128960688</v>
+        <v>128960541</v>
       </c>
       <c r="B24" t="n">
-        <v>78043</v>
+        <v>98669</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691253</v>
+        <v>691727</v>
       </c>
       <c r="R24" t="n">
-        <v>7401236</v>
+        <v>7401372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3224,32 +3224,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128960539</v>
+        <v>128960373</v>
       </c>
       <c r="B25" t="n">
-        <v>98659</v>
+        <v>79629</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691733</v>
+        <v>691245</v>
       </c>
       <c r="R25" t="n">
-        <v>7401349</v>
+        <v>7401304</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,32 +3335,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128960541</v>
+        <v>128960688</v>
       </c>
       <c r="B26" t="n">
-        <v>98659</v>
+        <v>78047</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691727</v>
+        <v>691253</v>
       </c>
       <c r="R26" t="n">
-        <v>7401372</v>
+        <v>7401236</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,32 +3446,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128960373</v>
+        <v>128960423</v>
       </c>
       <c r="B27" t="n">
-        <v>79625</v>
+        <v>98558</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>233</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691245</v>
+        <v>691723</v>
       </c>
       <c r="R27" t="n">
-        <v>7401304</v>
+        <v>7401406</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3557,32 +3557,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128960573</v>
+        <v>128960400</v>
       </c>
       <c r="B28" t="n">
-        <v>91687</v>
+        <v>92443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1503</v>
+        <v>4745</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691704</v>
+        <v>691245</v>
       </c>
       <c r="R28" t="n">
-        <v>7401335</v>
+        <v>7401292</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3671,7 +3671,7 @@
         <v>128960666</v>
       </c>
       <c r="B29" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3779,32 +3779,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128960400</v>
+        <v>128960573</v>
       </c>
       <c r="B30" t="n">
-        <v>92436</v>
+        <v>91694</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4745</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691245</v>
+        <v>691704</v>
       </c>
       <c r="R30" t="n">
-        <v>7401292</v>
+        <v>7401335</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3893,7 +3893,7 @@
         <v>128960454</v>
       </c>
       <c r="B31" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128960540</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,32 +4112,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128960551</v>
+        <v>128960675</v>
       </c>
       <c r="B33" t="n">
-        <v>92150</v>
+        <v>92826</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5454</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691848</v>
+        <v>691653</v>
       </c>
       <c r="R33" t="n">
-        <v>7401397</v>
+        <v>7401394</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4223,10 +4223,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128960614</v>
+        <v>128960551</v>
       </c>
       <c r="B34" t="n">
-        <v>78701</v>
+        <v>92157</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4234,21 +4234,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>353</v>
+        <v>5454</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691275</v>
+        <v>691848</v>
       </c>
       <c r="R34" t="n">
-        <v>7401328</v>
+        <v>7401397</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4334,32 +4334,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128960675</v>
+        <v>128960614</v>
       </c>
       <c r="B35" t="n">
-        <v>92819</v>
+        <v>78705</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4369,10 +4369,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>691653</v>
+        <v>691275</v>
       </c>
       <c r="R35" t="n">
-        <v>7401394</v>
+        <v>7401328</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4448,7 +4448,7 @@
         <v>128960522</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4556,32 +4556,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128960424</v>
+        <v>128960686</v>
       </c>
       <c r="B37" t="n">
-        <v>98548</v>
+        <v>78047</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>233</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691756</v>
+        <v>691639</v>
       </c>
       <c r="R37" t="n">
-        <v>7401403</v>
+        <v>7401330</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,10 +4667,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128960561</v>
+        <v>128960424</v>
       </c>
       <c r="B38" t="n">
-        <v>91687</v>
+        <v>98558</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>233</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691650</v>
+        <v>691756</v>
       </c>
       <c r="R38" t="n">
-        <v>7401329</v>
+        <v>7401403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,10 +4778,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128960571</v>
+        <v>128960561</v>
       </c>
       <c r="B39" t="n">
-        <v>91687</v>
+        <v>91694</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691659</v>
+        <v>691650</v>
       </c>
       <c r="R39" t="n">
-        <v>7401322</v>
+        <v>7401329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,32 +4889,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128960686</v>
+        <v>128960571</v>
       </c>
       <c r="B40" t="n">
-        <v>78043</v>
+        <v>91694</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691639</v>
+        <v>691659</v>
       </c>
       <c r="R40" t="n">
-        <v>7401330</v>
+        <v>7401322</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5003,7 +5003,7 @@
         <v>128960662</v>
       </c>
       <c r="B41" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128960527</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5225,7 +5225,7 @@
         <v>128960377</v>
       </c>
       <c r="B43" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5333,10 +5333,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128960422</v>
+        <v>128960431</v>
       </c>
       <c r="B44" t="n">
-        <v>98548</v>
+        <v>98558</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691717</v>
+        <v>691733</v>
       </c>
       <c r="R44" t="n">
-        <v>7401426</v>
+        <v>7401377</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5398,22 +5398,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5444,10 +5444,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128960431</v>
+        <v>128960422</v>
       </c>
       <c r="B45" t="n">
-        <v>98548</v>
+        <v>98558</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691733</v>
+        <v>691717</v>
       </c>
       <c r="R45" t="n">
-        <v>7401377</v>
+        <v>7401426</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5509,22 +5509,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5558,7 +5558,7 @@
         <v>128960695</v>
       </c>
       <c r="B46" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5666,32 +5666,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128960622</v>
+        <v>128960586</v>
       </c>
       <c r="B47" t="n">
-        <v>78701</v>
+        <v>91794</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691669</v>
+        <v>691611</v>
       </c>
       <c r="R47" t="n">
-        <v>7401313</v>
+        <v>7401170</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5731,22 +5731,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5777,32 +5777,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128960586</v>
+        <v>128960622</v>
       </c>
       <c r="B48" t="n">
-        <v>91787</v>
+        <v>78705</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691611</v>
+        <v>691669</v>
       </c>
       <c r="R48" t="n">
-        <v>7401170</v>
+        <v>7401313</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5842,22 +5842,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5891,7 +5891,7 @@
         <v>128960434</v>
       </c>
       <c r="B49" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5999,10 +5999,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128960531</v>
+        <v>128960458</v>
       </c>
       <c r="B50" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6034,10 +6034,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>691819</v>
+        <v>691458</v>
       </c>
       <c r="R50" t="n">
-        <v>7401453</v>
+        <v>7401226</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6064,22 +6064,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6110,10 +6110,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128960529</v>
+        <v>128960520</v>
       </c>
       <c r="B51" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6145,10 +6145,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>691510</v>
+        <v>691345</v>
       </c>
       <c r="R51" t="n">
-        <v>7401400</v>
+        <v>7401412</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6221,10 +6221,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128960458</v>
+        <v>128960531</v>
       </c>
       <c r="B52" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6256,10 +6256,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>691458</v>
+        <v>691819</v>
       </c>
       <c r="R52" t="n">
-        <v>7401226</v>
+        <v>7401453</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6286,22 +6286,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6332,10 +6332,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128960520</v>
+        <v>128960529</v>
       </c>
       <c r="B53" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6367,10 +6367,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>691345</v>
+        <v>691510</v>
       </c>
       <c r="R53" t="n">
-        <v>7401412</v>
+        <v>7401400</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6402,7 +6402,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6412,7 +6412,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6446,7 +6446,7 @@
         <v>128960617</v>
       </c>
       <c r="B54" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>128960457</v>
       </c>
       <c r="B55" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>128960664</v>
       </c>
       <c r="B56" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128960395</v>
+        <v>128960533</v>
       </c>
       <c r="B57" t="n">
-        <v>92436</v>
+        <v>98669</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691427</v>
+        <v>691773</v>
       </c>
       <c r="R57" t="n">
-        <v>7401226</v>
+        <v>7401347</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6841,22 +6841,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6890,7 +6890,7 @@
         <v>128960534</v>
       </c>
       <c r="B58" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6998,32 +6998,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128960533</v>
+        <v>128960395</v>
       </c>
       <c r="B59" t="n">
-        <v>98659</v>
+        <v>92443</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691773</v>
+        <v>691427</v>
       </c>
       <c r="R59" t="n">
-        <v>7401347</v>
+        <v>7401226</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7063,22 +7063,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7112,7 +7112,7 @@
         <v>128960535</v>
       </c>
       <c r="B60" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>128960613</v>
       </c>
       <c r="B61" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7334,7 +7334,7 @@
         <v>128960401</v>
       </c>
       <c r="B62" t="n">
-        <v>92436</v>
+        <v>92443</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>128960376</v>
       </c>
       <c r="B63" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7556,7 +7556,7 @@
         <v>128960350</v>
       </c>
       <c r="B64" t="n">
-        <v>91701</v>
+        <v>91708</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7664,10 +7664,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128960624</v>
+        <v>128960347</v>
       </c>
       <c r="B65" t="n">
-        <v>78701</v>
+        <v>91454</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7675,21 +7675,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>691444</v>
+        <v>691668</v>
       </c>
       <c r="R65" t="n">
-        <v>7401426</v>
+        <v>7401306</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7775,32 +7775,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128960347</v>
+        <v>128960536</v>
       </c>
       <c r="B66" t="n">
-        <v>91448</v>
+        <v>98669</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>691668</v>
+        <v>691728</v>
       </c>
       <c r="R66" t="n">
-        <v>7401306</v>
+        <v>7401388</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128960692</v>
+        <v>128960518</v>
       </c>
       <c r="B67" t="n">
-        <v>78438</v>
+        <v>98669</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691580</v>
+        <v>691236</v>
       </c>
       <c r="R67" t="n">
-        <v>7401425</v>
+        <v>7401263</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7997,32 +7997,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128960518</v>
+        <v>128960624</v>
       </c>
       <c r="B68" t="n">
-        <v>98659</v>
+        <v>78705</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>691236</v>
+        <v>691444</v>
       </c>
       <c r="R68" t="n">
-        <v>7401263</v>
+        <v>7401426</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8108,32 +8108,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128960536</v>
+        <v>128960692</v>
       </c>
       <c r="B69" t="n">
-        <v>98659</v>
+        <v>78442</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>691728</v>
+        <v>691580</v>
       </c>
       <c r="R69" t="n">
-        <v>7401388</v>
+        <v>7401425</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8219,32 +8219,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128960364</v>
+        <v>128960537</v>
       </c>
       <c r="B70" t="n">
-        <v>79625</v>
+        <v>98669</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>691580</v>
+        <v>691719</v>
       </c>
       <c r="R70" t="n">
-        <v>7401428</v>
+        <v>7401396</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8330,10 +8330,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128960537</v>
+        <v>128960452</v>
       </c>
       <c r="B71" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8365,10 +8365,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>691719</v>
+        <v>691486</v>
       </c>
       <c r="R71" t="n">
-        <v>7401396</v>
+        <v>7401432</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8441,32 +8441,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128960452</v>
+        <v>128960364</v>
       </c>
       <c r="B72" t="n">
-        <v>98659</v>
+        <v>79629</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>691486</v>
+        <v>691580</v>
       </c>
       <c r="R72" t="n">
-        <v>7401432</v>
+        <v>7401428</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8555,7 +8555,7 @@
         <v>128960386</v>
       </c>
       <c r="B73" t="n">
-        <v>91801</v>
+        <v>91808</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>128960387</v>
       </c>
       <c r="B74" t="n">
-        <v>86926</v>
+        <v>86930</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>128960443</v>
       </c>
       <c r="B75" t="n">
-        <v>91789</v>
+        <v>91796</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>128960413</v>
       </c>
       <c r="B76" t="n">
-        <v>88782</v>
+        <v>88786</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -13913,10 +13913,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128960650</v>
+        <v>128960405</v>
       </c>
       <c r="B123" t="n">
-        <v>92819</v>
+        <v>80173</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13924,21 +13924,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>690728</v>
+        <v>690835</v>
       </c>
       <c r="R123" t="n">
-        <v>7400633</v>
+        <v>7400894</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128960646</v>
+        <v>128960650</v>
       </c>
       <c r="B124" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>691445</v>
+        <v>690728</v>
       </c>
       <c r="R124" t="n">
-        <v>7400907</v>
+        <v>7400633</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14089,22 +14089,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14135,32 +14135,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128960399</v>
+        <v>128960646</v>
       </c>
       <c r="B125" t="n">
-        <v>92436</v>
+        <v>92826</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>690819</v>
+        <v>691445</v>
       </c>
       <c r="R125" t="n">
-        <v>7400882</v>
+        <v>7400907</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,22 +14200,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14246,32 +14246,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128960405</v>
+        <v>128960476</v>
       </c>
       <c r="B126" t="n">
-        <v>80169</v>
+        <v>98669</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>690835</v>
+        <v>691094</v>
       </c>
       <c r="R126" t="n">
-        <v>7400894</v>
+        <v>7400693</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14311,22 +14311,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14357,32 +14357,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128960476</v>
+        <v>128960399</v>
       </c>
       <c r="B127" t="n">
-        <v>98659</v>
+        <v>92443</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>691094</v>
+        <v>690819</v>
       </c>
       <c r="R127" t="n">
-        <v>7400693</v>
+        <v>7400882</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14422,22 +14422,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14471,7 +14471,7 @@
         <v>128960503</v>
       </c>
       <c r="B128" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14582,7 +14582,7 @@
         <v>128960370</v>
       </c>
       <c r="B129" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14690,10 +14690,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128960369</v>
+        <v>128960354</v>
       </c>
       <c r="B130" t="n">
-        <v>79625</v>
+        <v>96915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14701,21 +14701,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>53</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>691330</v>
+        <v>691515</v>
       </c>
       <c r="R130" t="n">
-        <v>7400743</v>
+        <v>7401011</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14760,7 +14760,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14770,7 +14770,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14801,32 +14801,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128960496</v>
+        <v>128960626</v>
       </c>
       <c r="B131" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14836,10 +14836,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>691471</v>
+        <v>691772</v>
       </c>
       <c r="R131" t="n">
-        <v>7401095</v>
+        <v>7400877</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14871,7 +14871,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14881,7 +14881,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14912,32 +14912,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128960511</v>
+        <v>128960629</v>
       </c>
       <c r="B132" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>690875</v>
+        <v>691778</v>
       </c>
       <c r="R132" t="n">
-        <v>7400942</v>
+        <v>7401031</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14977,22 +14977,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15023,32 +15023,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128960464</v>
+        <v>128960432</v>
       </c>
       <c r="B133" t="n">
-        <v>98659</v>
+        <v>93022</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15058,10 +15058,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>691251</v>
+        <v>690722</v>
       </c>
       <c r="R133" t="n">
-        <v>7400808</v>
+        <v>7400676</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15088,22 +15088,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15134,32 +15134,32 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128960488</v>
+        <v>128960378</v>
       </c>
       <c r="B134" t="n">
-        <v>98659</v>
+        <v>90562</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>691464</v>
+        <v>690754</v>
       </c>
       <c r="R134" t="n">
-        <v>7400741</v>
+        <v>7400823</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15199,22 +15199,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15248,7 +15248,7 @@
         <v>128960556</v>
       </c>
       <c r="B135" t="n">
-        <v>91540</v>
+        <v>91547</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15356,32 +15356,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128960378</v>
+        <v>128960511</v>
       </c>
       <c r="B136" t="n">
-        <v>90558</v>
+        <v>98669</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15391,10 +15391,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>690754</v>
+        <v>690875</v>
       </c>
       <c r="R136" t="n">
-        <v>7400823</v>
+        <v>7400942</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15426,7 +15426,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15436,7 +15436,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15467,32 +15467,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128960626</v>
+        <v>128960488</v>
       </c>
       <c r="B137" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15502,10 +15502,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>691772</v>
+        <v>691464</v>
       </c>
       <c r="R137" t="n">
-        <v>7400877</v>
+        <v>7400741</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15578,32 +15578,32 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128960629</v>
+        <v>128960464</v>
       </c>
       <c r="B138" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15613,10 +15613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>691778</v>
+        <v>691251</v>
       </c>
       <c r="R138" t="n">
-        <v>7401031</v>
+        <v>7400808</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15648,7 +15648,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15658,7 +15658,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15689,32 +15689,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128960402</v>
+        <v>128960496</v>
       </c>
       <c r="B139" t="n">
-        <v>92845</v>
+        <v>98669</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15724,10 +15724,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>690717</v>
+        <v>691471</v>
       </c>
       <c r="R139" t="n">
-        <v>7400812</v>
+        <v>7401095</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15754,22 +15754,22 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15800,10 +15800,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128960354</v>
+        <v>128960369</v>
       </c>
       <c r="B140" t="n">
-        <v>96905</v>
+        <v>79629</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15811,21 +15811,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>53</v>
+        <v>229821</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>691515</v>
+        <v>691330</v>
       </c>
       <c r="R140" t="n">
-        <v>7401011</v>
+        <v>7400743</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15911,10 +15911,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128960432</v>
+        <v>128960402</v>
       </c>
       <c r="B141" t="n">
-        <v>93014</v>
+        <v>92852</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15922,21 +15922,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2079</v>
+        <v>5448</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15946,10 +15946,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>690722</v>
+        <v>690717</v>
       </c>
       <c r="R141" t="n">
-        <v>7400676</v>
+        <v>7400812</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15981,7 +15981,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16022,32 +16022,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128960479</v>
+        <v>128960414</v>
       </c>
       <c r="B142" t="n">
-        <v>98659</v>
+        <v>80145</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16057,10 +16057,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>691286</v>
+        <v>691163</v>
       </c>
       <c r="R142" t="n">
-        <v>7400554</v>
+        <v>7400622</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16133,10 +16133,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128960504</v>
+        <v>128960559</v>
       </c>
       <c r="B143" t="n">
-        <v>98659</v>
+        <v>91694</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>690949</v>
+        <v>691433</v>
       </c>
       <c r="R143" t="n">
-        <v>7400850</v>
+        <v>7400873</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16198,22 +16198,22 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16244,32 +16244,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128960480</v>
+        <v>128960642</v>
       </c>
       <c r="B144" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16279,10 +16279,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>691030</v>
+        <v>691479</v>
       </c>
       <c r="R144" t="n">
-        <v>7400688</v>
+        <v>7400776</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16314,7 +16314,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16355,32 +16355,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128960559</v>
+        <v>128960636</v>
       </c>
       <c r="B145" t="n">
-        <v>91687</v>
+        <v>92826</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16390,10 +16390,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>691433</v>
+        <v>691313</v>
       </c>
       <c r="R145" t="n">
-        <v>7400873</v>
+        <v>7400890</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16466,32 +16466,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128960414</v>
+        <v>128960479</v>
       </c>
       <c r="B146" t="n">
-        <v>80141</v>
+        <v>98669</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>691163</v>
+        <v>691286</v>
       </c>
       <c r="R146" t="n">
-        <v>7400622</v>
+        <v>7400554</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16577,32 +16577,32 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128960642</v>
+        <v>128960480</v>
       </c>
       <c r="B147" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16612,10 +16612,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>691479</v>
+        <v>691030</v>
       </c>
       <c r="R147" t="n">
-        <v>7400776</v>
+        <v>7400688</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16647,7 +16647,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16688,32 +16688,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128960636</v>
+        <v>128960504</v>
       </c>
       <c r="B148" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16723,10 +16723,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>691313</v>
+        <v>690949</v>
       </c>
       <c r="R148" t="n">
-        <v>7400890</v>
+        <v>7400850</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16753,22 +16753,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16802,7 +16802,7 @@
         <v>128960602</v>
       </c>
       <c r="B149" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>128960510</v>
       </c>
       <c r="B150" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17024,7 +17024,7 @@
         <v>128960683</v>
       </c>
       <c r="B151" t="n">
-        <v>80175</v>
+        <v>80179</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17135,7 +17135,7 @@
         <v>128960685</v>
       </c>
       <c r="B152" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>128960421</v>
       </c>
       <c r="B153" t="n">
-        <v>98548</v>
+        <v>98558</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17357,7 +17357,7 @@
         <v>128960465</v>
       </c>
       <c r="B154" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17465,32 +17465,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128960639</v>
+        <v>128960606</v>
       </c>
       <c r="B155" t="n">
-        <v>92819</v>
+        <v>78705</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17500,10 +17500,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>691173</v>
+        <v>691096</v>
       </c>
       <c r="R155" t="n">
-        <v>7400751</v>
+        <v>7400927</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17576,10 +17576,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128960634</v>
+        <v>128960639</v>
       </c>
       <c r="B156" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>691432</v>
+        <v>691173</v>
       </c>
       <c r="R156" t="n">
-        <v>7400884</v>
+        <v>7400751</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17687,32 +17687,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128960633</v>
+        <v>128960469</v>
       </c>
       <c r="B157" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17722,10 +17722,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>691476</v>
+        <v>691149</v>
       </c>
       <c r="R157" t="n">
-        <v>7400909</v>
+        <v>7400912</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17798,32 +17798,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128960394</v>
+        <v>128960468</v>
       </c>
       <c r="B158" t="n">
-        <v>92436</v>
+        <v>98669</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17833,10 +17833,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>691657</v>
+        <v>691175</v>
       </c>
       <c r="R158" t="n">
-        <v>7400847</v>
+        <v>7400884</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17909,32 +17909,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128960416</v>
+        <v>128960477</v>
       </c>
       <c r="B159" t="n">
-        <v>92831</v>
+        <v>98669</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17944,10 +17944,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>690733</v>
+        <v>691104</v>
       </c>
       <c r="R159" t="n">
-        <v>7400794</v>
+        <v>7400683</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17974,22 +17974,22 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18020,32 +18020,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128960357</v>
+        <v>128960634</v>
       </c>
       <c r="B160" t="n">
-        <v>79654</v>
+        <v>92826</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18055,10 +18055,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691748</v>
+        <v>691432</v>
       </c>
       <c r="R160" t="n">
-        <v>7400820</v>
+        <v>7400884</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18131,32 +18131,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128960365</v>
+        <v>128960633</v>
       </c>
       <c r="B161" t="n">
-        <v>79625</v>
+        <v>92826</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>691772</v>
+        <v>691476</v>
       </c>
       <c r="R161" t="n">
-        <v>7401045</v>
+        <v>7400909</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18242,32 +18242,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128960469</v>
+        <v>128960416</v>
       </c>
       <c r="B162" t="n">
-        <v>98659</v>
+        <v>92838</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>691149</v>
+        <v>690733</v>
       </c>
       <c r="R162" t="n">
-        <v>7400912</v>
+        <v>7400794</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18307,22 +18307,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18353,32 +18353,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128960477</v>
+        <v>128960357</v>
       </c>
       <c r="B163" t="n">
-        <v>98659</v>
+        <v>79658</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18388,10 +18388,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>691104</v>
+        <v>691748</v>
       </c>
       <c r="R163" t="n">
-        <v>7400683</v>
+        <v>7400820</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18464,32 +18464,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128960468</v>
+        <v>128960394</v>
       </c>
       <c r="B164" t="n">
-        <v>98659</v>
+        <v>92443</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18499,10 +18499,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>691175</v>
+        <v>691657</v>
       </c>
       <c r="R164" t="n">
-        <v>7400884</v>
+        <v>7400847</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18575,10 +18575,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128960606</v>
+        <v>128960365</v>
       </c>
       <c r="B165" t="n">
-        <v>78701</v>
+        <v>79629</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18586,21 +18586,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>353</v>
+        <v>229821</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18610,10 +18610,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>691096</v>
+        <v>691772</v>
       </c>
       <c r="R165" t="n">
-        <v>7400927</v>
+        <v>7401045</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18686,10 +18686,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128960620</v>
+        <v>128960397</v>
       </c>
       <c r="B166" t="n">
-        <v>78701</v>
+        <v>92443</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18697,21 +18697,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18721,10 +18721,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>691007</v>
+        <v>690679</v>
       </c>
       <c r="R166" t="n">
-        <v>7401068</v>
+        <v>7400680</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18797,32 +18797,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128960569</v>
+        <v>128960620</v>
       </c>
       <c r="B167" t="n">
-        <v>91687</v>
+        <v>78705</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1503</v>
+        <v>353</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18832,10 +18832,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691471</v>
+        <v>691007</v>
       </c>
       <c r="R167" t="n">
-        <v>7400861</v>
+        <v>7401068</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18862,22 +18862,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18908,32 +18908,32 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128960397</v>
+        <v>128960569</v>
       </c>
       <c r="B168" t="n">
-        <v>92436</v>
+        <v>91694</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4745</v>
+        <v>1503</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18943,10 +18943,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>690679</v>
+        <v>691471</v>
       </c>
       <c r="R168" t="n">
-        <v>7400680</v>
+        <v>7400861</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18973,22 +18973,22 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19019,10 +19019,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128960509</v>
+        <v>128960485</v>
       </c>
       <c r="B169" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19054,10 +19054,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>690841</v>
+        <v>691491</v>
       </c>
       <c r="R169" t="n">
-        <v>7400937</v>
+        <v>7400689</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19084,22 +19084,22 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19130,10 +19130,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128960485</v>
+        <v>128960508</v>
       </c>
       <c r="B170" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19165,10 +19165,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>691491</v>
+        <v>690820</v>
       </c>
       <c r="R170" t="n">
-        <v>7400689</v>
+        <v>7400917</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19195,22 +19195,22 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19241,10 +19241,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128960508</v>
+        <v>128960484</v>
       </c>
       <c r="B171" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>690820</v>
+        <v>691205</v>
       </c>
       <c r="R171" t="n">
-        <v>7400917</v>
+        <v>7400756</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19306,22 +19306,22 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19352,10 +19352,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128960515</v>
+        <v>128960509</v>
       </c>
       <c r="B172" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19387,10 +19387,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>691061</v>
+        <v>690841</v>
       </c>
       <c r="R172" t="n">
-        <v>7401094</v>
+        <v>7400937</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19463,10 +19463,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128960484</v>
+        <v>128960456</v>
       </c>
       <c r="B173" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691205</v>
+        <v>691641</v>
       </c>
       <c r="R173" t="n">
-        <v>7400756</v>
+        <v>7400939</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19543,7 +19543,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19574,10 +19574,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128960456</v>
+        <v>128960515</v>
       </c>
       <c r="B174" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19609,10 +19609,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>691641</v>
+        <v>691061</v>
       </c>
       <c r="R174" t="n">
-        <v>7400939</v>
+        <v>7401094</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19639,22 +19639,22 @@
       </c>
       <c r="Y174" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19685,32 +19685,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128960658</v>
+        <v>128960495</v>
       </c>
       <c r="B175" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19720,10 +19720,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>690788</v>
+        <v>691488</v>
       </c>
       <c r="R175" t="n">
-        <v>7400864</v>
+        <v>7401092</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19750,22 +19750,22 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19796,32 +19796,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128960406</v>
+        <v>128960475</v>
       </c>
       <c r="B176" t="n">
-        <v>80169</v>
+        <v>98669</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19831,10 +19831,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>691215</v>
+        <v>691050</v>
       </c>
       <c r="R176" t="n">
-        <v>7400790</v>
+        <v>7400705</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19907,10 +19907,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128960495</v>
+        <v>128960473</v>
       </c>
       <c r="B177" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19942,10 +19942,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>691488</v>
+        <v>690998</v>
       </c>
       <c r="R177" t="n">
-        <v>7401092</v>
+        <v>7400742</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20018,32 +20018,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128960475</v>
+        <v>128960406</v>
       </c>
       <c r="B178" t="n">
-        <v>98659</v>
+        <v>80173</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20053,10 +20053,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>691050</v>
+        <v>691215</v>
       </c>
       <c r="R178" t="n">
-        <v>7400705</v>
+        <v>7400790</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20129,32 +20129,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128960473</v>
+        <v>128960658</v>
       </c>
       <c r="B179" t="n">
-        <v>98659</v>
+        <v>92826</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>690998</v>
+        <v>690788</v>
       </c>
       <c r="R179" t="n">
-        <v>7400742</v>
+        <v>7400864</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20194,22 +20194,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20243,7 +20243,7 @@
         <v>128960439</v>
       </c>
       <c r="B180" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>128960598</v>
       </c>
       <c r="B181" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20465,7 +20465,7 @@
         <v>128960472</v>
       </c>
       <c r="B182" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>128960550</v>
       </c>
       <c r="B183" t="n">
-        <v>92150</v>
+        <v>92157</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20684,10 +20684,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>128960474</v>
+        <v>128960512</v>
       </c>
       <c r="B184" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20719,10 +20719,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>691032</v>
+        <v>691026</v>
       </c>
       <c r="R184" t="n">
-        <v>7400748</v>
+        <v>7401085</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20749,22 +20749,22 @@
       </c>
       <c r="Y184" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20798,7 +20798,7 @@
         <v>128960478</v>
       </c>
       <c r="B185" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>128960471</v>
       </c>
       <c r="B186" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>128960461</v>
       </c>
       <c r="B187" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21128,10 +21128,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>128960505</v>
+        <v>128960474</v>
       </c>
       <c r="B188" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21163,10 +21163,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>690992</v>
+        <v>691032</v>
       </c>
       <c r="R188" t="n">
-        <v>7400806</v>
+        <v>7400748</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21193,22 +21193,22 @@
       </c>
       <c r="Y188" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -21242,7 +21242,7 @@
         <v>128960470</v>
       </c>
       <c r="B189" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21350,10 +21350,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>128960512</v>
+        <v>128960505</v>
       </c>
       <c r="B190" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21385,10 +21385,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>691026</v>
+        <v>690992</v>
       </c>
       <c r="R190" t="n">
-        <v>7401085</v>
+        <v>7400806</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21420,7 +21420,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21464,7 +21464,7 @@
         <v>128960359</v>
       </c>
       <c r="B191" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>128960481</v>
       </c>
       <c r="B192" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>128960684</v>
       </c>
       <c r="B193" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21794,32 +21794,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128960342</v>
+        <v>128960644</v>
       </c>
       <c r="B194" t="n">
-        <v>91448</v>
+        <v>92826</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21829,10 +21829,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>691704</v>
+        <v>691471</v>
       </c>
       <c r="R194" t="n">
-        <v>7401045</v>
+        <v>7400823</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21905,32 +21905,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128960644</v>
+        <v>128960507</v>
       </c>
       <c r="B195" t="n">
-        <v>92819</v>
+        <v>98669</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21940,10 +21940,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>691471</v>
+        <v>690928</v>
       </c>
       <c r="R195" t="n">
-        <v>7400823</v>
+        <v>7400812</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21970,22 +21970,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22019,7 +22019,7 @@
         <v>128960493</v>
       </c>
       <c r="B196" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22127,10 +22127,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128960507</v>
+        <v>128960506</v>
       </c>
       <c r="B197" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22162,10 +22162,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>690928</v>
+        <v>690964</v>
       </c>
       <c r="R197" t="n">
-        <v>7400812</v>
+        <v>7400788</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22197,7 +22197,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -22207,7 +22207,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22238,32 +22238,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128960506</v>
+        <v>128960342</v>
       </c>
       <c r="B198" t="n">
-        <v>98659</v>
+        <v>91454</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22273,10 +22273,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>690964</v>
+        <v>691704</v>
       </c>
       <c r="R198" t="n">
-        <v>7400788</v>
+        <v>7401045</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22303,22 +22303,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22352,7 +22352,7 @@
         <v>128960641</v>
       </c>
       <c r="B199" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>128960631</v>
       </c>
       <c r="B200" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>128960396</v>
       </c>
       <c r="B201" t="n">
-        <v>92436</v>
+        <v>92443</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22682,10 +22682,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128960341</v>
+        <v>128960599</v>
       </c>
       <c r="B202" t="n">
-        <v>91448</v>
+        <v>78705</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22693,21 +22693,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22717,10 +22717,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>691820</v>
+        <v>691564</v>
       </c>
       <c r="R202" t="n">
-        <v>7400734</v>
+        <v>7401001</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22796,7 +22796,7 @@
         <v>128960578</v>
       </c>
       <c r="B203" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22907,7 +22907,7 @@
         <v>128960605</v>
       </c>
       <c r="B204" t="n">
-        <v>78701</v>
+        <v>78705</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23015,32 +23015,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128960599</v>
+        <v>128960661</v>
       </c>
       <c r="B205" t="n">
-        <v>78701</v>
+        <v>92826</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23050,10 +23050,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>691564</v>
+        <v>691007</v>
       </c>
       <c r="R205" t="n">
-        <v>7401001</v>
+        <v>7401047</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23080,22 +23080,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23126,32 +23126,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128960661</v>
+        <v>128960341</v>
       </c>
       <c r="B206" t="n">
-        <v>92819</v>
+        <v>91454</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23161,10 +23161,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>691007</v>
+        <v>691820</v>
       </c>
       <c r="R206" t="n">
-        <v>7401047</v>
+        <v>7400734</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23191,22 +23191,22 @@
       </c>
       <c r="Y206" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23240,7 +23240,7 @@
         <v>128960437</v>
       </c>
       <c r="B207" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23348,10 +23348,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128960463</v>
+        <v>128960459</v>
       </c>
       <c r="B208" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23383,10 +23383,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>691259</v>
+        <v>691498</v>
       </c>
       <c r="R208" t="n">
-        <v>7400802</v>
+        <v>7401073</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23459,10 +23459,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128960459</v>
+        <v>128960463</v>
       </c>
       <c r="B209" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23494,10 +23494,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>691498</v>
+        <v>691259</v>
       </c>
       <c r="R209" t="n">
-        <v>7401073</v>
+        <v>7400802</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23570,32 +23570,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128960611</v>
+        <v>128960483</v>
       </c>
       <c r="B210" t="n">
-        <v>78701</v>
+        <v>98669</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23605,10 +23605,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>690824</v>
+        <v>691042</v>
       </c>
       <c r="R210" t="n">
-        <v>7400642</v>
+        <v>7400691</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23635,22 +23635,22 @@
       </c>
       <c r="Y210" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23681,32 +23681,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128960587</v>
+        <v>128960371</v>
       </c>
       <c r="B211" t="n">
-        <v>91787</v>
+        <v>79629</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23716,10 +23716,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>691522</v>
+        <v>691493</v>
       </c>
       <c r="R211" t="n">
-        <v>7401008</v>
+        <v>7400837</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23751,7 +23751,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -23761,7 +23761,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23795,7 +23795,7 @@
         <v>128960687</v>
       </c>
       <c r="B212" t="n">
-        <v>78043</v>
+        <v>78047</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23903,10 +23903,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128960690</v>
+        <v>128960611</v>
       </c>
       <c r="B213" t="n">
-        <v>78438</v>
+        <v>78705</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23914,21 +23914,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23938,10 +23938,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>690817</v>
+        <v>690824</v>
       </c>
       <c r="R213" t="n">
-        <v>7400668</v>
+        <v>7400642</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23973,7 +23973,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23983,7 +23983,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24014,10 +24014,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128960483</v>
+        <v>128960587</v>
       </c>
       <c r="B214" t="n">
-        <v>98659</v>
+        <v>91794</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24025,21 +24025,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -24049,10 +24049,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>691042</v>
+        <v>691522</v>
       </c>
       <c r="R214" t="n">
-        <v>7400691</v>
+        <v>7401008</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24084,7 +24084,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -24094,7 +24094,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24125,10 +24125,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128960371</v>
+        <v>128960690</v>
       </c>
       <c r="B215" t="n">
-        <v>79625</v>
+        <v>78442</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24136,21 +24136,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24160,10 +24160,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>691493</v>
+        <v>690817</v>
       </c>
       <c r="R215" t="n">
-        <v>7400837</v>
+        <v>7400668</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24190,22 +24190,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24239,7 +24239,7 @@
         <v>128960655</v>
       </c>
       <c r="B216" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>128960344</v>
       </c>
       <c r="B217" t="n">
-        <v>91448</v>
+        <v>91454</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>128960489</v>
       </c>
       <c r="B218" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>128960513</v>
       </c>
       <c r="B219" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>128960467</v>
       </c>
       <c r="B220" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24791,32 +24791,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128960608</v>
+        <v>128960356</v>
       </c>
       <c r="B221" t="n">
-        <v>78701</v>
+        <v>91497</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24826,10 +24826,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>691209</v>
+        <v>691028</v>
       </c>
       <c r="R221" t="n">
-        <v>7400623</v>
+        <v>7400838</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24861,7 +24861,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24905,7 +24905,7 @@
         <v>128960582</v>
       </c>
       <c r="B222" t="n">
-        <v>91787</v>
+        <v>91794</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25013,32 +25013,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128960356</v>
+        <v>128960608</v>
       </c>
       <c r="B223" t="n">
-        <v>91491</v>
+        <v>78705</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25048,10 +25048,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>691028</v>
+        <v>691209</v>
       </c>
       <c r="R223" t="n">
-        <v>7400838</v>
+        <v>7400623</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25124,10 +25124,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128960693</v>
+        <v>128960436</v>
       </c>
       <c r="B224" t="n">
-        <v>78438</v>
+        <v>90156</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25135,21 +25135,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6437</v>
+        <v>4962</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25159,10 +25159,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>691595</v>
+        <v>691019</v>
       </c>
       <c r="R224" t="n">
-        <v>7401115</v>
+        <v>7400845</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25194,7 +25194,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25235,32 +25235,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128960358</v>
+        <v>128960455</v>
       </c>
       <c r="B225" t="n">
-        <v>79654</v>
+        <v>98669</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25270,10 +25270,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>691772</v>
+        <v>691615</v>
       </c>
       <c r="R225" t="n">
-        <v>7400877</v>
+        <v>7400959</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25346,32 +25346,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128960436</v>
+        <v>128960451</v>
       </c>
       <c r="B226" t="n">
-        <v>90152</v>
+        <v>98669</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25381,10 +25381,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>691019</v>
+        <v>691520</v>
       </c>
       <c r="R226" t="n">
-        <v>7400845</v>
+        <v>7401010</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25416,7 +25416,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25426,7 +25426,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25457,10 +25457,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128960486</v>
+        <v>128960487</v>
       </c>
       <c r="B227" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25492,10 +25492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>691497</v>
+        <v>691504</v>
       </c>
       <c r="R227" t="n">
-        <v>7400703</v>
+        <v>7400725</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25571,7 +25571,7 @@
         <v>128960497</v>
       </c>
       <c r="B228" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25679,10 +25679,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128960451</v>
+        <v>128960486</v>
       </c>
       <c r="B229" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25714,10 +25714,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>691520</v>
+        <v>691497</v>
       </c>
       <c r="R229" t="n">
-        <v>7401010</v>
+        <v>7400703</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25790,32 +25790,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128960455</v>
+        <v>128960693</v>
       </c>
       <c r="B230" t="n">
-        <v>98659</v>
+        <v>78442</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25825,10 +25825,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691615</v>
+        <v>691595</v>
       </c>
       <c r="R230" t="n">
-        <v>7400959</v>
+        <v>7401115</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25860,7 +25860,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25901,32 +25901,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128960487</v>
+        <v>128960358</v>
       </c>
       <c r="B231" t="n">
-        <v>98659</v>
+        <v>79658</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25936,10 +25936,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>691504</v>
+        <v>691772</v>
       </c>
       <c r="R231" t="n">
-        <v>7400725</v>
+        <v>7400877</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25971,7 +25971,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26015,7 +26015,7 @@
         <v>128960366</v>
       </c>
       <c r="B232" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>128960360</v>
       </c>
       <c r="B233" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26234,32 +26234,32 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128960409</v>
+        <v>128960653</v>
       </c>
       <c r="B234" t="n">
-        <v>91476</v>
+        <v>92826</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>691353</v>
+        <v>690703</v>
       </c>
       <c r="R234" t="n">
-        <v>7400865</v>
+        <v>7400802</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26299,22 +26299,22 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26345,10 +26345,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128960596</v>
+        <v>128960409</v>
       </c>
       <c r="B235" t="n">
-        <v>78701</v>
+        <v>91482</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26356,21 +26356,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>353</v>
+        <v>112</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26380,10 +26380,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>691802</v>
+        <v>691353</v>
       </c>
       <c r="R235" t="n">
-        <v>7400967</v>
+        <v>7400865</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26415,7 +26415,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26425,7 +26425,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26456,10 +26456,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128960545</v>
+        <v>128960596</v>
       </c>
       <c r="B236" t="n">
-        <v>79114</v>
+        <v>78705</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26467,21 +26467,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>864</v>
+        <v>353</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -26491,10 +26491,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>691266</v>
+        <v>691802</v>
       </c>
       <c r="R236" t="n">
-        <v>7400806</v>
+        <v>7400967</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26567,10 +26567,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128960345</v>
+        <v>128960393</v>
       </c>
       <c r="B237" t="n">
-        <v>91448</v>
+        <v>92851</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26578,21 +26578,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3242</v>
+        <v>3100</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -26602,10 +26602,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>691005</v>
+        <v>690878</v>
       </c>
       <c r="R237" t="n">
-        <v>7401070</v>
+        <v>7400754</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -26647,7 +26647,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26678,10 +26678,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128960393</v>
+        <v>128960345</v>
       </c>
       <c r="B238" t="n">
-        <v>92844</v>
+        <v>91454</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -26689,21 +26689,21 @@
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3100</v>
+        <v>3242</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -26713,10 +26713,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>690878</v>
+        <v>691005</v>
       </c>
       <c r="R238" t="n">
-        <v>7400754</v>
+        <v>7401070</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26748,7 +26748,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26789,32 +26789,32 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128960653</v>
+        <v>128960545</v>
       </c>
       <c r="B239" t="n">
-        <v>92819</v>
+        <v>79118</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26824,10 +26824,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>690703</v>
+        <v>691266</v>
       </c>
       <c r="R239" t="n">
-        <v>7400802</v>
+        <v>7400806</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26854,22 +26854,22 @@
       </c>
       <c r="Y239" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26903,7 +26903,7 @@
         <v>128960368</v>
       </c>
       <c r="B240" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27011,10 +27011,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128960580</v>
+        <v>128960563</v>
       </c>
       <c r="B241" t="n">
-        <v>91787</v>
+        <v>91694</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27022,21 +27022,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>65</v>
+        <v>1503</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27046,10 +27046,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>691495</v>
+        <v>691283</v>
       </c>
       <c r="R241" t="n">
-        <v>7400757</v>
+        <v>7400566</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27122,32 +27122,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128960563</v>
+        <v>128960363</v>
       </c>
       <c r="B242" t="n">
-        <v>91687</v>
+        <v>79629</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>1503</v>
+        <v>229821</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27157,10 +27157,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>691283</v>
+        <v>690997</v>
       </c>
       <c r="R242" t="n">
-        <v>7400566</v>
+        <v>7401042</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27187,22 +27187,22 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27233,10 +27233,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128960363</v>
+        <v>128960361</v>
       </c>
       <c r="B243" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27268,10 +27268,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>690997</v>
+        <v>691629</v>
       </c>
       <c r="R243" t="n">
-        <v>7401042</v>
+        <v>7400883</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27298,22 +27298,22 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27344,32 +27344,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128960361</v>
+        <v>128960580</v>
       </c>
       <c r="B244" t="n">
-        <v>79625</v>
+        <v>91794</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>229821</v>
+        <v>65</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27379,10 +27379,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>691629</v>
+        <v>691495</v>
       </c>
       <c r="R244" t="n">
-        <v>7400883</v>
+        <v>7400757</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27414,7 +27414,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27424,7 +27424,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27458,7 +27458,7 @@
         <v>128960628</v>
       </c>
       <c r="B245" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>128960398</v>
       </c>
       <c r="B246" t="n">
-        <v>92436</v>
+        <v>92443</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -27677,32 +27677,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128960362</v>
+        <v>128960460</v>
       </c>
       <c r="B247" t="n">
-        <v>79625</v>
+        <v>98669</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -27712,10 +27712,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>691425</v>
+        <v>691513</v>
       </c>
       <c r="R247" t="n">
-        <v>7400943</v>
+        <v>7401038</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27747,7 +27747,7 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -27757,7 +27757,7 @@
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27788,32 +27788,32 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>128960460</v>
+        <v>128960362</v>
       </c>
       <c r="B248" t="n">
-        <v>98659</v>
+        <v>79629</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -27823,10 +27823,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>691513</v>
+        <v>691425</v>
       </c>
       <c r="R248" t="n">
-        <v>7401038</v>
+        <v>7400943</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -27858,7 +27858,7 @@
       </c>
       <c r="Z248" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -27868,7 +27868,7 @@
       </c>
       <c r="AB248" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD248" t="b">
@@ -27902,7 +27902,7 @@
         <v>128960677</v>
       </c>
       <c r="B249" t="n">
-        <v>88777</v>
+        <v>88781</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28010,32 +28010,32 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>128960419</v>
+        <v>128960382</v>
       </c>
       <c r="B250" t="n">
-        <v>92151</v>
+        <v>91808</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>483</v>
+        <v>71</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Rostskinn</t>
+          <t>Urskogsporing</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Crustoderma dryinum</t>
+          <t>Fomitopsis infirma</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
+          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -28045,10 +28045,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>690849</v>
+        <v>691067</v>
       </c>
       <c r="R250" t="n">
-        <v>7400685</v>
+        <v>7401023</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -28080,7 +28080,7 @@
       </c>
       <c r="Z250" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -28090,7 +28090,7 @@
       </c>
       <c r="AB250" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="AD250" t="b">
@@ -28121,32 +28121,32 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>128960382</v>
+        <v>128960419</v>
       </c>
       <c r="B251" t="n">
-        <v>91801</v>
+        <v>92158</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>71</v>
+        <v>483</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Urskogsporing</t>
+          <t>Rostskinn</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Fomitopsis infirma</t>
+          <t>Crustoderma dryinum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Renvall &amp; Niemelä) Miettinen &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis) Parmasto</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -28156,10 +28156,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>691067</v>
+        <v>690849</v>
       </c>
       <c r="R251" t="n">
-        <v>7401023</v>
+        <v>7400685</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -28191,7 +28191,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -28201,7 +28201,7 @@
       </c>
       <c r="AB251" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD251" t="b">
@@ -28235,7 +28235,7 @@
         <v>128960678</v>
       </c>
       <c r="B252" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>128960380</v>
       </c>
       <c r="B253" t="n">
-        <v>91801</v>
+        <v>91808</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>128960381</v>
       </c>
       <c r="B254" t="n">
-        <v>91801</v>
+        <v>91808</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128960696</v>
+        <v>128960549</v>
       </c>
       <c r="B3" t="n">
-        <v>78442</v>
+        <v>92157</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>5454</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691640</v>
+        <v>691837</v>
       </c>
       <c r="R3" t="n">
-        <v>7401329</v>
+        <v>7401375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128960549</v>
+        <v>128960696</v>
       </c>
       <c r="B4" t="n">
-        <v>92157</v>
+        <v>78442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5454</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691837</v>
+        <v>691640</v>
       </c>
       <c r="R4" t="n">
-        <v>7401375</v>
+        <v>7401329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2780,32 +2780,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128960673</v>
+        <v>128960379</v>
       </c>
       <c r="B21" t="n">
-        <v>92826</v>
+        <v>90562</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691654</v>
+        <v>691278</v>
       </c>
       <c r="R21" t="n">
-        <v>7401356</v>
+        <v>7401369</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,32 +2891,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128960379</v>
+        <v>128960673</v>
       </c>
       <c r="B22" t="n">
-        <v>90562</v>
+        <v>92826</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691278</v>
+        <v>691654</v>
       </c>
       <c r="R22" t="n">
-        <v>7401369</v>
+        <v>7401356</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3002,32 +3002,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128960539</v>
+        <v>128960688</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>78047</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691733</v>
+        <v>691253</v>
       </c>
       <c r="R23" t="n">
-        <v>7401349</v>
+        <v>7401236</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,10 +3113,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128960541</v>
+        <v>128960423</v>
       </c>
       <c r="B24" t="n">
-        <v>98669</v>
+        <v>98558</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,21 +3124,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>233</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691727</v>
+        <v>691723</v>
       </c>
       <c r="R24" t="n">
-        <v>7401372</v>
+        <v>7401406</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3178,22 +3178,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,32 +3335,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128960688</v>
+        <v>128960539</v>
       </c>
       <c r="B26" t="n">
-        <v>78047</v>
+        <v>98669</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691253</v>
+        <v>691733</v>
       </c>
       <c r="R26" t="n">
-        <v>7401236</v>
+        <v>7401349</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,10 +3446,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128960423</v>
+        <v>128960541</v>
       </c>
       <c r="B27" t="n">
-        <v>98558</v>
+        <v>98669</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,21 +3457,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>233</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691723</v>
+        <v>691727</v>
       </c>
       <c r="R27" t="n">
-        <v>7401406</v>
+        <v>7401372</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3511,22 +3511,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3557,32 +3557,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128960400</v>
+        <v>128960666</v>
       </c>
       <c r="B28" t="n">
-        <v>92443</v>
+        <v>92826</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>691245</v>
+        <v>691773</v>
       </c>
       <c r="R28" t="n">
-        <v>7401292</v>
+        <v>7401444</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3637,7 +3637,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128960666</v>
+        <v>128960454</v>
       </c>
       <c r="B29" t="n">
-        <v>92826</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691773</v>
+        <v>691681</v>
       </c>
       <c r="R29" t="n">
-        <v>7401444</v>
+        <v>7401433</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3779,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128960573</v>
+        <v>128960540</v>
       </c>
       <c r="B30" t="n">
-        <v>91694</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691704</v>
+        <v>691741</v>
       </c>
       <c r="R30" t="n">
-        <v>7401335</v>
+        <v>7401356</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3890,10 +3890,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128960454</v>
+        <v>128960573</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>91694</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691681</v>
+        <v>691704</v>
       </c>
       <c r="R31" t="n">
-        <v>7401433</v>
+        <v>7401335</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,32 +4001,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128960540</v>
+        <v>128960400</v>
       </c>
       <c r="B32" t="n">
-        <v>98669</v>
+        <v>92443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691741</v>
+        <v>691245</v>
       </c>
       <c r="R32" t="n">
-        <v>7401356</v>
+        <v>7401292</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4556,32 +4556,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128960686</v>
+        <v>128960424</v>
       </c>
       <c r="B37" t="n">
-        <v>78047</v>
+        <v>98558</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>233</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691639</v>
+        <v>691756</v>
       </c>
       <c r="R37" t="n">
-        <v>7401330</v>
+        <v>7401403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,10 +4667,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128960424</v>
+        <v>128960561</v>
       </c>
       <c r="B38" t="n">
-        <v>98558</v>
+        <v>91694</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>233</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691756</v>
+        <v>691650</v>
       </c>
       <c r="R38" t="n">
-        <v>7401403</v>
+        <v>7401329</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,7 +4778,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128960561</v>
+        <v>128960571</v>
       </c>
       <c r="B39" t="n">
         <v>91694</v>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691650</v>
+        <v>691659</v>
       </c>
       <c r="R39" t="n">
-        <v>7401329</v>
+        <v>7401322</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,32 +4889,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128960571</v>
+        <v>128960686</v>
       </c>
       <c r="B40" t="n">
-        <v>91694</v>
+        <v>78047</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691659</v>
+        <v>691639</v>
       </c>
       <c r="R40" t="n">
-        <v>7401322</v>
+        <v>7401330</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,32 +5000,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128960662</v>
+        <v>128960431</v>
       </c>
       <c r="B41" t="n">
-        <v>92826</v>
+        <v>98558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>233</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691259</v>
+        <v>691733</v>
       </c>
       <c r="R41" t="n">
-        <v>7401348</v>
+        <v>7401377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128960527</v>
+        <v>128960422</v>
       </c>
       <c r="B42" t="n">
-        <v>98669</v>
+        <v>98558</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5122,21 +5122,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>233</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691373</v>
+        <v>691717</v>
       </c>
       <c r="R42" t="n">
-        <v>7401425</v>
+        <v>7401426</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5176,22 +5176,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128960377</v>
+        <v>128960662</v>
       </c>
       <c r="B43" t="n">
-        <v>79629</v>
+        <v>92826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691728</v>
+        <v>691259</v>
       </c>
       <c r="R43" t="n">
-        <v>7401382</v>
+        <v>7401348</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,32 +5333,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128960431</v>
+        <v>128960695</v>
       </c>
       <c r="B44" t="n">
-        <v>98558</v>
+        <v>78442</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>233</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691733</v>
+        <v>691255</v>
       </c>
       <c r="R44" t="n">
-        <v>7401377</v>
+        <v>7401234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5444,10 +5444,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128960422</v>
+        <v>128960527</v>
       </c>
       <c r="B45" t="n">
-        <v>98558</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5455,21 +5455,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>233</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691717</v>
+        <v>691373</v>
       </c>
       <c r="R45" t="n">
-        <v>7401426</v>
+        <v>7401425</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5509,22 +5509,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5555,10 +5555,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128960695</v>
+        <v>128960377</v>
       </c>
       <c r="B46" t="n">
-        <v>78442</v>
+        <v>79629</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,21 +5566,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691255</v>
+        <v>691728</v>
       </c>
       <c r="R46" t="n">
-        <v>7401234</v>
+        <v>7401382</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7664,10 +7664,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128960347</v>
+        <v>128960624</v>
       </c>
       <c r="B65" t="n">
-        <v>91454</v>
+        <v>78705</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7675,21 +7675,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>691668</v>
+        <v>691444</v>
       </c>
       <c r="R65" t="n">
-        <v>7401306</v>
+        <v>7401426</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7775,32 +7775,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128960536</v>
+        <v>128960692</v>
       </c>
       <c r="B66" t="n">
-        <v>98669</v>
+        <v>78442</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>691728</v>
+        <v>691580</v>
       </c>
       <c r="R66" t="n">
-        <v>7401388</v>
+        <v>7401425</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,32 +7886,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128960518</v>
+        <v>128960347</v>
       </c>
       <c r="B67" t="n">
-        <v>98669</v>
+        <v>91454</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691236</v>
+        <v>691668</v>
       </c>
       <c r="R67" t="n">
-        <v>7401263</v>
+        <v>7401306</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7997,32 +7997,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128960624</v>
+        <v>128960536</v>
       </c>
       <c r="B68" t="n">
-        <v>78705</v>
+        <v>98669</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>691444</v>
+        <v>691728</v>
       </c>
       <c r="R68" t="n">
-        <v>7401426</v>
+        <v>7401388</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8108,32 +8108,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128960692</v>
+        <v>128960518</v>
       </c>
       <c r="B69" t="n">
-        <v>78442</v>
+        <v>98669</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>691580</v>
+        <v>691236</v>
       </c>
       <c r="R69" t="n">
-        <v>7401425</v>
+        <v>7401263</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -15023,10 +15023,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128960432</v>
+        <v>128960378</v>
       </c>
       <c r="B133" t="n">
-        <v>93022</v>
+        <v>90562</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15034,21 +15034,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15058,10 +15058,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>690722</v>
+        <v>690754</v>
       </c>
       <c r="R133" t="n">
-        <v>7400676</v>
+        <v>7400823</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15093,7 +15093,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15103,7 +15103,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15134,10 +15134,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128960378</v>
+        <v>128960556</v>
       </c>
       <c r="B134" t="n">
-        <v>90562</v>
+        <v>91547</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15145,21 +15145,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>690754</v>
+        <v>691520</v>
       </c>
       <c r="R134" t="n">
-        <v>7400823</v>
+        <v>7401010</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15199,22 +15199,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15245,10 +15245,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128960556</v>
+        <v>128960402</v>
       </c>
       <c r="B135" t="n">
-        <v>91547</v>
+        <v>92852</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15256,21 +15256,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1204</v>
+        <v>5448</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>691520</v>
+        <v>690717</v>
       </c>
       <c r="R135" t="n">
-        <v>7401010</v>
+        <v>7400812</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15310,22 +15310,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15356,32 +15356,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128960511</v>
+        <v>128960369</v>
       </c>
       <c r="B136" t="n">
-        <v>98669</v>
+        <v>79629</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15391,10 +15391,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>690875</v>
+        <v>691330</v>
       </c>
       <c r="R136" t="n">
-        <v>7400942</v>
+        <v>7400743</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15421,22 +15421,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15467,32 +15467,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128960488</v>
+        <v>128960432</v>
       </c>
       <c r="B137" t="n">
-        <v>98669</v>
+        <v>93022</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>220787</v>
+        <v>2079</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15502,10 +15502,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>691464</v>
+        <v>690722</v>
       </c>
       <c r="R137" t="n">
-        <v>7400741</v>
+        <v>7400676</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15532,22 +15532,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15578,7 +15578,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128960464</v>
+        <v>128960511</v>
       </c>
       <c r="B138" t="n">
         <v>98669</v>
@@ -15613,10 +15613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>691251</v>
+        <v>690875</v>
       </c>
       <c r="R138" t="n">
-        <v>7400808</v>
+        <v>7400942</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15643,22 +15643,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15689,7 +15689,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128960496</v>
+        <v>128960488</v>
       </c>
       <c r="B139" t="n">
         <v>98669</v>
@@ -15724,10 +15724,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691471</v>
+        <v>691464</v>
       </c>
       <c r="R139" t="n">
-        <v>7401095</v>
+        <v>7400741</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15800,32 +15800,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128960369</v>
+        <v>128960464</v>
       </c>
       <c r="B140" t="n">
-        <v>79629</v>
+        <v>98669</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>691330</v>
+        <v>691251</v>
       </c>
       <c r="R140" t="n">
-        <v>7400743</v>
+        <v>7400808</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15911,32 +15911,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128960402</v>
+        <v>128960496</v>
       </c>
       <c r="B141" t="n">
-        <v>92852</v>
+        <v>98669</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15946,10 +15946,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>690717</v>
+        <v>691471</v>
       </c>
       <c r="R141" t="n">
-        <v>7400812</v>
+        <v>7401095</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15976,22 +15976,22 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -17576,32 +17576,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128960639</v>
+        <v>128960357</v>
       </c>
       <c r="B156" t="n">
-        <v>92826</v>
+        <v>79658</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>691173</v>
+        <v>691748</v>
       </c>
       <c r="R156" t="n">
-        <v>7400751</v>
+        <v>7400820</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17687,32 +17687,32 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128960469</v>
+        <v>128960394</v>
       </c>
       <c r="B157" t="n">
-        <v>98669</v>
+        <v>92443</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17722,10 +17722,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>691149</v>
+        <v>691657</v>
       </c>
       <c r="R157" t="n">
-        <v>7400912</v>
+        <v>7400847</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17798,32 +17798,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128960468</v>
+        <v>128960639</v>
       </c>
       <c r="B158" t="n">
-        <v>98669</v>
+        <v>92826</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17833,10 +17833,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>691175</v>
+        <v>691173</v>
       </c>
       <c r="R158" t="n">
-        <v>7400884</v>
+        <v>7400751</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17909,32 +17909,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128960477</v>
+        <v>128960634</v>
       </c>
       <c r="B159" t="n">
-        <v>98669</v>
+        <v>92826</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17944,10 +17944,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>691104</v>
+        <v>691432</v>
       </c>
       <c r="R159" t="n">
-        <v>7400683</v>
+        <v>7400884</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17979,7 +17979,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18020,7 +18020,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128960634</v>
+        <v>128960633</v>
       </c>
       <c r="B160" t="n">
         <v>92826</v>
@@ -18055,10 +18055,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691432</v>
+        <v>691476</v>
       </c>
       <c r="R160" t="n">
-        <v>7400884</v>
+        <v>7400909</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18131,10 +18131,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128960633</v>
+        <v>128960416</v>
       </c>
       <c r="B161" t="n">
-        <v>92826</v>
+        <v>92838</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18142,21 +18142,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>691476</v>
+        <v>690733</v>
       </c>
       <c r="R161" t="n">
-        <v>7400909</v>
+        <v>7400794</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18196,22 +18196,22 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18242,32 +18242,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128960416</v>
+        <v>128960469</v>
       </c>
       <c r="B162" t="n">
-        <v>92838</v>
+        <v>98669</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>690733</v>
+        <v>691149</v>
       </c>
       <c r="R162" t="n">
-        <v>7400794</v>
+        <v>7400912</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18307,22 +18307,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18353,32 +18353,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128960357</v>
+        <v>128960468</v>
       </c>
       <c r="B163" t="n">
-        <v>79658</v>
+        <v>98669</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18388,10 +18388,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>691748</v>
+        <v>691175</v>
       </c>
       <c r="R163" t="n">
-        <v>7400820</v>
+        <v>7400884</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18464,32 +18464,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128960394</v>
+        <v>128960477</v>
       </c>
       <c r="B164" t="n">
-        <v>92443</v>
+        <v>98669</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18499,10 +18499,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>691657</v>
+        <v>691104</v>
       </c>
       <c r="R164" t="n">
-        <v>7400847</v>
+        <v>7400683</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18534,7 +18534,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18544,7 +18544,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18686,10 +18686,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128960397</v>
+        <v>128960620</v>
       </c>
       <c r="B166" t="n">
-        <v>92443</v>
+        <v>78705</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18697,21 +18697,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4745</v>
+        <v>353</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18721,10 +18721,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>690679</v>
+        <v>691007</v>
       </c>
       <c r="R166" t="n">
-        <v>7400680</v>
+        <v>7401068</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18756,7 +18756,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18766,7 +18766,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18797,32 +18797,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128960620</v>
+        <v>128960485</v>
       </c>
       <c r="B167" t="n">
-        <v>78705</v>
+        <v>98669</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18832,10 +18832,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691007</v>
+        <v>691491</v>
       </c>
       <c r="R167" t="n">
-        <v>7401068</v>
+        <v>7400689</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18862,22 +18862,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18908,10 +18908,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128960569</v>
+        <v>128960508</v>
       </c>
       <c r="B168" t="n">
-        <v>91694</v>
+        <v>98669</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18919,21 +18919,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18943,10 +18943,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691471</v>
+        <v>690820</v>
       </c>
       <c r="R168" t="n">
-        <v>7400861</v>
+        <v>7400917</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18973,22 +18973,22 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19019,7 +19019,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128960485</v>
+        <v>128960484</v>
       </c>
       <c r="B169" t="n">
         <v>98669</v>
@@ -19054,10 +19054,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691491</v>
+        <v>691205</v>
       </c>
       <c r="R169" t="n">
-        <v>7400689</v>
+        <v>7400756</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19089,7 +19089,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19130,7 +19130,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128960508</v>
+        <v>128960509</v>
       </c>
       <c r="B170" t="n">
         <v>98669</v>
@@ -19165,10 +19165,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>690820</v>
+        <v>690841</v>
       </c>
       <c r="R170" t="n">
-        <v>7400917</v>
+        <v>7400937</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19200,7 +19200,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19241,7 +19241,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128960484</v>
+        <v>128960456</v>
       </c>
       <c r="B171" t="n">
         <v>98669</v>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>691205</v>
+        <v>691641</v>
       </c>
       <c r="R171" t="n">
-        <v>7400756</v>
+        <v>7400939</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19311,7 +19311,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19352,7 +19352,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128960509</v>
+        <v>128960515</v>
       </c>
       <c r="B172" t="n">
         <v>98669</v>
@@ -19387,10 +19387,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>690841</v>
+        <v>691061</v>
       </c>
       <c r="R172" t="n">
-        <v>7400937</v>
+        <v>7401094</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19463,10 +19463,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128960456</v>
+        <v>128960569</v>
       </c>
       <c r="B173" t="n">
-        <v>98669</v>
+        <v>91694</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19474,21 +19474,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691641</v>
+        <v>691471</v>
       </c>
       <c r="R173" t="n">
-        <v>7400939</v>
+        <v>7400861</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19543,7 +19543,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19574,32 +19574,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128960515</v>
+        <v>128960397</v>
       </c>
       <c r="B174" t="n">
-        <v>98669</v>
+        <v>92443</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19609,10 +19609,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>691061</v>
+        <v>690679</v>
       </c>
       <c r="R174" t="n">
-        <v>7401094</v>
+        <v>7400680</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19685,32 +19685,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128960495</v>
+        <v>128960406</v>
       </c>
       <c r="B175" t="n">
-        <v>98669</v>
+        <v>80173</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19720,10 +19720,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>691488</v>
+        <v>691215</v>
       </c>
       <c r="R175" t="n">
-        <v>7401092</v>
+        <v>7400790</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19755,7 +19755,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19796,7 +19796,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128960475</v>
+        <v>128960495</v>
       </c>
       <c r="B176" t="n">
         <v>98669</v>
@@ -19831,10 +19831,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>691050</v>
+        <v>691488</v>
       </c>
       <c r="R176" t="n">
-        <v>7400705</v>
+        <v>7401092</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19907,7 +19907,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128960473</v>
+        <v>128960475</v>
       </c>
       <c r="B177" t="n">
         <v>98669</v>
@@ -19942,10 +19942,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>690998</v>
+        <v>691050</v>
       </c>
       <c r="R177" t="n">
-        <v>7400742</v>
+        <v>7400705</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20018,32 +20018,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128960406</v>
+        <v>128960473</v>
       </c>
       <c r="B178" t="n">
-        <v>80173</v>
+        <v>98669</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20053,10 +20053,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>691215</v>
+        <v>690998</v>
       </c>
       <c r="R178" t="n">
-        <v>7400790</v>
+        <v>7400742</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20088,7 +20088,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20240,32 +20240,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128960439</v>
+        <v>128960472</v>
       </c>
       <c r="B180" t="n">
-        <v>90156</v>
+        <v>98669</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20275,10 +20275,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>690708</v>
+        <v>690998</v>
       </c>
       <c r="R180" t="n">
-        <v>7400815</v>
+        <v>7400789</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20305,22 +20305,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20462,32 +20462,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128960472</v>
+        <v>128960439</v>
       </c>
       <c r="B182" t="n">
-        <v>98669</v>
+        <v>90156</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>220787</v>
+        <v>4962</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20497,10 +20497,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>690998</v>
+        <v>690708</v>
       </c>
       <c r="R182" t="n">
-        <v>7400789</v>
+        <v>7400815</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20527,22 +20527,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -21683,32 +21683,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128960684</v>
+        <v>128960644</v>
       </c>
       <c r="B193" t="n">
-        <v>78047</v>
+        <v>92826</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21718,10 +21718,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>691442</v>
+        <v>691471</v>
       </c>
       <c r="R193" t="n">
-        <v>7400932</v>
+        <v>7400823</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21794,32 +21794,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128960644</v>
+        <v>128960342</v>
       </c>
       <c r="B194" t="n">
-        <v>92826</v>
+        <v>91454</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21829,10 +21829,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>691471</v>
+        <v>691704</v>
       </c>
       <c r="R194" t="n">
-        <v>7400823</v>
+        <v>7401045</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21905,32 +21905,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128960507</v>
+        <v>128960684</v>
       </c>
       <c r="B195" t="n">
-        <v>98669</v>
+        <v>78047</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21940,10 +21940,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>690928</v>
+        <v>691442</v>
       </c>
       <c r="R195" t="n">
-        <v>7400812</v>
+        <v>7400932</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21970,22 +21970,22 @@
       </c>
       <c r="Y195" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22016,7 +22016,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>128960493</v>
+        <v>128960507</v>
       </c>
       <c r="B196" t="n">
         <v>98669</v>
@@ -22051,10 +22051,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>691483</v>
+        <v>690928</v>
       </c>
       <c r="R196" t="n">
-        <v>7401085</v>
+        <v>7400812</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22081,22 +22081,22 @@
       </c>
       <c r="Y196" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -22127,7 +22127,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>128960506</v>
+        <v>128960493</v>
       </c>
       <c r="B197" t="n">
         <v>98669</v>
@@ -22162,10 +22162,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>690964</v>
+        <v>691483</v>
       </c>
       <c r="R197" t="n">
-        <v>7400788</v>
+        <v>7401085</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22192,22 +22192,22 @@
       </c>
       <c r="Y197" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -22238,32 +22238,32 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>128960342</v>
+        <v>128960506</v>
       </c>
       <c r="B198" t="n">
-        <v>91454</v>
+        <v>98669</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -22273,10 +22273,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>691704</v>
+        <v>690964</v>
       </c>
       <c r="R198" t="n">
-        <v>7401045</v>
+        <v>7400788</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22303,22 +22303,22 @@
       </c>
       <c r="Y198" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -23126,32 +23126,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128960341</v>
+        <v>128960459</v>
       </c>
       <c r="B206" t="n">
-        <v>91454</v>
+        <v>98669</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23161,10 +23161,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>691820</v>
+        <v>691498</v>
       </c>
       <c r="R206" t="n">
-        <v>7400734</v>
+        <v>7401073</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23196,7 +23196,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23237,32 +23237,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128960437</v>
+        <v>128960463</v>
       </c>
       <c r="B207" t="n">
-        <v>90156</v>
+        <v>98669</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23272,10 +23272,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>691225</v>
+        <v>691259</v>
       </c>
       <c r="R207" t="n">
-        <v>7400593</v>
+        <v>7400802</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23307,7 +23307,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23348,32 +23348,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128960459</v>
+        <v>128960341</v>
       </c>
       <c r="B208" t="n">
-        <v>98669</v>
+        <v>91454</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23383,10 +23383,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>691498</v>
+        <v>691820</v>
       </c>
       <c r="R208" t="n">
-        <v>7401073</v>
+        <v>7400734</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23459,32 +23459,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128960463</v>
+        <v>128960437</v>
       </c>
       <c r="B209" t="n">
-        <v>98669</v>
+        <v>90156</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>220787</v>
+        <v>4962</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23494,10 +23494,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>691259</v>
+        <v>691225</v>
       </c>
       <c r="R209" t="n">
-        <v>7400802</v>
+        <v>7400593</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -26234,32 +26234,32 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128960653</v>
+        <v>128960409</v>
       </c>
       <c r="B234" t="n">
-        <v>92826</v>
+        <v>91482</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4364</v>
+        <v>112</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>690703</v>
+        <v>691353</v>
       </c>
       <c r="R234" t="n">
-        <v>7400802</v>
+        <v>7400865</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26299,22 +26299,22 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26345,10 +26345,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128960409</v>
+        <v>128960596</v>
       </c>
       <c r="B235" t="n">
-        <v>91482</v>
+        <v>78705</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26356,21 +26356,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>112</v>
+        <v>353</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26380,10 +26380,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>691353</v>
+        <v>691802</v>
       </c>
       <c r="R235" t="n">
-        <v>7400865</v>
+        <v>7400967</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26415,7 +26415,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -26425,7 +26425,7 @@
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26456,32 +26456,32 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128960596</v>
+        <v>128960653</v>
       </c>
       <c r="B236" t="n">
-        <v>78705</v>
+        <v>92826</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -26491,10 +26491,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>691802</v>
+        <v>690703</v>
       </c>
       <c r="R236" t="n">
-        <v>7400967</v>
+        <v>7400802</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26521,22 +26521,22 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -27011,10 +27011,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>128960563</v>
+        <v>128960580</v>
       </c>
       <c r="B241" t="n">
-        <v>91694</v>
+        <v>91794</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27022,21 +27022,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>1503</v>
+        <v>65</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -27046,10 +27046,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>691283</v>
+        <v>691495</v>
       </c>
       <c r="R241" t="n">
-        <v>7400566</v>
+        <v>7400757</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -27081,7 +27081,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -27091,7 +27091,7 @@
       </c>
       <c r="AB241" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD241" t="b">
@@ -27122,32 +27122,32 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>128960363</v>
+        <v>128960563</v>
       </c>
       <c r="B242" t="n">
-        <v>79629</v>
+        <v>91694</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>229821</v>
+        <v>1503</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -27157,10 +27157,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>690997</v>
+        <v>691283</v>
       </c>
       <c r="R242" t="n">
-        <v>7401042</v>
+        <v>7400566</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -27187,22 +27187,22 @@
       </c>
       <c r="Y242" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z242" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA242" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB242" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD242" t="b">
@@ -27233,7 +27233,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>128960361</v>
+        <v>128960363</v>
       </c>
       <c r="B243" t="n">
         <v>79629</v>
@@ -27268,10 +27268,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>691629</v>
+        <v>690997</v>
       </c>
       <c r="R243" t="n">
-        <v>7400883</v>
+        <v>7401042</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -27298,22 +27298,22 @@
       </c>
       <c r="Y243" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB243" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD243" t="b">
@@ -27344,32 +27344,32 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>128960580</v>
+        <v>128960361</v>
       </c>
       <c r="B244" t="n">
-        <v>91794</v>
+        <v>79629</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>65</v>
+        <v>229821</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -27379,10 +27379,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>691495</v>
+        <v>691629</v>
       </c>
       <c r="R244" t="n">
-        <v>7400757</v>
+        <v>7400883</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -27414,7 +27414,7 @@
       </c>
       <c r="Z244" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA244" t="inlineStr">
@@ -27424,7 +27424,7 @@
       </c>
       <c r="AB244" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD244" t="b">
@@ -27455,32 +27455,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128960628</v>
+        <v>128960398</v>
       </c>
       <c r="B245" t="n">
-        <v>92826</v>
+        <v>92443</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>691884</v>
+        <v>690713</v>
       </c>
       <c r="R245" t="n">
-        <v>7401043</v>
+        <v>7400706</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27520,22 +27520,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27566,32 +27566,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128960398</v>
+        <v>128960628</v>
       </c>
       <c r="B246" t="n">
-        <v>92443</v>
+        <v>92826</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -27601,10 +27601,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>690713</v>
+        <v>691884</v>
       </c>
       <c r="R246" t="n">
-        <v>7400706</v>
+        <v>7401043</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27631,22 +27631,22 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD246" t="b">

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128960549</v>
+        <v>128960696</v>
       </c>
       <c r="B3" t="n">
-        <v>92157</v>
+        <v>78442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5454</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691837</v>
+        <v>691640</v>
       </c>
       <c r="R3" t="n">
-        <v>7401375</v>
+        <v>7401329</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128960696</v>
+        <v>128960549</v>
       </c>
       <c r="B4" t="n">
-        <v>78442</v>
+        <v>92164</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>5454</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691640</v>
+        <v>691837</v>
       </c>
       <c r="R4" t="n">
-        <v>7401329</v>
+        <v>7401375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128960691</v>
+        <v>128960450</v>
       </c>
       <c r="B5" t="n">
-        <v>78442</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691190</v>
+        <v>691723</v>
       </c>
       <c r="R5" t="n">
-        <v>7401223</v>
+        <v>7401427</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,22 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,32 +1115,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128960372</v>
+        <v>128960524</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691253</v>
+        <v>691395</v>
       </c>
       <c r="R6" t="n">
-        <v>7401236</v>
+        <v>7401429</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,32 +1226,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128960450</v>
+        <v>128960691</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>78442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691723</v>
+        <v>691190</v>
       </c>
       <c r="R7" t="n">
-        <v>7401427</v>
+        <v>7401223</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,22 +1291,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,32 +1337,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128960524</v>
+        <v>128960372</v>
       </c>
       <c r="B8" t="n">
-        <v>98669</v>
+        <v>79629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691395</v>
+        <v>691253</v>
       </c>
       <c r="R8" t="n">
-        <v>7401429</v>
+        <v>7401236</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,32 +1448,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128960670</v>
+        <v>128960616</v>
       </c>
       <c r="B9" t="n">
-        <v>92826</v>
+        <v>78705</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691851</v>
+        <v>691854</v>
       </c>
       <c r="R9" t="n">
-        <v>7401441</v>
+        <v>7401445</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,32 +1559,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128960343</v>
+        <v>128960426</v>
       </c>
       <c r="B10" t="n">
-        <v>91454</v>
+        <v>98565</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>233</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691612</v>
+        <v>691727</v>
       </c>
       <c r="R10" t="n">
-        <v>7401171</v>
+        <v>7401372</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1624,22 +1624,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,32 +1670,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128960426</v>
+        <v>128960670</v>
       </c>
       <c r="B11" t="n">
-        <v>98558</v>
+        <v>92833</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>233</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691727</v>
+        <v>691851</v>
       </c>
       <c r="R11" t="n">
-        <v>7401372</v>
+        <v>7401441</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,10 +1781,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128960616</v>
+        <v>128960689</v>
       </c>
       <c r="B12" t="n">
-        <v>78705</v>
+        <v>78442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1792,21 +1792,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691854</v>
+        <v>691341</v>
       </c>
       <c r="R12" t="n">
-        <v>7401445</v>
+        <v>7401206</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,22 +1846,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128960689</v>
+        <v>128960343</v>
       </c>
       <c r="B13" t="n">
-        <v>78442</v>
+        <v>91461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>3242</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691341</v>
+        <v>691612</v>
       </c>
       <c r="R13" t="n">
-        <v>7401206</v>
+        <v>7401171</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,7 +2006,7 @@
         <v>128960498</v>
       </c>
       <c r="B14" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>128960544</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128960348</v>
+        <v>128960618</v>
       </c>
       <c r="B16" t="n">
-        <v>91454</v>
+        <v>78705</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691730</v>
+        <v>691741</v>
       </c>
       <c r="R16" t="n">
-        <v>7401383</v>
+        <v>7401356</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,10 +2336,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128960433</v>
+        <v>128960348</v>
       </c>
       <c r="B17" t="n">
-        <v>93022</v>
+        <v>91461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,21 +2347,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2079</v>
+        <v>3242</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691276</v>
+        <v>691730</v>
       </c>
       <c r="R17" t="n">
-        <v>7401328</v>
+        <v>7401383</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,10 +2447,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128960618</v>
+        <v>128960433</v>
       </c>
       <c r="B18" t="n">
-        <v>78705</v>
+        <v>93029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2458,21 +2458,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691741</v>
+        <v>691276</v>
       </c>
       <c r="R18" t="n">
-        <v>7401356</v>
+        <v>7401328</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2561,7 +2561,7 @@
         <v>128960542</v>
       </c>
       <c r="B19" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
         <v>128960519</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>128960379</v>
       </c>
       <c r="B21" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>128960673</v>
       </c>
       <c r="B22" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3002,32 +3002,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128960688</v>
+        <v>128960539</v>
       </c>
       <c r="B23" t="n">
-        <v>78047</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691253</v>
+        <v>691733</v>
       </c>
       <c r="R23" t="n">
-        <v>7401236</v>
+        <v>7401349</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,10 +3113,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128960423</v>
+        <v>128960541</v>
       </c>
       <c r="B24" t="n">
-        <v>98558</v>
+        <v>98676</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3124,21 +3124,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>233</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691723</v>
+        <v>691727</v>
       </c>
       <c r="R24" t="n">
-        <v>7401406</v>
+        <v>7401372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3178,22 +3178,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128960539</v>
+        <v>128960423</v>
       </c>
       <c r="B26" t="n">
-        <v>98669</v>
+        <v>98565</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>233</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691733</v>
+        <v>691723</v>
       </c>
       <c r="R26" t="n">
-        <v>7401349</v>
+        <v>7401406</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,22 +3400,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,32 +3446,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128960541</v>
+        <v>128960688</v>
       </c>
       <c r="B27" t="n">
-        <v>98669</v>
+        <v>78047</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691727</v>
+        <v>691253</v>
       </c>
       <c r="R27" t="n">
-        <v>7401372</v>
+        <v>7401236</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3560,7 +3560,7 @@
         <v>128960666</v>
       </c>
       <c r="B28" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128960454</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>128960540</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>128960573</v>
       </c>
       <c r="B31" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128960400</v>
       </c>
       <c r="B32" t="n">
-        <v>92443</v>
+        <v>92450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,32 +4112,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128960675</v>
+        <v>128960551</v>
       </c>
       <c r="B33" t="n">
-        <v>92826</v>
+        <v>92164</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>5454</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691653</v>
+        <v>691848</v>
       </c>
       <c r="R33" t="n">
-        <v>7401394</v>
+        <v>7401397</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4223,32 +4223,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128960551</v>
+        <v>128960522</v>
       </c>
       <c r="B34" t="n">
-        <v>92157</v>
+        <v>98676</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5454</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691848</v>
+        <v>691354</v>
       </c>
       <c r="R34" t="n">
-        <v>7401397</v>
+        <v>7401418</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4445,32 +4445,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128960522</v>
+        <v>128960675</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691354</v>
+        <v>691653</v>
       </c>
       <c r="R36" t="n">
-        <v>7401418</v>
+        <v>7401394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,32 +4556,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128960424</v>
+        <v>128960686</v>
       </c>
       <c r="B37" t="n">
-        <v>98558</v>
+        <v>78047</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>233</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691756</v>
+        <v>691639</v>
       </c>
       <c r="R37" t="n">
-        <v>7401403</v>
+        <v>7401330</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,10 +4667,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128960561</v>
+        <v>128960424</v>
       </c>
       <c r="B38" t="n">
-        <v>91694</v>
+        <v>98565</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1503</v>
+        <v>233</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691650</v>
+        <v>691756</v>
       </c>
       <c r="R38" t="n">
-        <v>7401329</v>
+        <v>7401403</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,10 +4778,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128960571</v>
+        <v>128960561</v>
       </c>
       <c r="B39" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691659</v>
+        <v>691650</v>
       </c>
       <c r="R39" t="n">
-        <v>7401322</v>
+        <v>7401329</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4889,32 +4889,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128960686</v>
+        <v>128960571</v>
       </c>
       <c r="B40" t="n">
-        <v>78047</v>
+        <v>91701</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6487</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691639</v>
+        <v>691659</v>
       </c>
       <c r="R40" t="n">
-        <v>7401330</v>
+        <v>7401322</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5000,10 +5000,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128960431</v>
+        <v>128960422</v>
       </c>
       <c r="B41" t="n">
-        <v>98558</v>
+        <v>98565</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691733</v>
+        <v>691717</v>
       </c>
       <c r="R41" t="n">
-        <v>7401377</v>
+        <v>7401426</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5065,22 +5065,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,10 +5111,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128960422</v>
+        <v>128960431</v>
       </c>
       <c r="B42" t="n">
-        <v>98558</v>
+        <v>98565</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691717</v>
+        <v>691733</v>
       </c>
       <c r="R42" t="n">
-        <v>7401426</v>
+        <v>7401377</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5176,22 +5176,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128960662</v>
+        <v>128960695</v>
       </c>
       <c r="B43" t="n">
-        <v>92826</v>
+        <v>78442</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691259</v>
+        <v>691255</v>
       </c>
       <c r="R43" t="n">
-        <v>7401348</v>
+        <v>7401234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,32 +5333,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128960695</v>
+        <v>128960662</v>
       </c>
       <c r="B44" t="n">
-        <v>78442</v>
+        <v>92833</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691255</v>
+        <v>691259</v>
       </c>
       <c r="R44" t="n">
-        <v>7401234</v>
+        <v>7401348</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,7 +5447,7 @@
         <v>128960527</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5666,32 +5666,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128960586</v>
+        <v>128960622</v>
       </c>
       <c r="B47" t="n">
-        <v>91794</v>
+        <v>78705</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691611</v>
+        <v>691669</v>
       </c>
       <c r="R47" t="n">
-        <v>7401170</v>
+        <v>7401313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5731,22 +5731,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5777,32 +5777,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128960622</v>
+        <v>128960586</v>
       </c>
       <c r="B48" t="n">
-        <v>78705</v>
+        <v>91801</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691669</v>
+        <v>691611</v>
       </c>
       <c r="R48" t="n">
-        <v>7401313</v>
+        <v>7401170</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5842,22 +5842,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5891,7 +5891,7 @@
         <v>128960434</v>
       </c>
       <c r="B49" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6002,7 +6002,7 @@
         <v>128960458</v>
       </c>
       <c r="B50" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>128960520</v>
       </c>
       <c r="B51" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>128960531</v>
       </c>
       <c r="B52" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128960529</v>
       </c>
       <c r="B53" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>128960457</v>
       </c>
       <c r="B55" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>128960664</v>
       </c>
       <c r="B56" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>128960533</v>
       </c>
       <c r="B57" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6890,7 +6890,7 @@
         <v>128960534</v>
       </c>
       <c r="B58" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128960395</v>
       </c>
       <c r="B59" t="n">
-        <v>92443</v>
+        <v>92450</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>128960535</v>
       </c>
       <c r="B60" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7331,10 +7331,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128960401</v>
+        <v>128960376</v>
       </c>
       <c r="B62" t="n">
-        <v>92443</v>
+        <v>79629</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7342,21 +7342,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4745</v>
+        <v>229821</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691473</v>
+        <v>691639</v>
       </c>
       <c r="R62" t="n">
-        <v>7401417</v>
+        <v>7401330</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7442,10 +7442,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128960376</v>
+        <v>128960401</v>
       </c>
       <c r="B63" t="n">
-        <v>79629</v>
+        <v>92450</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7453,21 +7453,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229821</v>
+        <v>4745</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>691639</v>
+        <v>691473</v>
       </c>
       <c r="R63" t="n">
-        <v>7401330</v>
+        <v>7401417</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7556,7 +7556,7 @@
         <v>128960350</v>
       </c>
       <c r="B64" t="n">
-        <v>91708</v>
+        <v>91715</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7775,10 +7775,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128960692</v>
+        <v>128960347</v>
       </c>
       <c r="B66" t="n">
-        <v>78442</v>
+        <v>91461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>3242</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>691580</v>
+        <v>691668</v>
       </c>
       <c r="R66" t="n">
-        <v>7401425</v>
+        <v>7401306</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,10 +7886,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128960347</v>
+        <v>128960692</v>
       </c>
       <c r="B67" t="n">
-        <v>91454</v>
+        <v>78442</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7897,21 +7897,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3242</v>
+        <v>6437</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691668</v>
+        <v>691580</v>
       </c>
       <c r="R67" t="n">
-        <v>7401306</v>
+        <v>7401425</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8000,7 +8000,7 @@
         <v>128960536</v>
       </c>
       <c r="B68" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>128960518</v>
       </c>
       <c r="B69" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>128960537</v>
       </c>
       <c r="B70" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>128960452</v>
       </c>
       <c r="B71" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>128960386</v>
       </c>
       <c r="B73" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>128960387</v>
       </c>
       <c r="B74" t="n">
-        <v>86930</v>
+        <v>86937</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>128960443</v>
       </c>
       <c r="B75" t="n">
-        <v>91796</v>
+        <v>91803</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>128960413</v>
       </c>
       <c r="B76" t="n">
-        <v>88786</v>
+        <v>88793</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -13913,10 +13913,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128960405</v>
+        <v>128960650</v>
       </c>
       <c r="B123" t="n">
-        <v>80173</v>
+        <v>92833</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13924,21 +13924,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>690835</v>
+        <v>690728</v>
       </c>
       <c r="R123" t="n">
-        <v>7400894</v>
+        <v>7400633</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14024,10 +14024,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128960650</v>
+        <v>128960646</v>
       </c>
       <c r="B124" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>690728</v>
+        <v>691445</v>
       </c>
       <c r="R124" t="n">
-        <v>7400633</v>
+        <v>7400907</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14089,22 +14089,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14135,32 +14135,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128960646</v>
+        <v>128960399</v>
       </c>
       <c r="B125" t="n">
-        <v>92826</v>
+        <v>92450</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>691445</v>
+        <v>690819</v>
       </c>
       <c r="R125" t="n">
-        <v>7400907</v>
+        <v>7400882</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,22 +14200,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14246,32 +14246,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128960476</v>
+        <v>128960405</v>
       </c>
       <c r="B126" t="n">
-        <v>98669</v>
+        <v>80173</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>691094</v>
+        <v>690835</v>
       </c>
       <c r="R126" t="n">
-        <v>7400693</v>
+        <v>7400894</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14311,22 +14311,22 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14357,10 +14357,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128960399</v>
+        <v>128960370</v>
       </c>
       <c r="B127" t="n">
-        <v>92443</v>
+        <v>79629</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14368,21 +14368,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4745</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>690819</v>
+        <v>691375</v>
       </c>
       <c r="R127" t="n">
-        <v>7400882</v>
+        <v>7400750</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14422,22 +14422,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14471,7 +14471,7 @@
         <v>128960503</v>
       </c>
       <c r="B128" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14579,32 +14579,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128960370</v>
+        <v>128960476</v>
       </c>
       <c r="B129" t="n">
-        <v>79629</v>
+        <v>98676</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14614,10 +14614,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>691375</v>
+        <v>691094</v>
       </c>
       <c r="R129" t="n">
-        <v>7400750</v>
+        <v>7400693</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14693,7 +14693,7 @@
         <v>128960354</v>
       </c>
       <c r="B130" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14804,7 +14804,7 @@
         <v>128960626</v>
       </c>
       <c r="B131" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14915,7 +14915,7 @@
         <v>128960629</v>
       </c>
       <c r="B132" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15023,10 +15023,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128960378</v>
+        <v>128960556</v>
       </c>
       <c r="B133" t="n">
-        <v>90562</v>
+        <v>91554</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15034,21 +15034,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15058,10 +15058,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>690754</v>
+        <v>691520</v>
       </c>
       <c r="R133" t="n">
-        <v>7400823</v>
+        <v>7401010</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15088,22 +15088,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15134,10 +15134,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128960556</v>
+        <v>128960378</v>
       </c>
       <c r="B134" t="n">
-        <v>91547</v>
+        <v>90569</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15145,21 +15145,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1204</v>
+        <v>1962</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>691520</v>
+        <v>690754</v>
       </c>
       <c r="R134" t="n">
-        <v>7401010</v>
+        <v>7400823</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15199,22 +15199,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15245,10 +15245,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128960402</v>
+        <v>128960369</v>
       </c>
       <c r="B135" t="n">
-        <v>92852</v>
+        <v>79629</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15256,21 +15256,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5448</v>
+        <v>229821</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>690717</v>
+        <v>691330</v>
       </c>
       <c r="R135" t="n">
-        <v>7400812</v>
+        <v>7400743</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15310,22 +15310,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15356,10 +15356,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128960369</v>
+        <v>128960432</v>
       </c>
       <c r="B136" t="n">
-        <v>79629</v>
+        <v>93029</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15367,21 +15367,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15391,10 +15391,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>691330</v>
+        <v>690722</v>
       </c>
       <c r="R136" t="n">
-        <v>7400743</v>
+        <v>7400676</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15421,22 +15421,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15467,10 +15467,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128960432</v>
+        <v>128960402</v>
       </c>
       <c r="B137" t="n">
-        <v>93022</v>
+        <v>92859</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15478,21 +15478,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2079</v>
+        <v>5448</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15502,10 +15502,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>690722</v>
+        <v>690717</v>
       </c>
       <c r="R137" t="n">
-        <v>7400676</v>
+        <v>7400812</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15537,7 +15537,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15547,7 +15547,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15581,7 +15581,7 @@
         <v>128960511</v>
       </c>
       <c r="B138" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>128960488</v>
       </c>
       <c r="B139" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>128960464</v>
       </c>
       <c r="B140" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15914,7 +15914,7 @@
         <v>128960496</v>
       </c>
       <c r="B141" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16022,32 +16022,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128960414</v>
+        <v>128960479</v>
       </c>
       <c r="B142" t="n">
-        <v>80145</v>
+        <v>98676</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16057,10 +16057,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>691163</v>
+        <v>691286</v>
       </c>
       <c r="R142" t="n">
-        <v>7400622</v>
+        <v>7400554</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16133,10 +16133,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128960559</v>
+        <v>128960480</v>
       </c>
       <c r="B143" t="n">
-        <v>91694</v>
+        <v>98676</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>691433</v>
+        <v>691030</v>
       </c>
       <c r="R143" t="n">
-        <v>7400873</v>
+        <v>7400688</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16244,32 +16244,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128960642</v>
+        <v>128960414</v>
       </c>
       <c r="B144" t="n">
-        <v>92826</v>
+        <v>80145</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>4364</v>
+        <v>2081</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16279,10 +16279,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>691479</v>
+        <v>691163</v>
       </c>
       <c r="R144" t="n">
-        <v>7400776</v>
+        <v>7400622</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16314,7 +16314,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16355,10 +16355,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128960636</v>
+        <v>128960642</v>
       </c>
       <c r="B145" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16390,10 +16390,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>691313</v>
+        <v>691479</v>
       </c>
       <c r="R145" t="n">
-        <v>7400890</v>
+        <v>7400776</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16466,32 +16466,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128960479</v>
+        <v>128960636</v>
       </c>
       <c r="B146" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>691286</v>
+        <v>691313</v>
       </c>
       <c r="R146" t="n">
-        <v>7400554</v>
+        <v>7400890</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16577,10 +16577,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128960480</v>
+        <v>128960559</v>
       </c>
       <c r="B147" t="n">
-        <v>98669</v>
+        <v>91701</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16588,21 +16588,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16612,10 +16612,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>691030</v>
+        <v>691433</v>
       </c>
       <c r="R147" t="n">
-        <v>7400688</v>
+        <v>7400873</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16647,7 +16647,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16691,7 +16691,7 @@
         <v>128960504</v>
       </c>
       <c r="B148" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>128960510</v>
       </c>
       <c r="B150" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17021,32 +17021,32 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128960683</v>
+        <v>128960421</v>
       </c>
       <c r="B151" t="n">
-        <v>80179</v>
+        <v>98565</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6463</v>
+        <v>233</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17056,10 +17056,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>690835</v>
+        <v>691475</v>
       </c>
       <c r="R151" t="n">
-        <v>7400892</v>
+        <v>7401113</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17086,22 +17086,22 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17132,32 +17132,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128960685</v>
+        <v>128960683</v>
       </c>
       <c r="B152" t="n">
-        <v>78047</v>
+        <v>80179</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6487</v>
+        <v>6463</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17167,10 +17167,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>690998</v>
+        <v>690835</v>
       </c>
       <c r="R152" t="n">
-        <v>7401040</v>
+        <v>7400892</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17202,7 +17202,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17212,7 +17212,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128960421</v>
+        <v>128960685</v>
       </c>
       <c r="B153" t="n">
-        <v>98558</v>
+        <v>78047</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>233</v>
+        <v>6487</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>691475</v>
+        <v>690998</v>
       </c>
       <c r="R153" t="n">
-        <v>7401113</v>
+        <v>7401040</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17308,22 +17308,22 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17357,7 +17357,7 @@
         <v>128960465</v>
       </c>
       <c r="B154" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17465,10 +17465,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128960606</v>
+        <v>128960394</v>
       </c>
       <c r="B155" t="n">
-        <v>78705</v>
+        <v>92450</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17476,21 +17476,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>353</v>
+        <v>4745</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17500,10 +17500,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>691096</v>
+        <v>691657</v>
       </c>
       <c r="R155" t="n">
-        <v>7400927</v>
+        <v>7400847</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17576,32 +17576,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128960357</v>
+        <v>128960469</v>
       </c>
       <c r="B156" t="n">
-        <v>79658</v>
+        <v>98676</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>691748</v>
+        <v>691149</v>
       </c>
       <c r="R156" t="n">
-        <v>7400820</v>
+        <v>7400912</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17687,10 +17687,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128960394</v>
+        <v>128960365</v>
       </c>
       <c r="B157" t="n">
-        <v>92443</v>
+        <v>79629</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17698,21 +17698,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4745</v>
+        <v>229821</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17722,10 +17722,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>691657</v>
+        <v>691772</v>
       </c>
       <c r="R157" t="n">
-        <v>7400847</v>
+        <v>7401045</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17798,32 +17798,32 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128960639</v>
+        <v>128960468</v>
       </c>
       <c r="B158" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17833,10 +17833,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>691173</v>
+        <v>691175</v>
       </c>
       <c r="R158" t="n">
-        <v>7400751</v>
+        <v>7400884</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17909,32 +17909,32 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128960634</v>
+        <v>128960477</v>
       </c>
       <c r="B159" t="n">
-        <v>92826</v>
+        <v>98676</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -17944,10 +17944,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>691432</v>
+        <v>691104</v>
       </c>
       <c r="R159" t="n">
-        <v>7400884</v>
+        <v>7400683</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17979,7 +17979,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18020,32 +18020,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128960633</v>
+        <v>128960606</v>
       </c>
       <c r="B160" t="n">
-        <v>92826</v>
+        <v>78705</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18055,10 +18055,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691476</v>
+        <v>691096</v>
       </c>
       <c r="R160" t="n">
-        <v>7400909</v>
+        <v>7400927</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18131,10 +18131,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128960416</v>
+        <v>128960639</v>
       </c>
       <c r="B161" t="n">
-        <v>92838</v>
+        <v>92833</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18142,21 +18142,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>690733</v>
+        <v>691173</v>
       </c>
       <c r="R161" t="n">
-        <v>7400794</v>
+        <v>7400751</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18196,22 +18196,22 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18242,32 +18242,32 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128960469</v>
+        <v>128960634</v>
       </c>
       <c r="B162" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>691149</v>
+        <v>691432</v>
       </c>
       <c r="R162" t="n">
-        <v>7400912</v>
+        <v>7400884</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18312,7 +18312,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18353,32 +18353,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128960468</v>
+        <v>128960633</v>
       </c>
       <c r="B163" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18388,10 +18388,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>691175</v>
+        <v>691476</v>
       </c>
       <c r="R163" t="n">
-        <v>7400884</v>
+        <v>7400909</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18464,32 +18464,32 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>128960477</v>
+        <v>128960416</v>
       </c>
       <c r="B164" t="n">
-        <v>98669</v>
+        <v>92845</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18499,10 +18499,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>691104</v>
+        <v>690733</v>
       </c>
       <c r="R164" t="n">
-        <v>7400683</v>
+        <v>7400794</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18529,22 +18529,22 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18575,10 +18575,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128960365</v>
+        <v>128960357</v>
       </c>
       <c r="B165" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18586,21 +18586,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18610,10 +18610,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>691772</v>
+        <v>691748</v>
       </c>
       <c r="R165" t="n">
-        <v>7401045</v>
+        <v>7400820</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18797,32 +18797,32 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>128960485</v>
+        <v>128960397</v>
       </c>
       <c r="B167" t="n">
-        <v>98669</v>
+        <v>92450</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18832,10 +18832,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>691491</v>
+        <v>690679</v>
       </c>
       <c r="R167" t="n">
-        <v>7400689</v>
+        <v>7400680</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18862,22 +18862,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18908,10 +18908,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128960508</v>
+        <v>128960569</v>
       </c>
       <c r="B168" t="n">
-        <v>98669</v>
+        <v>91701</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18919,21 +18919,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18943,10 +18943,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>690820</v>
+        <v>691471</v>
       </c>
       <c r="R168" t="n">
-        <v>7400917</v>
+        <v>7400861</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18973,22 +18973,22 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19019,10 +19019,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128960484</v>
+        <v>128960485</v>
       </c>
       <c r="B169" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19054,10 +19054,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691205</v>
+        <v>691491</v>
       </c>
       <c r="R169" t="n">
-        <v>7400756</v>
+        <v>7400689</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19089,7 +19089,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -19099,7 +19099,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19130,10 +19130,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128960509</v>
+        <v>128960508</v>
       </c>
       <c r="B170" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19165,10 +19165,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>690841</v>
+        <v>690820</v>
       </c>
       <c r="R170" t="n">
-        <v>7400937</v>
+        <v>7400917</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19200,7 +19200,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19241,10 +19241,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128960456</v>
+        <v>128960484</v>
       </c>
       <c r="B171" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>691641</v>
+        <v>691205</v>
       </c>
       <c r="R171" t="n">
-        <v>7400939</v>
+        <v>7400756</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19311,7 +19311,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19321,7 +19321,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19352,10 +19352,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128960515</v>
+        <v>128960509</v>
       </c>
       <c r="B172" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19387,10 +19387,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>691061</v>
+        <v>690841</v>
       </c>
       <c r="R172" t="n">
-        <v>7401094</v>
+        <v>7400937</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19422,7 +19422,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19432,7 +19432,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19463,10 +19463,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128960569</v>
+        <v>128960456</v>
       </c>
       <c r="B173" t="n">
-        <v>91694</v>
+        <v>98676</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19474,21 +19474,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691471</v>
+        <v>691641</v>
       </c>
       <c r="R173" t="n">
-        <v>7400861</v>
+        <v>7400939</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19543,7 +19543,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19574,32 +19574,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128960397</v>
+        <v>128960515</v>
       </c>
       <c r="B174" t="n">
-        <v>92443</v>
+        <v>98676</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19609,10 +19609,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>690679</v>
+        <v>691061</v>
       </c>
       <c r="R174" t="n">
-        <v>7400680</v>
+        <v>7401094</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19685,32 +19685,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128960406</v>
+        <v>128960495</v>
       </c>
       <c r="B175" t="n">
-        <v>80173</v>
+        <v>98676</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19720,10 +19720,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>691215</v>
+        <v>691488</v>
       </c>
       <c r="R175" t="n">
-        <v>7400790</v>
+        <v>7401092</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19755,7 +19755,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19765,7 +19765,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19796,10 +19796,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128960495</v>
+        <v>128960475</v>
       </c>
       <c r="B176" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19831,10 +19831,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>691488</v>
+        <v>691050</v>
       </c>
       <c r="R176" t="n">
-        <v>7401092</v>
+        <v>7400705</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19907,10 +19907,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128960475</v>
+        <v>128960473</v>
       </c>
       <c r="B177" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19942,10 +19942,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>691050</v>
+        <v>690998</v>
       </c>
       <c r="R177" t="n">
-        <v>7400705</v>
+        <v>7400742</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20018,32 +20018,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128960473</v>
+        <v>128960658</v>
       </c>
       <c r="B178" t="n">
-        <v>98669</v>
+        <v>92833</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20053,10 +20053,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>690998</v>
+        <v>690788</v>
       </c>
       <c r="R178" t="n">
-        <v>7400742</v>
+        <v>7400864</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20083,22 +20083,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20129,10 +20129,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128960658</v>
+        <v>128960406</v>
       </c>
       <c r="B179" t="n">
-        <v>92826</v>
+        <v>80173</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20140,21 +20140,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>690788</v>
+        <v>691215</v>
       </c>
       <c r="R179" t="n">
-        <v>7400864</v>
+        <v>7400790</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20194,22 +20194,22 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20240,32 +20240,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128960472</v>
+        <v>128960598</v>
       </c>
       <c r="B180" t="n">
-        <v>98669</v>
+        <v>78705</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20275,10 +20275,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>690998</v>
+        <v>691672</v>
       </c>
       <c r="R180" t="n">
-        <v>7400789</v>
+        <v>7401058</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20310,7 +20310,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20320,7 +20320,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20351,32 +20351,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128960598</v>
+        <v>128960472</v>
       </c>
       <c r="B181" t="n">
-        <v>78705</v>
+        <v>98676</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20386,10 +20386,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>691672</v>
+        <v>690998</v>
       </c>
       <c r="R181" t="n">
-        <v>7401058</v>
+        <v>7400789</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20465,7 +20465,7 @@
         <v>128960439</v>
       </c>
       <c r="B182" t="n">
-        <v>90156</v>
+        <v>90163</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20576,7 +20576,7 @@
         <v>128960550</v>
       </c>
       <c r="B183" t="n">
-        <v>92157</v>
+        <v>92164</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>128960512</v>
       </c>
       <c r="B184" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>128960478</v>
       </c>
       <c r="B185" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>128960471</v>
       </c>
       <c r="B186" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>128960461</v>
       </c>
       <c r="B187" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>128960474</v>
       </c>
       <c r="B188" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>128960470</v>
       </c>
       <c r="B189" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>128960505</v>
       </c>
       <c r="B190" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>128960481</v>
       </c>
       <c r="B192" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21683,32 +21683,32 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>128960644</v>
+        <v>128960342</v>
       </c>
       <c r="B193" t="n">
-        <v>92826</v>
+        <v>91461</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -21718,10 +21718,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>691471</v>
+        <v>691704</v>
       </c>
       <c r="R193" t="n">
-        <v>7400823</v>
+        <v>7401045</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21753,7 +21753,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21763,7 +21763,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21794,10 +21794,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128960342</v>
+        <v>128960684</v>
       </c>
       <c r="B194" t="n">
-        <v>91454</v>
+        <v>78047</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21805,21 +21805,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>3242</v>
+        <v>6487</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21829,10 +21829,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>691704</v>
+        <v>691442</v>
       </c>
       <c r="R194" t="n">
-        <v>7401045</v>
+        <v>7400932</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21905,32 +21905,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128960684</v>
+        <v>128960644</v>
       </c>
       <c r="B195" t="n">
-        <v>78047</v>
+        <v>92833</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21940,10 +21940,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>691442</v>
+        <v>691471</v>
       </c>
       <c r="R195" t="n">
-        <v>7400932</v>
+        <v>7400823</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21975,7 +21975,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22019,7 +22019,7 @@
         <v>128960507</v>
       </c>
       <c r="B196" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>128960493</v>
       </c>
       <c r="B197" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>128960506</v>
       </c>
       <c r="B198" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>128960641</v>
       </c>
       <c r="B199" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>128960631</v>
       </c>
       <c r="B200" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>128960396</v>
       </c>
       <c r="B201" t="n">
-        <v>92443</v>
+        <v>92450</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22682,32 +22682,32 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>128960599</v>
+        <v>128960578</v>
       </c>
       <c r="B202" t="n">
-        <v>78705</v>
+        <v>91801</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22717,10 +22717,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>691564</v>
+        <v>691498</v>
       </c>
       <c r="R202" t="n">
-        <v>7401001</v>
+        <v>7400703</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22752,7 +22752,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22762,7 +22762,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22793,32 +22793,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128960578</v>
+        <v>128960599</v>
       </c>
       <c r="B203" t="n">
-        <v>91794</v>
+        <v>78705</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22828,10 +22828,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>691498</v>
+        <v>691564</v>
       </c>
       <c r="R203" t="n">
-        <v>7400703</v>
+        <v>7401001</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22863,7 +22863,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22873,7 +22873,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -23018,7 +23018,7 @@
         <v>128960661</v>
       </c>
       <c r="B205" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23126,32 +23126,32 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128960459</v>
+        <v>128960341</v>
       </c>
       <c r="B206" t="n">
-        <v>98669</v>
+        <v>91461</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23161,10 +23161,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>691498</v>
+        <v>691820</v>
       </c>
       <c r="R206" t="n">
-        <v>7401073</v>
+        <v>7400734</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23196,7 +23196,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23237,32 +23237,32 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>128960463</v>
+        <v>128960437</v>
       </c>
       <c r="B207" t="n">
-        <v>98669</v>
+        <v>90163</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>220787</v>
+        <v>4962</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -23272,10 +23272,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>691259</v>
+        <v>691225</v>
       </c>
       <c r="R207" t="n">
-        <v>7400802</v>
+        <v>7400593</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23307,7 +23307,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -23317,7 +23317,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>12:44</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -23348,32 +23348,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>128960341</v>
+        <v>128960459</v>
       </c>
       <c r="B208" t="n">
-        <v>91454</v>
+        <v>98676</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>3242</v>
+        <v>220787</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23383,10 +23383,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>691820</v>
+        <v>691498</v>
       </c>
       <c r="R208" t="n">
-        <v>7400734</v>
+        <v>7401073</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23418,7 +23418,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23459,32 +23459,32 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>128960437</v>
+        <v>128960463</v>
       </c>
       <c r="B209" t="n">
-        <v>90156</v>
+        <v>98676</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23494,10 +23494,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>691225</v>
+        <v>691259</v>
       </c>
       <c r="R209" t="n">
-        <v>7400593</v>
+        <v>7400802</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23529,7 +23529,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>12:44</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23570,10 +23570,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128960483</v>
+        <v>128960587</v>
       </c>
       <c r="B210" t="n">
-        <v>98669</v>
+        <v>91801</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23581,21 +23581,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>220787</v>
+        <v>65</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23605,10 +23605,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>691042</v>
+        <v>691522</v>
       </c>
       <c r="R210" t="n">
-        <v>7400691</v>
+        <v>7401008</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23681,10 +23681,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128960371</v>
+        <v>128960611</v>
       </c>
       <c r="B211" t="n">
-        <v>79629</v>
+        <v>78705</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23692,21 +23692,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23716,10 +23716,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>691493</v>
+        <v>690824</v>
       </c>
       <c r="R211" t="n">
-        <v>7400837</v>
+        <v>7400642</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23746,22 +23746,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>09:34</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23903,32 +23903,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128960611</v>
+        <v>128960483</v>
       </c>
       <c r="B213" t="n">
-        <v>78705</v>
+        <v>98676</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23938,10 +23938,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>690824</v>
+        <v>691042</v>
       </c>
       <c r="R213" t="n">
-        <v>7400642</v>
+        <v>7400691</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23968,22 +23968,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24014,32 +24014,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128960587</v>
+        <v>128960690</v>
       </c>
       <c r="B214" t="n">
-        <v>91794</v>
+        <v>78442</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>65</v>
+        <v>6437</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -24049,10 +24049,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>691522</v>
+        <v>690817</v>
       </c>
       <c r="R214" t="n">
-        <v>7401008</v>
+        <v>7400668</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24079,22 +24079,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24125,10 +24125,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>128960690</v>
+        <v>128960371</v>
       </c>
       <c r="B215" t="n">
-        <v>78442</v>
+        <v>79629</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24136,21 +24136,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -24160,10 +24160,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>690817</v>
+        <v>691493</v>
       </c>
       <c r="R215" t="n">
-        <v>7400668</v>
+        <v>7400837</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24190,22 +24190,22 @@
       </c>
       <c r="Y215" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -24236,32 +24236,32 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>128960655</v>
+        <v>128960344</v>
       </c>
       <c r="B216" t="n">
-        <v>92826</v>
+        <v>91461</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4364</v>
+        <v>3242</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -24271,10 +24271,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>690734</v>
+        <v>691060</v>
       </c>
       <c r="R216" t="n">
-        <v>7400797</v>
+        <v>7400887</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24301,22 +24301,22 @@
       </c>
       <c r="Y216" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -24347,32 +24347,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>128960344</v>
+        <v>128960655</v>
       </c>
       <c r="B217" t="n">
-        <v>91454</v>
+        <v>92833</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -24382,10 +24382,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>691060</v>
+        <v>690734</v>
       </c>
       <c r="R217" t="n">
-        <v>7400887</v>
+        <v>7400797</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24412,22 +24412,22 @@
       </c>
       <c r="Y217" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24461,7 +24461,7 @@
         <v>128960489</v>
       </c>
       <c r="B218" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>128960513</v>
       </c>
       <c r="B219" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>128960467</v>
       </c>
       <c r="B220" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24791,32 +24791,32 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>128960356</v>
+        <v>128960582</v>
       </c>
       <c r="B221" t="n">
-        <v>91497</v>
+        <v>91801</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>5447</v>
+        <v>65</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24826,10 +24826,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>691028</v>
+        <v>691723</v>
       </c>
       <c r="R221" t="n">
-        <v>7400838</v>
+        <v>7400616</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24861,7 +24861,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24871,7 +24871,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24902,32 +24902,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128960582</v>
+        <v>128960608</v>
       </c>
       <c r="B222" t="n">
-        <v>91794</v>
+        <v>78705</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24937,10 +24937,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>691723</v>
+        <v>691209</v>
       </c>
       <c r="R222" t="n">
-        <v>7400616</v>
+        <v>7400623</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24972,7 +24972,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:31</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25013,32 +25013,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128960608</v>
+        <v>128960455</v>
       </c>
       <c r="B223" t="n">
-        <v>78705</v>
+        <v>98676</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25048,10 +25048,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>691209</v>
+        <v>691615</v>
       </c>
       <c r="R223" t="n">
-        <v>7400623</v>
+        <v>7400959</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25124,32 +25124,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128960436</v>
+        <v>128960451</v>
       </c>
       <c r="B224" t="n">
-        <v>90156</v>
+        <v>98676</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25159,10 +25159,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>691019</v>
+        <v>691520</v>
       </c>
       <c r="R224" t="n">
-        <v>7400845</v>
+        <v>7401010</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25194,7 +25194,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25235,10 +25235,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128960455</v>
+        <v>128960487</v>
       </c>
       <c r="B225" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25270,10 +25270,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>691615</v>
+        <v>691504</v>
       </c>
       <c r="R225" t="n">
-        <v>7400959</v>
+        <v>7400725</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25346,10 +25346,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128960451</v>
+        <v>128960497</v>
       </c>
       <c r="B226" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25381,10 +25381,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>691520</v>
+        <v>691469</v>
       </c>
       <c r="R226" t="n">
-        <v>7401010</v>
+        <v>7401129</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25416,7 +25416,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25426,7 +25426,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25457,10 +25457,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128960487</v>
+        <v>128960486</v>
       </c>
       <c r="B227" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25492,10 +25492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>691504</v>
+        <v>691497</v>
       </c>
       <c r="R227" t="n">
-        <v>7400725</v>
+        <v>7400703</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25568,32 +25568,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128960497</v>
+        <v>128960366</v>
       </c>
       <c r="B228" t="n">
-        <v>98669</v>
+        <v>79629</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25603,10 +25603,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>691469</v>
+        <v>691628</v>
       </c>
       <c r="R228" t="n">
-        <v>7401129</v>
+        <v>7401071</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25638,7 +25638,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25648,7 +25648,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25679,32 +25679,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128960486</v>
+        <v>128960360</v>
       </c>
       <c r="B229" t="n">
-        <v>98669</v>
+        <v>79629</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -25714,10 +25714,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>691497</v>
+        <v>691748</v>
       </c>
       <c r="R229" t="n">
-        <v>7400703</v>
+        <v>7400820</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25790,32 +25790,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128960693</v>
+        <v>128960356</v>
       </c>
       <c r="B230" t="n">
-        <v>78442</v>
+        <v>91504</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6437</v>
+        <v>5447</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25825,10 +25825,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691595</v>
+        <v>691028</v>
       </c>
       <c r="R230" t="n">
-        <v>7401115</v>
+        <v>7400838</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25860,7 +25860,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25901,10 +25901,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128960358</v>
+        <v>128960436</v>
       </c>
       <c r="B231" t="n">
-        <v>79658</v>
+        <v>90163</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25912,21 +25912,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6453</v>
+        <v>4962</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25936,10 +25936,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>691772</v>
+        <v>691019</v>
       </c>
       <c r="R231" t="n">
-        <v>7400877</v>
+        <v>7400845</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25971,7 +25971,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26012,10 +26012,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128960366</v>
+        <v>128960693</v>
       </c>
       <c r="B232" t="n">
-        <v>79629</v>
+        <v>78442</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26023,21 +26023,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26047,10 +26047,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>691628</v>
+        <v>691595</v>
       </c>
       <c r="R232" t="n">
-        <v>7401071</v>
+        <v>7401115</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26123,10 +26123,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128960360</v>
+        <v>128960358</v>
       </c>
       <c r="B233" t="n">
-        <v>79629</v>
+        <v>79658</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26134,21 +26134,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -26158,10 +26158,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>691748</v>
+        <v>691772</v>
       </c>
       <c r="R233" t="n">
-        <v>7400820</v>
+        <v>7400877</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26193,7 +26193,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26203,7 +26203,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26237,7 +26237,7 @@
         <v>128960409</v>
       </c>
       <c r="B234" t="n">
-        <v>91482</v>
+        <v>91489</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26456,32 +26456,32 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128960653</v>
+        <v>128960393</v>
       </c>
       <c r="B236" t="n">
-        <v>92826</v>
+        <v>92858</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -26491,10 +26491,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>690703</v>
+        <v>690878</v>
       </c>
       <c r="R236" t="n">
-        <v>7400802</v>
+        <v>7400754</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26526,7 +26526,7 @@
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
@@ -26536,7 +26536,7 @@
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26567,10 +26567,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128960393</v>
+        <v>128960345</v>
       </c>
       <c r="B237" t="n">
-        <v>92851</v>
+        <v>91461</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26578,21 +26578,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3100</v>
+        <v>3242</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -26602,10 +26602,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>690878</v>
+        <v>691005</v>
       </c>
       <c r="R237" t="n">
-        <v>7400754</v>
+        <v>7401070</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26637,7 +26637,7 @@
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
@@ -26647,7 +26647,7 @@
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26678,32 +26678,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128960345</v>
+        <v>128960653</v>
       </c>
       <c r="B238" t="n">
-        <v>91454</v>
+        <v>92833</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>3242</v>
+        <v>4364</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -26713,10 +26713,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>691005</v>
+        <v>690703</v>
       </c>
       <c r="R238" t="n">
-        <v>7401070</v>
+        <v>7400802</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26748,7 +26748,7 @@
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -26758,7 +26758,7 @@
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26789,10 +26789,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128960545</v>
+        <v>128960368</v>
       </c>
       <c r="B239" t="n">
-        <v>79118</v>
+        <v>79629</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26800,21 +26800,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>864</v>
+        <v>229821</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26824,10 +26824,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>691266</v>
+        <v>691561</v>
       </c>
       <c r="R239" t="n">
-        <v>7400806</v>
+        <v>7401113</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -26869,7 +26869,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26900,10 +26900,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128960368</v>
+        <v>128960545</v>
       </c>
       <c r="B240" t="n">
-        <v>79629</v>
+        <v>79118</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26911,21 +26911,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26935,10 +26935,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>691561</v>
+        <v>691266</v>
       </c>
       <c r="R240" t="n">
-        <v>7401113</v>
+        <v>7400806</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26970,7 +26970,7 @@
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
@@ -26980,7 +26980,7 @@
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27014,7 +27014,7 @@
         <v>128960580</v>
       </c>
       <c r="B241" t="n">
-        <v>91794</v>
+        <v>91801</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>128960563</v>
       </c>
       <c r="B242" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27455,32 +27455,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128960398</v>
+        <v>128960628</v>
       </c>
       <c r="B245" t="n">
-        <v>92443</v>
+        <v>92833</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>690713</v>
+        <v>691884</v>
       </c>
       <c r="R245" t="n">
-        <v>7400706</v>
+        <v>7401043</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27520,22 +27520,22 @@
       </c>
       <c r="Y245" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27566,32 +27566,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128960628</v>
+        <v>128960398</v>
       </c>
       <c r="B246" t="n">
-        <v>92826</v>
+        <v>92450</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -27601,10 +27601,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>691884</v>
+        <v>690713</v>
       </c>
       <c r="R246" t="n">
-        <v>7401043</v>
+        <v>7400706</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27631,22 +27631,22 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27680,7 +27680,7 @@
         <v>128960460</v>
       </c>
       <c r="B247" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>128960677</v>
       </c>
       <c r="B249" t="n">
-        <v>88781</v>
+        <v>88788</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>128960382</v>
       </c>
       <c r="B250" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>128960419</v>
       </c>
       <c r="B251" t="n">
-        <v>92158</v>
+        <v>92165</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>128960678</v>
       </c>
       <c r="B252" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>128960380</v>
       </c>
       <c r="B253" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>128960381</v>
       </c>
       <c r="B254" t="n">
-        <v>91808</v>
+        <v>91815</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128960696</v>
+        <v>128960549</v>
       </c>
       <c r="B3" t="n">
-        <v>78442</v>
+        <v>92166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6437</v>
+        <v>5454</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691640</v>
+        <v>691837</v>
       </c>
       <c r="R3" t="n">
-        <v>7401329</v>
+        <v>7401375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128960549</v>
+        <v>128960696</v>
       </c>
       <c r="B4" t="n">
-        <v>92164</v>
+        <v>78444</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5454</v>
+        <v>6437</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691837</v>
+        <v>691640</v>
       </c>
       <c r="R4" t="n">
-        <v>7401375</v>
+        <v>7401329</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,7 +1007,7 @@
         <v>128960450</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>128960524</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128960691</v>
+        <v>128960372</v>
       </c>
       <c r="B7" t="n">
-        <v>78442</v>
+        <v>79631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1237,21 +1237,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691190</v>
+        <v>691253</v>
       </c>
       <c r="R7" t="n">
-        <v>7401223</v>
+        <v>7401236</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128960372</v>
+        <v>128960691</v>
       </c>
       <c r="B8" t="n">
-        <v>79629</v>
+        <v>78444</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>6437</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691253</v>
+        <v>691190</v>
       </c>
       <c r="R8" t="n">
-        <v>7401236</v>
+        <v>7401223</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,10 +1448,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128960616</v>
+        <v>128960343</v>
       </c>
       <c r="B9" t="n">
-        <v>78705</v>
+        <v>91463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,21 +1459,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691854</v>
+        <v>691612</v>
       </c>
       <c r="R9" t="n">
-        <v>7401445</v>
+        <v>7401171</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,22 +1513,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,32 +1559,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128960426</v>
+        <v>128960670</v>
       </c>
       <c r="B10" t="n">
-        <v>98565</v>
+        <v>92835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>233</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691727</v>
+        <v>691851</v>
       </c>
       <c r="R10" t="n">
-        <v>7401372</v>
+        <v>7401441</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,32 +1670,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128960670</v>
+        <v>128960689</v>
       </c>
       <c r="B11" t="n">
-        <v>92833</v>
+        <v>78444</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691851</v>
+        <v>691341</v>
       </c>
       <c r="R11" t="n">
-        <v>7401441</v>
+        <v>7401206</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1735,22 +1735,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,32 +1781,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128960689</v>
+        <v>128960426</v>
       </c>
       <c r="B12" t="n">
-        <v>78442</v>
+        <v>98567</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>233</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691341</v>
+        <v>691727</v>
       </c>
       <c r="R12" t="n">
-        <v>7401206</v>
+        <v>7401372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1846,22 +1846,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128960343</v>
+        <v>128960616</v>
       </c>
       <c r="B13" t="n">
-        <v>91461</v>
+        <v>78707</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691612</v>
+        <v>691854</v>
       </c>
       <c r="R13" t="n">
-        <v>7401171</v>
+        <v>7401445</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,22 +1957,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,7 +2006,7 @@
         <v>128960498</v>
       </c>
       <c r="B14" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>128960544</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,10 +2225,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128960618</v>
+        <v>128960348</v>
       </c>
       <c r="B16" t="n">
-        <v>78705</v>
+        <v>91463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2236,21 +2236,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691741</v>
+        <v>691730</v>
       </c>
       <c r="R16" t="n">
-        <v>7401356</v>
+        <v>7401383</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2336,10 +2336,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128960348</v>
+        <v>128960433</v>
       </c>
       <c r="B17" t="n">
-        <v>91461</v>
+        <v>93031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2347,21 +2347,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3242</v>
+        <v>2079</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>691730</v>
+        <v>691276</v>
       </c>
       <c r="R17" t="n">
-        <v>7401383</v>
+        <v>7401328</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2447,32 +2447,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128960433</v>
+        <v>128960542</v>
       </c>
       <c r="B18" t="n">
-        <v>93029</v>
+        <v>98678</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691276</v>
+        <v>691733</v>
       </c>
       <c r="R18" t="n">
-        <v>7401328</v>
+        <v>7401377</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,10 +2558,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128960542</v>
+        <v>128960519</v>
       </c>
       <c r="B19" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691733</v>
+        <v>691230</v>
       </c>
       <c r="R19" t="n">
-        <v>7401377</v>
+        <v>7401270</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,32 +2669,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128960519</v>
+        <v>128960618</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>78707</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691230</v>
+        <v>691741</v>
       </c>
       <c r="R20" t="n">
-        <v>7401270</v>
+        <v>7401356</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2780,32 +2780,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128960379</v>
+        <v>128960673</v>
       </c>
       <c r="B21" t="n">
-        <v>90569</v>
+        <v>92835</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2815,10 +2815,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>691278</v>
+        <v>691654</v>
       </c>
       <c r="R21" t="n">
-        <v>7401369</v>
+        <v>7401356</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2860,7 +2860,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2891,32 +2891,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128960673</v>
+        <v>128960379</v>
       </c>
       <c r="B22" t="n">
-        <v>92833</v>
+        <v>90571</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691654</v>
+        <v>691278</v>
       </c>
       <c r="R22" t="n">
-        <v>7401356</v>
+        <v>7401369</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3002,10 +3002,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128960539</v>
+        <v>128960423</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>98567</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3013,21 +3013,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>233</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>691733</v>
+        <v>691723</v>
       </c>
       <c r="R23" t="n">
-        <v>7401349</v>
+        <v>7401406</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3067,22 +3067,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3113,32 +3113,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128960541</v>
+        <v>128960688</v>
       </c>
       <c r="B24" t="n">
-        <v>98676</v>
+        <v>78049</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3148,10 +3148,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>691727</v>
+        <v>691253</v>
       </c>
       <c r="R24" t="n">
-        <v>7401372</v>
+        <v>7401236</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3193,7 +3193,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3224,32 +3224,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128960373</v>
+        <v>128960539</v>
       </c>
       <c r="B25" t="n">
-        <v>79629</v>
+        <v>98678</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>691245</v>
+        <v>691733</v>
       </c>
       <c r="R25" t="n">
-        <v>7401304</v>
+        <v>7401349</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:54</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3335,10 +3335,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128960423</v>
+        <v>128960541</v>
       </c>
       <c r="B26" t="n">
-        <v>98565</v>
+        <v>98678</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3346,21 +3346,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>233</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3370,10 +3370,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>691723</v>
+        <v>691727</v>
       </c>
       <c r="R26" t="n">
-        <v>7401406</v>
+        <v>7401372</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3400,22 +3400,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3446,10 +3446,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128960688</v>
+        <v>128960373</v>
       </c>
       <c r="B27" t="n">
-        <v>78047</v>
+        <v>79631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3457,21 +3457,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6487</v>
+        <v>229821</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3481,10 +3481,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>691253</v>
+        <v>691245</v>
       </c>
       <c r="R27" t="n">
-        <v>7401236</v>
+        <v>7401304</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3516,7 +3516,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3560,7 +3560,7 @@
         <v>128960666</v>
       </c>
       <c r="B28" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>128960454</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>128960540</v>
       </c>
       <c r="B30" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3893,7 +3893,7 @@
         <v>128960573</v>
       </c>
       <c r="B31" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>128960400</v>
       </c>
       <c r="B32" t="n">
-        <v>92450</v>
+        <v>92452</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4112,32 +4112,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128960551</v>
+        <v>128960675</v>
       </c>
       <c r="B33" t="n">
-        <v>92164</v>
+        <v>92835</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5454</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4147,10 +4147,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>691848</v>
+        <v>691653</v>
       </c>
       <c r="R33" t="n">
-        <v>7401397</v>
+        <v>7401394</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4182,7 +4182,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4223,32 +4223,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128960522</v>
+        <v>128960551</v>
       </c>
       <c r="B34" t="n">
-        <v>98676</v>
+        <v>92166</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>5454</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4258,10 +4258,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>691354</v>
+        <v>691848</v>
       </c>
       <c r="R34" t="n">
-        <v>7401418</v>
+        <v>7401397</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4337,7 +4337,7 @@
         <v>128960614</v>
       </c>
       <c r="B35" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4445,32 +4445,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128960675</v>
+        <v>128960522</v>
       </c>
       <c r="B36" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4480,10 +4480,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>691653</v>
+        <v>691354</v>
       </c>
       <c r="R36" t="n">
-        <v>7401394</v>
+        <v>7401418</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4556,32 +4556,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128960686</v>
+        <v>128960424</v>
       </c>
       <c r="B37" t="n">
-        <v>78047</v>
+        <v>98567</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>233</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691639</v>
+        <v>691756</v>
       </c>
       <c r="R37" t="n">
-        <v>7401330</v>
+        <v>7401403</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,10 +4667,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128960424</v>
+        <v>128960571</v>
       </c>
       <c r="B38" t="n">
-        <v>98565</v>
+        <v>91703</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>233</v>
+        <v>1503</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691756</v>
+        <v>691659</v>
       </c>
       <c r="R38" t="n">
-        <v>7401403</v>
+        <v>7401322</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4781,7 +4781,7 @@
         <v>128960561</v>
       </c>
       <c r="B39" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4889,32 +4889,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128960571</v>
+        <v>128960686</v>
       </c>
       <c r="B40" t="n">
-        <v>91701</v>
+        <v>78049</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>6487</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4924,10 +4924,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>691659</v>
+        <v>691639</v>
       </c>
       <c r="R40" t="n">
-        <v>7401322</v>
+        <v>7401330</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4959,7 +4959,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5003,7 +5003,7 @@
         <v>128960422</v>
       </c>
       <c r="B41" t="n">
-        <v>98565</v>
+        <v>98567</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>128960431</v>
       </c>
       <c r="B42" t="n">
-        <v>98565</v>
+        <v>98567</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5222,32 +5222,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128960695</v>
+        <v>128960662</v>
       </c>
       <c r="B43" t="n">
-        <v>78442</v>
+        <v>92835</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691255</v>
+        <v>691259</v>
       </c>
       <c r="R43" t="n">
-        <v>7401234</v>
+        <v>7401348</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,32 +5333,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128960662</v>
+        <v>128960695</v>
       </c>
       <c r="B44" t="n">
-        <v>92833</v>
+        <v>78444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691259</v>
+        <v>691255</v>
       </c>
       <c r="R44" t="n">
-        <v>7401348</v>
+        <v>7401234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5447,7 +5447,7 @@
         <v>128960527</v>
       </c>
       <c r="B45" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>128960377</v>
       </c>
       <c r="B46" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5666,32 +5666,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128960622</v>
+        <v>128960586</v>
       </c>
       <c r="B47" t="n">
-        <v>78705</v>
+        <v>91803</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691669</v>
+        <v>691611</v>
       </c>
       <c r="R47" t="n">
-        <v>7401313</v>
+        <v>7401170</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5731,22 +5731,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5777,32 +5777,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128960586</v>
+        <v>128960434</v>
       </c>
       <c r="B48" t="n">
-        <v>91801</v>
+        <v>93031</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>65</v>
+        <v>2079</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691611</v>
+        <v>691450</v>
       </c>
       <c r="R48" t="n">
-        <v>7401170</v>
+        <v>7401402</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5842,22 +5842,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128960434</v>
+        <v>128960622</v>
       </c>
       <c r="B49" t="n">
-        <v>93029</v>
+        <v>78707</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691450</v>
+        <v>691669</v>
       </c>
       <c r="R49" t="n">
-        <v>7401402</v>
+        <v>7401313</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6002,7 +6002,7 @@
         <v>128960458</v>
       </c>
       <c r="B50" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>128960520</v>
       </c>
       <c r="B51" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>128960531</v>
       </c>
       <c r="B52" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>128960529</v>
       </c>
       <c r="B53" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>128960617</v>
       </c>
       <c r="B54" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6557,7 +6557,7 @@
         <v>128960457</v>
       </c>
       <c r="B55" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>128960664</v>
       </c>
       <c r="B56" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6776,32 +6776,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128960533</v>
+        <v>128960395</v>
       </c>
       <c r="B57" t="n">
-        <v>98676</v>
+        <v>92452</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691773</v>
+        <v>691427</v>
       </c>
       <c r="R57" t="n">
-        <v>7401347</v>
+        <v>7401226</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6841,22 +6841,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6887,10 +6887,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128960534</v>
+        <v>128960533</v>
       </c>
       <c r="B58" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6922,10 +6922,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>691770</v>
+        <v>691773</v>
       </c>
       <c r="R58" t="n">
-        <v>7401379</v>
+        <v>7401347</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6957,7 +6957,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6998,32 +6998,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128960395</v>
+        <v>128960534</v>
       </c>
       <c r="B59" t="n">
-        <v>92450</v>
+        <v>98678</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7033,10 +7033,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>691427</v>
+        <v>691770</v>
       </c>
       <c r="R59" t="n">
-        <v>7401226</v>
+        <v>7401379</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7063,22 +7063,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7112,7 +7112,7 @@
         <v>128960535</v>
       </c>
       <c r="B60" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>128960613</v>
       </c>
       <c r="B61" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7331,10 +7331,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128960376</v>
+        <v>128960401</v>
       </c>
       <c r="B62" t="n">
-        <v>79629</v>
+        <v>92452</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7342,21 +7342,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229821</v>
+        <v>4745</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7366,10 +7366,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>691639</v>
+        <v>691473</v>
       </c>
       <c r="R62" t="n">
-        <v>7401330</v>
+        <v>7401417</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7401,7 +7401,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7442,10 +7442,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128960401</v>
+        <v>128960376</v>
       </c>
       <c r="B63" t="n">
-        <v>92450</v>
+        <v>79631</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7453,21 +7453,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4745</v>
+        <v>229821</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7477,10 +7477,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>691473</v>
+        <v>691639</v>
       </c>
       <c r="R63" t="n">
-        <v>7401417</v>
+        <v>7401330</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7556,7 +7556,7 @@
         <v>128960350</v>
       </c>
       <c r="B64" t="n">
-        <v>91715</v>
+        <v>91717</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7664,10 +7664,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128960624</v>
+        <v>128960347</v>
       </c>
       <c r="B65" t="n">
-        <v>78705</v>
+        <v>91463</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7675,21 +7675,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>691444</v>
+        <v>691668</v>
       </c>
       <c r="R65" t="n">
-        <v>7401426</v>
+        <v>7401306</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7775,10 +7775,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128960347</v>
+        <v>128960692</v>
       </c>
       <c r="B66" t="n">
-        <v>91461</v>
+        <v>78444</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7786,21 +7786,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>3242</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>691668</v>
+        <v>691580</v>
       </c>
       <c r="R66" t="n">
-        <v>7401306</v>
+        <v>7401425</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7886,10 +7886,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128960692</v>
+        <v>128960624</v>
       </c>
       <c r="B67" t="n">
-        <v>78442</v>
+        <v>78707</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7897,21 +7897,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7921,10 +7921,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>691580</v>
+        <v>691444</v>
       </c>
       <c r="R67" t="n">
-        <v>7401425</v>
+        <v>7401426</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8000,7 +8000,7 @@
         <v>128960536</v>
       </c>
       <c r="B68" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8111,7 +8111,7 @@
         <v>128960518</v>
       </c>
       <c r="B69" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>128960537</v>
       </c>
       <c r="B70" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8333,7 +8333,7 @@
         <v>128960452</v>
       </c>
       <c r="B71" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>128960364</v>
       </c>
       <c r="B72" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8555,7 +8555,7 @@
         <v>128960386</v>
       </c>
       <c r="B73" t="n">
-        <v>91815</v>
+        <v>91817</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8666,7 +8666,7 @@
         <v>128960387</v>
       </c>
       <c r="B74" t="n">
-        <v>86937</v>
+        <v>86939</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8777,7 +8777,7 @@
         <v>128960443</v>
       </c>
       <c r="B75" t="n">
-        <v>91803</v>
+        <v>91805</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>128960413</v>
       </c>
       <c r="B76" t="n">
-        <v>88793</v>
+        <v>88795</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -13913,10 +13913,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128960650</v>
+        <v>128960646</v>
       </c>
       <c r="B123" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>690728</v>
+        <v>691445</v>
       </c>
       <c r="R123" t="n">
-        <v>7400633</v>
+        <v>7400907</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13978,22 +13978,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14024,32 +14024,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128960646</v>
+        <v>128960399</v>
       </c>
       <c r="B124" t="n">
-        <v>92833</v>
+        <v>92452</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>691445</v>
+        <v>690819</v>
       </c>
       <c r="R124" t="n">
-        <v>7400907</v>
+        <v>7400882</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14089,22 +14089,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14135,32 +14135,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128960399</v>
+        <v>128960405</v>
       </c>
       <c r="B125" t="n">
-        <v>92450</v>
+        <v>80175</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4745</v>
+        <v>6462</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>690819</v>
+        <v>690835</v>
       </c>
       <c r="R125" t="n">
-        <v>7400882</v>
+        <v>7400894</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14205,7 +14205,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14215,7 +14215,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14246,10 +14246,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128960405</v>
+        <v>128960650</v>
       </c>
       <c r="B126" t="n">
-        <v>80173</v>
+        <v>92835</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14257,21 +14257,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6462</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>690835</v>
+        <v>690728</v>
       </c>
       <c r="R126" t="n">
-        <v>7400894</v>
+        <v>7400633</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14357,32 +14357,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128960370</v>
+        <v>128960503</v>
       </c>
       <c r="B127" t="n">
-        <v>79629</v>
+        <v>98678</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>691375</v>
+        <v>690957</v>
       </c>
       <c r="R127" t="n">
-        <v>7400750</v>
+        <v>7400856</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14422,22 +14422,22 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14468,10 +14468,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128960503</v>
+        <v>128960476</v>
       </c>
       <c r="B128" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>690957</v>
+        <v>691094</v>
       </c>
       <c r="R128" t="n">
-        <v>7400856</v>
+        <v>7400693</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14533,22 +14533,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14579,32 +14579,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128960476</v>
+        <v>128960370</v>
       </c>
       <c r="B129" t="n">
-        <v>98676</v>
+        <v>79631</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14614,10 +14614,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>691094</v>
+        <v>691375</v>
       </c>
       <c r="R129" t="n">
-        <v>7400693</v>
+        <v>7400750</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14693,7 +14693,7 @@
         <v>128960354</v>
       </c>
       <c r="B130" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14801,32 +14801,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>128960626</v>
+        <v>128960378</v>
       </c>
       <c r="B131" t="n">
-        <v>92833</v>
+        <v>90571</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14836,10 +14836,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>691772</v>
+        <v>690754</v>
       </c>
       <c r="R131" t="n">
-        <v>7400877</v>
+        <v>7400823</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14866,22 +14866,22 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14912,32 +14912,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>128960629</v>
+        <v>128960432</v>
       </c>
       <c r="B132" t="n">
-        <v>92833</v>
+        <v>93031</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>2079</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14947,10 +14947,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>691778</v>
+        <v>690722</v>
       </c>
       <c r="R132" t="n">
-        <v>7401031</v>
+        <v>7400676</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14977,22 +14977,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:56</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15023,10 +15023,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128960556</v>
+        <v>128960402</v>
       </c>
       <c r="B133" t="n">
-        <v>91554</v>
+        <v>92861</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15034,21 +15034,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1204</v>
+        <v>5448</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15058,10 +15058,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>691520</v>
+        <v>690717</v>
       </c>
       <c r="R133" t="n">
-        <v>7401010</v>
+        <v>7400812</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15088,22 +15088,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15134,10 +15134,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128960378</v>
+        <v>128960556</v>
       </c>
       <c r="B134" t="n">
-        <v>90569</v>
+        <v>91556</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15145,21 +15145,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1962</v>
+        <v>1204</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>690754</v>
+        <v>691520</v>
       </c>
       <c r="R134" t="n">
-        <v>7400823</v>
+        <v>7401010</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15199,22 +15199,22 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15245,32 +15245,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128960369</v>
+        <v>128960511</v>
       </c>
       <c r="B135" t="n">
-        <v>79629</v>
+        <v>98678</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>691330</v>
+        <v>690875</v>
       </c>
       <c r="R135" t="n">
-        <v>7400743</v>
+        <v>7400942</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15310,22 +15310,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15356,32 +15356,32 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>128960432</v>
+        <v>128960488</v>
       </c>
       <c r="B136" t="n">
-        <v>93029</v>
+        <v>98678</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2079</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15391,10 +15391,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>690722</v>
+        <v>691464</v>
       </c>
       <c r="R136" t="n">
-        <v>7400676</v>
+        <v>7400741</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15421,22 +15421,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>17:56</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15467,32 +15467,32 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>128960402</v>
+        <v>128960464</v>
       </c>
       <c r="B137" t="n">
-        <v>92859</v>
+        <v>98678</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15502,10 +15502,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>690717</v>
+        <v>691251</v>
       </c>
       <c r="R137" t="n">
-        <v>7400812</v>
+        <v>7400808</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15532,22 +15532,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15578,10 +15578,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128960511</v>
+        <v>128960496</v>
       </c>
       <c r="B138" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15613,10 +15613,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>690875</v>
+        <v>691471</v>
       </c>
       <c r="R138" t="n">
-        <v>7400942</v>
+        <v>7401095</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15643,22 +15643,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15689,32 +15689,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128960488</v>
+        <v>128960626</v>
       </c>
       <c r="B139" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15724,10 +15724,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>691464</v>
+        <v>691772</v>
       </c>
       <c r="R139" t="n">
-        <v>7400741</v>
+        <v>7400877</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15759,7 +15759,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15769,7 +15769,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15800,32 +15800,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128960464</v>
+        <v>128960629</v>
       </c>
       <c r="B140" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15835,10 +15835,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>691251</v>
+        <v>691778</v>
       </c>
       <c r="R140" t="n">
-        <v>7400808</v>
+        <v>7401031</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15880,7 +15880,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15911,32 +15911,32 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128960496</v>
+        <v>128960369</v>
       </c>
       <c r="B141" t="n">
-        <v>98676</v>
+        <v>79631</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15946,10 +15946,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>691471</v>
+        <v>691330</v>
       </c>
       <c r="R141" t="n">
-        <v>7401095</v>
+        <v>7400743</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15981,7 +15981,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15991,7 +15991,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16022,32 +16022,32 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128960479</v>
+        <v>128960414</v>
       </c>
       <c r="B142" t="n">
-        <v>98676</v>
+        <v>80147</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -16057,10 +16057,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>691286</v>
+        <v>691163</v>
       </c>
       <c r="R142" t="n">
-        <v>7400554</v>
+        <v>7400622</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -16102,7 +16102,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16133,10 +16133,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128960480</v>
+        <v>128960559</v>
       </c>
       <c r="B143" t="n">
-        <v>98676</v>
+        <v>91703</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16144,21 +16144,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16168,10 +16168,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>691030</v>
+        <v>691433</v>
       </c>
       <c r="R143" t="n">
-        <v>7400688</v>
+        <v>7400873</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16203,7 +16203,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16213,7 +16213,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16244,32 +16244,32 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128960414</v>
+        <v>128960642</v>
       </c>
       <c r="B144" t="n">
-        <v>80145</v>
+        <v>92835</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>2081</v>
+        <v>4364</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16279,10 +16279,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>691163</v>
+        <v>691479</v>
       </c>
       <c r="R144" t="n">
-        <v>7400622</v>
+        <v>7400776</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16314,7 +16314,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16324,7 +16324,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16355,32 +16355,32 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128960642</v>
+        <v>128960479</v>
       </c>
       <c r="B145" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16390,10 +16390,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>691479</v>
+        <v>691286</v>
       </c>
       <c r="R145" t="n">
-        <v>7400776</v>
+        <v>7400554</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16425,7 +16425,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16435,7 +16435,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16466,32 +16466,32 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128960636</v>
+        <v>128960480</v>
       </c>
       <c r="B146" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16501,10 +16501,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>691313</v>
+        <v>691030</v>
       </c>
       <c r="R146" t="n">
-        <v>7400890</v>
+        <v>7400688</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16536,7 +16536,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16546,7 +16546,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16577,10 +16577,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128960559</v>
+        <v>128960504</v>
       </c>
       <c r="B147" t="n">
-        <v>91701</v>
+        <v>98678</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16588,21 +16588,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16612,10 +16612,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>691433</v>
+        <v>690949</v>
       </c>
       <c r="R147" t="n">
-        <v>7400873</v>
+        <v>7400850</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16642,22 +16642,22 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16688,32 +16688,32 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128960504</v>
+        <v>128960636</v>
       </c>
       <c r="B148" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16723,10 +16723,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>690949</v>
+        <v>691313</v>
       </c>
       <c r="R148" t="n">
-        <v>7400850</v>
+        <v>7400890</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16753,22 +16753,22 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16802,7 +16802,7 @@
         <v>128960602</v>
       </c>
       <c r="B149" t="n">
-        <v>78705</v>
+        <v>78707</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16913,7 +16913,7 @@
         <v>128960510</v>
       </c>
       <c r="B150" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17021,10 +17021,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128960421</v>
+        <v>128960465</v>
       </c>
       <c r="B151" t="n">
-        <v>98565</v>
+        <v>98678</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17032,21 +17032,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>233</v>
+        <v>220787</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17056,10 +17056,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>691475</v>
+        <v>691184</v>
       </c>
       <c r="R151" t="n">
-        <v>7401113</v>
+        <v>7400869</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17132,32 +17132,32 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128960683</v>
+        <v>128960421</v>
       </c>
       <c r="B152" t="n">
-        <v>80179</v>
+        <v>98567</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6463</v>
+        <v>233</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -17167,10 +17167,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>690835</v>
+        <v>691475</v>
       </c>
       <c r="R152" t="n">
-        <v>7400892</v>
+        <v>7401113</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17197,22 +17197,22 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17243,32 +17243,32 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128960685</v>
+        <v>128960683</v>
       </c>
       <c r="B153" t="n">
-        <v>78047</v>
+        <v>80181</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6487</v>
+        <v>6463</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17278,10 +17278,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>690998</v>
+        <v>690835</v>
       </c>
       <c r="R153" t="n">
-        <v>7401040</v>
+        <v>7400892</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17323,7 +17323,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17354,32 +17354,32 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128960465</v>
+        <v>128960685</v>
       </c>
       <c r="B154" t="n">
-        <v>98676</v>
+        <v>78049</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17389,10 +17389,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>691184</v>
+        <v>690998</v>
       </c>
       <c r="R154" t="n">
-        <v>7400869</v>
+        <v>7401040</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17419,22 +17419,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17465,32 +17465,32 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128960394</v>
+        <v>128960633</v>
       </c>
       <c r="B155" t="n">
-        <v>92450</v>
+        <v>92835</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17500,10 +17500,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>691657</v>
+        <v>691476</v>
       </c>
       <c r="R155" t="n">
-        <v>7400847</v>
+        <v>7400909</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17576,32 +17576,32 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128960469</v>
+        <v>128960634</v>
       </c>
       <c r="B156" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17611,10 +17611,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>691149</v>
+        <v>691432</v>
       </c>
       <c r="R156" t="n">
-        <v>7400912</v>
+        <v>7400884</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17687,10 +17687,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128960365</v>
+        <v>128960357</v>
       </c>
       <c r="B157" t="n">
-        <v>79629</v>
+        <v>79660</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17698,21 +17698,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -17722,10 +17722,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>691772</v>
+        <v>691748</v>
       </c>
       <c r="R157" t="n">
-        <v>7401045</v>
+        <v>7400820</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17798,10 +17798,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>128960468</v>
+        <v>128960469</v>
       </c>
       <c r="B158" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17833,10 +17833,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>691175</v>
+        <v>691149</v>
       </c>
       <c r="R158" t="n">
-        <v>7400884</v>
+        <v>7400912</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17878,7 +17878,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -17909,10 +17909,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>128960477</v>
+        <v>128960468</v>
       </c>
       <c r="B159" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17944,10 +17944,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>691104</v>
+        <v>691175</v>
       </c>
       <c r="R159" t="n">
-        <v>7400683</v>
+        <v>7400884</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -17979,7 +17979,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -17989,7 +17989,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18020,32 +18020,32 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>128960606</v>
+        <v>128960477</v>
       </c>
       <c r="B160" t="n">
-        <v>78705</v>
+        <v>98678</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -18055,10 +18055,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>691096</v>
+        <v>691104</v>
       </c>
       <c r="R160" t="n">
-        <v>7400927</v>
+        <v>7400683</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18090,7 +18090,7 @@
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -18100,7 +18100,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18131,32 +18131,32 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>128960639</v>
+        <v>128960365</v>
       </c>
       <c r="B161" t="n">
-        <v>92833</v>
+        <v>79631</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18166,10 +18166,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>691173</v>
+        <v>691772</v>
       </c>
       <c r="R161" t="n">
-        <v>7400751</v>
+        <v>7401045</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18201,7 +18201,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18242,10 +18242,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>128960634</v>
+        <v>128960639</v>
       </c>
       <c r="B162" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18277,10 +18277,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>691432</v>
+        <v>691173</v>
       </c>
       <c r="R162" t="n">
-        <v>7400884</v>
+        <v>7400751</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18312,7 +18312,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -18322,7 +18322,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18353,32 +18353,32 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>128960633</v>
+        <v>128960394</v>
       </c>
       <c r="B163" t="n">
-        <v>92833</v>
+        <v>92452</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -18388,10 +18388,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>691476</v>
+        <v>691657</v>
       </c>
       <c r="R163" t="n">
-        <v>7400909</v>
+        <v>7400847</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18423,7 +18423,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -18433,7 +18433,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18467,7 +18467,7 @@
         <v>128960416</v>
       </c>
       <c r="B164" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18575,10 +18575,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>128960357</v>
+        <v>128960606</v>
       </c>
       <c r="B165" t="n">
-        <v>79658</v>
+        <v>78707</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18586,21 +18586,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18610,10 +18610,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>691748</v>
+        <v>691096</v>
       </c>
       <c r="R165" t="n">
-        <v>7400820</v>
+        <v>7400927</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18645,7 +18645,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18655,7 +18655,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18686,32 +18686,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>128960620</v>
+        <v>128960569</v>
       </c>
       <c r="B166" t="n">
-        <v>78705</v>
+        <v>91703</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>353</v>
+        <v>1503</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18721,10 +18721,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>691007</v>
+        <v>691471</v>
       </c>
       <c r="R166" t="n">
-        <v>7401068</v>
+        <v>7400861</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18751,22 +18751,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18800,7 +18800,7 @@
         <v>128960397</v>
       </c>
       <c r="B167" t="n">
-        <v>92450</v>
+        <v>92452</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18908,10 +18908,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>128960569</v>
+        <v>128960485</v>
       </c>
       <c r="B168" t="n">
-        <v>91701</v>
+        <v>98678</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18919,21 +18919,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18943,10 +18943,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>691471</v>
+        <v>691491</v>
       </c>
       <c r="R168" t="n">
-        <v>7400861</v>
+        <v>7400689</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18978,7 +18978,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18988,7 +18988,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:09</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19019,10 +19019,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>128960485</v>
+        <v>128960508</v>
       </c>
       <c r="B169" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19054,10 +19054,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>691491</v>
+        <v>690820</v>
       </c>
       <c r="R169" t="n">
-        <v>7400689</v>
+        <v>7400917</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19084,22 +19084,22 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>10:09</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19130,10 +19130,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>128960508</v>
+        <v>128960484</v>
       </c>
       <c r="B170" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19165,10 +19165,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>690820</v>
+        <v>691205</v>
       </c>
       <c r="R170" t="n">
-        <v>7400917</v>
+        <v>7400756</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19195,22 +19195,22 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19241,10 +19241,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>128960484</v>
+        <v>128960509</v>
       </c>
       <c r="B171" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19276,10 +19276,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>691205</v>
+        <v>690841</v>
       </c>
       <c r="R171" t="n">
-        <v>7400756</v>
+        <v>7400937</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19306,22 +19306,22 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19352,10 +19352,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>128960509</v>
+        <v>128960456</v>
       </c>
       <c r="B172" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19387,10 +19387,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>690841</v>
+        <v>691641</v>
       </c>
       <c r="R172" t="n">
-        <v>7400937</v>
+        <v>7400939</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19417,22 +19417,22 @@
       </c>
       <c r="Y172" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19463,10 +19463,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>128960456</v>
+        <v>128960515</v>
       </c>
       <c r="B173" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19498,10 +19498,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>691641</v>
+        <v>691061</v>
       </c>
       <c r="R173" t="n">
-        <v>7400939</v>
+        <v>7401094</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19528,22 +19528,22 @@
       </c>
       <c r="Y173" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19574,32 +19574,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>128960515</v>
+        <v>128960620</v>
       </c>
       <c r="B174" t="n">
-        <v>98676</v>
+        <v>78707</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19609,10 +19609,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>691061</v>
+        <v>691007</v>
       </c>
       <c r="R174" t="n">
-        <v>7401094</v>
+        <v>7401068</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19654,7 +19654,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:44</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19685,32 +19685,32 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>128960495</v>
+        <v>128960658</v>
       </c>
       <c r="B175" t="n">
-        <v>98676</v>
+        <v>92835</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -19720,10 +19720,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>691488</v>
+        <v>690788</v>
       </c>
       <c r="R175" t="n">
-        <v>7401092</v>
+        <v>7400864</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19750,22 +19750,22 @@
       </c>
       <c r="Y175" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19796,32 +19796,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>128960475</v>
+        <v>128960406</v>
       </c>
       <c r="B176" t="n">
-        <v>98676</v>
+        <v>80175</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19831,10 +19831,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>691050</v>
+        <v>691215</v>
       </c>
       <c r="R176" t="n">
-        <v>7400705</v>
+        <v>7400790</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19866,7 +19866,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19876,7 +19876,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19907,10 +19907,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>128960473</v>
+        <v>128960495</v>
       </c>
       <c r="B177" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19942,10 +19942,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>690998</v>
+        <v>691488</v>
       </c>
       <c r="R177" t="n">
-        <v>7400742</v>
+        <v>7401092</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19977,7 +19977,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -20018,32 +20018,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>128960658</v>
+        <v>128960475</v>
       </c>
       <c r="B178" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -20053,10 +20053,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>690788</v>
+        <v>691050</v>
       </c>
       <c r="R178" t="n">
-        <v>7400864</v>
+        <v>7400705</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20083,22 +20083,22 @@
       </c>
       <c r="Y178" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -20129,32 +20129,32 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>128960406</v>
+        <v>128960473</v>
       </c>
       <c r="B179" t="n">
-        <v>80173</v>
+        <v>98678</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -20164,10 +20164,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>691215</v>
+        <v>690998</v>
       </c>
       <c r="R179" t="n">
-        <v>7400790</v>
+        <v>7400742</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20199,7 +20199,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -20209,7 +20209,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -20240,10 +20240,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>128960598</v>
+        <v>128960439</v>
       </c>
       <c r="B180" t="n">
-        <v>78705</v>
+        <v>90165</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20251,21 +20251,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>353</v>
+        <v>4962</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -20275,10 +20275,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>691672</v>
+        <v>690708</v>
       </c>
       <c r="R180" t="n">
-        <v>7401058</v>
+        <v>7400815</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20305,22 +20305,22 @@
       </c>
       <c r="Y180" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20351,32 +20351,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>128960472</v>
+        <v>128960598</v>
       </c>
       <c r="B181" t="n">
-        <v>98676</v>
+        <v>78707</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20386,10 +20386,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>690998</v>
+        <v>691672</v>
       </c>
       <c r="R181" t="n">
-        <v>7400789</v>
+        <v>7401058</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20421,7 +20421,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20431,7 +20431,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20462,32 +20462,32 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>128960439</v>
+        <v>128960472</v>
       </c>
       <c r="B182" t="n">
-        <v>90163</v>
+        <v>98678</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20497,10 +20497,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>690708</v>
+        <v>690998</v>
       </c>
       <c r="R182" t="n">
-        <v>7400815</v>
+        <v>7400789</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20527,22 +20527,22 @@
       </c>
       <c r="Y182" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20576,7 +20576,7 @@
         <v>128960550</v>
       </c>
       <c r="B183" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20687,7 +20687,7 @@
         <v>128960512</v>
       </c>
       <c r="B184" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>128960478</v>
       </c>
       <c r="B185" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>128960471</v>
       </c>
       <c r="B186" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21020,7 +21020,7 @@
         <v>128960461</v>
       </c>
       <c r="B187" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21131,7 +21131,7 @@
         <v>128960474</v>
       </c>
       <c r="B188" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21242,7 +21242,7 @@
         <v>128960470</v>
       </c>
       <c r="B189" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>128960505</v>
       </c>
       <c r="B190" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>128960359</v>
       </c>
       <c r="B191" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21575,7 +21575,7 @@
         <v>128960481</v>
       </c>
       <c r="B192" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21686,7 +21686,7 @@
         <v>128960342</v>
       </c>
       <c r="B193" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21794,32 +21794,32 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>128960684</v>
+        <v>128960644</v>
       </c>
       <c r="B194" t="n">
-        <v>78047</v>
+        <v>92835</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6487</v>
+        <v>4364</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21829,10 +21829,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>691442</v>
+        <v>691471</v>
       </c>
       <c r="R194" t="n">
-        <v>7400932</v>
+        <v>7400823</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21864,7 +21864,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21874,7 +21874,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>09:39</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21905,32 +21905,32 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>128960644</v>
+        <v>128960684</v>
       </c>
       <c r="B195" t="n">
-        <v>92833</v>
+        <v>78049</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>6487</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21940,10 +21940,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>691471</v>
+        <v>691442</v>
       </c>
       <c r="R195" t="n">
-        <v>7400823</v>
+        <v>7400932</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21975,7 +21975,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>09:39</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -22019,7 +22019,7 @@
         <v>128960507</v>
       </c>
       <c r="B196" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>128960493</v>
       </c>
       <c r="B197" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22241,7 +22241,7 @@
         <v>128960506</v>
       </c>
       <c r="B198" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>128960641</v>
       </c>
       <c r="B199" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>128960631</v>
       </c>
       <c r="B200" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22574,7 +22574,7 @@
         <v>128960396</v>
       </c>
       <c r="B201" t="n">
-        <v>92450</v>
+        <v>92452</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22685,7 +22685,7 @@
         <v>128960578</v>
       </c>
       <c r="B202" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22793,32 +22793,32 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>128960599</v>
+        <v>128960661</v>
       </c>
       <c r="B203" t="n">
-        <v>78705</v>
+        <v>92835</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E203" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22828,10 +22828,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>691564</v>
+        <v>691007</v>
       </c>
       <c r="R203" t="n">
-        <v>7401001</v>
+        <v>7401047</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22858,22 +22858,22 @@
       </c>
       <c r="Y203" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22904,10 +22904,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>128960605</v>
+        <v>128960341</v>
       </c>
       <c r="B204" t="n">
-        <v>78705</v>
+        <v>91463</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22915,21 +22915,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22939,10 +22939,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>691194</v>
+        <v>691820</v>
       </c>
       <c r="R204" t="n">
-        <v>7400846</v>
+        <v>7400734</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22974,7 +22974,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22984,7 +22984,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>12:23</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -23015,32 +23015,32 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>128960661</v>
+        <v>128960605</v>
       </c>
       <c r="B205" t="n">
-        <v>92833</v>
+        <v>78707</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -23050,10 +23050,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>691007</v>
+        <v>691194</v>
       </c>
       <c r="R205" t="n">
-        <v>7401047</v>
+        <v>7400846</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23080,22 +23080,22 @@
       </c>
       <c r="Y205" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>12:23</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -23126,10 +23126,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>128960341</v>
+        <v>128960599</v>
       </c>
       <c r="B206" t="n">
-        <v>91461</v>
+        <v>78707</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23137,21 +23137,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>3242</v>
+        <v>353</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -23161,10 +23161,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>691820</v>
+        <v>691564</v>
       </c>
       <c r="R206" t="n">
-        <v>7400734</v>
+        <v>7401001</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23196,7 +23196,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -23206,7 +23206,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -23240,7 +23240,7 @@
         <v>128960437</v>
       </c>
       <c r="B207" t="n">
-        <v>90163</v>
+        <v>90165</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>128960459</v>
       </c>
       <c r="B208" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>128960463</v>
       </c>
       <c r="B209" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23570,32 +23570,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>128960587</v>
+        <v>128960687</v>
       </c>
       <c r="B210" t="n">
-        <v>91801</v>
+        <v>78049</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>65</v>
+        <v>6487</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23605,10 +23605,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>691522</v>
+        <v>691772</v>
       </c>
       <c r="R210" t="n">
-        <v>7401008</v>
+        <v>7401045</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23640,7 +23640,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23681,32 +23681,32 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>128960611</v>
+        <v>128960587</v>
       </c>
       <c r="B211" t="n">
-        <v>78705</v>
+        <v>91803</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>353</v>
+        <v>65</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23716,10 +23716,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>690824</v>
+        <v>691522</v>
       </c>
       <c r="R211" t="n">
-        <v>7400642</v>
+        <v>7401008</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23746,22 +23746,22 @@
       </c>
       <c r="Y211" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23792,10 +23792,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>128960687</v>
+        <v>128960690</v>
       </c>
       <c r="B212" t="n">
-        <v>78047</v>
+        <v>78444</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23803,21 +23803,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6487</v>
+        <v>6437</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23827,10 +23827,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>691772</v>
+        <v>690817</v>
       </c>
       <c r="R212" t="n">
-        <v>7401045</v>
+        <v>7400668</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23857,22 +23857,22 @@
       </c>
       <c r="Y212" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23903,32 +23903,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>128960483</v>
+        <v>128960611</v>
       </c>
       <c r="B213" t="n">
-        <v>98676</v>
+        <v>78707</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23938,10 +23938,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>691042</v>
+        <v>690824</v>
       </c>
       <c r="R213" t="n">
-        <v>7400691</v>
+        <v>7400642</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23968,22 +23968,22 @@
       </c>
       <c r="Y213" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -24014,32 +24014,32 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>128960690</v>
+        <v>128960483</v>
       </c>
       <c r="B214" t="n">
-        <v>78442</v>
+        <v>98678</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -24049,10 +24049,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>690817</v>
+        <v>691042</v>
       </c>
       <c r="R214" t="n">
-        <v>7400668</v>
+        <v>7400691</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24079,22 +24079,22 @@
       </c>
       <c r="Y214" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -24128,7 +24128,7 @@
         <v>128960371</v>
       </c>
       <c r="B215" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>128960344</v>
       </c>
       <c r="B216" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>128960655</v>
       </c>
       <c r="B217" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24461,7 +24461,7 @@
         <v>128960489</v>
       </c>
       <c r="B218" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>128960513</v>
       </c>
       <c r="B219" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>128960467</v>
       </c>
       <c r="B220" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24794,7 +24794,7 @@
         <v>128960582</v>
       </c>
       <c r="B221" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24902,32 +24902,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>128960608</v>
+        <v>128960356</v>
       </c>
       <c r="B222" t="n">
-        <v>78705</v>
+        <v>91506</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>353</v>
+        <v>5447</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24937,10 +24937,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>691209</v>
+        <v>691028</v>
       </c>
       <c r="R222" t="n">
-        <v>7400623</v>
+        <v>7400838</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24972,7 +24972,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24982,7 +24982,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -25013,32 +25013,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>128960455</v>
+        <v>128960608</v>
       </c>
       <c r="B223" t="n">
-        <v>98676</v>
+        <v>78707</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -25048,10 +25048,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>691615</v>
+        <v>691209</v>
       </c>
       <c r="R223" t="n">
-        <v>7400959</v>
+        <v>7400623</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -25083,7 +25083,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -25093,7 +25093,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -25124,32 +25124,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>128960451</v>
+        <v>128960693</v>
       </c>
       <c r="B224" t="n">
-        <v>98676</v>
+        <v>78444</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -25159,10 +25159,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>691520</v>
+        <v>691595</v>
       </c>
       <c r="R224" t="n">
-        <v>7401010</v>
+        <v>7401115</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25194,7 +25194,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -25204,7 +25204,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -25235,32 +25235,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>128960487</v>
+        <v>128960358</v>
       </c>
       <c r="B225" t="n">
-        <v>98676</v>
+        <v>79660</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -25270,10 +25270,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>691504</v>
+        <v>691772</v>
       </c>
       <c r="R225" t="n">
-        <v>7400725</v>
+        <v>7400877</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -25315,7 +25315,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -25346,32 +25346,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>128960497</v>
+        <v>128960436</v>
       </c>
       <c r="B226" t="n">
-        <v>98676</v>
+        <v>90165</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>220787</v>
+        <v>4962</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -25381,10 +25381,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>691469</v>
+        <v>691019</v>
       </c>
       <c r="R226" t="n">
-        <v>7401129</v>
+        <v>7400845</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25416,7 +25416,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -25426,7 +25426,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>12:09</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25457,10 +25457,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>128960486</v>
+        <v>128960455</v>
       </c>
       <c r="B227" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25492,10 +25492,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>691497</v>
+        <v>691615</v>
       </c>
       <c r="R227" t="n">
-        <v>7400703</v>
+        <v>7400959</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25527,7 +25527,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25537,7 +25537,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>10:06</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25568,32 +25568,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>128960366</v>
+        <v>128960451</v>
       </c>
       <c r="B228" t="n">
-        <v>79629</v>
+        <v>98678</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25603,10 +25603,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>691628</v>
+        <v>691520</v>
       </c>
       <c r="R228" t="n">
-        <v>7401071</v>
+        <v>7401010</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25638,7 +25638,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25648,7 +25648,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD228" t="b">
@@ -25679,32 +25679,32 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>128960360</v>
+        <v>128960487</v>
       </c>
       <c r="B229" t="n">
-        <v>79629</v>
+        <v>98678</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -25714,10 +25714,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>691748</v>
+        <v>691504</v>
       </c>
       <c r="R229" t="n">
-        <v>7400820</v>
+        <v>7400725</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25749,7 +25749,7 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="AB229" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AD229" t="b">
@@ -25790,32 +25790,32 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>128960356</v>
+        <v>128960497</v>
       </c>
       <c r="B230" t="n">
-        <v>91504</v>
+        <v>98678</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -25825,10 +25825,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>691028</v>
+        <v>691469</v>
       </c>
       <c r="R230" t="n">
-        <v>7400838</v>
+        <v>7401129</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25860,7 +25860,7 @@
       </c>
       <c r="Z230" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
@@ -25870,7 +25870,7 @@
       </c>
       <c r="AB230" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -25901,32 +25901,32 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>128960436</v>
+        <v>128960486</v>
       </c>
       <c r="B231" t="n">
-        <v>90163</v>
+        <v>98678</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4962</v>
+        <v>220787</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -25936,10 +25936,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>691019</v>
+        <v>691497</v>
       </c>
       <c r="R231" t="n">
-        <v>7400845</v>
+        <v>7400703</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25971,7 +25971,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -25981,7 +25981,7 @@
       </c>
       <c r="AB231" t="inlineStr">
         <is>
-          <t>12:09</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="AD231" t="b">
@@ -26012,10 +26012,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>128960693</v>
+        <v>128960366</v>
       </c>
       <c r="B232" t="n">
-        <v>78442</v>
+        <v>79631</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26023,21 +26023,21 @@
         </is>
       </c>
       <c r="E232" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
@@ -26047,10 +26047,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>691595</v>
+        <v>691628</v>
       </c>
       <c r="R232" t="n">
-        <v>7401115</v>
+        <v>7401071</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -26082,7 +26082,7 @@
       </c>
       <c r="Z232" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA232" t="inlineStr">
@@ -26092,7 +26092,7 @@
       </c>
       <c r="AB232" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26123,10 +26123,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>128960358</v>
+        <v>128960360</v>
       </c>
       <c r="B233" t="n">
-        <v>79658</v>
+        <v>79631</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26134,21 +26134,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>6453</v>
+        <v>229821</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -26158,10 +26158,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>691772</v>
+        <v>691748</v>
       </c>
       <c r="R233" t="n">
-        <v>7400877</v>
+        <v>7400820</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26193,7 +26193,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -26203,7 +26203,7 @@
       </c>
       <c r="AB233" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26234,32 +26234,32 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>128960409</v>
+        <v>128960653</v>
       </c>
       <c r="B234" t="n">
-        <v>91489</v>
+        <v>92835</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -26269,10 +26269,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>691353</v>
+        <v>690703</v>
       </c>
       <c r="R234" t="n">
-        <v>7400865</v>
+        <v>7400802</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26299,22 +26299,22 @@
       </c>
       <c r="Y234" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z234" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA234" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB234" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD234" t="b">
@@ -26345,10 +26345,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>128960596</v>
+        <v>128960345</v>
       </c>
       <c r="B235" t="n">
-        <v>78705</v>
+        <v>91463</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26356,21 +26356,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>353</v>
+        <v>3242</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -26380,10 +26380,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>691802</v>
+        <v>691005</v>
       </c>
       <c r="R235" t="n">
-        <v>7400967</v>
+        <v>7401070</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -26410,22 +26410,22 @@
       </c>
       <c r="Y235" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB235" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:51</t>
         </is>
       </c>
       <c r="AD235" t="b">
@@ -26456,10 +26456,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>128960393</v>
+        <v>128960596</v>
       </c>
       <c r="B236" t="n">
-        <v>92858</v>
+        <v>78707</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -26467,21 +26467,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>3100</v>
+        <v>353</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -26491,10 +26491,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>690878</v>
+        <v>691802</v>
       </c>
       <c r="R236" t="n">
-        <v>7400754</v>
+        <v>7400967</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -26521,22 +26521,22 @@
       </c>
       <c r="Y236" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z236" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA236" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB236" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AD236" t="b">
@@ -26567,10 +26567,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>128960345</v>
+        <v>128960545</v>
       </c>
       <c r="B237" t="n">
-        <v>91461</v>
+        <v>79120</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -26578,21 +26578,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>3242</v>
+        <v>864</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -26602,10 +26602,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>691005</v>
+        <v>691266</v>
       </c>
       <c r="R237" t="n">
-        <v>7401070</v>
+        <v>7400806</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -26632,22 +26632,22 @@
       </c>
       <c r="Y237" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z237" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA237" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB237" t="inlineStr">
         <is>
-          <t>16:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD237" t="b">
@@ -26678,32 +26678,32 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>128960653</v>
+        <v>128960368</v>
       </c>
       <c r="B238" t="n">
-        <v>92833</v>
+        <v>79631</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -26713,10 +26713,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>690703</v>
+        <v>691561</v>
       </c>
       <c r="R238" t="n">
-        <v>7400802</v>
+        <v>7401113</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -26743,22 +26743,22 @@
       </c>
       <c r="Y238" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z238" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB238" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AD238" t="b">
@@ -26789,10 +26789,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>128960368</v>
+        <v>128960409</v>
       </c>
       <c r="B239" t="n">
-        <v>79629</v>
+        <v>91491</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -26800,21 +26800,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>229821</v>
+        <v>112</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -26824,10 +26824,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>691561</v>
+        <v>691353</v>
       </c>
       <c r="R239" t="n">
-        <v>7401113</v>
+        <v>7400865</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -26859,7 +26859,7 @@
       </c>
       <c r="Z239" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA239" t="inlineStr">
@@ -26869,7 +26869,7 @@
       </c>
       <c r="AB239" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD239" t="b">
@@ -26900,10 +26900,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>128960545</v>
+        <v>128960393</v>
       </c>
       <c r="B240" t="n">
-        <v>79118</v>
+        <v>92860</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -26911,21 +26911,21 @@
         </is>
       </c>
       <c r="E240" t="n">
-        <v>864</v>
+        <v>3100</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -26935,10 +26935,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>691266</v>
+        <v>690878</v>
       </c>
       <c r="R240" t="n">
-        <v>7400806</v>
+        <v>7400754</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -26965,22 +26965,22 @@
       </c>
       <c r="Y240" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z240" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA240" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB240" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD240" t="b">
@@ -27014,7 +27014,7 @@
         <v>128960580</v>
       </c>
       <c r="B241" t="n">
-        <v>91801</v>
+        <v>91803</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>128960563</v>
       </c>
       <c r="B242" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27236,7 +27236,7 @@
         <v>128960363</v>
       </c>
       <c r="B243" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27347,7 +27347,7 @@
         <v>128960361</v>
       </c>
       <c r="B244" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27455,32 +27455,32 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>128960628</v>
+        <v>128960460</v>
       </c>
       <c r="B245" t="n">
-        <v>92833</v>
+        <v>98678</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -27490,10 +27490,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>691884</v>
+        <v>691513</v>
       </c>
       <c r="R245" t="n">
-        <v>7401043</v>
+        <v>7401038</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -27525,7 +27525,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -27535,7 +27535,7 @@
       </c>
       <c r="AB245" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD245" t="b">
@@ -27566,32 +27566,32 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>128960398</v>
+        <v>128960628</v>
       </c>
       <c r="B246" t="n">
-        <v>92450</v>
+        <v>92835</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -27601,10 +27601,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>690713</v>
+        <v>691884</v>
       </c>
       <c r="R246" t="n">
-        <v>7400706</v>
+        <v>7401043</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -27631,22 +27631,22 @@
       </c>
       <c r="Y246" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z246" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB246" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD246" t="b">
@@ -27677,32 +27677,32 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>128960460</v>
+        <v>128960398</v>
       </c>
       <c r="B247" t="n">
-        <v>98676</v>
+        <v>92452</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -27712,10 +27712,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>691513</v>
+        <v>690713</v>
       </c>
       <c r="R247" t="n">
-        <v>7401038</v>
+        <v>7400706</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -27742,22 +27742,22 @@
       </c>
       <c r="Y247" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD247" t="b">
@@ -27791,7 +27791,7 @@
         <v>128960362</v>
       </c>
       <c r="B248" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         <v>128960677</v>
       </c>
       <c r="B249" t="n">
-        <v>88788</v>
+        <v>88790</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28013,7 +28013,7 @@
         <v>128960382</v>
       </c>
       <c r="B250" t="n">
-        <v>91815</v>
+        <v>91817</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>128960419</v>
       </c>
       <c r="B251" t="n">
-        <v>92165</v>
+        <v>92167</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         <v>128960678</v>
       </c>
       <c r="B252" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28346,7 +28346,7 @@
         <v>128960380</v>
       </c>
       <c r="B253" t="n">
-        <v>91815</v>
+        <v>91817</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -28457,7 +28457,7 @@
         <v>128960381</v>
       </c>
       <c r="B254" t="n">
-        <v>91815</v>
+        <v>91817</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>

--- a/artfynd/A 3557-2025 artfynd.xlsx
+++ b/artfynd/A 3557-2025 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128960549</v>
+        <v>128960696</v>
       </c>
       <c r="B3" t="n">
-        <v>92166</v>
+        <v>78444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5454</v>
+        <v>6437</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hornvaxskinn</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Crustoderma corneum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bourdot &amp; Galzin) Nakasone</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691837</v>
+        <v>691640</v>
       </c>
       <c r="R3" t="n">
-        <v>7401375</v>
+        <v>7401329</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +893,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128960696</v>
+        <v>128960549</v>
       </c>
       <c r="B4" t="n">
-        <v>78444</v>
+        <v>92166</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,21 +904,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6437</v>
+        <v>5454</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Hornvaxskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Crustoderma corneum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Bourdot &amp; Galzin) Nakasone</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -928,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691640</v>
+        <v>691837</v>
       </c>
       <c r="R4" t="n">
-        <v>7401329</v>
+        <v>7401375</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,32 +1004,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128960450</v>
+        <v>128960691</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>78444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691723</v>
+        <v>691190</v>
       </c>
       <c r="R5" t="n">
-        <v>7401427</v>
+        <v>7401223</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,22 +1069,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>16:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,7 +1115,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128960524</v>
+        <v>128960450</v>
       </c>
       <c r="B6" t="n">
         <v>98678</v>
@@ -1150,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691395</v>
+        <v>691723</v>
       </c>
       <c r="R6" t="n">
-        <v>7401429</v>
+        <v>7401427</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,32 +1226,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128960372</v>
+        <v>128960524</v>
       </c>
       <c r="B7" t="n">
-        <v>79631</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691253</v>
+        <v>691395</v>
       </c>
       <c r="R7" t="n">
-        <v>7401236</v>
+        <v>7401429</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1337,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128960691</v>
+        <v>128960372</v>
       </c>
       <c r="B8" t="n">
-        <v>78444</v>
+        <v>79631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1348,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6437</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1372,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691190</v>
+        <v>691253</v>
       </c>
       <c r="R8" t="n">
-        <v>7401223</v>
+        <v>7401236</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:02</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1448,32 +1448,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128960343</v>
+        <v>128960426</v>
       </c>
       <c r="B9" t="n">
-        <v>91463</v>
+        <v>98567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3242</v>
+        <v>233</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691612</v>
+        <v>691727</v>
       </c>
       <c r="R9" t="n">
-        <v>7401171</v>
+        <v>7401372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1513,22 +1513,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,32 +1559,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128960670</v>
+        <v>128960616</v>
       </c>
       <c r="B10" t="n">
-        <v>92835</v>
+        <v>78707</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691851</v>
+        <v>691854</v>
       </c>
       <c r="R10" t="n">
-        <v>7401441</v>
+        <v>7401445</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128960689</v>
+        <v>128960343</v>
       </c>
       <c r="B11" t="n">
-        <v>78444</v>
+        <v>91463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6437</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691341</v>
+        <v>691612</v>
       </c>
       <c r="R11" t="n">
-        <v>7401206</v>
+        <v>7401171</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:19</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1781,32 +1781,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128960426</v>
+        <v>128960670</v>
       </c>
       <c r="B12" t="n">
-        <v>98567</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>233</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691727</v>
+        <v>691851</v>
       </c>
       <c r="R12" t="n">
-        <v>7401372</v>
+        <v>7401441</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1892,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128960616</v>
+        <v>128960689</v>
       </c>
       <c r="B13" t="n">
-        <v>78707</v>
+        <v>78444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1903,21 +1903,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691854</v>
+        <v>691341</v>
       </c>
       <c r="R13" t="n">
-        <v>7401445</v>
+        <v>7401206</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1957,22 +1957,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:21</t>
+          <t>08:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2447,32 +2447,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128960542</v>
+        <v>128960618</v>
       </c>
       <c r="B18" t="n">
-        <v>98678</v>
+        <v>78707</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2482,10 +2482,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>691733</v>
+        <v>691741</v>
       </c>
       <c r="R18" t="n">
-        <v>7401377</v>
+        <v>7401356</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2558,7 +2558,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128960519</v>
+        <v>128960542</v>
       </c>
       <c r="B19" t="n">
         <v>98678</v>
@@ -2593,10 +2593,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>691230</v>
+        <v>691733</v>
       </c>
       <c r="R19" t="n">
-        <v>7401270</v>
+        <v>7401377</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2628,7 +2628,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2669,32 +2669,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128960618</v>
+        <v>128960519</v>
       </c>
       <c r="B20" t="n">
-        <v>78707</v>
+        <v>98678</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2704,10 +2704,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>691741</v>
+        <v>691230</v>
       </c>
       <c r="R20" t="n">
-        <v>7401356</v>
+        <v>7401270</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3668,32 +3668,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128960454</v>
+        <v>128960400</v>
       </c>
       <c r="B29" t="n">
-        <v>98678</v>
+        <v>92452</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3703,10 +3703,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>691681</v>
+        <v>691245</v>
       </c>
       <c r="R29" t="n">
-        <v>7401433</v>
+        <v>7401292</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3779,10 +3779,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128960540</v>
+        <v>128960573</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>91703</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3790,21 +3790,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1503</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3814,10 +3814,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>691741</v>
+        <v>691704</v>
       </c>
       <c r="R30" t="n">
-        <v>7401356</v>
+        <v>7401335</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3890,10 +3890,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128960573</v>
+        <v>128960454</v>
       </c>
       <c r="B31" t="n">
-        <v>91703</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>691704</v>
+        <v>691681</v>
       </c>
       <c r="R31" t="n">
-        <v>7401335</v>
+        <v>7401433</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,7 +3960,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4001,32 +4001,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128960400</v>
+        <v>128960540</v>
       </c>
       <c r="B32" t="n">
-        <v>92452</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4036,10 +4036,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>691245</v>
+        <v>691741</v>
       </c>
       <c r="R32" t="n">
-        <v>7401292</v>
+        <v>7401356</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4556,10 +4556,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128960424</v>
+        <v>128960571</v>
       </c>
       <c r="B37" t="n">
-        <v>98567</v>
+        <v>91703</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4567,21 +4567,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>233</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4591,10 +4591,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>691756</v>
+        <v>691659</v>
       </c>
       <c r="R37" t="n">
-        <v>7401403</v>
+        <v>7401322</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4626,7 +4626,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4667,7 +4667,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128960571</v>
+        <v>128960561</v>
       </c>
       <c r="B38" t="n">
         <v>91703</v>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>691659</v>
+        <v>691650</v>
       </c>
       <c r="R38" t="n">
-        <v>7401322</v>
+        <v>7401329</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4747,7 +4747,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4778,10 +4778,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128960561</v>
+        <v>128960424</v>
       </c>
       <c r="B39" t="n">
-        <v>91703</v>
+        <v>98567</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4789,21 +4789,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>233</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4813,10 +4813,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>691650</v>
+        <v>691756</v>
       </c>
       <c r="R39" t="n">
-        <v>7401329</v>
+        <v>7401403</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4858,7 +4858,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5000,7 +5000,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128960422</v>
+        <v>128960431</v>
       </c>
       <c r="B41" t="n">
         <v>98567</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>691717</v>
+        <v>691733</v>
       </c>
       <c r="R41" t="n">
-        <v>7401426</v>
+        <v>7401377</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5065,22 +5065,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>12:37</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5111,7 +5111,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128960431</v>
+        <v>128960422</v>
       </c>
       <c r="B42" t="n">
         <v>98567</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>691733</v>
+        <v>691717</v>
       </c>
       <c r="R42" t="n">
-        <v>7401377</v>
+        <v>7401426</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5176,22 +5176,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:37</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5222,32 +5222,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128960662</v>
+        <v>128960695</v>
       </c>
       <c r="B43" t="n">
-        <v>92835</v>
+        <v>78444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6437</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>691259</v>
+        <v>691255</v>
       </c>
       <c r="R43" t="n">
-        <v>7401348</v>
+        <v>7401234</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:50</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5333,32 +5333,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128960695</v>
+        <v>128960527</v>
       </c>
       <c r="B44" t="n">
-        <v>78444</v>
+        <v>98678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5368,10 +5368,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>691255</v>
+        <v>691373</v>
       </c>
       <c r="R44" t="n">
-        <v>7401234</v>
+        <v>7401425</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5403,7 +5403,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:50</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5444,32 +5444,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128960527</v>
+        <v>128960377</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>79631</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5479,10 +5479,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>691373</v>
+        <v>691728</v>
       </c>
       <c r="R45" t="n">
-        <v>7401425</v>
+        <v>7401382</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5555,32 +5555,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128960377</v>
+        <v>128960662</v>
       </c>
       <c r="B46" t="n">
-        <v>79631</v>
+        <v>92835</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5590,10 +5590,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>691728</v>
+        <v>691259</v>
       </c>
       <c r="R46" t="n">
-        <v>7401382</v>
+        <v>7401348</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5635,7 +5635,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5666,32 +5666,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128960586</v>
+        <v>128960622</v>
       </c>
       <c r="B47" t="n">
-        <v>91803</v>
+        <v>78707</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5701,10 +5701,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>691611</v>
+        <v>691669</v>
       </c>
       <c r="R47" t="n">
-        <v>7401170</v>
+        <v>7401313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5731,22 +5731,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5777,32 +5777,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128960434</v>
+        <v>128960586</v>
       </c>
       <c r="B48" t="n">
-        <v>93031</v>
+        <v>91803</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5812,10 +5812,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>691450</v>
+        <v>691611</v>
       </c>
       <c r="R48" t="n">
-        <v>7401402</v>
+        <v>7401170</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5842,22 +5842,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128960622</v>
+        <v>128960434</v>
       </c>
       <c r="B49" t="n">
-        <v>78707</v>
+        <v>93031</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>2079</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>691669</v>
+        <v>691450</v>
       </c>
       <c r="R49" t="n">
-        <v>7401313</v>
+        <v>7401402</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6665,32 +6665,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128960664</v>
+        <v>128960395</v>
       </c>
       <c r="B56" t="n">
-        <v>92835</v>
+        <v>92452</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6700,10 +6700,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>691754</v>
+        <v>691427</v>
       </c>
       <c r="R56" t="n">
-        <v>7401434</v>
+        <v>7401226</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6730,22 +6730,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6776,32 +6776,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128960395</v>
+        <v>128960664</v>
       </c>
       <c r="B57" t="n">
-        <v>92452</v>
+        <v>92835</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6811,10 +6811,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>691427</v>
+        <v>691754</v>
       </c>
       <c r="R57" t="n">
-        <v>7401226</v>
+        <v>7401434</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6841,22 +6841,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7664,10 +7664,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128960347</v>
+        <v>128960692</v>
       </c>
       <c r="B65" t="n">
-        <v>91463</v>
+        <v>78444</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7675,21 +7675,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3242</v>
+        <v>6437</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7699,10 +7699,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>691668</v>
+        <v>691580</v>
       </c>
       <c r="R65" t="n">
-        <v>7401306</v>
+        <v>7401425</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7734,7 +7734,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7775,32 +7775,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128960692</v>
+        <v>128960518</v>
       </c>
       <c r="B66" t="n">
-        <v>78444</v>
+        <v>98678</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6437</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7810,10 +7810,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>691580</v>
+        <v>691236</v>
       </c>
       <c r="R66" t="n">
-        <v>7401425</v>
+        <v>7401263</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>14:56</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7997,32 +7997,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128960536</v>
+        <v>128960347</v>
       </c>
       <c r="B68" t="n">
-        <v>98678</v>
+        <v>91463</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>3242</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>691728</v>
+        <v>691668</v>
       </c>
       <c r="R68" t="n">
-        <v>7401388</v>
+        <v>7401306</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8067,7 +8067,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8108,7 +8108,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128960518</v>
+        <v>128960536</v>
       </c>
       <c r="B69" t="n">
         <v>98678</v>
@@ -8143,10 +8143,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>691236</v>
+        <v>691728</v>
       </c>
       <c r="R69" t="n">
-        <v>7401263</v>
+        <v>7401388</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8188,7 +8188,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -13913,32 +13913,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>128960646</v>
+        <v>128960503</v>
       </c>
       <c r="B123" t="n">
-        <v>92835</v>
+        <v>98678</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13948,10 +13948,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>691445</v>
+        <v>690957</v>
       </c>
       <c r="R123" t="n">
-        <v>7400907</v>
+        <v>7400856</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13978,22 +13978,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14024,32 +14024,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>128960399</v>
+        <v>128960476</v>
       </c>
       <c r="B124" t="n">
-        <v>92452</v>
+        <v>98678</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4745</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>690819</v>
+        <v>691094</v>
       </c>
       <c r="R124" t="n">
-        <v>7400882</v>
+        <v>7400693</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14089,22 +14089,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14135,32 +14135,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>128960405</v>
+        <v>128960370</v>
       </c>
       <c r="B125" t="n">
-        <v>80175</v>
+        <v>79631</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6462</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14170,10 +14170,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>690835</v>
+        <v>691375</v>
       </c>
       <c r="R125" t="n">
-        <v>7400894</v>
+        <v>7400750</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14200,22 +14200,22 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14246,10 +14246,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>128960650</v>
+        <v>128960405</v>
       </c>
       <c r="B126" t="n">
-        <v>92835</v>
+        <v>80175</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14257,21 +14257,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14281,10 +14281,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>690728</v>
+        <v>690835</v>
       </c>
       <c r="R126" t="n">
-        <v>7400633</v>
+        <v>7400894</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14316,7 +14316,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14326,7 +14326,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14357,32 +14357,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>128960503</v>
+        <v>128960650</v>
       </c>
       <c r="B127" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14392,10 +14392,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>690957</v>
+        <v>690728</v>
       </c>
       <c r="R127" t="n">
-        <v>7400856</v>
+        <v>7400633</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14427,7 +14427,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14437,7 +14437,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14468,32 +14468,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>128960476</v>
+        <v>128960399</v>
       </c>
       <c r="B128" t="n">
-        <v>98678</v>
+        <v>92452</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>4745</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14503,10 +14503,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>691094</v>
+        <v>690819</v>
       </c>
       <c r="R128" t="n">
-        <v>7400693</v>
+        <v>7400882</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14533,22 +14533,22 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14579,32 +14579,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128960370</v>
+        <v>128960646</v>
       </c>
       <c r="B129" t="n">
-        <v>79631</v>
+        <v>92835</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14614,10 +14614,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>691375</v>
+        <v>691445</v>
       </c>
       <c r="R129" t="n">
-        <v>7400750</v>
+        <v>7400907</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14649,7 +14649,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14659,7 +14659,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14690,10 +14690,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>128960354</v>
+        <v>128960402</v>
       </c>
       <c r="B130" t="n">
-        <v>96924</v>
+        <v>92861</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14701,21 +14701,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>53</v>
+        <v>5448</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>691515</v>
+        <v>690717</v>
       </c>
       <c r="R130" t="n">
-        <v>7401011</v>
+        <v>7400812</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14755,22 +14755,22 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-21</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15023,10 +15023,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>128960402</v>
+        <v>128960556</v>
       </c>
       <c r="B133" t="n">
-        <v>92861</v>
+        <v>91556</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15034,21 +15034,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5448</v>
+        <v>1204</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15058,10 +15058,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>690717</v>
+        <v>691520</v>
       </c>
       <c r="R133" t="n">
-        <v>7400812</v>
+        <v>7401010</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15088,22 +15088,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15134,10 +15134,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>128960556</v>
+        <v>128960354</v>
       </c>
       <c r="B134" t="n">
-        <v>91556</v>
+        <v>96924</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15145,21 +15145,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1204</v>
+        <v>53</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15169,10 +15169,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>691520</v>
+        <v>691515</v>
       </c>
       <c r="R134" t="n">
-        <v>7401010</v>
+        <v>7401011</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15204,7 +15204,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15214,7 +15214,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15245,32 +15245,32 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>128960511</v>
+        <v>128960626</v>
       </c>
       <c r="B135" t="n">
-        <v>98678</v>
+        <v>92835</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15280,10 +15280,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>690875</v>
+        <v>691772</v>
       </c>
       <c r="R135" t="n">
-        <v>7400942</v>
+        <v>7400877</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15310,22 +15310,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-09-21</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">